--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.6062</v>
+        <v>19.241</v>
       </c>
       <c r="C2" t="n">
-        <v>32.387</v>
+        <v>14.5877</v>
       </c>
       <c r="D2" t="n">
-        <v>32.5778</v>
+        <v>32.0478</v>
       </c>
       <c r="E2" t="n">
-        <v>9.565379999999999</v>
+        <v>8.40147</v>
       </c>
       <c r="F2" t="n">
-        <v>27.1623</v>
+        <v>27.4222</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.7733</v>
+        <v>18.7165</v>
       </c>
       <c r="C3" t="n">
-        <v>31.4192</v>
+        <v>14.5845</v>
       </c>
       <c r="D3" t="n">
-        <v>32.6133</v>
+        <v>32.2228</v>
       </c>
       <c r="E3" t="n">
-        <v>9.32273</v>
+        <v>8.119540000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>26.8447</v>
+        <v>27.3039</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.3828</v>
+        <v>18.2394</v>
       </c>
       <c r="C4" t="n">
-        <v>31.6064</v>
+        <v>14.9056</v>
       </c>
       <c r="D4" t="n">
-        <v>32.7914</v>
+        <v>32.1479</v>
       </c>
       <c r="E4" t="n">
-        <v>8.69012</v>
+        <v>7.92113</v>
       </c>
       <c r="F4" t="n">
-        <v>26.5249</v>
+        <v>27.1226</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.7575</v>
+        <v>17.9863</v>
       </c>
       <c r="C5" t="n">
-        <v>30.9821</v>
+        <v>15.2181</v>
       </c>
       <c r="D5" t="n">
-        <v>32.8616</v>
+        <v>32.3821</v>
       </c>
       <c r="E5" t="n">
-        <v>8.8696</v>
+        <v>7.68357</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2113</v>
+        <v>26.8957</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.1577</v>
+        <v>17.2489</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5866</v>
+        <v>15.36</v>
       </c>
       <c r="D6" t="n">
-        <v>33.0478</v>
+        <v>32.5224</v>
       </c>
       <c r="E6" t="n">
-        <v>8.33783</v>
+        <v>7.62159</v>
       </c>
       <c r="F6" t="n">
-        <v>25.9688</v>
+        <v>26.297</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.497</v>
+        <v>16.7245</v>
       </c>
       <c r="C7" t="n">
-        <v>29.8976</v>
+        <v>15.4847</v>
       </c>
       <c r="D7" t="n">
-        <v>32.2158</v>
+        <v>31.6985</v>
       </c>
       <c r="E7" t="n">
-        <v>8.259729999999999</v>
+        <v>7.4218</v>
       </c>
       <c r="F7" t="n">
-        <v>25.6555</v>
+        <v>26.0139</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.7005</v>
+        <v>15.9178</v>
       </c>
       <c r="C8" t="n">
-        <v>29.0627</v>
+        <v>17.2192</v>
       </c>
       <c r="D8" t="n">
-        <v>32.355</v>
+        <v>31.901</v>
       </c>
       <c r="E8" t="n">
-        <v>7.94142</v>
+        <v>7.3537</v>
       </c>
       <c r="F8" t="n">
-        <v>25.3148</v>
+        <v>25.762</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.9044</v>
+        <v>14.9758</v>
       </c>
       <c r="C9" t="n">
-        <v>28.8929</v>
+        <v>17.3442</v>
       </c>
       <c r="D9" t="n">
-        <v>32.4327</v>
+        <v>32.0154</v>
       </c>
       <c r="E9" t="n">
-        <v>16.6127</v>
+        <v>16.7571</v>
       </c>
       <c r="F9" t="n">
-        <v>30.0795</v>
+        <v>30.394</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>23.0269</v>
+        <v>22.8105</v>
       </c>
       <c r="C10" t="n">
-        <v>35.7897</v>
+        <v>17.5238</v>
       </c>
       <c r="D10" t="n">
-        <v>32.3032</v>
+        <v>32.0976</v>
       </c>
       <c r="E10" t="n">
-        <v>15.9206</v>
+        <v>16.0512</v>
       </c>
       <c r="F10" t="n">
-        <v>29.8281</v>
+        <v>29.9726</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.6172</v>
+        <v>22.5853</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7501</v>
+        <v>17.4371</v>
       </c>
       <c r="D11" t="n">
-        <v>32.4645</v>
+        <v>32.1403</v>
       </c>
       <c r="E11" t="n">
-        <v>15.7629</v>
+        <v>15.4922</v>
       </c>
       <c r="F11" t="n">
-        <v>29.4551</v>
+        <v>29.888</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>22.3166</v>
+        <v>22.255</v>
       </c>
       <c r="C12" t="n">
-        <v>35.0854</v>
+        <v>17.3935</v>
       </c>
       <c r="D12" t="n">
-        <v>32.639</v>
+        <v>32.2141</v>
       </c>
       <c r="E12" t="n">
-        <v>15.2948</v>
+        <v>15.1888</v>
       </c>
       <c r="F12" t="n">
-        <v>29.1187</v>
+        <v>29.6807</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.7949</v>
+        <v>21.7009</v>
       </c>
       <c r="C13" t="n">
-        <v>34.649</v>
+        <v>17.3352</v>
       </c>
       <c r="D13" t="n">
-        <v>32.8203</v>
+        <v>32.3003</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9892</v>
+        <v>15.0045</v>
       </c>
       <c r="F13" t="n">
-        <v>28.9763</v>
+        <v>29.3701</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.3589</v>
+        <v>21.2999</v>
       </c>
       <c r="C14" t="n">
-        <v>34.1746</v>
+        <v>17.2244</v>
       </c>
       <c r="D14" t="n">
-        <v>32.8092</v>
+        <v>32.4811</v>
       </c>
       <c r="E14" t="n">
-        <v>14.5336</v>
+        <v>14.5832</v>
       </c>
       <c r="F14" t="n">
-        <v>28.6264</v>
+        <v>29.1229</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.9592</v>
+        <v>20.7159</v>
       </c>
       <c r="C15" t="n">
-        <v>32.416</v>
+        <v>17.3103</v>
       </c>
       <c r="D15" t="n">
-        <v>32.9891</v>
+        <v>32.4678</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2247</v>
+        <v>14.372</v>
       </c>
       <c r="F15" t="n">
-        <v>28.3446</v>
+        <v>28.8255</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.3653</v>
+        <v>20.3598</v>
       </c>
       <c r="C16" t="n">
-        <v>32.8922</v>
+        <v>17.3378</v>
       </c>
       <c r="D16" t="n">
-        <v>32.9481</v>
+        <v>32.7405</v>
       </c>
       <c r="E16" t="n">
-        <v>13.8842</v>
+        <v>14.1029</v>
       </c>
       <c r="F16" t="n">
-        <v>28.0055</v>
+        <v>28.4471</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.721</v>
+        <v>19.8434</v>
       </c>
       <c r="C17" t="n">
-        <v>32.3346</v>
+        <v>17.3269</v>
       </c>
       <c r="D17" t="n">
-        <v>33.1364</v>
+        <v>32.6084</v>
       </c>
       <c r="E17" t="n">
-        <v>13.635</v>
+        <v>13.8279</v>
       </c>
       <c r="F17" t="n">
-        <v>27.7153</v>
+        <v>28.109</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.2279</v>
+        <v>19.3942</v>
       </c>
       <c r="C18" t="n">
-        <v>32.2731</v>
+        <v>17.2414</v>
       </c>
       <c r="D18" t="n">
-        <v>33.2023</v>
+        <v>32.8382</v>
       </c>
       <c r="E18" t="n">
-        <v>13.3665</v>
+        <v>13.5174</v>
       </c>
       <c r="F18" t="n">
-        <v>27.3301</v>
+        <v>27.7333</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.7604</v>
+        <v>18.7832</v>
       </c>
       <c r="C19" t="n">
-        <v>31.223</v>
+        <v>17.2748</v>
       </c>
       <c r="D19" t="n">
-        <v>33.357</v>
+        <v>32.9361</v>
       </c>
       <c r="E19" t="n">
-        <v>13.1222</v>
+        <v>13.3551</v>
       </c>
       <c r="F19" t="n">
-        <v>27.1405</v>
+        <v>27.4199</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.2222</v>
+        <v>18.3376</v>
       </c>
       <c r="C20" t="n">
-        <v>31.0659</v>
+        <v>17.2912</v>
       </c>
       <c r="D20" t="n">
-        <v>33.4089</v>
+        <v>33.041</v>
       </c>
       <c r="E20" t="n">
-        <v>12.8397</v>
+        <v>13.0664</v>
       </c>
       <c r="F20" t="n">
-        <v>26.7898</v>
+        <v>27.2508</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.5339</v>
+        <v>17.6572</v>
       </c>
       <c r="C21" t="n">
-        <v>30.3915</v>
+        <v>17.2341</v>
       </c>
       <c r="D21" t="n">
-        <v>32.787</v>
+        <v>32.3358</v>
       </c>
       <c r="E21" t="n">
-        <v>12.4157</v>
+        <v>12.8131</v>
       </c>
       <c r="F21" t="n">
-        <v>26.324</v>
+        <v>26.6946</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.6897</v>
+        <v>16.9162</v>
       </c>
       <c r="C22" t="n">
-        <v>29.1225</v>
+        <v>18.6908</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6856</v>
+        <v>32.4073</v>
       </c>
       <c r="E22" t="n">
-        <v>12.0905</v>
+        <v>12.4032</v>
       </c>
       <c r="F22" t="n">
-        <v>26.0988</v>
+        <v>26.4127</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0205</v>
+        <v>16.0896</v>
       </c>
       <c r="C23" t="n">
-        <v>28.7585</v>
+        <v>18.4952</v>
       </c>
       <c r="D23" t="n">
-        <v>32.745</v>
+        <v>32.2756</v>
       </c>
       <c r="E23" t="n">
-        <v>17.9848</v>
+        <v>17.9115</v>
       </c>
       <c r="F23" t="n">
-        <v>30.4562</v>
+        <v>30.897</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.4885</v>
+        <v>23.4555</v>
       </c>
       <c r="C24" t="n">
-        <v>36.1504</v>
+        <v>18.4392</v>
       </c>
       <c r="D24" t="n">
-        <v>32.8504</v>
+        <v>32.4461</v>
       </c>
       <c r="E24" t="n">
-        <v>17.2807</v>
+        <v>17.3464</v>
       </c>
       <c r="F24" t="n">
-        <v>30.1648</v>
+        <v>30.5295</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>23.1061</v>
+        <v>22.9453</v>
       </c>
       <c r="C25" t="n">
-        <v>35.5933</v>
+        <v>18.2828</v>
       </c>
       <c r="D25" t="n">
-        <v>32.7422</v>
+        <v>32.6176</v>
       </c>
       <c r="E25" t="n">
-        <v>16.8562</v>
+        <v>16.8674</v>
       </c>
       <c r="F25" t="n">
-        <v>29.9466</v>
+        <v>30.3907</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.7971</v>
+        <v>22.5193</v>
       </c>
       <c r="C26" t="n">
-        <v>35.2206</v>
+        <v>18.1973</v>
       </c>
       <c r="D26" t="n">
-        <v>32.7006</v>
+        <v>32.7278</v>
       </c>
       <c r="E26" t="n">
-        <v>16.5267</v>
+        <v>16.3651</v>
       </c>
       <c r="F26" t="n">
-        <v>29.7768</v>
+        <v>30.0169</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>22.2761</v>
+        <v>22.0849</v>
       </c>
       <c r="C27" t="n">
-        <v>34.9529</v>
+        <v>18.2442</v>
       </c>
       <c r="D27" t="n">
-        <v>32.7929</v>
+        <v>32.6862</v>
       </c>
       <c r="E27" t="n">
-        <v>16.1174</v>
+        <v>16.0993</v>
       </c>
       <c r="F27" t="n">
-        <v>29.4189</v>
+        <v>29.5858</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.8868</v>
+        <v>21.6913</v>
       </c>
       <c r="C28" t="n">
-        <v>34.5036</v>
+        <v>18.1654</v>
       </c>
       <c r="D28" t="n">
-        <v>33.0972</v>
+        <v>32.4305</v>
       </c>
       <c r="E28" t="n">
-        <v>15.6628</v>
+        <v>15.8612</v>
       </c>
       <c r="F28" t="n">
-        <v>29.1388</v>
+        <v>29.2683</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.3318</v>
+        <v>21.1204</v>
       </c>
       <c r="C29" t="n">
-        <v>33.9968</v>
+        <v>17.9888</v>
       </c>
       <c r="D29" t="n">
-        <v>33.2697</v>
+        <v>32.5441</v>
       </c>
       <c r="E29" t="n">
-        <v>15.2409</v>
+        <v>15.5847</v>
       </c>
       <c r="F29" t="n">
-        <v>28.7785</v>
+        <v>29.1214</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6854</v>
+        <v>20.7176</v>
       </c>
       <c r="C30" t="n">
-        <v>33.3813</v>
+        <v>17.859</v>
       </c>
       <c r="D30" t="n">
-        <v>33.4102</v>
+        <v>32.7954</v>
       </c>
       <c r="E30" t="n">
-        <v>14.9577</v>
+        <v>15.2222</v>
       </c>
       <c r="F30" t="n">
-        <v>28.525</v>
+        <v>28.7549</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.2192</v>
+        <v>20.1794</v>
       </c>
       <c r="C31" t="n">
-        <v>32.5888</v>
+        <v>17.7785</v>
       </c>
       <c r="D31" t="n">
-        <v>33.3864</v>
+        <v>32.8309</v>
       </c>
       <c r="E31" t="n">
-        <v>14.7662</v>
+        <v>14.9046</v>
       </c>
       <c r="F31" t="n">
-        <v>28.1259</v>
+        <v>28.571</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6486</v>
+        <v>19.6262</v>
       </c>
       <c r="C32" t="n">
-        <v>32.4723</v>
+        <v>17.7647</v>
       </c>
       <c r="D32" t="n">
-        <v>33.5474</v>
+        <v>33.0879</v>
       </c>
       <c r="E32" t="n">
-        <v>14.3228</v>
+        <v>14.5975</v>
       </c>
       <c r="F32" t="n">
-        <v>27.8454</v>
+        <v>28.2629</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0307</v>
+        <v>19.1363</v>
       </c>
       <c r="C33" t="n">
-        <v>31.4465</v>
+        <v>17.5813</v>
       </c>
       <c r="D33" t="n">
-        <v>33.8557</v>
+        <v>33.2216</v>
       </c>
       <c r="E33" t="n">
-        <v>14.0183</v>
+        <v>14.3056</v>
       </c>
       <c r="F33" t="n">
-        <v>27.3854</v>
+        <v>27.9217</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.6145</v>
+        <v>18.5359</v>
       </c>
       <c r="C34" t="n">
-        <v>31.5902</v>
+        <v>17.653</v>
       </c>
       <c r="D34" t="n">
-        <v>33.9392</v>
+        <v>33.2507</v>
       </c>
       <c r="E34" t="n">
-        <v>13.6812</v>
+        <v>13.998</v>
       </c>
       <c r="F34" t="n">
-        <v>27.1364</v>
+        <v>27.5286</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9189</v>
+        <v>17.9915</v>
       </c>
       <c r="C35" t="n">
-        <v>30.8037</v>
+        <v>17.5434</v>
       </c>
       <c r="D35" t="n">
-        <v>33.4353</v>
+        <v>32.7102</v>
       </c>
       <c r="E35" t="n">
-        <v>13.3631</v>
+        <v>13.6515</v>
       </c>
       <c r="F35" t="n">
-        <v>26.6641</v>
+        <v>27.1818</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.3118</v>
+        <v>17.3646</v>
       </c>
       <c r="C36" t="n">
-        <v>30.04</v>
+        <v>17.4788</v>
       </c>
       <c r="D36" t="n">
-        <v>33.1293</v>
+        <v>32.7655</v>
       </c>
       <c r="E36" t="n">
-        <v>12.8535</v>
+        <v>13.2918</v>
       </c>
       <c r="F36" t="n">
-        <v>26.3403</v>
+        <v>26.7193</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.3617</v>
+        <v>16.501</v>
       </c>
       <c r="C37" t="n">
-        <v>28.7195</v>
+        <v>18.7737</v>
       </c>
       <c r="D37" t="n">
-        <v>33.0212</v>
+        <v>32.7163</v>
       </c>
       <c r="E37" t="n">
-        <v>18.0566</v>
+        <v>18.3617</v>
       </c>
       <c r="F37" t="n">
-        <v>30.8008</v>
+        <v>31.0303</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.6995</v>
+        <v>23.6872</v>
       </c>
       <c r="C38" t="n">
-        <v>35.4199</v>
+        <v>18.5993</v>
       </c>
       <c r="D38" t="n">
-        <v>33.2222</v>
+        <v>32.6466</v>
       </c>
       <c r="E38" t="n">
-        <v>17.6505</v>
+        <v>17.8577</v>
       </c>
       <c r="F38" t="n">
-        <v>30.6086</v>
+        <v>30.7522</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.3326</v>
+        <v>23.3005</v>
       </c>
       <c r="C39" t="n">
-        <v>35.2031</v>
+        <v>18.5542</v>
       </c>
       <c r="D39" t="n">
-        <v>33.2973</v>
+        <v>32.6708</v>
       </c>
       <c r="E39" t="n">
-        <v>17.3155</v>
+        <v>17.394</v>
       </c>
       <c r="F39" t="n">
-        <v>30.1722</v>
+        <v>30.6242</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>23.0392</v>
+        <v>22.8411</v>
       </c>
       <c r="C40" t="n">
-        <v>34.7634</v>
+        <v>18.4106</v>
       </c>
       <c r="D40" t="n">
-        <v>33.2941</v>
+        <v>32.7145</v>
       </c>
       <c r="E40" t="n">
-        <v>16.8292</v>
+        <v>16.9559</v>
       </c>
       <c r="F40" t="n">
-        <v>29.6892</v>
+        <v>30.1412</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4939</v>
+        <v>22.4231</v>
       </c>
       <c r="C41" t="n">
-        <v>34.4315</v>
+        <v>18.2905</v>
       </c>
       <c r="D41" t="n">
-        <v>33.4042</v>
+        <v>32.7149</v>
       </c>
       <c r="E41" t="n">
-        <v>16.5258</v>
+        <v>16.5541</v>
       </c>
       <c r="F41" t="n">
-        <v>29.4629</v>
+        <v>29.9168</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>22.0018</v>
+        <v>21.9174</v>
       </c>
       <c r="C42" t="n">
-        <v>33.9416</v>
+        <v>18.2115</v>
       </c>
       <c r="D42" t="n">
-        <v>33.3549</v>
+        <v>32.6476</v>
       </c>
       <c r="E42" t="n">
-        <v>16.1307</v>
+        <v>16.2238</v>
       </c>
       <c r="F42" t="n">
-        <v>29.1631</v>
+        <v>29.7099</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.5467</v>
+        <v>21.3321</v>
       </c>
       <c r="C43" t="n">
-        <v>33.4815</v>
+        <v>18.0917</v>
       </c>
       <c r="D43" t="n">
-        <v>33.1089</v>
+        <v>32.9286</v>
       </c>
       <c r="E43" t="n">
-        <v>15.7004</v>
+        <v>15.9266</v>
       </c>
       <c r="F43" t="n">
-        <v>28.8604</v>
+        <v>29.3932</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.9831</v>
+        <v>20.9611</v>
       </c>
       <c r="C44" t="n">
-        <v>33.2733</v>
+        <v>18.0209</v>
       </c>
       <c r="D44" t="n">
-        <v>33.3912</v>
+        <v>33.152</v>
       </c>
       <c r="E44" t="n">
-        <v>15.4492</v>
+        <v>15.7011</v>
       </c>
       <c r="F44" t="n">
-        <v>28.5114</v>
+        <v>29.0889</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.6156</v>
+        <v>20.4386</v>
       </c>
       <c r="C45" t="n">
-        <v>33.0259</v>
+        <v>17.8822</v>
       </c>
       <c r="D45" t="n">
-        <v>33.3018</v>
+        <v>33.274</v>
       </c>
       <c r="E45" t="n">
-        <v>15.0244</v>
+        <v>15.2963</v>
       </c>
       <c r="F45" t="n">
-        <v>28.2235</v>
+        <v>28.7271</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9192</v>
+        <v>20.0827</v>
       </c>
       <c r="C46" t="n">
-        <v>32.6008</v>
+        <v>17.7759</v>
       </c>
       <c r="D46" t="n">
-        <v>33.6617</v>
+        <v>33.2187</v>
       </c>
       <c r="E46" t="n">
-        <v>14.7192</v>
+        <v>15.0218</v>
       </c>
       <c r="F46" t="n">
-        <v>27.9758</v>
+        <v>28.3631</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.4288</v>
+        <v>19.4107</v>
       </c>
       <c r="C47" t="n">
-        <v>31.8156</v>
+        <v>17.7962</v>
       </c>
       <c r="D47" t="n">
-        <v>33.7315</v>
+        <v>33.4201</v>
       </c>
       <c r="E47" t="n">
-        <v>14.4012</v>
+        <v>14.715</v>
       </c>
       <c r="F47" t="n">
-        <v>27.7002</v>
+        <v>28.0157</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.7556</v>
+        <v>18.902</v>
       </c>
       <c r="C48" t="n">
-        <v>31.0295</v>
+        <v>17.6484</v>
       </c>
       <c r="D48" t="n">
-        <v>34.0369</v>
+        <v>33.5476</v>
       </c>
       <c r="E48" t="n">
-        <v>14.0275</v>
+        <v>14.4139</v>
       </c>
       <c r="F48" t="n">
-        <v>27.2765</v>
+        <v>27.6786</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1479</v>
+        <v>18.2366</v>
       </c>
       <c r="C49" t="n">
-        <v>30.9214</v>
+        <v>17.57</v>
       </c>
       <c r="D49" t="n">
-        <v>33.8724</v>
+        <v>33.6975</v>
       </c>
       <c r="E49" t="n">
-        <v>13.6464</v>
+        <v>14.0347</v>
       </c>
       <c r="F49" t="n">
-        <v>26.9558</v>
+        <v>27.2322</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.469</v>
+        <v>17.5587</v>
       </c>
       <c r="C50" t="n">
-        <v>30.4204</v>
+        <v>17.5468</v>
       </c>
       <c r="D50" t="n">
-        <v>33.5347</v>
+        <v>33.2129</v>
       </c>
       <c r="E50" t="n">
-        <v>13.2656</v>
+        <v>13.7225</v>
       </c>
       <c r="F50" t="n">
-        <v>26.5582</v>
+        <v>26.8783</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.7124</v>
+        <v>16.8426</v>
       </c>
       <c r="C51" t="n">
-        <v>29.3762</v>
+        <v>18.9665</v>
       </c>
       <c r="D51" t="n">
-        <v>33.5045</v>
+        <v>33.3672</v>
       </c>
       <c r="E51" t="n">
-        <v>18.5607</v>
+        <v>18.5684</v>
       </c>
       <c r="F51" t="n">
-        <v>30.9401</v>
+        <v>31.3005</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.6925</v>
+        <v>15.9084</v>
       </c>
       <c r="C52" t="n">
-        <v>29.019</v>
+        <v>18.8413</v>
       </c>
       <c r="D52" t="n">
-        <v>33.6106</v>
+        <v>33.1745</v>
       </c>
       <c r="E52" t="n">
-        <v>17.9688</v>
+        <v>18.0142</v>
       </c>
       <c r="F52" t="n">
-        <v>30.596</v>
+        <v>30.9289</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.5134</v>
+        <v>23.477</v>
       </c>
       <c r="C53" t="n">
-        <v>35.5641</v>
+        <v>18.6426</v>
       </c>
       <c r="D53" t="n">
-        <v>33.7737</v>
+        <v>33.0138</v>
       </c>
       <c r="E53" t="n">
-        <v>17.5436</v>
+        <v>17.6669</v>
       </c>
       <c r="F53" t="n">
-        <v>30.2776</v>
+        <v>30.6668</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1824</v>
+        <v>23.0557</v>
       </c>
       <c r="C54" t="n">
-        <v>35.18</v>
+        <v>18.4822</v>
       </c>
       <c r="D54" t="n">
-        <v>33.5824</v>
+        <v>33.2633</v>
       </c>
       <c r="E54" t="n">
-        <v>17.1566</v>
+        <v>17.1399</v>
       </c>
       <c r="F54" t="n">
-        <v>30.0259</v>
+        <v>30.3538</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6912</v>
+        <v>22.5607</v>
       </c>
       <c r="C55" t="n">
-        <v>34.9885</v>
+        <v>18.3628</v>
       </c>
       <c r="D55" t="n">
-        <v>33.67</v>
+        <v>33.4069</v>
       </c>
       <c r="E55" t="n">
-        <v>16.7803</v>
+        <v>16.8135</v>
       </c>
       <c r="F55" t="n">
-        <v>29.6667</v>
+        <v>30.0659</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.249</v>
+        <v>22.1319</v>
       </c>
       <c r="C56" t="n">
-        <v>34.7042</v>
+        <v>18.2324</v>
       </c>
       <c r="D56" t="n">
-        <v>33.7929</v>
+        <v>33.5194</v>
       </c>
       <c r="E56" t="n">
-        <v>16.3819</v>
+        <v>16.5465</v>
       </c>
       <c r="F56" t="n">
-        <v>29.3156</v>
+        <v>29.764</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.7579</v>
+        <v>21.5558</v>
       </c>
       <c r="C57" t="n">
-        <v>34.3657</v>
+        <v>18.1017</v>
       </c>
       <c r="D57" t="n">
-        <v>34.2574</v>
+        <v>33.578</v>
       </c>
       <c r="E57" t="n">
-        <v>16.016</v>
+        <v>16.1178</v>
       </c>
       <c r="F57" t="n">
-        <v>29.0165</v>
+        <v>29.4595</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.2142</v>
+        <v>21.033</v>
       </c>
       <c r="C58" t="n">
-        <v>32.9587</v>
+        <v>17.9974</v>
       </c>
       <c r="D58" t="n">
-        <v>35.0233</v>
+        <v>33.5478</v>
       </c>
       <c r="E58" t="n">
-        <v>15.6811</v>
+        <v>15.8438</v>
       </c>
       <c r="F58" t="n">
-        <v>28.6529</v>
+        <v>29.147</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.6326</v>
+        <v>20.5322</v>
       </c>
       <c r="C59" t="n">
-        <v>33.41</v>
+        <v>17.8972</v>
       </c>
       <c r="D59" t="n">
-        <v>34.6171</v>
+        <v>33.7441</v>
       </c>
       <c r="E59" t="n">
-        <v>15.3752</v>
+        <v>15.5076</v>
       </c>
       <c r="F59" t="n">
-        <v>28.3445</v>
+        <v>28.8254</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.1534</v>
+        <v>20.0238</v>
       </c>
       <c r="C60" t="n">
-        <v>32.8103</v>
+        <v>17.8063</v>
       </c>
       <c r="D60" t="n">
-        <v>34.9028</v>
+        <v>34.0996</v>
       </c>
       <c r="E60" t="n">
-        <v>15.001</v>
+        <v>15.2404</v>
       </c>
       <c r="F60" t="n">
-        <v>28.0209</v>
+        <v>28.547</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5521</v>
+        <v>19.5556</v>
       </c>
       <c r="C61" t="n">
-        <v>34.9591</v>
+        <v>17.7192</v>
       </c>
       <c r="D61" t="n">
-        <v>35.3237</v>
+        <v>34.4478</v>
       </c>
       <c r="E61" t="n">
-        <v>14.721</v>
+        <v>14.9299</v>
       </c>
       <c r="F61" t="n">
-        <v>27.7389</v>
+        <v>28.2419</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9004</v>
+        <v>18.9962</v>
       </c>
       <c r="C62" t="n">
-        <v>31.6846</v>
+        <v>17.6357</v>
       </c>
       <c r="D62" t="n">
-        <v>36.0398</v>
+        <v>34.7503</v>
       </c>
       <c r="E62" t="n">
-        <v>14.408</v>
+        <v>14.6454</v>
       </c>
       <c r="F62" t="n">
-        <v>27.4386</v>
+        <v>27.8808</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3415</v>
+        <v>18.4639</v>
       </c>
       <c r="C63" t="n">
-        <v>33.0123</v>
+        <v>17.5844</v>
       </c>
       <c r="D63" t="n">
-        <v>35.9435</v>
+        <v>35.0818</v>
       </c>
       <c r="E63" t="n">
-        <v>14.0174</v>
+        <v>14.3367</v>
       </c>
       <c r="F63" t="n">
-        <v>27.0639</v>
+        <v>27.4921</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.677</v>
+        <v>17.7976</v>
       </c>
       <c r="C64" t="n">
-        <v>32.8351</v>
+        <v>17.5238</v>
       </c>
       <c r="D64" t="n">
-        <v>39.9869</v>
+        <v>39.2477</v>
       </c>
       <c r="E64" t="n">
-        <v>13.624</v>
+        <v>13.9742</v>
       </c>
       <c r="F64" t="n">
-        <v>26.7174</v>
+        <v>27.0974</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>16.8304</v>
+        <v>17.0636</v>
       </c>
       <c r="C65" t="n">
-        <v>31.6404</v>
+        <v>19.1229</v>
       </c>
       <c r="D65" t="n">
-        <v>40.1637</v>
+        <v>39.8754</v>
       </c>
       <c r="E65" t="n">
-        <v>13.1706</v>
+        <v>13.6609</v>
       </c>
       <c r="F65" t="n">
-        <v>26.3737</v>
+        <v>26.7091</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.0601</v>
+        <v>16.1492</v>
       </c>
       <c r="C66" t="n">
-        <v>31.8927</v>
+        <v>18.9064</v>
       </c>
       <c r="D66" t="n">
-        <v>40.87</v>
+        <v>40.1163</v>
       </c>
       <c r="E66" t="n">
-        <v>18.621</v>
+        <v>18.7024</v>
       </c>
       <c r="F66" t="n">
-        <v>30.8112</v>
+        <v>31.1304</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.7274</v>
+        <v>23.6071</v>
       </c>
       <c r="C67" t="n">
-        <v>39.4914</v>
+        <v>18.7496</v>
       </c>
       <c r="D67" t="n">
-        <v>39.3933</v>
+        <v>40.4999</v>
       </c>
       <c r="E67" t="n">
-        <v>17.9778</v>
+        <v>18.4028</v>
       </c>
       <c r="F67" t="n">
-        <v>30.403</v>
+        <v>30.7683</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.3258</v>
+        <v>23.2214</v>
       </c>
       <c r="C68" t="n">
-        <v>39.0629</v>
+        <v>18.6049</v>
       </c>
       <c r="D68" t="n">
-        <v>40.7563</v>
+        <v>39.4277</v>
       </c>
       <c r="E68" t="n">
-        <v>17.5332</v>
+        <v>17.9561</v>
       </c>
       <c r="F68" t="n">
-        <v>30.2181</v>
+        <v>30.4576</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.9187</v>
+        <v>22.807</v>
       </c>
       <c r="C69" t="n">
-        <v>38.48</v>
+        <v>18.4652</v>
       </c>
       <c r="D69" t="n">
-        <v>41.0691</v>
+        <v>40.7586</v>
       </c>
       <c r="E69" t="n">
-        <v>17.1422</v>
+        <v>17.3665</v>
       </c>
       <c r="F69" t="n">
-        <v>29.8813</v>
+        <v>30.1469</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.4311</v>
+        <v>22.258</v>
       </c>
       <c r="C70" t="n">
-        <v>38.1453</v>
+        <v>18.2956</v>
       </c>
       <c r="D70" t="n">
-        <v>41.221</v>
+        <v>39.7302</v>
       </c>
       <c r="E70" t="n">
-        <v>16.7087</v>
+        <v>16.8271</v>
       </c>
       <c r="F70" t="n">
-        <v>29.5727</v>
+        <v>29.8242</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.9307</v>
+        <v>21.7515</v>
       </c>
       <c r="C71" t="n">
-        <v>37.5278</v>
+        <v>18.2263</v>
       </c>
       <c r="D71" t="n">
-        <v>40.0295</v>
+        <v>39.3906</v>
       </c>
       <c r="E71" t="n">
-        <v>16.2429</v>
+        <v>16.4329</v>
       </c>
       <c r="F71" t="n">
-        <v>29.1852</v>
+        <v>29.4652</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.3952</v>
+        <v>21.2364</v>
       </c>
       <c r="C72" t="n">
-        <v>41.0615</v>
+        <v>18.0512</v>
       </c>
       <c r="D72" t="n">
-        <v>40.0292</v>
+        <v>40.5647</v>
       </c>
       <c r="E72" t="n">
-        <v>15.8305</v>
+        <v>16.1134</v>
       </c>
       <c r="F72" t="n">
-        <v>28.8827</v>
+        <v>29.1905</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.849</v>
+        <v>20.7301</v>
       </c>
       <c r="C73" t="n">
-        <v>46.5749</v>
+        <v>17.9551</v>
       </c>
       <c r="D73" t="n">
-        <v>39.6001</v>
+        <v>41.1362</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5079</v>
+        <v>15.7585</v>
       </c>
       <c r="F73" t="n">
-        <v>28.5507</v>
+        <v>28.882</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.3272</v>
+        <v>20.2096</v>
       </c>
       <c r="C74" t="n">
-        <v>49.635</v>
+        <v>17.8952</v>
       </c>
       <c r="D74" t="n">
-        <v>41.5744</v>
+        <v>40.6831</v>
       </c>
       <c r="E74" t="n">
-        <v>15.2451</v>
+        <v>15.451</v>
       </c>
       <c r="F74" t="n">
-        <v>28.333</v>
+        <v>28.7737</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.7333</v>
+        <v>19.7203</v>
       </c>
       <c r="C75" t="n">
-        <v>39.7792</v>
+        <v>17.8361</v>
       </c>
       <c r="D75" t="n">
-        <v>41.3512</v>
+        <v>40.7969</v>
       </c>
       <c r="E75" t="n">
-        <v>14.8622</v>
+        <v>15.1469</v>
       </c>
       <c r="F75" t="n">
-        <v>27.9111</v>
+        <v>28.2964</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1354</v>
+        <v>19.1945</v>
       </c>
       <c r="C76" t="n">
-        <v>45.9412</v>
+        <v>17.7194</v>
       </c>
       <c r="D76" t="n">
-        <v>41.3674</v>
+        <v>41.0396</v>
       </c>
       <c r="E76" t="n">
-        <v>14.5805</v>
+        <v>14.824</v>
       </c>
       <c r="F76" t="n">
-        <v>27.5031</v>
+        <v>28.0505</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5534</v>
+        <v>18.6395</v>
       </c>
       <c r="C77" t="n">
-        <v>35.4589</v>
+        <v>17.6571</v>
       </c>
       <c r="D77" t="n">
-        <v>39.6164</v>
+        <v>41.0715</v>
       </c>
       <c r="E77" t="n">
-        <v>14.2344</v>
+        <v>14.5239</v>
       </c>
       <c r="F77" t="n">
-        <v>27.1796</v>
+        <v>27.6587</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.8367</v>
+        <v>17.9616</v>
       </c>
       <c r="C78" t="n">
-        <v>42.6854</v>
+        <v>17.6333</v>
       </c>
       <c r="D78" t="n">
-        <v>46.5541</v>
+        <v>47.4003</v>
       </c>
       <c r="E78" t="n">
-        <v>13.8546</v>
+        <v>14.1969</v>
       </c>
       <c r="F78" t="n">
-        <v>26.8469</v>
+        <v>27.2612</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.1179</v>
+        <v>17.2127</v>
       </c>
       <c r="C79" t="n">
-        <v>33.0953</v>
+        <v>19.3006</v>
       </c>
       <c r="D79" t="n">
-        <v>48.1396</v>
+        <v>46.493</v>
       </c>
       <c r="E79" t="n">
-        <v>13.3866</v>
+        <v>13.8802</v>
       </c>
       <c r="F79" t="n">
-        <v>26.5039</v>
+        <v>26.8365</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.332</v>
+        <v>16.5007</v>
       </c>
       <c r="C80" t="n">
-        <v>37.9874</v>
+        <v>19.086</v>
       </c>
       <c r="D80" t="n">
-        <v>45.8148</v>
+        <v>45.827</v>
       </c>
       <c r="E80" t="n">
-        <v>18.4899</v>
+        <v>18.5093</v>
       </c>
       <c r="F80" t="n">
-        <v>30.9433</v>
+        <v>31.0454</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.8414</v>
+        <v>23.77</v>
       </c>
       <c r="C81" t="n">
-        <v>38.5255</v>
+        <v>18.9435</v>
       </c>
       <c r="D81" t="n">
-        <v>46.8555</v>
+        <v>45.081</v>
       </c>
       <c r="E81" t="n">
-        <v>17.9706</v>
+        <v>18.0195</v>
       </c>
       <c r="F81" t="n">
-        <v>30.602</v>
+        <v>30.7302</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.463</v>
+        <v>23.3531</v>
       </c>
       <c r="C82" t="n">
-        <v>37.8681</v>
+        <v>18.7843</v>
       </c>
       <c r="D82" t="n">
-        <v>46.0065</v>
+        <v>46.5643</v>
       </c>
       <c r="E82" t="n">
-        <v>17.683</v>
+        <v>17.6242</v>
       </c>
       <c r="F82" t="n">
-        <v>29.8976</v>
+        <v>30.6312</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>23.069</v>
+        <v>22.8751</v>
       </c>
       <c r="C83" t="n">
-        <v>37.4032</v>
+        <v>18.6074</v>
       </c>
       <c r="D83" t="n">
-        <v>44.1733</v>
+        <v>46.1005</v>
       </c>
       <c r="E83" t="n">
-        <v>17.3199</v>
+        <v>17.289</v>
       </c>
       <c r="F83" t="n">
-        <v>29.6247</v>
+        <v>30.1926</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.5369</v>
+        <v>22.4329</v>
       </c>
       <c r="C84" t="n">
-        <v>36.9064</v>
+        <v>18.4437</v>
       </c>
       <c r="D84" t="n">
-        <v>43.9147</v>
+        <v>45.4796</v>
       </c>
       <c r="E84" t="n">
-        <v>16.7849</v>
+        <v>16.8969</v>
       </c>
       <c r="F84" t="n">
-        <v>29.3517</v>
+        <v>29.7657</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>22.068</v>
+        <v>21.9138</v>
       </c>
       <c r="C85" t="n">
-        <v>36.326</v>
+        <v>18.3182</v>
       </c>
       <c r="D85" t="n">
-        <v>43.4815</v>
+        <v>45.205</v>
       </c>
       <c r="E85" t="n">
-        <v>16.38</v>
+        <v>16.5701</v>
       </c>
       <c r="F85" t="n">
-        <v>29.0063</v>
+        <v>29.4867</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.5243</v>
+        <v>21.3706</v>
       </c>
       <c r="C86" t="n">
-        <v>35.7477</v>
+        <v>18.1518</v>
       </c>
       <c r="D86" t="n">
-        <v>44.4224</v>
+        <v>44.5204</v>
       </c>
       <c r="E86" t="n">
-        <v>16.0421</v>
+        <v>16.2566</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6286</v>
+        <v>29.1997</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>21.0241</v>
+        <v>20.885</v>
       </c>
       <c r="C87" t="n">
-        <v>36.2071</v>
+        <v>18.105</v>
       </c>
       <c r="D87" t="n">
-        <v>43.9621</v>
+        <v>42.4314</v>
       </c>
       <c r="E87" t="n">
-        <v>15.6993</v>
+        <v>15.9406</v>
       </c>
       <c r="F87" t="n">
-        <v>28.3591</v>
+        <v>28.9143</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.4821</v>
+        <v>20.349</v>
       </c>
       <c r="C88" t="n">
-        <v>45.0968</v>
+        <v>17.9999</v>
       </c>
       <c r="D88" t="n">
-        <v>43.7096</v>
+        <v>42.9925</v>
       </c>
       <c r="E88" t="n">
-        <v>15.3302</v>
+        <v>15.6051</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0746</v>
+        <v>28.6377</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8861</v>
+        <v>19.8405</v>
       </c>
       <c r="C89" t="n">
-        <v>43.6392</v>
+        <v>17.8591</v>
       </c>
       <c r="D89" t="n">
-        <v>43.6165</v>
+        <v>42.8583</v>
       </c>
       <c r="E89" t="n">
-        <v>15.0035</v>
+        <v>15.3024</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7353</v>
+        <v>28.3219</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2582</v>
+        <v>19.3095</v>
       </c>
       <c r="C90" t="n">
-        <v>41.9109</v>
+        <v>17.7775</v>
       </c>
       <c r="D90" t="n">
-        <v>43.3447</v>
+        <v>41.6805</v>
       </c>
       <c r="E90" t="n">
-        <v>14.6569</v>
+        <v>14.9663</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4086</v>
+        <v>28.0232</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.6802</v>
+        <v>18.7474</v>
       </c>
       <c r="C91" t="n">
-        <v>44.1551</v>
+        <v>17.6725</v>
       </c>
       <c r="D91" t="n">
-        <v>43.0113</v>
+        <v>42.0907</v>
       </c>
       <c r="E91" t="n">
-        <v>14.2865</v>
+        <v>14.6577</v>
       </c>
       <c r="F91" t="n">
-        <v>27.0207</v>
+        <v>27.6777</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.075</v>
+        <v>18.1897</v>
       </c>
       <c r="C92" t="n">
-        <v>47.0917</v>
+        <v>17.6072</v>
       </c>
       <c r="D92" t="n">
-        <v>48.2761</v>
+        <v>48.6127</v>
       </c>
       <c r="E92" t="n">
-        <v>13.9415</v>
+        <v>14.339</v>
       </c>
       <c r="F92" t="n">
-        <v>26.7174</v>
+        <v>27.2557</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.3412</v>
+        <v>17.4494</v>
       </c>
       <c r="C93" t="n">
-        <v>34.62</v>
+        <v>17.5217</v>
       </c>
       <c r="D93" t="n">
-        <v>48.1404</v>
+        <v>47.9375</v>
       </c>
       <c r="E93" t="n">
-        <v>13.6702</v>
+        <v>14.03</v>
       </c>
       <c r="F93" t="n">
-        <v>26.3303</v>
+        <v>26.9659</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.5434</v>
+        <v>16.6855</v>
       </c>
       <c r="C94" t="n">
-        <v>34.1406</v>
+        <v>19.0785</v>
       </c>
       <c r="D94" t="n">
-        <v>47.1703</v>
+        <v>48.7808</v>
       </c>
       <c r="E94" t="n">
-        <v>18.6704</v>
+        <v>18.6581</v>
       </c>
       <c r="F94" t="n">
-        <v>30.7571</v>
+        <v>31.5496</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.9358</v>
+        <v>23.8729</v>
       </c>
       <c r="C95" t="n">
-        <v>43.0391</v>
+        <v>18.8806</v>
       </c>
       <c r="D95" t="n">
-        <v>44.885</v>
+        <v>48.1176</v>
       </c>
       <c r="E95" t="n">
-        <v>18.1399</v>
+        <v>18.201</v>
       </c>
       <c r="F95" t="n">
-        <v>30.3046</v>
+        <v>30.9448</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.5871</v>
+        <v>23.4968</v>
       </c>
       <c r="C96" t="n">
-        <v>36.265</v>
+        <v>18.706</v>
       </c>
       <c r="D96" t="n">
-        <v>46.8455</v>
+        <v>47.3218</v>
       </c>
       <c r="E96" t="n">
-        <v>17.6794</v>
+        <v>17.8013</v>
       </c>
       <c r="F96" t="n">
-        <v>29.9868</v>
+        <v>30.5929</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.1831</v>
+        <v>23.0491</v>
       </c>
       <c r="C97" t="n">
-        <v>35.8033</v>
+        <v>18.5068</v>
       </c>
       <c r="D97" t="n">
-        <v>45.9835</v>
+        <v>44.6181</v>
       </c>
       <c r="E97" t="n">
-        <v>17.2956</v>
+        <v>17.3859</v>
       </c>
       <c r="F97" t="n">
-        <v>29.623</v>
+        <v>30.2788</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.6824</v>
+        <v>22.5493</v>
       </c>
       <c r="C98" t="n">
-        <v>35.3003</v>
+        <v>18.3643</v>
       </c>
       <c r="D98" t="n">
-        <v>45.3637</v>
+        <v>44.1941</v>
       </c>
       <c r="E98" t="n">
-        <v>16.8943</v>
+        <v>16.9838</v>
       </c>
       <c r="F98" t="n">
-        <v>29.4327</v>
+        <v>30.0106</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.1892</v>
+        <v>22.0618</v>
       </c>
       <c r="C99" t="n">
-        <v>34.7647</v>
+        <v>18.2167</v>
       </c>
       <c r="D99" t="n">
-        <v>44.5975</v>
+        <v>43.3661</v>
       </c>
       <c r="E99" t="n">
-        <v>16.489</v>
+        <v>16.6418</v>
       </c>
       <c r="F99" t="n">
-        <v>28.9629</v>
+        <v>29.7052</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.6765</v>
+        <v>21.5199</v>
       </c>
       <c r="C100" t="n">
-        <v>34.1601</v>
+        <v>18.1047</v>
       </c>
       <c r="D100" t="n">
-        <v>42.6413</v>
+        <v>42.6602</v>
       </c>
       <c r="E100" t="n">
-        <v>16.195</v>
+        <v>16.3502</v>
       </c>
       <c r="F100" t="n">
-        <v>28.688</v>
+        <v>29.3461</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>21.1382</v>
+        <v>21.0229</v>
       </c>
       <c r="C101" t="n">
-        <v>41.2215</v>
+        <v>17.9945</v>
       </c>
       <c r="D101" t="n">
-        <v>43.9625</v>
+        <v>44.1342</v>
       </c>
       <c r="E101" t="n">
-        <v>15.8379</v>
+        <v>16.0253</v>
       </c>
       <c r="F101" t="n">
-        <v>28.4697</v>
+        <v>29.1084</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.5677</v>
+        <v>20.5036</v>
       </c>
       <c r="C102" t="n">
-        <v>47.6138</v>
+        <v>17.8791</v>
       </c>
       <c r="D102" t="n">
-        <v>43.1397</v>
+        <v>44.104</v>
       </c>
       <c r="E102" t="n">
-        <v>15.4383</v>
+        <v>15.6948</v>
       </c>
       <c r="F102" t="n">
-        <v>28.1029</v>
+        <v>28.708</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9911</v>
+        <v>19.9878</v>
       </c>
       <c r="C103" t="n">
-        <v>42.4258</v>
+        <v>17.7771</v>
       </c>
       <c r="D103" t="n">
-        <v>43.1233</v>
+        <v>43.6686</v>
       </c>
       <c r="E103" t="n">
-        <v>15.2115</v>
+        <v>15.4068</v>
       </c>
       <c r="F103" t="n">
-        <v>27.7892</v>
+        <v>28.4156</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3882</v>
+        <v>19.444</v>
       </c>
       <c r="C104" t="n">
-        <v>43.7564</v>
+        <v>17.7261</v>
       </c>
       <c r="D104" t="n">
-        <v>42.0808</v>
+        <v>43.1676</v>
       </c>
       <c r="E104" t="n">
-        <v>14.887</v>
+        <v>15.0742</v>
       </c>
       <c r="F104" t="n">
-        <v>27.4462</v>
+        <v>28.1708</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.7817</v>
+        <v>18.8988</v>
       </c>
       <c r="C105" t="n">
-        <v>47.8877</v>
+        <v>17.6019</v>
       </c>
       <c r="D105" t="n">
-        <v>42.1023</v>
+        <v>42.9503</v>
       </c>
       <c r="E105" t="n">
-        <v>14.4624</v>
+        <v>14.8072</v>
       </c>
       <c r="F105" t="n">
-        <v>27.1565</v>
+        <v>27.8249</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.1394</v>
+        <v>18.3136</v>
       </c>
       <c r="C106" t="n">
-        <v>44.2975</v>
+        <v>17.5339</v>
       </c>
       <c r="D106" t="n">
-        <v>41.7304</v>
+        <v>42.3314</v>
       </c>
       <c r="E106" t="n">
-        <v>14.1191</v>
+        <v>14.5108</v>
       </c>
       <c r="F106" t="n">
-        <v>26.7899</v>
+        <v>27.4191</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.4355</v>
+        <v>17.6411</v>
       </c>
       <c r="C107" t="n">
-        <v>43.2704</v>
+        <v>17.4568</v>
       </c>
       <c r="D107" t="n">
-        <v>43.7578</v>
+        <v>44.5863</v>
       </c>
       <c r="E107" t="n">
-        <v>13.7357</v>
+        <v>14.1766</v>
       </c>
       <c r="F107" t="n">
-        <v>26.4929</v>
+        <v>27.0714</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.6643</v>
+        <v>16.8609</v>
       </c>
       <c r="C108" t="n">
-        <v>39.6331</v>
+        <v>19.1101</v>
       </c>
       <c r="D108" t="n">
-        <v>45.7302</v>
+        <v>45.3447</v>
       </c>
       <c r="E108" t="n">
-        <v>18.7594</v>
+        <v>18.6986</v>
       </c>
       <c r="F108" t="n">
-        <v>30.7871</v>
+        <v>31.3304</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.6688</v>
+        <v>15.955</v>
       </c>
       <c r="C109" t="n">
-        <v>35.1107</v>
+        <v>18.9375</v>
       </c>
       <c r="D109" t="n">
-        <v>45.7798</v>
+        <v>42.9703</v>
       </c>
       <c r="E109" t="n">
-        <v>18.3256</v>
+        <v>18.2769</v>
       </c>
       <c r="F109" t="n">
-        <v>30.4802</v>
+        <v>30.9535</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.6574</v>
+        <v>23.5323</v>
       </c>
       <c r="C110" t="n">
-        <v>43.7762</v>
+        <v>18.7353</v>
       </c>
       <c r="D110" t="n">
-        <v>42.8422</v>
+        <v>42.4841</v>
       </c>
       <c r="E110" t="n">
-        <v>17.8574</v>
+        <v>17.8693</v>
       </c>
       <c r="F110" t="n">
-        <v>30.0373</v>
+        <v>30.6285</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.2577</v>
+        <v>23.1179</v>
       </c>
       <c r="C111" t="n">
-        <v>43.5336</v>
+        <v>18.6181</v>
       </c>
       <c r="D111" t="n">
-        <v>42.2603</v>
+        <v>45.1277</v>
       </c>
       <c r="E111" t="n">
-        <v>17.3616</v>
+        <v>17.4885</v>
       </c>
       <c r="F111" t="n">
-        <v>29.6895</v>
+        <v>30.2935</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.8029</v>
+        <v>22.6481</v>
       </c>
       <c r="C112" t="n">
-        <v>43.22</v>
+        <v>18.471</v>
       </c>
       <c r="D112" t="n">
-        <v>42.6144</v>
+        <v>44.5424</v>
       </c>
       <c r="E112" t="n">
-        <v>16.9728</v>
+        <v>17.1031</v>
       </c>
       <c r="F112" t="n">
-        <v>29.3158</v>
+        <v>29.9256</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.2719</v>
+        <v>22.1541</v>
       </c>
       <c r="C113" t="n">
-        <v>42.8442</v>
+        <v>18.3286</v>
       </c>
       <c r="D113" t="n">
-        <v>42.165</v>
+        <v>43.8935</v>
       </c>
       <c r="E113" t="n">
-        <v>16.6592</v>
+        <v>16.7347</v>
       </c>
       <c r="F113" t="n">
-        <v>29.21</v>
+        <v>29.7288</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.7509</v>
+        <v>21.6456</v>
       </c>
       <c r="C114" t="n">
-        <v>42.5989</v>
+        <v>18.2004</v>
       </c>
       <c r="D114" t="n">
-        <v>41.3722</v>
+        <v>43.5458</v>
       </c>
       <c r="E114" t="n">
-        <v>16.2918</v>
+        <v>16.4426</v>
       </c>
       <c r="F114" t="n">
-        <v>28.8274</v>
+        <v>29.4169</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.2248</v>
+        <v>21.1078</v>
       </c>
       <c r="C115" t="n">
-        <v>41.8988</v>
+        <v>18.075</v>
       </c>
       <c r="D115" t="n">
-        <v>41.6496</v>
+        <v>40.907</v>
       </c>
       <c r="E115" t="n">
-        <v>15.9256</v>
+        <v>16.0967</v>
       </c>
       <c r="F115" t="n">
-        <v>28.5106</v>
+        <v>29.0742</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.6745</v>
+        <v>20.6041</v>
       </c>
       <c r="C116" t="n">
-        <v>43.0803</v>
+        <v>17.9626</v>
       </c>
       <c r="D116" t="n">
-        <v>40.628</v>
+        <v>40.5868</v>
       </c>
       <c r="E116" t="n">
-        <v>15.5919</v>
+        <v>15.7909</v>
       </c>
       <c r="F116" t="n">
-        <v>28.1445</v>
+        <v>28.7788</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.1106</v>
+        <v>20.0822</v>
       </c>
       <c r="C117" t="n">
-        <v>32.0041</v>
+        <v>17.8605</v>
       </c>
       <c r="D117" t="n">
-        <v>40.7502</v>
+        <v>40.1565</v>
       </c>
       <c r="E117" t="n">
-        <v>15.2796</v>
+        <v>15.4854</v>
       </c>
       <c r="F117" t="n">
-        <v>27.8598</v>
+        <v>28.4437</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5348</v>
+        <v>19.5536</v>
       </c>
       <c r="C118" t="n">
-        <v>38.4175</v>
+        <v>17.7314</v>
       </c>
       <c r="D118" t="n">
-        <v>39.617</v>
+        <v>39.8806</v>
       </c>
       <c r="E118" t="n">
-        <v>14.9514</v>
+        <v>15.1902</v>
       </c>
       <c r="F118" t="n">
-        <v>27.5468</v>
+        <v>28.1431</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9013</v>
+        <v>19.0123</v>
       </c>
       <c r="C119" t="n">
-        <v>40.5398</v>
+        <v>17.6824</v>
       </c>
       <c r="D119" t="n">
-        <v>41.0675</v>
+        <v>39.5947</v>
       </c>
       <c r="E119" t="n">
-        <v>14.5965</v>
+        <v>14.8836</v>
       </c>
       <c r="F119" t="n">
-        <v>27.2492</v>
+        <v>27.7839</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.2777</v>
+        <v>18.4066</v>
       </c>
       <c r="C120" t="n">
-        <v>39.8551</v>
+        <v>17.6048</v>
       </c>
       <c r="D120" t="n">
-        <v>40.8494</v>
+        <v>39.4443</v>
       </c>
       <c r="E120" t="n">
-        <v>14.2473</v>
+        <v>14.5638</v>
       </c>
       <c r="F120" t="n">
-        <v>26.9032</v>
+        <v>27.4291</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.6153</v>
+        <v>17.7588</v>
       </c>
       <c r="C121" t="n">
-        <v>43.0675</v>
+        <v>17.5187</v>
       </c>
       <c r="D121" t="n">
-        <v>46.6535</v>
+        <v>47.4227</v>
       </c>
       <c r="E121" t="n">
-        <v>13.8848</v>
+        <v>14.2506</v>
       </c>
       <c r="F121" t="n">
-        <v>26.4601</v>
+        <v>27.0529</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>16.9027</v>
+        <v>17.0916</v>
       </c>
       <c r="C122" t="n">
-        <v>36.6584</v>
+        <v>19.1371</v>
       </c>
       <c r="D122" t="n">
-        <v>47.4042</v>
+        <v>46.791</v>
       </c>
       <c r="E122" t="n">
-        <v>13.4822</v>
+        <v>13.8971</v>
       </c>
       <c r="F122" t="n">
-        <v>26.1623</v>
+        <v>26.7149</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.0029</v>
+        <v>16.2349</v>
       </c>
       <c r="C123" t="n">
-        <v>37.8592</v>
+        <v>18.9256</v>
       </c>
       <c r="D123" t="n">
-        <v>47.0682</v>
+        <v>46.0041</v>
       </c>
       <c r="E123" t="n">
-        <v>18.2402</v>
+        <v>18.3693</v>
       </c>
       <c r="F123" t="n">
-        <v>30.3196</v>
+        <v>30.8993</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.731</v>
+        <v>23.6216</v>
       </c>
       <c r="C124" t="n">
-        <v>49.0105</v>
+        <v>18.7487</v>
       </c>
       <c r="D124" t="n">
-        <v>44.9102</v>
+        <v>45.5274</v>
       </c>
       <c r="E124" t="n">
-        <v>17.8302</v>
+        <v>17.9551</v>
       </c>
       <c r="F124" t="n">
-        <v>30.0253</v>
+        <v>30.6548</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.3177</v>
+        <v>23.2069</v>
       </c>
       <c r="C125" t="n">
-        <v>45.5114</v>
+        <v>18.5754</v>
       </c>
       <c r="D125" t="n">
-        <v>44.6338</v>
+        <v>46.2386</v>
       </c>
       <c r="E125" t="n">
-        <v>17.3963</v>
+        <v>17.5523</v>
       </c>
       <c r="F125" t="n">
-        <v>29.6945</v>
+        <v>30.2819</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.885</v>
+        <v>22.7498</v>
       </c>
       <c r="C126" t="n">
-        <v>48.398</v>
+        <v>18.4242</v>
       </c>
       <c r="D126" t="n">
-        <v>43.5931</v>
+        <v>46.9696</v>
       </c>
       <c r="E126" t="n">
-        <v>16.9998</v>
+        <v>17.1873</v>
       </c>
       <c r="F126" t="n">
-        <v>29.4154</v>
+        <v>30.0695</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.3978</v>
+        <v>22.2563</v>
       </c>
       <c r="C127" t="n">
-        <v>40.4796</v>
+        <v>18.283</v>
       </c>
       <c r="D127" t="n">
-        <v>44.329</v>
+        <v>43.9761</v>
       </c>
       <c r="E127" t="n">
-        <v>16.632</v>
+        <v>16.8065</v>
       </c>
       <c r="F127" t="n">
-        <v>29.0023</v>
+        <v>29.7553</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.8972</v>
+        <v>21.7466</v>
       </c>
       <c r="C128" t="n">
-        <v>53.3022</v>
+        <v>18.1533</v>
       </c>
       <c r="D128" t="n">
-        <v>43.7223</v>
+        <v>43.6435</v>
       </c>
       <c r="E128" t="n">
-        <v>16.2591</v>
+        <v>16.4617</v>
       </c>
       <c r="F128" t="n">
-        <v>28.7829</v>
+        <v>29.4466</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.3606</v>
+        <v>21.2348</v>
       </c>
       <c r="C129" t="n">
-        <v>38.4694</v>
+        <v>18.033</v>
       </c>
       <c r="D129" t="n">
-        <v>44.3185</v>
+        <v>45.1253</v>
       </c>
       <c r="E129" t="n">
-        <v>15.9058</v>
+        <v>16.1577</v>
       </c>
       <c r="F129" t="n">
-        <v>28.4842</v>
+        <v>29.1223</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.8074</v>
+        <v>20.7007</v>
       </c>
       <c r="C130" t="n">
-        <v>42.7734</v>
+        <v>17.9185</v>
       </c>
       <c r="D130" t="n">
-        <v>43.801</v>
+        <v>44.4558</v>
       </c>
       <c r="E130" t="n">
-        <v>15.5501</v>
+        <v>15.8312</v>
       </c>
       <c r="F130" t="n">
-        <v>28.1375</v>
+        <v>28.8256</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.2609</v>
+        <v>20.1994</v>
       </c>
       <c r="C131" t="n">
-        <v>45.9563</v>
+        <v>17.822</v>
       </c>
       <c r="D131" t="n">
-        <v>43.3503</v>
+        <v>44.0468</v>
       </c>
       <c r="E131" t="n">
-        <v>15.2372</v>
+        <v>15.53</v>
       </c>
       <c r="F131" t="n">
-        <v>27.8596</v>
+        <v>28.5353</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6691</v>
+        <v>19.6849</v>
       </c>
       <c r="C132" t="n">
-        <v>38.8676</v>
+        <v>17.7272</v>
       </c>
       <c r="D132" t="n">
-        <v>41.0126</v>
+        <v>43.4996</v>
       </c>
       <c r="E132" t="n">
-        <v>14.8946</v>
+        <v>15.2352</v>
       </c>
       <c r="F132" t="n">
-        <v>27.5479</v>
+        <v>28.2276</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.075</v>
+        <v>19.1085</v>
       </c>
       <c r="C133" t="n">
-        <v>43.2547</v>
+        <v>17.6415</v>
       </c>
       <c r="D133" t="n">
-        <v>42.5655</v>
+        <v>43.0724</v>
       </c>
       <c r="E133" t="n">
-        <v>14.5557</v>
+        <v>14.9293</v>
       </c>
       <c r="F133" t="n">
-        <v>27.2022</v>
+        <v>27.9047</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.4387</v>
+        <v>18.5248</v>
       </c>
       <c r="C134" t="n">
-        <v>45.0011</v>
+        <v>17.5613</v>
       </c>
       <c r="D134" t="n">
-        <v>41.1758</v>
+        <v>42.6467</v>
       </c>
       <c r="E134" t="n">
-        <v>14.3412</v>
+        <v>14.6385</v>
       </c>
       <c r="F134" t="n">
-        <v>26.9558</v>
+        <v>27.4999</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.7922</v>
+        <v>17.9101</v>
       </c>
       <c r="C135" t="n">
-        <v>39.835</v>
+        <v>17.4833</v>
       </c>
       <c r="D135" t="n">
-        <v>48.4132</v>
+        <v>50.9687</v>
       </c>
       <c r="E135" t="n">
-        <v>13.9671</v>
+        <v>14.3299</v>
       </c>
       <c r="F135" t="n">
-        <v>26.6361</v>
+        <v>27.1472</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.0031</v>
+        <v>17.1919</v>
       </c>
       <c r="C136" t="n">
-        <v>36.1495</v>
+        <v>19.1946</v>
       </c>
       <c r="D136" t="n">
-        <v>48.7347</v>
+        <v>50.3449</v>
       </c>
       <c r="E136" t="n">
-        <v>13.5708</v>
+        <v>13.9835</v>
       </c>
       <c r="F136" t="n">
-        <v>26.212</v>
+        <v>26.7884</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.1535</v>
+        <v>16.3553</v>
       </c>
       <c r="C137" t="n">
-        <v>39.0694</v>
+        <v>18.9739</v>
       </c>
       <c r="D137" t="n">
-        <v>46.0122</v>
+        <v>46.5224</v>
       </c>
       <c r="E137" t="n">
-        <v>18.4682</v>
+        <v>18.4319</v>
       </c>
       <c r="F137" t="n">
-        <v>30.4312</v>
+        <v>31.0523</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.8006</v>
+        <v>23.702</v>
       </c>
       <c r="C138" t="n">
-        <v>47.4506</v>
+        <v>18.8018</v>
       </c>
       <c r="D138" t="n">
-        <v>46.7399</v>
+        <v>49.2414</v>
       </c>
       <c r="E138" t="n">
-        <v>18.0156</v>
+        <v>18.0116</v>
       </c>
       <c r="F138" t="n">
-        <v>30.1522</v>
+        <v>30.7323</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.4272</v>
+        <v>23.3023</v>
       </c>
       <c r="C139" t="n">
-        <v>49.0226</v>
+        <v>18.6282</v>
       </c>
       <c r="D139" t="n">
-        <v>46.1223</v>
+        <v>47.106</v>
       </c>
       <c r="E139" t="n">
-        <v>17.5882</v>
+        <v>17.64</v>
       </c>
       <c r="F139" t="n">
-        <v>29.8221</v>
+        <v>30.4036</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.989</v>
+        <v>22.8444</v>
       </c>
       <c r="C140" t="n">
-        <v>40.1964</v>
+        <v>18.465</v>
       </c>
       <c r="D140" t="n">
-        <v>46.3734</v>
+        <v>47.6828</v>
       </c>
       <c r="E140" t="n">
-        <v>17.0786</v>
+        <v>17.2392</v>
       </c>
       <c r="F140" t="n">
-        <v>29.3962</v>
+        <v>30.1121</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.4959</v>
+        <v>22.3579</v>
       </c>
       <c r="C141" t="n">
-        <v>43.3064</v>
+        <v>18.3156</v>
       </c>
       <c r="D141" t="n">
-        <v>44.9351</v>
+        <v>46.7413</v>
       </c>
       <c r="E141" t="n">
-        <v>16.7091</v>
+        <v>16.8704</v>
       </c>
       <c r="F141" t="n">
-        <v>29.1586</v>
+        <v>29.7868</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.9694</v>
+        <v>21.8383</v>
       </c>
       <c r="C142" t="n">
-        <v>49.6178</v>
+        <v>18.1846</v>
       </c>
       <c r="D142" t="n">
-        <v>44.5934</v>
+        <v>46.2169</v>
       </c>
       <c r="E142" t="n">
-        <v>16.3469</v>
+        <v>16.5429</v>
       </c>
       <c r="F142" t="n">
-        <v>28.7949</v>
+        <v>29.5107</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.4481</v>
+        <v>21.3144</v>
       </c>
       <c r="C143" t="n">
-        <v>46.4922</v>
+        <v>18.0609</v>
       </c>
       <c r="D143" t="n">
-        <v>44.7111</v>
+        <v>45.5887</v>
       </c>
       <c r="E143" t="n">
-        <v>15.9788</v>
+        <v>16.2245</v>
       </c>
       <c r="F143" t="n">
-        <v>28.5825</v>
+        <v>29.2084</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.9358</v>
+        <v>18.9438</v>
       </c>
       <c r="C2" t="n">
-        <v>14.2134</v>
+        <v>14.1537</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0992</v>
+        <v>31.8424</v>
       </c>
       <c r="E2" t="n">
-        <v>7.18203</v>
+        <v>7.28564</v>
       </c>
       <c r="F2" t="n">
-        <v>27.2574</v>
+        <v>27.1388</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4662</v>
+        <v>18.4179</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5448</v>
+        <v>14.4819</v>
       </c>
       <c r="D3" t="n">
-        <v>32.0611</v>
+        <v>32.0085</v>
       </c>
       <c r="E3" t="n">
-        <v>6.63095</v>
+        <v>6.82721</v>
       </c>
       <c r="F3" t="n">
-        <v>26.9225</v>
+        <v>26.808</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.0885</v>
+        <v>18.0845</v>
       </c>
       <c r="C4" t="n">
-        <v>14.7306</v>
+        <v>14.811</v>
       </c>
       <c r="D4" t="n">
-        <v>32.322</v>
+        <v>32.152</v>
       </c>
       <c r="E4" t="n">
-        <v>6.55712</v>
+        <v>6.19557</v>
       </c>
       <c r="F4" t="n">
-        <v>26.6196</v>
+        <v>26.6888</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.4428</v>
+        <v>17.6244</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8732</v>
+        <v>14.8626</v>
       </c>
       <c r="D5" t="n">
-        <v>32.5022</v>
+        <v>32.4311</v>
       </c>
       <c r="E5" t="n">
-        <v>5.87674</v>
+        <v>5.91732</v>
       </c>
       <c r="F5" t="n">
-        <v>26.6969</v>
+        <v>26.4763</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.0739</v>
+        <v>17.2234</v>
       </c>
       <c r="C6" t="n">
-        <v>15.0781</v>
+        <v>15.0291</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5329</v>
+        <v>32.3849</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8355</v>
+        <v>5.65017</v>
       </c>
       <c r="F6" t="n">
-        <v>26.2826</v>
+        <v>26.2082</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3634</v>
+        <v>16.3891</v>
       </c>
       <c r="C7" t="n">
-        <v>15.3796</v>
+        <v>15.3393</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8193</v>
+        <v>31.7305</v>
       </c>
       <c r="E7" t="n">
-        <v>5.65976</v>
+        <v>15.6022</v>
       </c>
       <c r="F7" t="n">
-        <v>25.7314</v>
+        <v>30.8725</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.6896</v>
+        <v>15.7558</v>
       </c>
       <c r="C8" t="n">
-        <v>16.957</v>
+        <v>16.9408</v>
       </c>
       <c r="D8" t="n">
-        <v>31.8969</v>
+        <v>31.803</v>
       </c>
       <c r="E8" t="n">
-        <v>6.01917</v>
+        <v>15.252</v>
       </c>
       <c r="F8" t="n">
-        <v>25.6575</v>
+        <v>30.4335</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.1364</v>
+        <v>14.9366</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0926</v>
+        <v>17.0452</v>
       </c>
       <c r="D9" t="n">
-        <v>31.9271</v>
+        <v>31.9131</v>
       </c>
       <c r="E9" t="n">
-        <v>15.6968</v>
+        <v>14.88</v>
       </c>
       <c r="F9" t="n">
-        <v>30.0395</v>
+        <v>30.2371</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.7843</v>
+        <v>22.7746</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1463</v>
+        <v>17.044</v>
       </c>
       <c r="D10" t="n">
-        <v>31.8977</v>
+        <v>31.8392</v>
       </c>
       <c r="E10" t="n">
-        <v>14.8661</v>
+        <v>14.514</v>
       </c>
       <c r="F10" t="n">
-        <v>30.0282</v>
+        <v>29.7047</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.3618</v>
+        <v>22.2925</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1877</v>
+        <v>17.1652</v>
       </c>
       <c r="D11" t="n">
-        <v>32.1717</v>
+        <v>32.0798</v>
       </c>
       <c r="E11" t="n">
-        <v>14.5749</v>
+        <v>14.3033</v>
       </c>
       <c r="F11" t="n">
-        <v>29.7461</v>
+        <v>29.5588</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.9836</v>
+        <v>21.9974</v>
       </c>
       <c r="C12" t="n">
-        <v>17.1115</v>
+        <v>17.0506</v>
       </c>
       <c r="D12" t="n">
-        <v>32.2366</v>
+        <v>32.2784</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2035</v>
+        <v>13.8358</v>
       </c>
       <c r="F12" t="n">
-        <v>29.6273</v>
+        <v>29.5546</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5992</v>
+        <v>21.5609</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2497</v>
+        <v>17.2697</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1801</v>
+        <v>32.0809</v>
       </c>
       <c r="E13" t="n">
-        <v>14.0603</v>
+        <v>13.5826</v>
       </c>
       <c r="F13" t="n">
-        <v>29.3258</v>
+        <v>29.1444</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.1742</v>
+        <v>21.165</v>
       </c>
       <c r="C14" t="n">
-        <v>17.2264</v>
+        <v>17.183</v>
       </c>
       <c r="D14" t="n">
-        <v>32.394</v>
+        <v>32.1933</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8277</v>
+        <v>13.3317</v>
       </c>
       <c r="F14" t="n">
-        <v>28.966</v>
+        <v>28.8359</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.7824</v>
+        <v>20.7821</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2785</v>
+        <v>17.2846</v>
       </c>
       <c r="D15" t="n">
-        <v>32.5337</v>
+        <v>32.5027</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5231</v>
+        <v>13.1997</v>
       </c>
       <c r="F15" t="n">
-        <v>28.6448</v>
+        <v>28.4471</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.1043</v>
+        <v>20.1257</v>
       </c>
       <c r="C16" t="n">
-        <v>17.2037</v>
+        <v>17.175</v>
       </c>
       <c r="D16" t="n">
-        <v>32.2778</v>
+        <v>32.5607</v>
       </c>
       <c r="E16" t="n">
-        <v>13.6121</v>
+        <v>12.9692</v>
       </c>
       <c r="F16" t="n">
-        <v>27.9426</v>
+        <v>28.234</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.7853</v>
+        <v>19.6161</v>
       </c>
       <c r="C17" t="n">
-        <v>17.2617</v>
+        <v>17.1553</v>
       </c>
       <c r="D17" t="n">
-        <v>32.3029</v>
+        <v>32.4718</v>
       </c>
       <c r="E17" t="n">
-        <v>13.247</v>
+        <v>12.8313</v>
       </c>
       <c r="F17" t="n">
-        <v>27.6228</v>
+        <v>27.804</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.2368</v>
+        <v>19.2149</v>
       </c>
       <c r="C18" t="n">
-        <v>17.2183</v>
+        <v>17.1894</v>
       </c>
       <c r="D18" t="n">
-        <v>32.6364</v>
+        <v>32.8508</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9531</v>
+        <v>12.5483</v>
       </c>
       <c r="F18" t="n">
-        <v>27.4068</v>
+        <v>27.6163</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.7583</v>
+        <v>18.6103</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1976</v>
+        <v>17.0991</v>
       </c>
       <c r="D19" t="n">
-        <v>32.8288</v>
+        <v>33.0025</v>
       </c>
       <c r="E19" t="n">
-        <v>12.5778</v>
+        <v>12.271</v>
       </c>
       <c r="F19" t="n">
-        <v>26.9917</v>
+        <v>27.219</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.139</v>
+        <v>18.0459</v>
       </c>
       <c r="C20" t="n">
-        <v>17.307</v>
+        <v>17.2871</v>
       </c>
       <c r="D20" t="n">
-        <v>32.8759</v>
+        <v>33.0077</v>
       </c>
       <c r="E20" t="n">
-        <v>12.5137</v>
+        <v>12.1832</v>
       </c>
       <c r="F20" t="n">
-        <v>26.6216</v>
+        <v>26.8723</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.5044</v>
+        <v>17.4448</v>
       </c>
       <c r="C21" t="n">
-        <v>17.2332</v>
+        <v>17.1349</v>
       </c>
       <c r="D21" t="n">
-        <v>32.1819</v>
+        <v>32.517</v>
       </c>
       <c r="E21" t="n">
-        <v>12.1213</v>
+        <v>17.7308</v>
       </c>
       <c r="F21" t="n">
-        <v>26.171</v>
+        <v>31.2646</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7732</v>
+        <v>16.7485</v>
       </c>
       <c r="C22" t="n">
-        <v>18.8412</v>
+        <v>18.7719</v>
       </c>
       <c r="D22" t="n">
-        <v>32.2832</v>
+        <v>32.3341</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7087</v>
+        <v>16.8825</v>
       </c>
       <c r="F22" t="n">
-        <v>25.8512</v>
+        <v>31.0114</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0498</v>
+        <v>16.0282</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5685</v>
+        <v>18.6134</v>
       </c>
       <c r="D23" t="n">
-        <v>32.2208</v>
+        <v>32.3465</v>
       </c>
       <c r="E23" t="n">
-        <v>17.4286</v>
+        <v>16.555</v>
       </c>
       <c r="F23" t="n">
-        <v>30.7018</v>
+        <v>30.881</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.4161</v>
+        <v>23.3924</v>
       </c>
       <c r="C24" t="n">
-        <v>18.4026</v>
+        <v>18.5281</v>
       </c>
       <c r="D24" t="n">
-        <v>32.2413</v>
+        <v>32.2761</v>
       </c>
       <c r="E24" t="n">
-        <v>16.8168</v>
+        <v>16.2122</v>
       </c>
       <c r="F24" t="n">
-        <v>30.2862</v>
+        <v>30.3882</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.9287</v>
+        <v>22.978</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3984</v>
+        <v>18.3561</v>
       </c>
       <c r="D25" t="n">
-        <v>32.5683</v>
+        <v>32.7187</v>
       </c>
       <c r="E25" t="n">
-        <v>16.2498</v>
+        <v>15.7336</v>
       </c>
       <c r="F25" t="n">
-        <v>29.9297</v>
+        <v>30.0457</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.5308</v>
+        <v>22.4948</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2862</v>
+        <v>18.2889</v>
       </c>
       <c r="D26" t="n">
-        <v>32.6093</v>
+        <v>32.8181</v>
       </c>
       <c r="E26" t="n">
-        <v>15.8688</v>
+        <v>15.4052</v>
       </c>
       <c r="F26" t="n">
-        <v>29.8015</v>
+        <v>29.8891</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>22.0833</v>
+        <v>22.0214</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1315</v>
+        <v>18.1223</v>
       </c>
       <c r="D27" t="n">
-        <v>32.5884</v>
+        <v>32.8089</v>
       </c>
       <c r="E27" t="n">
-        <v>15.7564</v>
+        <v>15.099</v>
       </c>
       <c r="F27" t="n">
-        <v>29.3497</v>
+        <v>29.6624</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.6951</v>
+        <v>21.5241</v>
       </c>
       <c r="C28" t="n">
-        <v>18.0109</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>32.3475</v>
+        <v>32.7976</v>
       </c>
       <c r="E28" t="n">
-        <v>15.2802</v>
+        <v>14.8119</v>
       </c>
       <c r="F28" t="n">
-        <v>29.0766</v>
+        <v>29.2484</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.0674</v>
+        <v>21.0586</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9726</v>
+        <v>17.9425</v>
       </c>
       <c r="D29" t="n">
-        <v>32.2994</v>
+        <v>32.9684</v>
       </c>
       <c r="E29" t="n">
-        <v>14.7164</v>
+        <v>14.5266</v>
       </c>
       <c r="F29" t="n">
-        <v>28.7073</v>
+        <v>28.7519</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6846</v>
+        <v>20.5961</v>
       </c>
       <c r="C30" t="n">
-        <v>17.9256</v>
+        <v>17.9004</v>
       </c>
       <c r="D30" t="n">
-        <v>32.6646</v>
+        <v>33.1141</v>
       </c>
       <c r="E30" t="n">
-        <v>14.3705</v>
+        <v>14.2481</v>
       </c>
       <c r="F30" t="n">
-        <v>28.5563</v>
+        <v>28.6281</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.1206</v>
+        <v>20.0851</v>
       </c>
       <c r="C31" t="n">
-        <v>17.8113</v>
+        <v>17.7818</v>
       </c>
       <c r="D31" t="n">
-        <v>32.6952</v>
+        <v>33.1571</v>
       </c>
       <c r="E31" t="n">
-        <v>14.1195</v>
+        <v>14.0706</v>
       </c>
       <c r="F31" t="n">
-        <v>28.0565</v>
+        <v>28.1635</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.7038</v>
+        <v>19.6668</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7778</v>
+        <v>17.7206</v>
       </c>
       <c r="D32" t="n">
-        <v>32.9005</v>
+        <v>33.2267</v>
       </c>
       <c r="E32" t="n">
-        <v>13.7823</v>
+        <v>13.6639</v>
       </c>
       <c r="F32" t="n">
-        <v>27.6948</v>
+        <v>27.9256</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.098</v>
+        <v>19.0595</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6952</v>
+        <v>17.6482</v>
       </c>
       <c r="D33" t="n">
-        <v>32.9414</v>
+        <v>33.1816</v>
       </c>
       <c r="E33" t="n">
-        <v>13.7915</v>
+        <v>13.725</v>
       </c>
       <c r="F33" t="n">
-        <v>27.2922</v>
+        <v>27.4452</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4959</v>
+        <v>18.4692</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5775</v>
+        <v>17.5806</v>
       </c>
       <c r="D34" t="n">
-        <v>33.0101</v>
+        <v>33.3094</v>
       </c>
       <c r="E34" t="n">
-        <v>13.47</v>
+        <v>13.4034</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9669</v>
+        <v>27.1673</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9637</v>
+        <v>17.9371</v>
       </c>
       <c r="C35" t="n">
-        <v>17.5087</v>
+        <v>17.4849</v>
       </c>
       <c r="D35" t="n">
-        <v>32.5998</v>
+        <v>32.7276</v>
       </c>
       <c r="E35" t="n">
-        <v>13.1555</v>
+        <v>18.0402</v>
       </c>
       <c r="F35" t="n">
-        <v>26.5323</v>
+        <v>31.6455</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.3328</v>
+        <v>17.2681</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4557</v>
+        <v>17.3968</v>
       </c>
       <c r="D36" t="n">
-        <v>32.4804</v>
+        <v>32.6763</v>
       </c>
       <c r="E36" t="n">
-        <v>12.7317</v>
+        <v>17.5438</v>
       </c>
       <c r="F36" t="n">
-        <v>26.1068</v>
+        <v>31.38</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.4182</v>
+        <v>16.5581</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8497</v>
+        <v>18.8348</v>
       </c>
       <c r="D37" t="n">
-        <v>32.5505</v>
+        <v>32.4591</v>
       </c>
       <c r="E37" t="n">
-        <v>17.3395</v>
+        <v>17.0555</v>
       </c>
       <c r="F37" t="n">
-        <v>30.9706</v>
+        <v>30.8222</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.7336</v>
+        <v>23.6684</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6699</v>
+        <v>18.6537</v>
       </c>
       <c r="D38" t="n">
-        <v>32.5304</v>
+        <v>32.4014</v>
       </c>
       <c r="E38" t="n">
-        <v>16.9274</v>
+        <v>16.7234</v>
       </c>
       <c r="F38" t="n">
-        <v>30.6781</v>
+        <v>30.6045</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.2913</v>
+        <v>23.2901</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5373</v>
+        <v>18.5582</v>
       </c>
       <c r="D39" t="n">
-        <v>32.4923</v>
+        <v>32.4994</v>
       </c>
       <c r="E39" t="n">
-        <v>16.5591</v>
+        <v>16.3452</v>
       </c>
       <c r="F39" t="n">
-        <v>30.1846</v>
+        <v>30.0555</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.9268</v>
+        <v>22.9245</v>
       </c>
       <c r="C40" t="n">
-        <v>18.4353</v>
+        <v>18.3765</v>
       </c>
       <c r="D40" t="n">
-        <v>32.3923</v>
+        <v>32.8644</v>
       </c>
       <c r="E40" t="n">
-        <v>16.1384</v>
+        <v>16.0651</v>
       </c>
       <c r="F40" t="n">
-        <v>29.9816</v>
+        <v>29.8162</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4942</v>
+        <v>22.4374</v>
       </c>
       <c r="C41" t="n">
-        <v>18.3108</v>
+        <v>18.2166</v>
       </c>
       <c r="D41" t="n">
-        <v>32.4383</v>
+        <v>32.8835</v>
       </c>
       <c r="E41" t="n">
-        <v>15.8112</v>
+        <v>15.6862</v>
       </c>
       <c r="F41" t="n">
-        <v>29.5325</v>
+        <v>29.5868</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.9979</v>
+        <v>21.9777</v>
       </c>
       <c r="C42" t="n">
-        <v>18.0743</v>
+        <v>18.1238</v>
       </c>
       <c r="D42" t="n">
-        <v>32.6736</v>
+        <v>32.9233</v>
       </c>
       <c r="E42" t="n">
-        <v>15.4782</v>
+        <v>15.3792</v>
       </c>
       <c r="F42" t="n">
-        <v>29.1957</v>
+        <v>29.3132</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4273</v>
+        <v>21.4231</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9842</v>
+        <v>17.9569</v>
       </c>
       <c r="D43" t="n">
-        <v>32.714</v>
+        <v>32.7666</v>
       </c>
       <c r="E43" t="n">
-        <v>15.2062</v>
+        <v>15.0749</v>
       </c>
       <c r="F43" t="n">
-        <v>28.887</v>
+        <v>29.0072</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.9423</v>
+        <v>20.8945</v>
       </c>
       <c r="C44" t="n">
-        <v>17.9116</v>
+        <v>17.8675</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7041</v>
+        <v>32.7785</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9351</v>
+        <v>14.8501</v>
       </c>
       <c r="F44" t="n">
-        <v>28.6089</v>
+        <v>28.7564</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4315</v>
+        <v>20.4267</v>
       </c>
       <c r="C45" t="n">
-        <v>17.7955</v>
+        <v>17.783</v>
       </c>
       <c r="D45" t="n">
-        <v>32.8684</v>
+        <v>33.0033</v>
       </c>
       <c r="E45" t="n">
-        <v>14.6107</v>
+        <v>14.4902</v>
       </c>
       <c r="F45" t="n">
-        <v>28.1471</v>
+        <v>28.2851</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9501</v>
+        <v>19.9065</v>
       </c>
       <c r="C46" t="n">
-        <v>17.7325</v>
+        <v>17.6852</v>
       </c>
       <c r="D46" t="n">
-        <v>32.8534</v>
+        <v>33.0424</v>
       </c>
       <c r="E46" t="n">
-        <v>14.3305</v>
+        <v>14.2297</v>
       </c>
       <c r="F46" t="n">
-        <v>27.9083</v>
+        <v>27.9684</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3878</v>
+        <v>19.3675</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5934</v>
+        <v>17.5766</v>
       </c>
       <c r="D47" t="n">
-        <v>33.1174</v>
+        <v>33.1175</v>
       </c>
       <c r="E47" t="n">
-        <v>14.0252</v>
+        <v>13.9642</v>
       </c>
       <c r="F47" t="n">
-        <v>27.5476</v>
+        <v>27.7035</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8032</v>
+        <v>18.8192</v>
       </c>
       <c r="C48" t="n">
-        <v>17.5</v>
+        <v>17.4988</v>
       </c>
       <c r="D48" t="n">
-        <v>33.1955</v>
+        <v>33.2499</v>
       </c>
       <c r="E48" t="n">
-        <v>13.748</v>
+        <v>13.6411</v>
       </c>
       <c r="F48" t="n">
-        <v>27.245</v>
+        <v>27.3252</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1254</v>
+        <v>18.1584</v>
       </c>
       <c r="C49" t="n">
-        <v>17.4144</v>
+        <v>17.4164</v>
       </c>
       <c r="D49" t="n">
-        <v>33.5313</v>
+        <v>33.5289</v>
       </c>
       <c r="E49" t="n">
-        <v>13.2329</v>
+        <v>13.3276</v>
       </c>
       <c r="F49" t="n">
-        <v>27.0158</v>
+        <v>27.2075</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.5586</v>
+        <v>17.5449</v>
       </c>
       <c r="C50" t="n">
-        <v>17.3544</v>
+        <v>17.3506</v>
       </c>
       <c r="D50" t="n">
-        <v>33.0275</v>
+        <v>32.8773</v>
       </c>
       <c r="E50" t="n">
-        <v>12.9352</v>
+        <v>17.6331</v>
       </c>
       <c r="F50" t="n">
-        <v>26.5069</v>
+        <v>31.474</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.7682</v>
+        <v>16.8151</v>
       </c>
       <c r="C51" t="n">
-        <v>18.8995</v>
+        <v>18.8302</v>
       </c>
       <c r="D51" t="n">
-        <v>33.0764</v>
+        <v>32.9274</v>
       </c>
       <c r="E51" t="n">
-        <v>17.5699</v>
+        <v>17.2655</v>
       </c>
       <c r="F51" t="n">
-        <v>30.887</v>
+        <v>30.9989</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.9602</v>
+        <v>15.8705</v>
       </c>
       <c r="C52" t="n">
-        <v>18.7514</v>
+        <v>18.7058</v>
       </c>
       <c r="D52" t="n">
-        <v>32.8856</v>
+        <v>32.8745</v>
       </c>
       <c r="E52" t="n">
-        <v>17.0489</v>
+        <v>16.8935</v>
       </c>
       <c r="F52" t="n">
-        <v>30.5731</v>
+        <v>30.7021</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.526</v>
+        <v>23.4888</v>
       </c>
       <c r="C53" t="n">
-        <v>18.5061</v>
+        <v>18.4774</v>
       </c>
       <c r="D53" t="n">
-        <v>33.0524</v>
+        <v>32.9756</v>
       </c>
       <c r="E53" t="n">
-        <v>16.5133</v>
+        <v>16.2997</v>
       </c>
       <c r="F53" t="n">
-        <v>30.3116</v>
+        <v>30.5221</v>
       </c>
     </row>
     <row r="54">
@@ -6122,16 +6122,16 @@
         <v>23.1214</v>
       </c>
       <c r="C54" t="n">
-        <v>18.4396</v>
+        <v>18.3815</v>
       </c>
       <c r="D54" t="n">
-        <v>33.4911</v>
+        <v>33.175</v>
       </c>
       <c r="E54" t="n">
-        <v>16.4999</v>
+        <v>16.216</v>
       </c>
       <c r="F54" t="n">
-        <v>30.0089</v>
+        <v>29.9445</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6239</v>
+        <v>22.6102</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2755</v>
+        <v>18.233</v>
       </c>
       <c r="D55" t="n">
-        <v>33.5302</v>
+        <v>33.008</v>
       </c>
       <c r="E55" t="n">
-        <v>16.0012</v>
+        <v>15.9147</v>
       </c>
       <c r="F55" t="n">
-        <v>29.5085</v>
+        <v>29.7257</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1366</v>
+        <v>22.1333</v>
       </c>
       <c r="C56" t="n">
-        <v>18.1195</v>
+        <v>18.0936</v>
       </c>
       <c r="D56" t="n">
-        <v>33.6921</v>
+        <v>33.1465</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7166</v>
+        <v>15.7556</v>
       </c>
       <c r="F56" t="n">
-        <v>29.3096</v>
+        <v>29.5289</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.6165</v>
+        <v>21.5875</v>
       </c>
       <c r="C57" t="n">
-        <v>18.0374</v>
+        <v>18.0189</v>
       </c>
       <c r="D57" t="n">
-        <v>33.7629</v>
+        <v>33.5038</v>
       </c>
       <c r="E57" t="n">
-        <v>15.2252</v>
+        <v>15.4562</v>
       </c>
       <c r="F57" t="n">
-        <v>28.9553</v>
+        <v>29.1722</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0873</v>
+        <v>21.0765</v>
       </c>
       <c r="C58" t="n">
-        <v>17.9258</v>
+        <v>17.937</v>
       </c>
       <c r="D58" t="n">
-        <v>33.5639</v>
+        <v>33.7417</v>
       </c>
       <c r="E58" t="n">
-        <v>14.9822</v>
+        <v>14.849</v>
       </c>
       <c r="F58" t="n">
-        <v>28.6633</v>
+        <v>28.7933</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5841</v>
+        <v>20.5916</v>
       </c>
       <c r="C59" t="n">
-        <v>17.8264</v>
+        <v>17.7699</v>
       </c>
       <c r="D59" t="n">
-        <v>33.9566</v>
+        <v>34.0485</v>
       </c>
       <c r="E59" t="n">
-        <v>14.7215</v>
+        <v>14.6441</v>
       </c>
       <c r="F59" t="n">
-        <v>28.4125</v>
+        <v>28.4663</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0404</v>
+        <v>19.9939</v>
       </c>
       <c r="C60" t="n">
-        <v>17.7377</v>
+        <v>17.7382</v>
       </c>
       <c r="D60" t="n">
-        <v>34.2061</v>
+        <v>34.4297</v>
       </c>
       <c r="E60" t="n">
-        <v>14.4429</v>
+        <v>14.4062</v>
       </c>
       <c r="F60" t="n">
-        <v>28.0742</v>
+        <v>28.1911</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5481</v>
+        <v>19.4844</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6509</v>
+        <v>17.6012</v>
       </c>
       <c r="D61" t="n">
-        <v>34.5066</v>
+        <v>34.7948</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3738</v>
+        <v>14.3145</v>
       </c>
       <c r="F61" t="n">
-        <v>27.5743</v>
+        <v>27.7812</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>19.0168</v>
+        <v>19.0037</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5903</v>
+        <v>17.5452</v>
       </c>
       <c r="D62" t="n">
-        <v>34.7127</v>
+        <v>35.1026</v>
       </c>
       <c r="E62" t="n">
-        <v>13.9613</v>
+        <v>13.8282</v>
       </c>
       <c r="F62" t="n">
-        <v>27.2713</v>
+        <v>27.5211</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3929</v>
+        <v>18.3376</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4993</v>
+        <v>17.4637</v>
       </c>
       <c r="D63" t="n">
-        <v>34.8604</v>
+        <v>35.4399</v>
       </c>
       <c r="E63" t="n">
-        <v>13.6818</v>
+        <v>13.5141</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9877</v>
+        <v>27.2038</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7637</v>
+        <v>17.7264</v>
       </c>
       <c r="C64" t="n">
-        <v>17.407</v>
+        <v>17.4203</v>
       </c>
       <c r="D64" t="n">
-        <v>38.9422</v>
+        <v>39.5426</v>
       </c>
       <c r="E64" t="n">
-        <v>13.2564</v>
+        <v>18.2804</v>
       </c>
       <c r="F64" t="n">
-        <v>26.6098</v>
+        <v>31.5704</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0242</v>
+        <v>17.0356</v>
       </c>
       <c r="C65" t="n">
-        <v>19.0409</v>
+        <v>19.007</v>
       </c>
       <c r="D65" t="n">
-        <v>39.1533</v>
+        <v>38.8738</v>
       </c>
       <c r="E65" t="n">
-        <v>12.8897</v>
+        <v>18.0858</v>
       </c>
       <c r="F65" t="n">
-        <v>26.2377</v>
+        <v>31.217</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.2</v>
+        <v>16.1227</v>
       </c>
       <c r="C66" t="n">
-        <v>18.8232</v>
+        <v>18.7187</v>
       </c>
       <c r="D66" t="n">
-        <v>39.5337</v>
+        <v>39.0455</v>
       </c>
       <c r="E66" t="n">
-        <v>17.3629</v>
+        <v>17.506</v>
       </c>
       <c r="F66" t="n">
-        <v>30.8204</v>
+        <v>30.9731</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6817</v>
+        <v>23.6267</v>
       </c>
       <c r="C67" t="n">
-        <v>18.6178</v>
+        <v>18.5877</v>
       </c>
       <c r="D67" t="n">
-        <v>39.8812</v>
+        <v>39.1038</v>
       </c>
       <c r="E67" t="n">
-        <v>17.022</v>
+        <v>17.2152</v>
       </c>
       <c r="F67" t="n">
-        <v>30.4655</v>
+        <v>30.5699</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2458</v>
+        <v>23.2273</v>
       </c>
       <c r="C68" t="n">
-        <v>18.4791</v>
+        <v>18.4289</v>
       </c>
       <c r="D68" t="n">
-        <v>38.7046</v>
+        <v>40.5285</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6211</v>
+        <v>16.5963</v>
       </c>
       <c r="F68" t="n">
-        <v>30.1046</v>
+        <v>30.3222</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.8283</v>
+        <v>22.7429</v>
       </c>
       <c r="C69" t="n">
-        <v>18.343</v>
+        <v>18.2974</v>
       </c>
       <c r="D69" t="n">
-        <v>39.9797</v>
+        <v>40.8663</v>
       </c>
       <c r="E69" t="n">
-        <v>16.0392</v>
+        <v>16.0814</v>
       </c>
       <c r="F69" t="n">
-        <v>29.6804</v>
+        <v>29.8376</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.3145</v>
+        <v>22.2573</v>
       </c>
       <c r="C70" t="n">
-        <v>18.3412</v>
+        <v>18.3034</v>
       </c>
       <c r="D70" t="n">
-        <v>38.7442</v>
+        <v>40.7372</v>
       </c>
       <c r="E70" t="n">
-        <v>15.6595</v>
+        <v>15.7154</v>
       </c>
       <c r="F70" t="n">
-        <v>29.3069</v>
+        <v>29.495</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.772</v>
+        <v>21.7376</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1988</v>
+        <v>18.1486</v>
       </c>
       <c r="D71" t="n">
-        <v>38.8432</v>
+        <v>39.4202</v>
       </c>
       <c r="E71" t="n">
-        <v>15.4098</v>
+        <v>15.3352</v>
       </c>
       <c r="F71" t="n">
-        <v>29.0099</v>
+        <v>29.186</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2644</v>
+        <v>21.2263</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0837</v>
+        <v>18.0338</v>
       </c>
       <c r="D72" t="n">
-        <v>39.8885</v>
+        <v>39.5284</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3094</v>
+        <v>15.2747</v>
       </c>
       <c r="F72" t="n">
-        <v>28.7955</v>
+        <v>28.8381</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.735</v>
+        <v>20.7096</v>
       </c>
       <c r="C73" t="n">
-        <v>18.0244</v>
+        <v>17.9448</v>
       </c>
       <c r="D73" t="n">
-        <v>40.177</v>
+        <v>39.4606</v>
       </c>
       <c r="E73" t="n">
-        <v>15.0362</v>
+        <v>14.9919</v>
       </c>
       <c r="F73" t="n">
-        <v>28.405</v>
+        <v>28.613</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1967</v>
+        <v>20.1444</v>
       </c>
       <c r="C74" t="n">
-        <v>17.9114</v>
+        <v>17.8669</v>
       </c>
       <c r="D74" t="n">
-        <v>40.1051</v>
+        <v>39.3334</v>
       </c>
       <c r="E74" t="n">
-        <v>14.7599</v>
+        <v>14.7006</v>
       </c>
       <c r="F74" t="n">
-        <v>28.073</v>
+        <v>28.2933</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6909</v>
+        <v>19.6437</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7997</v>
+        <v>17.7463</v>
       </c>
       <c r="D75" t="n">
-        <v>40.1166</v>
+        <v>39.4247</v>
       </c>
       <c r="E75" t="n">
-        <v>14.2685</v>
+        <v>14.2264</v>
       </c>
       <c r="F75" t="n">
-        <v>27.8456</v>
+        <v>27.9794</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1379</v>
+        <v>19.0956</v>
       </c>
       <c r="C76" t="n">
-        <v>17.7008</v>
+        <v>17.6901</v>
       </c>
       <c r="D76" t="n">
-        <v>40.1317</v>
+        <v>39.4517</v>
       </c>
       <c r="E76" t="n">
-        <v>13.9813</v>
+        <v>14.0026</v>
       </c>
       <c r="F76" t="n">
-        <v>27.3918</v>
+        <v>27.7065</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5602</v>
+        <v>18.5542</v>
       </c>
       <c r="C77" t="n">
-        <v>17.6315</v>
+        <v>17.6102</v>
       </c>
       <c r="D77" t="n">
-        <v>40.1099</v>
+        <v>39.4927</v>
       </c>
       <c r="E77" t="n">
-        <v>13.6883</v>
+        <v>13.745</v>
       </c>
       <c r="F77" t="n">
-        <v>27.0791</v>
+        <v>27.4001</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.976</v>
+        <v>17.9409</v>
       </c>
       <c r="C78" t="n">
-        <v>17.47</v>
+        <v>17.4444</v>
       </c>
       <c r="D78" t="n">
-        <v>46.1119</v>
+        <v>45.6494</v>
       </c>
       <c r="E78" t="n">
-        <v>13.5445</v>
+        <v>18.4954</v>
       </c>
       <c r="F78" t="n">
-        <v>26.7082</v>
+        <v>31.7488</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2222</v>
+        <v>17.2049</v>
       </c>
       <c r="C79" t="n">
-        <v>19.3759</v>
+        <v>19.3469</v>
       </c>
       <c r="D79" t="n">
-        <v>45.6684</v>
+        <v>45.9425</v>
       </c>
       <c r="E79" t="n">
-        <v>13.2171</v>
+        <v>17.8143</v>
       </c>
       <c r="F79" t="n">
-        <v>26.3528</v>
+        <v>31.3402</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4053</v>
+        <v>16.4085</v>
       </c>
       <c r="C80" t="n">
-        <v>19.1338</v>
+        <v>19.204</v>
       </c>
       <c r="D80" t="n">
-        <v>44.1453</v>
+        <v>46.9944</v>
       </c>
       <c r="E80" t="n">
-        <v>17.4923</v>
+        <v>17.4639</v>
       </c>
       <c r="F80" t="n">
-        <v>30.8823</v>
+        <v>31.0224</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7788</v>
+        <v>23.7801</v>
       </c>
       <c r="C81" t="n">
-        <v>18.9421</v>
+        <v>19.0214</v>
       </c>
       <c r="D81" t="n">
-        <v>43.9241</v>
+        <v>46.4031</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0497</v>
+        <v>17.1417</v>
       </c>
       <c r="F81" t="n">
-        <v>30.3977</v>
+        <v>30.6885</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3859</v>
+        <v>23.3793</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7584</v>
+        <v>18.7832</v>
       </c>
       <c r="D82" t="n">
-        <v>45.2386</v>
+        <v>44.1683</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7197</v>
+        <v>16.7775</v>
       </c>
       <c r="F82" t="n">
-        <v>30.0016</v>
+        <v>30.2437</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9422</v>
+        <v>22.9304</v>
       </c>
       <c r="C83" t="n">
-        <v>18.6253</v>
+        <v>18.6231</v>
       </c>
       <c r="D83" t="n">
-        <v>44.7871</v>
+        <v>43.9202</v>
       </c>
       <c r="E83" t="n">
-        <v>16.4091</v>
+        <v>16.4443</v>
       </c>
       <c r="F83" t="n">
-        <v>29.7308</v>
+        <v>29.9189</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4437</v>
+        <v>22.4358</v>
       </c>
       <c r="C84" t="n">
-        <v>18.3273</v>
+        <v>18.4798</v>
       </c>
       <c r="D84" t="n">
-        <v>44.2391</v>
+        <v>43.1929</v>
       </c>
       <c r="E84" t="n">
-        <v>16.084</v>
+        <v>16.1042</v>
       </c>
       <c r="F84" t="n">
-        <v>29.4269</v>
+        <v>29.7205</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9335</v>
+        <v>21.943</v>
       </c>
       <c r="C85" t="n">
-        <v>18.2146</v>
+        <v>18.1808</v>
       </c>
       <c r="D85" t="n">
-        <v>43.9632</v>
+        <v>44.7199</v>
       </c>
       <c r="E85" t="n">
-        <v>15.8117</v>
+        <v>15.8121</v>
       </c>
       <c r="F85" t="n">
-        <v>29.1366</v>
+        <v>29.4183</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.4074</v>
+        <v>21.4019</v>
       </c>
       <c r="C86" t="n">
-        <v>18.0974</v>
+        <v>18.1306</v>
       </c>
       <c r="D86" t="n">
-        <v>43.4552</v>
+        <v>43.9573</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4918</v>
+        <v>15.5345</v>
       </c>
       <c r="F86" t="n">
-        <v>28.8296</v>
+        <v>29.0934</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.9078</v>
+        <v>20.9006</v>
       </c>
       <c r="C87" t="n">
-        <v>18.0258</v>
+        <v>17.9838</v>
       </c>
       <c r="D87" t="n">
-        <v>41.8948</v>
+        <v>43.7462</v>
       </c>
       <c r="E87" t="n">
-        <v>15.2224</v>
+        <v>15.2213</v>
       </c>
       <c r="F87" t="n">
-        <v>28.4976</v>
+        <v>28.8129</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3671</v>
+        <v>20.3538</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8804</v>
+        <v>17.8884</v>
       </c>
       <c r="D88" t="n">
-        <v>41.7562</v>
+        <v>43.2839</v>
       </c>
       <c r="E88" t="n">
-        <v>14.9429</v>
+        <v>14.8852</v>
       </c>
       <c r="F88" t="n">
-        <v>28.1741</v>
+        <v>28.4335</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8509</v>
+        <v>19.8304</v>
       </c>
       <c r="C89" t="n">
-        <v>17.776</v>
+        <v>17.7711</v>
       </c>
       <c r="D89" t="n">
-        <v>41.1059</v>
+        <v>43.0821</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6278</v>
+        <v>14.6388</v>
       </c>
       <c r="F89" t="n">
-        <v>27.8334</v>
+        <v>28.0697</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.28</v>
+        <v>19.2955</v>
       </c>
       <c r="C90" t="n">
-        <v>17.695</v>
+        <v>17.6827</v>
       </c>
       <c r="D90" t="n">
-        <v>40.8676</v>
+        <v>43.0512</v>
       </c>
       <c r="E90" t="n">
-        <v>14.334</v>
+        <v>14.306</v>
       </c>
       <c r="F90" t="n">
-        <v>27.5003</v>
+        <v>27.7313</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7314</v>
+        <v>18.6823</v>
       </c>
       <c r="C91" t="n">
-        <v>17.585</v>
+        <v>17.5692</v>
       </c>
       <c r="D91" t="n">
-        <v>41.088</v>
+        <v>42.4424</v>
       </c>
       <c r="E91" t="n">
-        <v>14.0186</v>
+        <v>13.9949</v>
       </c>
       <c r="F91" t="n">
-        <v>27.133</v>
+        <v>27.3562</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.0922</v>
+        <v>18.0817</v>
       </c>
       <c r="C92" t="n">
-        <v>17.5221</v>
+        <v>17.4994</v>
       </c>
       <c r="D92" t="n">
-        <v>46.6562</v>
+        <v>47.9701</v>
       </c>
       <c r="E92" t="n">
-        <v>13.6881</v>
+        <v>18.1924</v>
       </c>
       <c r="F92" t="n">
-        <v>26.8159</v>
+        <v>31.6814</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.3716</v>
+        <v>17.3682</v>
       </c>
       <c r="C93" t="n">
-        <v>17.4302</v>
+        <v>17.4131</v>
       </c>
       <c r="D93" t="n">
-        <v>46.137</v>
+        <v>46.1778</v>
       </c>
       <c r="E93" t="n">
-        <v>13.3599</v>
+        <v>17.817</v>
       </c>
       <c r="F93" t="n">
-        <v>26.4338</v>
+        <v>31.6824</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6274</v>
+        <v>16.6371</v>
       </c>
       <c r="C94" t="n">
-        <v>19.1117</v>
+        <v>19.0236</v>
       </c>
       <c r="D94" t="n">
-        <v>46.7062</v>
+        <v>44.837</v>
       </c>
       <c r="E94" t="n">
-        <v>17.505</v>
+        <v>17.4113</v>
       </c>
       <c r="F94" t="n">
-        <v>31.0302</v>
+        <v>31.3142</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.893</v>
+        <v>23.8611</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8387</v>
+        <v>18.8358</v>
       </c>
       <c r="D95" t="n">
-        <v>46.1537</v>
+        <v>44.0557</v>
       </c>
       <c r="E95" t="n">
-        <v>17.0932</v>
+        <v>17.0464</v>
       </c>
       <c r="F95" t="n">
-        <v>30.4751</v>
+        <v>30.7183</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4813</v>
+        <v>23.4454</v>
       </c>
       <c r="C96" t="n">
-        <v>18.667</v>
+        <v>18.6839</v>
       </c>
       <c r="D96" t="n">
-        <v>45.4905</v>
+        <v>43.5134</v>
       </c>
       <c r="E96" t="n">
-        <v>16.6292</v>
+        <v>16.5767</v>
       </c>
       <c r="F96" t="n">
-        <v>30.2062</v>
+        <v>30.4244</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0326</v>
+        <v>23.0198</v>
       </c>
       <c r="C97" t="n">
-        <v>18.4996</v>
+        <v>18.5004</v>
       </c>
       <c r="D97" t="n">
-        <v>43.1888</v>
+        <v>45.6527</v>
       </c>
       <c r="E97" t="n">
-        <v>16.2402</v>
+        <v>16.2276</v>
       </c>
       <c r="F97" t="n">
-        <v>29.9568</v>
+        <v>30.0831</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5764</v>
+        <v>22.5419</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3661</v>
+        <v>18.3393</v>
       </c>
       <c r="D98" t="n">
-        <v>42.6893</v>
+        <v>45.0719</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9333</v>
+        <v>15.9114</v>
       </c>
       <c r="F98" t="n">
-        <v>29.5642</v>
+        <v>29.7246</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0612</v>
+        <v>22.0529</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2101</v>
+        <v>18.2032</v>
       </c>
       <c r="D99" t="n">
-        <v>42.0033</v>
+        <v>45.0199</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6296</v>
+        <v>15.7123</v>
       </c>
       <c r="F99" t="n">
-        <v>29.1939</v>
+        <v>29.228</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5243</v>
+        <v>21.5246</v>
       </c>
       <c r="C100" t="n">
-        <v>18.1859</v>
+        <v>18.187</v>
       </c>
       <c r="D100" t="n">
-        <v>41.4761</v>
+        <v>42.341</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3245</v>
+        <v>15.3864</v>
       </c>
       <c r="F100" t="n">
-        <v>28.9744</v>
+        <v>28.934</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.986</v>
+        <v>20.9913</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0586</v>
+        <v>18.0749</v>
       </c>
       <c r="D101" t="n">
-        <v>42.7052</v>
+        <v>42.195</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0532</v>
+        <v>15.0267</v>
       </c>
       <c r="F101" t="n">
-        <v>28.6059</v>
+        <v>28.5722</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4681</v>
+        <v>20.479</v>
       </c>
       <c r="C102" t="n">
-        <v>17.9657</v>
+        <v>17.9658</v>
       </c>
       <c r="D102" t="n">
-        <v>42.4975</v>
+        <v>41.3944</v>
       </c>
       <c r="E102" t="n">
-        <v>14.813</v>
+        <v>14.7645</v>
       </c>
       <c r="F102" t="n">
-        <v>28.2292</v>
+        <v>28.2896</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9217</v>
+        <v>19.9271</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8656</v>
+        <v>17.8525</v>
       </c>
       <c r="D103" t="n">
-        <v>42.001</v>
+        <v>40.963</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4958</v>
+        <v>14.4823</v>
       </c>
       <c r="F103" t="n">
-        <v>27.9014</v>
+        <v>27.9035</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.4133</v>
+        <v>19.4129</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7674</v>
+        <v>17.7491</v>
       </c>
       <c r="D104" t="n">
-        <v>41.9418</v>
+        <v>40.7126</v>
       </c>
       <c r="E104" t="n">
-        <v>14.2247</v>
+        <v>14.2183</v>
       </c>
       <c r="F104" t="n">
-        <v>27.5598</v>
+        <v>27.6025</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8295</v>
+        <v>18.826</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6707</v>
+        <v>17.6576</v>
       </c>
       <c r="D105" t="n">
-        <v>41.3913</v>
+        <v>40.7602</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9313</v>
+        <v>13.9339</v>
       </c>
       <c r="F105" t="n">
-        <v>27.2378</v>
+        <v>27.2477</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2714</v>
+        <v>18.2275</v>
       </c>
       <c r="C106" t="n">
-        <v>17.59</v>
+        <v>17.5832</v>
       </c>
       <c r="D106" t="n">
-        <v>41.4178</v>
+        <v>40.1417</v>
       </c>
       <c r="E106" t="n">
-        <v>13.6205</v>
+        <v>13.7088</v>
       </c>
       <c r="F106" t="n">
-        <v>26.9325</v>
+        <v>26.887</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6035</v>
+        <v>17.6093</v>
       </c>
       <c r="C107" t="n">
-        <v>17.5086</v>
+        <v>17.5057</v>
       </c>
       <c r="D107" t="n">
-        <v>43.5646</v>
+        <v>45.5145</v>
       </c>
       <c r="E107" t="n">
-        <v>13.3535</v>
+        <v>17.7678</v>
       </c>
       <c r="F107" t="n">
-        <v>26.555</v>
+        <v>31.2126</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8933</v>
+        <v>16.8916</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1931</v>
+        <v>19.1372</v>
       </c>
       <c r="D108" t="n">
-        <v>44.1148</v>
+        <v>46.3699</v>
       </c>
       <c r="E108" t="n">
-        <v>17.3952</v>
+        <v>17.3677</v>
       </c>
       <c r="F108" t="n">
-        <v>30.8311</v>
+        <v>30.9741</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9148</v>
+        <v>15.9451</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9509</v>
+        <v>18.9853</v>
       </c>
       <c r="D109" t="n">
-        <v>42.2204</v>
+        <v>45.7483</v>
       </c>
       <c r="E109" t="n">
-        <v>16.9966</v>
+        <v>16.9959</v>
       </c>
       <c r="F109" t="n">
-        <v>30.5669</v>
+        <v>30.655</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5737</v>
+        <v>23.5629</v>
       </c>
       <c r="C110" t="n">
-        <v>18.7126</v>
+        <v>18.692</v>
       </c>
       <c r="D110" t="n">
-        <v>41.6462</v>
+        <v>45.1687</v>
       </c>
       <c r="E110" t="n">
-        <v>16.7771</v>
+        <v>16.7943</v>
       </c>
       <c r="F110" t="n">
-        <v>30.0533</v>
+        <v>30.2639</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1341</v>
+        <v>23.1685</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5654</v>
+        <v>18.5348</v>
       </c>
       <c r="D111" t="n">
-        <v>43.6571</v>
+        <v>44.6119</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4594</v>
+        <v>16.4665</v>
       </c>
       <c r="F111" t="n">
-        <v>29.776</v>
+        <v>29.8908</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6677</v>
+        <v>22.6461</v>
       </c>
       <c r="C112" t="n">
-        <v>18.3811</v>
+        <v>18.3807</v>
       </c>
       <c r="D112" t="n">
-        <v>43.2287</v>
+        <v>41.2843</v>
       </c>
       <c r="E112" t="n">
-        <v>16.1768</v>
+        <v>16.1771</v>
       </c>
       <c r="F112" t="n">
-        <v>29.4396</v>
+        <v>29.579</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1668</v>
+        <v>22.1467</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2353</v>
+        <v>18.2682</v>
       </c>
       <c r="D113" t="n">
-        <v>42.5936</v>
+        <v>40.9057</v>
       </c>
       <c r="E113" t="n">
-        <v>15.8643</v>
+        <v>15.9401</v>
       </c>
       <c r="F113" t="n">
-        <v>29.0693</v>
+        <v>29.2133</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6389</v>
+        <v>21.6317</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1183</v>
+        <v>18.1255</v>
       </c>
       <c r="D114" t="n">
-        <v>42.4142</v>
+        <v>43.101</v>
       </c>
       <c r="E114" t="n">
-        <v>15.6304</v>
+        <v>15.6199</v>
       </c>
       <c r="F114" t="n">
-        <v>28.7781</v>
+        <v>28.95</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.123</v>
+        <v>21.0979</v>
       </c>
       <c r="C115" t="n">
-        <v>18.0027</v>
+        <v>17.9841</v>
       </c>
       <c r="D115" t="n">
-        <v>40.1681</v>
+        <v>42.7051</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3539</v>
+        <v>15.3491</v>
       </c>
       <c r="F115" t="n">
-        <v>28.4925</v>
+        <v>28.584</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.581</v>
+        <v>20.5791</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8831</v>
+        <v>17.8655</v>
       </c>
       <c r="D116" t="n">
-        <v>39.808</v>
+        <v>42.2999</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8314</v>
+        <v>14.8446</v>
       </c>
       <c r="F116" t="n">
-        <v>28.2852</v>
+        <v>28.3156</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.053</v>
+        <v>20.0359</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7885</v>
+        <v>17.7724</v>
       </c>
       <c r="D117" t="n">
-        <v>39.3756</v>
+        <v>41.9745</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5578</v>
+        <v>14.5548</v>
       </c>
       <c r="F117" t="n">
-        <v>28.0262</v>
+        <v>28.0168</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5091</v>
+        <v>19.5243</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6917</v>
+        <v>17.6742</v>
       </c>
       <c r="D118" t="n">
-        <v>39.1136</v>
+        <v>40.796</v>
       </c>
       <c r="E118" t="n">
-        <v>14.2869</v>
+        <v>14.319</v>
       </c>
       <c r="F118" t="n">
-        <v>27.7252</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9522</v>
+        <v>18.951</v>
       </c>
       <c r="C119" t="n">
-        <v>17.5972</v>
+        <v>17.5938</v>
       </c>
       <c r="D119" t="n">
-        <v>38.8547</v>
+        <v>40.5525</v>
       </c>
       <c r="E119" t="n">
-        <v>14.019</v>
+        <v>14.0009</v>
       </c>
       <c r="F119" t="n">
-        <v>27.3532</v>
+        <v>27.3765</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.4131</v>
+        <v>18.3815</v>
       </c>
       <c r="C120" t="n">
         <v>17.5244</v>
       </c>
       <c r="D120" t="n">
-        <v>38.6626</v>
+        <v>40.3193</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7261</v>
+        <v>13.7219</v>
       </c>
       <c r="F120" t="n">
-        <v>27.0152</v>
+        <v>27.0117</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7494</v>
+        <v>17.7444</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4367</v>
+        <v>17.439</v>
       </c>
       <c r="D121" t="n">
-        <v>45.6687</v>
+        <v>46.8819</v>
       </c>
       <c r="E121" t="n">
-        <v>13.4196</v>
+        <v>18.0933</v>
       </c>
       <c r="F121" t="n">
-        <v>26.5722</v>
+        <v>31.2576</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.0029</v>
+        <v>17.0069</v>
       </c>
       <c r="C122" t="n">
-        <v>19.184</v>
+        <v>19.2233</v>
       </c>
       <c r="D122" t="n">
-        <v>45.0839</v>
+        <v>46.485</v>
       </c>
       <c r="E122" t="n">
-        <v>13.0926</v>
+        <v>17.463</v>
       </c>
       <c r="F122" t="n">
-        <v>26.2242</v>
+        <v>30.8883</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.1909</v>
+        <v>16.1157</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9802</v>
+        <v>18.9612</v>
       </c>
       <c r="D123" t="n">
-        <v>44.5579</v>
+        <v>47.1677</v>
       </c>
       <c r="E123" t="n">
-        <v>17.2252</v>
+        <v>17.2073</v>
       </c>
       <c r="F123" t="n">
-        <v>30.5169</v>
+        <v>30.5164</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6579</v>
+        <v>23.6506</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7528</v>
+        <v>18.7413</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9684</v>
+        <v>43.9579</v>
       </c>
       <c r="E124" t="n">
-        <v>16.8661</v>
+        <v>16.8655</v>
       </c>
       <c r="F124" t="n">
-        <v>30.1645</v>
+        <v>30.1733</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.229</v>
+        <v>23.2296</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5818</v>
+        <v>18.6121</v>
       </c>
       <c r="D125" t="n">
-        <v>44.6289</v>
+        <v>43.7566</v>
       </c>
       <c r="E125" t="n">
-        <v>16.5175</v>
+        <v>16.5367</v>
       </c>
       <c r="F125" t="n">
-        <v>29.8012</v>
+        <v>29.9854</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.763</v>
+        <v>22.7614</v>
       </c>
       <c r="C126" t="n">
-        <v>18.4345</v>
+        <v>18.4186</v>
       </c>
       <c r="D126" t="n">
-        <v>45.2408</v>
+        <v>45.2804</v>
       </c>
       <c r="E126" t="n">
-        <v>16.2151</v>
+        <v>16.252</v>
       </c>
       <c r="F126" t="n">
-        <v>29.5066</v>
+        <v>29.4786</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2699</v>
+        <v>22.261</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2616</v>
+        <v>18.2908</v>
       </c>
       <c r="D127" t="n">
-        <v>42.6709</v>
+        <v>44.7013</v>
       </c>
       <c r="E127" t="n">
-        <v>15.9393</v>
+        <v>15.9136</v>
       </c>
       <c r="F127" t="n">
-        <v>29.1421</v>
+        <v>29.1804</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7428</v>
+        <v>21.7637</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1406</v>
+        <v>18.1799</v>
       </c>
       <c r="D128" t="n">
-        <v>42.3099</v>
+        <v>42.4639</v>
       </c>
       <c r="E128" t="n">
-        <v>15.6385</v>
+        <v>15.6325</v>
       </c>
       <c r="F128" t="n">
-        <v>28.9476</v>
+        <v>28.9622</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.2137</v>
+        <v>21.209</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0473</v>
+        <v>18.0455</v>
       </c>
       <c r="D129" t="n">
-        <v>43.5933</v>
+        <v>41.9476</v>
       </c>
       <c r="E129" t="n">
-        <v>15.4002</v>
+        <v>15.4066</v>
       </c>
       <c r="F129" t="n">
-        <v>28.5581</v>
+        <v>28.5605</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6887</v>
+        <v>20.6988</v>
       </c>
       <c r="C130" t="n">
-        <v>17.9224</v>
+        <v>17.913</v>
       </c>
       <c r="D130" t="n">
-        <v>43.1243</v>
+        <v>41.5127</v>
       </c>
       <c r="E130" t="n">
-        <v>14.8905</v>
+        <v>14.8956</v>
       </c>
       <c r="F130" t="n">
-        <v>28.3762</v>
+        <v>28.2853</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1835</v>
+        <v>20.1646</v>
       </c>
       <c r="C131" t="n">
-        <v>17.8527</v>
+        <v>17.826</v>
       </c>
       <c r="D131" t="n">
-        <v>42.6384</v>
+        <v>40.9948</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6151</v>
+        <v>14.6123</v>
       </c>
       <c r="F131" t="n">
-        <v>27.9898</v>
+        <v>28.0236</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6419</v>
+        <v>19.6244</v>
       </c>
       <c r="C132" t="n">
-        <v>17.7334</v>
+        <v>17.7187</v>
       </c>
       <c r="D132" t="n">
-        <v>42.1887</v>
+        <v>40.6069</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3452</v>
+        <v>14.3522</v>
       </c>
       <c r="F132" t="n">
-        <v>27.6412</v>
+        <v>27.6646</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.09</v>
+        <v>19.0792</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6422</v>
+        <v>17.6311</v>
       </c>
       <c r="D133" t="n">
-        <v>41.7882</v>
+        <v>40.315</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0777</v>
+        <v>14.0685</v>
       </c>
       <c r="F133" t="n">
-        <v>27.348</v>
+        <v>27.3893</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.538</v>
+        <v>18.5083</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5495</v>
+        <v>17.5636</v>
       </c>
       <c r="D134" t="n">
-        <v>41.5119</v>
+        <v>40.0019</v>
       </c>
       <c r="E134" t="n">
-        <v>13.7848</v>
+        <v>13.7784</v>
       </c>
       <c r="F134" t="n">
-        <v>27.0752</v>
+        <v>27.088</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8965</v>
+        <v>17.8636</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4752</v>
+        <v>17.4765</v>
       </c>
       <c r="D135" t="n">
-        <v>48.8036</v>
+        <v>47.4733</v>
       </c>
       <c r="E135" t="n">
-        <v>13.4812</v>
+        <v>17.8742</v>
       </c>
       <c r="F135" t="n">
-        <v>26.6446</v>
+        <v>31.3237</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.2341</v>
+        <v>17.1923</v>
       </c>
       <c r="C136" t="n">
-        <v>19.2128</v>
+        <v>19.1988</v>
       </c>
       <c r="D136" t="n">
-        <v>48.1091</v>
+        <v>46.4564</v>
       </c>
       <c r="E136" t="n">
-        <v>13.3021</v>
+        <v>17.59</v>
       </c>
       <c r="F136" t="n">
-        <v>26.2897</v>
+        <v>30.8402</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.3812</v>
+        <v>16.2972</v>
       </c>
       <c r="C137" t="n">
-        <v>18.9857</v>
+        <v>19.0013</v>
       </c>
       <c r="D137" t="n">
-        <v>44.9059</v>
+        <v>45.1865</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1438</v>
+        <v>17.1103</v>
       </c>
       <c r="F137" t="n">
-        <v>30.4869</v>
+        <v>30.5986</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7428</v>
+        <v>23.7395</v>
       </c>
       <c r="C138" t="n">
-        <v>18.8316</v>
+        <v>18.7988</v>
       </c>
       <c r="D138" t="n">
-        <v>47.1195</v>
+        <v>47.0075</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7669</v>
+        <v>16.7598</v>
       </c>
       <c r="F138" t="n">
-        <v>30.171</v>
+        <v>30.1946</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3327</v>
+        <v>23.3162</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6575</v>
+        <v>18.6419</v>
       </c>
       <c r="D139" t="n">
-        <v>45.3674</v>
+        <v>44.3171</v>
       </c>
       <c r="E139" t="n">
-        <v>16.5833</v>
+        <v>16.551</v>
       </c>
       <c r="F139" t="n">
-        <v>29.9078</v>
+        <v>30.018</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8618</v>
+        <v>22.8638</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4685</v>
+        <v>18.4755</v>
       </c>
       <c r="D140" t="n">
-        <v>45.8869</v>
+        <v>43.7195</v>
       </c>
       <c r="E140" t="n">
-        <v>16.2921</v>
+        <v>16.299</v>
       </c>
       <c r="F140" t="n">
-        <v>29.498</v>
+        <v>29.5876</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3685</v>
+        <v>22.3684</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3397</v>
+        <v>18.3135</v>
       </c>
       <c r="D141" t="n">
-        <v>45.0411</v>
+        <v>43.0287</v>
       </c>
       <c r="E141" t="n">
-        <v>15.9801</v>
+        <v>15.9597</v>
       </c>
       <c r="F141" t="n">
-        <v>29.2699</v>
+        <v>29.188</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8463</v>
+        <v>21.8585</v>
       </c>
       <c r="C142" t="n">
-        <v>18.1927</v>
+        <v>18.2068</v>
       </c>
       <c r="D142" t="n">
-        <v>44.5069</v>
+        <v>44.41</v>
       </c>
       <c r="E142" t="n">
-        <v>15.506</v>
+        <v>15.5134</v>
       </c>
       <c r="F142" t="n">
-        <v>28.8939</v>
+        <v>28.9871</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.3173</v>
+        <v>21.322</v>
       </c>
       <c r="C143" t="n">
-        <v>18.0964</v>
+        <v>18.0898</v>
       </c>
       <c r="D143" t="n">
-        <v>44.1914</v>
+        <v>43.6079</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2152</v>
+        <v>15.2088</v>
       </c>
       <c r="F143" t="n">
-        <v>28.579</v>
+        <v>28.5718</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.9438</v>
+        <v>19.1627</v>
       </c>
       <c r="C2" t="n">
-        <v>14.1537</v>
+        <v>14.1355</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8424</v>
+        <v>32.0339</v>
       </c>
       <c r="E2" t="n">
-        <v>7.28564</v>
+        <v>7.66204</v>
       </c>
       <c r="F2" t="n">
-        <v>27.1388</v>
+        <v>26.7627</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4179</v>
+        <v>18.4236</v>
       </c>
       <c r="C3" t="n">
-        <v>14.4819</v>
+        <v>14.4583</v>
       </c>
       <c r="D3" t="n">
-        <v>32.0085</v>
+        <v>32.1674</v>
       </c>
       <c r="E3" t="n">
-        <v>6.82721</v>
+        <v>6.94403</v>
       </c>
       <c r="F3" t="n">
-        <v>26.808</v>
+        <v>26.5475</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.0845</v>
+        <v>18.1792</v>
       </c>
       <c r="C4" t="n">
-        <v>14.811</v>
+        <v>14.7112</v>
       </c>
       <c r="D4" t="n">
-        <v>32.152</v>
+        <v>32.2504</v>
       </c>
       <c r="E4" t="n">
-        <v>6.19557</v>
+        <v>6.6251</v>
       </c>
       <c r="F4" t="n">
-        <v>26.6888</v>
+        <v>26.1894</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.6244</v>
+        <v>17.5038</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8626</v>
+        <v>14.8241</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4311</v>
+        <v>32.6231</v>
       </c>
       <c r="E5" t="n">
-        <v>5.91732</v>
+        <v>6.39803</v>
       </c>
       <c r="F5" t="n">
-        <v>26.4763</v>
+        <v>26.2694</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.2234</v>
+        <v>17.2022</v>
       </c>
       <c r="C6" t="n">
-        <v>15.0291</v>
+        <v>15.082</v>
       </c>
       <c r="D6" t="n">
-        <v>32.3849</v>
+        <v>32.6364</v>
       </c>
       <c r="E6" t="n">
-        <v>5.65017</v>
+        <v>6.15793</v>
       </c>
       <c r="F6" t="n">
-        <v>26.2082</v>
+        <v>26.3904</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3891</v>
+        <v>16.3915</v>
       </c>
       <c r="C7" t="n">
-        <v>15.3393</v>
+        <v>15.345</v>
       </c>
       <c r="D7" t="n">
-        <v>31.7305</v>
+        <v>31.7884</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6022</v>
+        <v>15.7486</v>
       </c>
       <c r="F7" t="n">
-        <v>30.8725</v>
+        <v>30.2949</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.7558</v>
+        <v>15.7681</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9408</v>
+        <v>16.9697</v>
       </c>
       <c r="D8" t="n">
-        <v>31.803</v>
+        <v>31.8508</v>
       </c>
       <c r="E8" t="n">
-        <v>15.252</v>
+        <v>15.4492</v>
       </c>
       <c r="F8" t="n">
-        <v>30.4335</v>
+        <v>29.8535</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.9366</v>
+        <v>14.9193</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0452</v>
+        <v>17.1183</v>
       </c>
       <c r="D9" t="n">
-        <v>31.9131</v>
+        <v>31.7785</v>
       </c>
       <c r="E9" t="n">
-        <v>14.88</v>
+        <v>15.0792</v>
       </c>
       <c r="F9" t="n">
-        <v>30.2371</v>
+        <v>29.8497</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.7746</v>
+        <v>22.9466</v>
       </c>
       <c r="C10" t="n">
-        <v>17.044</v>
+        <v>17.1091</v>
       </c>
       <c r="D10" t="n">
-        <v>31.8392</v>
+        <v>31.987</v>
       </c>
       <c r="E10" t="n">
-        <v>14.514</v>
+        <v>14.7859</v>
       </c>
       <c r="F10" t="n">
-        <v>29.7047</v>
+        <v>29.3348</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.2925</v>
+        <v>22.4208</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1652</v>
+        <v>17.1868</v>
       </c>
       <c r="D11" t="n">
-        <v>32.0798</v>
+        <v>32.0556</v>
       </c>
       <c r="E11" t="n">
-        <v>14.3033</v>
+        <v>14.4852</v>
       </c>
       <c r="F11" t="n">
-        <v>29.5588</v>
+        <v>29.2768</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.9974</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0506</v>
+        <v>17.0824</v>
       </c>
       <c r="D12" t="n">
-        <v>32.2784</v>
+        <v>32.2773</v>
       </c>
       <c r="E12" t="n">
-        <v>13.8358</v>
+        <v>14.1929</v>
       </c>
       <c r="F12" t="n">
-        <v>29.5546</v>
+        <v>28.9006</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5609</v>
+        <v>21.5553</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2697</v>
+        <v>17.2257</v>
       </c>
       <c r="D13" t="n">
-        <v>32.0809</v>
+        <v>32.2191</v>
       </c>
       <c r="E13" t="n">
-        <v>13.5826</v>
+        <v>14.0478</v>
       </c>
       <c r="F13" t="n">
-        <v>29.1444</v>
+        <v>28.6386</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.165</v>
+        <v>21.2091</v>
       </c>
       <c r="C14" t="n">
-        <v>17.183</v>
+        <v>17.2023</v>
       </c>
       <c r="D14" t="n">
-        <v>32.1933</v>
+        <v>32.2896</v>
       </c>
       <c r="E14" t="n">
-        <v>13.3317</v>
+        <v>13.7126</v>
       </c>
       <c r="F14" t="n">
-        <v>28.8359</v>
+        <v>28.6698</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.7821</v>
+        <v>20.7563</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2846</v>
+        <v>17.2467</v>
       </c>
       <c r="D15" t="n">
-        <v>32.5027</v>
+        <v>32.3851</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1997</v>
+        <v>13.4462</v>
       </c>
       <c r="F15" t="n">
-        <v>28.4471</v>
+        <v>27.9395</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.1257</v>
+        <v>20.0844</v>
       </c>
       <c r="C16" t="n">
-        <v>17.175</v>
+        <v>17.249</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5607</v>
+        <v>32.5172</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9692</v>
+        <v>13.3276</v>
       </c>
       <c r="F16" t="n">
-        <v>28.234</v>
+        <v>27.7387</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.6161</v>
+        <v>19.5686</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1553</v>
+        <v>17.1757</v>
       </c>
       <c r="D17" t="n">
-        <v>32.4718</v>
+        <v>32.6233</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8313</v>
+        <v>13.2557</v>
       </c>
       <c r="F17" t="n">
-        <v>27.804</v>
+        <v>27.4765</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.2149</v>
+        <v>19.0768</v>
       </c>
       <c r="C18" t="n">
-        <v>17.1894</v>
+        <v>17.1781</v>
       </c>
       <c r="D18" t="n">
-        <v>32.8508</v>
+        <v>32.832</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5483</v>
+        <v>12.9624</v>
       </c>
       <c r="F18" t="n">
-        <v>27.6163</v>
+        <v>27.127</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.6103</v>
+        <v>18.6199</v>
       </c>
       <c r="C19" t="n">
-        <v>17.0991</v>
+        <v>17.1637</v>
       </c>
       <c r="D19" t="n">
-        <v>33.0025</v>
+        <v>32.852</v>
       </c>
       <c r="E19" t="n">
-        <v>12.271</v>
+        <v>12.6632</v>
       </c>
       <c r="F19" t="n">
-        <v>27.219</v>
+        <v>26.7642</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.0459</v>
+        <v>18.0918</v>
       </c>
       <c r="C20" t="n">
-        <v>17.2871</v>
+        <v>17.2492</v>
       </c>
       <c r="D20" t="n">
-        <v>33.0077</v>
+        <v>33.0385</v>
       </c>
       <c r="E20" t="n">
-        <v>12.1832</v>
+        <v>12.3262</v>
       </c>
       <c r="F20" t="n">
-        <v>26.8723</v>
+        <v>26.5165</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.4448</v>
+        <v>17.4037</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1349</v>
+        <v>17.1368</v>
       </c>
       <c r="D21" t="n">
-        <v>32.517</v>
+        <v>32.4972</v>
       </c>
       <c r="E21" t="n">
-        <v>17.7308</v>
+        <v>17.8573</v>
       </c>
       <c r="F21" t="n">
-        <v>31.2646</v>
+        <v>30.668</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7485</v>
+        <v>16.7779</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7719</v>
+        <v>18.7214</v>
       </c>
       <c r="D22" t="n">
-        <v>32.3341</v>
+        <v>32.3933</v>
       </c>
       <c r="E22" t="n">
-        <v>16.8825</v>
+        <v>17.0606</v>
       </c>
       <c r="F22" t="n">
-        <v>31.0114</v>
+        <v>30.4133</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0282</v>
+        <v>16.0578</v>
       </c>
       <c r="C23" t="n">
-        <v>18.6134</v>
+        <v>18.5144</v>
       </c>
       <c r="D23" t="n">
-        <v>32.3465</v>
+        <v>32.403</v>
       </c>
       <c r="E23" t="n">
-        <v>16.555</v>
+        <v>16.6587</v>
       </c>
       <c r="F23" t="n">
-        <v>30.881</v>
+        <v>30.1589</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.3924</v>
+        <v>23.3137</v>
       </c>
       <c r="C24" t="n">
-        <v>18.5281</v>
+        <v>18.441</v>
       </c>
       <c r="D24" t="n">
-        <v>32.2761</v>
+        <v>32.2873</v>
       </c>
       <c r="E24" t="n">
-        <v>16.2122</v>
+        <v>16.1897</v>
       </c>
       <c r="F24" t="n">
-        <v>30.3882</v>
+        <v>29.9498</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.978</v>
+        <v>22.9111</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3561</v>
+        <v>18.3837</v>
       </c>
       <c r="D25" t="n">
-        <v>32.7187</v>
+        <v>32.7743</v>
       </c>
       <c r="E25" t="n">
-        <v>15.7336</v>
+        <v>15.772</v>
       </c>
       <c r="F25" t="n">
-        <v>30.0457</v>
+        <v>29.7251</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.4948</v>
+        <v>22.5691</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2889</v>
+        <v>18.2964</v>
       </c>
       <c r="D26" t="n">
-        <v>32.8181</v>
+        <v>32.82</v>
       </c>
       <c r="E26" t="n">
-        <v>15.4052</v>
+        <v>15.4168</v>
       </c>
       <c r="F26" t="n">
-        <v>29.8891</v>
+        <v>29.3992</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>22.0214</v>
+        <v>22.0788</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1223</v>
+        <v>18.1763</v>
       </c>
       <c r="D27" t="n">
-        <v>32.8089</v>
+        <v>32.8417</v>
       </c>
       <c r="E27" t="n">
-        <v>15.099</v>
+        <v>15.176</v>
       </c>
       <c r="F27" t="n">
-        <v>29.6624</v>
+        <v>29.1392</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.5241</v>
+        <v>21.6684</v>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>18.0292</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7976</v>
+        <v>32.7396</v>
       </c>
       <c r="E28" t="n">
-        <v>14.8119</v>
+        <v>14.8367</v>
       </c>
       <c r="F28" t="n">
-        <v>29.2484</v>
+        <v>28.8987</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.0586</v>
+        <v>21.0563</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9425</v>
+        <v>17.9835</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9684</v>
+        <v>32.7345</v>
       </c>
       <c r="E29" t="n">
-        <v>14.5266</v>
+        <v>14.5327</v>
       </c>
       <c r="F29" t="n">
-        <v>28.7519</v>
+        <v>28.4535</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.5961</v>
+        <v>20.6641</v>
       </c>
       <c r="C30" t="n">
-        <v>17.9004</v>
+        <v>17.9071</v>
       </c>
       <c r="D30" t="n">
-        <v>33.1141</v>
+        <v>33.0074</v>
       </c>
       <c r="E30" t="n">
-        <v>14.2481</v>
+        <v>14.2519</v>
       </c>
       <c r="F30" t="n">
-        <v>28.6281</v>
+        <v>28.3253</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0851</v>
+        <v>20.0455</v>
       </c>
       <c r="C31" t="n">
-        <v>17.7818</v>
+        <v>17.748</v>
       </c>
       <c r="D31" t="n">
-        <v>33.1571</v>
+        <v>33.1096</v>
       </c>
       <c r="E31" t="n">
-        <v>14.0706</v>
+        <v>13.9863</v>
       </c>
       <c r="F31" t="n">
-        <v>28.1635</v>
+        <v>27.9035</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6668</v>
+        <v>19.6351</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7206</v>
+        <v>17.726</v>
       </c>
       <c r="D32" t="n">
-        <v>33.2267</v>
+        <v>33.1541</v>
       </c>
       <c r="E32" t="n">
-        <v>13.6639</v>
+        <v>13.7001</v>
       </c>
       <c r="F32" t="n">
-        <v>27.9256</v>
+        <v>27.5311</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0595</v>
+        <v>19.0425</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6482</v>
+        <v>17.6538</v>
       </c>
       <c r="D33" t="n">
-        <v>33.1816</v>
+        <v>33.3213</v>
       </c>
       <c r="E33" t="n">
-        <v>13.725</v>
+        <v>13.7108</v>
       </c>
       <c r="F33" t="n">
-        <v>27.4452</v>
+        <v>27.1839</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4692</v>
+        <v>18.4699</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5806</v>
+        <v>17.5847</v>
       </c>
       <c r="D34" t="n">
-        <v>33.3094</v>
+        <v>33.3871</v>
       </c>
       <c r="E34" t="n">
-        <v>13.4034</v>
+        <v>13.3856</v>
       </c>
       <c r="F34" t="n">
-        <v>27.1673</v>
+        <v>26.9648</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9371</v>
+        <v>17.9179</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4849</v>
+        <v>17.4852</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7276</v>
+        <v>32.7154</v>
       </c>
       <c r="E35" t="n">
-        <v>18.0402</v>
+        <v>18.1944</v>
       </c>
       <c r="F35" t="n">
-        <v>31.6455</v>
+        <v>31.2863</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2681</v>
+        <v>17.2544</v>
       </c>
       <c r="C36" t="n">
-        <v>17.3968</v>
+        <v>17.4172</v>
       </c>
       <c r="D36" t="n">
-        <v>32.6763</v>
+        <v>32.7641</v>
       </c>
       <c r="E36" t="n">
-        <v>17.5438</v>
+        <v>17.5221</v>
       </c>
       <c r="F36" t="n">
-        <v>31.38</v>
+        <v>30.8763</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.5581</v>
+        <v>16.5597</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8348</v>
+        <v>18.8876</v>
       </c>
       <c r="D37" t="n">
-        <v>32.4591</v>
+        <v>32.4822</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0555</v>
+        <v>17.0653</v>
       </c>
       <c r="F37" t="n">
-        <v>30.8222</v>
+        <v>30.4301</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.6684</v>
+        <v>23.7411</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6537</v>
+        <v>18.6968</v>
       </c>
       <c r="D38" t="n">
-        <v>32.4014</v>
+        <v>32.4623</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7234</v>
+        <v>16.7869</v>
       </c>
       <c r="F38" t="n">
-        <v>30.6045</v>
+        <v>30.0498</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.2901</v>
+        <v>23.3591</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5582</v>
+        <v>18.5045</v>
       </c>
       <c r="D39" t="n">
-        <v>32.4994</v>
+        <v>32.5422</v>
       </c>
       <c r="E39" t="n">
-        <v>16.3452</v>
+        <v>16.468</v>
       </c>
       <c r="F39" t="n">
-        <v>30.0555</v>
+        <v>29.6715</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.9245</v>
+        <v>22.8674</v>
       </c>
       <c r="C40" t="n">
-        <v>18.3765</v>
+        <v>18.3821</v>
       </c>
       <c r="D40" t="n">
-        <v>32.8644</v>
+        <v>32.8861</v>
       </c>
       <c r="E40" t="n">
-        <v>16.0651</v>
+        <v>16.2201</v>
       </c>
       <c r="F40" t="n">
-        <v>29.8162</v>
+        <v>29.3312</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4374</v>
+        <v>22.4636</v>
       </c>
       <c r="C41" t="n">
-        <v>18.2166</v>
+        <v>18.2802</v>
       </c>
       <c r="D41" t="n">
-        <v>32.8835</v>
+        <v>33.0196</v>
       </c>
       <c r="E41" t="n">
-        <v>15.6862</v>
+        <v>15.9009</v>
       </c>
       <c r="F41" t="n">
-        <v>29.5868</v>
+        <v>29.149</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.9777</v>
+        <v>21.9685</v>
       </c>
       <c r="C42" t="n">
-        <v>18.1238</v>
+        <v>18.0845</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9233</v>
+        <v>32.9738</v>
       </c>
       <c r="E42" t="n">
-        <v>15.3792</v>
+        <v>15.543</v>
       </c>
       <c r="F42" t="n">
-        <v>29.3132</v>
+        <v>28.8322</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4231</v>
+        <v>21.4526</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9569</v>
+        <v>17.9589</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7666</v>
+        <v>32.9035</v>
       </c>
       <c r="E43" t="n">
-        <v>15.0749</v>
+        <v>15.1877</v>
       </c>
       <c r="F43" t="n">
-        <v>29.0072</v>
+        <v>28.5489</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.8945</v>
+        <v>20.896</v>
       </c>
       <c r="C44" t="n">
-        <v>17.8675</v>
+        <v>17.8747</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7785</v>
+        <v>32.829</v>
       </c>
       <c r="E44" t="n">
-        <v>14.8501</v>
+        <v>14.9882</v>
       </c>
       <c r="F44" t="n">
-        <v>28.7564</v>
+        <v>28.3148</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4267</v>
+        <v>20.4371</v>
       </c>
       <c r="C45" t="n">
-        <v>17.783</v>
+        <v>17.7859</v>
       </c>
       <c r="D45" t="n">
-        <v>33.0033</v>
+        <v>32.9362</v>
       </c>
       <c r="E45" t="n">
-        <v>14.4902</v>
+        <v>14.6118</v>
       </c>
       <c r="F45" t="n">
-        <v>28.2851</v>
+        <v>27.9237</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9065</v>
+        <v>19.8969</v>
       </c>
       <c r="C46" t="n">
-        <v>17.6852</v>
+        <v>17.711</v>
       </c>
       <c r="D46" t="n">
-        <v>33.0424</v>
+        <v>32.9751</v>
       </c>
       <c r="E46" t="n">
-        <v>14.2297</v>
+        <v>14.3039</v>
       </c>
       <c r="F46" t="n">
-        <v>27.9684</v>
+        <v>27.6985</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3675</v>
+        <v>19.3543</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5766</v>
+        <v>17.5741</v>
       </c>
       <c r="D47" t="n">
-        <v>33.1175</v>
+        <v>33.0612</v>
       </c>
       <c r="E47" t="n">
-        <v>13.9642</v>
+        <v>14.0109</v>
       </c>
       <c r="F47" t="n">
-        <v>27.7035</v>
+        <v>27.3583</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8192</v>
+        <v>18.8124</v>
       </c>
       <c r="C48" t="n">
-        <v>17.4988</v>
+        <v>17.4952</v>
       </c>
       <c r="D48" t="n">
-        <v>33.2499</v>
+        <v>33.2828</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6411</v>
+        <v>13.6891</v>
       </c>
       <c r="F48" t="n">
-        <v>27.3252</v>
+        <v>27.0369</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1584</v>
+        <v>18.1371</v>
       </c>
       <c r="C49" t="n">
-        <v>17.4164</v>
+        <v>17.3925</v>
       </c>
       <c r="D49" t="n">
-        <v>33.5289</v>
+        <v>33.5016</v>
       </c>
       <c r="E49" t="n">
-        <v>13.3276</v>
+        <v>13.3623</v>
       </c>
       <c r="F49" t="n">
-        <v>27.2075</v>
+        <v>26.8237</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.5449</v>
+        <v>17.5192</v>
       </c>
       <c r="C50" t="n">
-        <v>17.3506</v>
+        <v>17.3568</v>
       </c>
       <c r="D50" t="n">
-        <v>32.8773</v>
+        <v>33.08</v>
       </c>
       <c r="E50" t="n">
-        <v>17.6331</v>
+        <v>17.7651</v>
       </c>
       <c r="F50" t="n">
-        <v>31.474</v>
+        <v>30.9145</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.8151</v>
+        <v>16.7987</v>
       </c>
       <c r="C51" t="n">
-        <v>18.8302</v>
+        <v>18.8289</v>
       </c>
       <c r="D51" t="n">
-        <v>32.9274</v>
+        <v>33.3306</v>
       </c>
       <c r="E51" t="n">
-        <v>17.2655</v>
+        <v>17.4179</v>
       </c>
       <c r="F51" t="n">
-        <v>30.9989</v>
+        <v>30.5164</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.8705</v>
+        <v>15.8807</v>
       </c>
       <c r="C52" t="n">
-        <v>18.7058</v>
+        <v>18.6746</v>
       </c>
       <c r="D52" t="n">
-        <v>32.8745</v>
+        <v>33.1652</v>
       </c>
       <c r="E52" t="n">
-        <v>16.8935</v>
+        <v>17.1091</v>
       </c>
       <c r="F52" t="n">
-        <v>30.7021</v>
+        <v>30.1888</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.4888</v>
+        <v>23.5035</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4774</v>
+        <v>18.4933</v>
       </c>
       <c r="D53" t="n">
-        <v>32.9756</v>
+        <v>33.1148</v>
       </c>
       <c r="E53" t="n">
-        <v>16.2997</v>
+        <v>16.7439</v>
       </c>
       <c r="F53" t="n">
-        <v>30.5221</v>
+        <v>29.9288</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1214</v>
+        <v>23.1513</v>
       </c>
       <c r="C54" t="n">
-        <v>18.3815</v>
+        <v>18.3964</v>
       </c>
       <c r="D54" t="n">
-        <v>33.175</v>
+        <v>33.2834</v>
       </c>
       <c r="E54" t="n">
-        <v>16.216</v>
+        <v>16.4046</v>
       </c>
       <c r="F54" t="n">
-        <v>29.9445</v>
+        <v>29.5214</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6102</v>
+        <v>22.6469</v>
       </c>
       <c r="C55" t="n">
-        <v>18.233</v>
+        <v>18.2731</v>
       </c>
       <c r="D55" t="n">
-        <v>33.008</v>
+        <v>33.0573</v>
       </c>
       <c r="E55" t="n">
-        <v>15.9147</v>
+        <v>16.0582</v>
       </c>
       <c r="F55" t="n">
-        <v>29.7257</v>
+        <v>29.2291</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1333</v>
+        <v>22.1384</v>
       </c>
       <c r="C56" t="n">
-        <v>18.0936</v>
+        <v>18.1188</v>
       </c>
       <c r="D56" t="n">
-        <v>33.1465</v>
+        <v>33.2056</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7556</v>
+        <v>15.7989</v>
       </c>
       <c r="F56" t="n">
-        <v>29.5289</v>
+        <v>29.0491</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.5875</v>
+        <v>21.5999</v>
       </c>
       <c r="C57" t="n">
-        <v>18.0189</v>
+        <v>18.0584</v>
       </c>
       <c r="D57" t="n">
-        <v>33.5038</v>
+        <v>33.8383</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4562</v>
+        <v>15.484</v>
       </c>
       <c r="F57" t="n">
-        <v>29.1722</v>
+        <v>28.726</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0765</v>
+        <v>21.0824</v>
       </c>
       <c r="C58" t="n">
-        <v>17.937</v>
+        <v>17.8987</v>
       </c>
       <c r="D58" t="n">
-        <v>33.7417</v>
+        <v>33.9939</v>
       </c>
       <c r="E58" t="n">
-        <v>14.849</v>
+        <v>15.1708</v>
       </c>
       <c r="F58" t="n">
-        <v>28.7933</v>
+        <v>28.46</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5916</v>
+        <v>20.5953</v>
       </c>
       <c r="C59" t="n">
-        <v>17.7699</v>
+        <v>17.7875</v>
       </c>
       <c r="D59" t="n">
-        <v>34.0485</v>
+        <v>34.4644</v>
       </c>
       <c r="E59" t="n">
-        <v>14.6441</v>
+        <v>14.9015</v>
       </c>
       <c r="F59" t="n">
-        <v>28.4663</v>
+        <v>28.1763</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9939</v>
+        <v>20.0196</v>
       </c>
       <c r="C60" t="n">
-        <v>17.7382</v>
+        <v>17.7192</v>
       </c>
       <c r="D60" t="n">
-        <v>34.4297</v>
+        <v>34.7263</v>
       </c>
       <c r="E60" t="n">
-        <v>14.4062</v>
+        <v>14.5922</v>
       </c>
       <c r="F60" t="n">
-        <v>28.1911</v>
+        <v>27.8546</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.4844</v>
+        <v>19.5256</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6012</v>
+        <v>17.6266</v>
       </c>
       <c r="D61" t="n">
-        <v>34.7948</v>
+        <v>35.1658</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3145</v>
+        <v>14.3029</v>
       </c>
       <c r="F61" t="n">
-        <v>27.7812</v>
+        <v>27.4867</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>19.0037</v>
+        <v>18.9961</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5452</v>
+        <v>17.5518</v>
       </c>
       <c r="D62" t="n">
-        <v>35.1026</v>
+        <v>35.3949</v>
       </c>
       <c r="E62" t="n">
-        <v>13.8282</v>
+        <v>13.992</v>
       </c>
       <c r="F62" t="n">
-        <v>27.5211</v>
+        <v>27.2628</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3376</v>
+        <v>18.3451</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4637</v>
+        <v>17.4563</v>
       </c>
       <c r="D63" t="n">
-        <v>35.4399</v>
+        <v>35.745</v>
       </c>
       <c r="E63" t="n">
-        <v>13.5141</v>
+        <v>13.6664</v>
       </c>
       <c r="F63" t="n">
-        <v>27.2038</v>
+        <v>26.9569</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7264</v>
+        <v>17.7359</v>
       </c>
       <c r="C64" t="n">
-        <v>17.4203</v>
+        <v>17.4198</v>
       </c>
       <c r="D64" t="n">
-        <v>39.5426</v>
+        <v>39.5016</v>
       </c>
       <c r="E64" t="n">
-        <v>18.2804</v>
+        <v>18.6201</v>
       </c>
       <c r="F64" t="n">
-        <v>31.5704</v>
+        <v>31.1094</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0356</v>
+        <v>17.0479</v>
       </c>
       <c r="C65" t="n">
-        <v>19.007</v>
+        <v>19.0255</v>
       </c>
       <c r="D65" t="n">
-        <v>38.8738</v>
+        <v>39.4317</v>
       </c>
       <c r="E65" t="n">
-        <v>18.0858</v>
+        <v>18.3179</v>
       </c>
       <c r="F65" t="n">
-        <v>31.217</v>
+        <v>30.6765</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1227</v>
+        <v>16.1543</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7187</v>
+        <v>18.7708</v>
       </c>
       <c r="D66" t="n">
-        <v>39.0455</v>
+        <v>39.4606</v>
       </c>
       <c r="E66" t="n">
-        <v>17.506</v>
+        <v>17.6789</v>
       </c>
       <c r="F66" t="n">
-        <v>30.9731</v>
+        <v>30.3441</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6267</v>
+        <v>23.6495</v>
       </c>
       <c r="C67" t="n">
-        <v>18.5877</v>
+        <v>18.5734</v>
       </c>
       <c r="D67" t="n">
-        <v>39.1038</v>
+        <v>39.5662</v>
       </c>
       <c r="E67" t="n">
-        <v>17.2152</v>
+        <v>17.1818</v>
       </c>
       <c r="F67" t="n">
-        <v>30.5699</v>
+        <v>30.0135</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2273</v>
+        <v>23.2724</v>
       </c>
       <c r="C68" t="n">
-        <v>18.4289</v>
+        <v>18.4239</v>
       </c>
       <c r="D68" t="n">
-        <v>40.5285</v>
+        <v>40.9903</v>
       </c>
       <c r="E68" t="n">
-        <v>16.5963</v>
+        <v>16.6721</v>
       </c>
       <c r="F68" t="n">
-        <v>30.3222</v>
+        <v>29.702</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7429</v>
+        <v>22.7521</v>
       </c>
       <c r="C69" t="n">
-        <v>18.2974</v>
+        <v>18.3702</v>
       </c>
       <c r="D69" t="n">
-        <v>40.8663</v>
+        <v>41.3656</v>
       </c>
       <c r="E69" t="n">
-        <v>16.0814</v>
+        <v>16.1293</v>
       </c>
       <c r="F69" t="n">
-        <v>29.8376</v>
+        <v>29.4767</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.2573</v>
+        <v>22.2951</v>
       </c>
       <c r="C70" t="n">
-        <v>18.3034</v>
+        <v>18.2869</v>
       </c>
       <c r="D70" t="n">
-        <v>40.7372</v>
+        <v>41.2034</v>
       </c>
       <c r="E70" t="n">
-        <v>15.7154</v>
+        <v>15.7562</v>
       </c>
       <c r="F70" t="n">
-        <v>29.495</v>
+        <v>29.2206</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.7376</v>
+        <v>21.7788</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1486</v>
+        <v>18.1787</v>
       </c>
       <c r="D71" t="n">
-        <v>39.4202</v>
+        <v>39.9078</v>
       </c>
       <c r="E71" t="n">
-        <v>15.3352</v>
+        <v>15.4377</v>
       </c>
       <c r="F71" t="n">
-        <v>29.186</v>
+        <v>28.9826</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2263</v>
+        <v>21.2436</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0338</v>
+        <v>18.0527</v>
       </c>
       <c r="D72" t="n">
-        <v>39.5284</v>
+        <v>39.91</v>
       </c>
       <c r="E72" t="n">
-        <v>15.2747</v>
+        <v>15.3861</v>
       </c>
       <c r="F72" t="n">
-        <v>28.8381</v>
+        <v>28.5899</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7096</v>
+        <v>20.7266</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9448</v>
+        <v>17.9393</v>
       </c>
       <c r="D73" t="n">
-        <v>39.4606</v>
+        <v>39.5395</v>
       </c>
       <c r="E73" t="n">
-        <v>14.9919</v>
+        <v>15.079</v>
       </c>
       <c r="F73" t="n">
-        <v>28.613</v>
+        <v>28.3101</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1444</v>
+        <v>20.167</v>
       </c>
       <c r="C74" t="n">
-        <v>17.8669</v>
+        <v>17.8701</v>
       </c>
       <c r="D74" t="n">
-        <v>39.3334</v>
+        <v>39.5706</v>
       </c>
       <c r="E74" t="n">
-        <v>14.7006</v>
+        <v>14.8014</v>
       </c>
       <c r="F74" t="n">
-        <v>28.2933</v>
+        <v>28.0153</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6437</v>
+        <v>19.6615</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7463</v>
+        <v>17.7555</v>
       </c>
       <c r="D75" t="n">
-        <v>39.4247</v>
+        <v>39.9424</v>
       </c>
       <c r="E75" t="n">
-        <v>14.2264</v>
+        <v>14.5298</v>
       </c>
       <c r="F75" t="n">
-        <v>27.9794</v>
+        <v>27.7905</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0956</v>
+        <v>19.1023</v>
       </c>
       <c r="C76" t="n">
-        <v>17.6901</v>
+        <v>17.6646</v>
       </c>
       <c r="D76" t="n">
-        <v>39.4517</v>
+        <v>40.0256</v>
       </c>
       <c r="E76" t="n">
-        <v>14.0026</v>
+        <v>14.2125</v>
       </c>
       <c r="F76" t="n">
-        <v>27.7065</v>
+        <v>27.4598</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5542</v>
+        <v>18.5195</v>
       </c>
       <c r="C77" t="n">
-        <v>17.6102</v>
+        <v>17.6074</v>
       </c>
       <c r="D77" t="n">
-        <v>39.4927</v>
+        <v>39.8523</v>
       </c>
       <c r="E77" t="n">
-        <v>13.745</v>
+        <v>13.8939</v>
       </c>
       <c r="F77" t="n">
-        <v>27.4001</v>
+        <v>27.1589</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9409</v>
+        <v>17.9073</v>
       </c>
       <c r="C78" t="n">
-        <v>17.4444</v>
+        <v>17.4292</v>
       </c>
       <c r="D78" t="n">
-        <v>45.6494</v>
+        <v>46.7237</v>
       </c>
       <c r="E78" t="n">
-        <v>18.4954</v>
+        <v>18.3296</v>
       </c>
       <c r="F78" t="n">
-        <v>31.7488</v>
+        <v>31.0898</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2049</v>
+        <v>17.2118</v>
       </c>
       <c r="C79" t="n">
-        <v>19.3469</v>
+        <v>19.3649</v>
       </c>
       <c r="D79" t="n">
-        <v>45.9425</v>
+        <v>47.6454</v>
       </c>
       <c r="E79" t="n">
-        <v>17.8143</v>
+        <v>17.885</v>
       </c>
       <c r="F79" t="n">
-        <v>31.3402</v>
+        <v>30.7645</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4085</v>
+        <v>16.42</v>
       </c>
       <c r="C80" t="n">
-        <v>19.204</v>
+        <v>19.198</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9944</v>
+        <v>47.9823</v>
       </c>
       <c r="E80" t="n">
-        <v>17.4639</v>
+        <v>17.3814</v>
       </c>
       <c r="F80" t="n">
-        <v>31.0224</v>
+        <v>30.4542</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7801</v>
+        <v>23.7758</v>
       </c>
       <c r="C81" t="n">
-        <v>19.0214</v>
+        <v>18.9291</v>
       </c>
       <c r="D81" t="n">
-        <v>46.4031</v>
+        <v>47.3889</v>
       </c>
       <c r="E81" t="n">
-        <v>17.1417</v>
+        <v>17.0036</v>
       </c>
       <c r="F81" t="n">
-        <v>30.6885</v>
+        <v>30.165</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3793</v>
+        <v>23.3889</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7832</v>
+        <v>18.7376</v>
       </c>
       <c r="D82" t="n">
-        <v>44.1683</v>
+        <v>45.1585</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7775</v>
+        <v>16.7236</v>
       </c>
       <c r="F82" t="n">
-        <v>30.2437</v>
+        <v>29.7657</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9304</v>
+        <v>22.9295</v>
       </c>
       <c r="C83" t="n">
-        <v>18.6231</v>
+        <v>18.6122</v>
       </c>
       <c r="D83" t="n">
-        <v>43.9202</v>
+        <v>44.7682</v>
       </c>
       <c r="E83" t="n">
-        <v>16.4443</v>
+        <v>16.4083</v>
       </c>
       <c r="F83" t="n">
-        <v>29.9189</v>
+        <v>29.4952</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4358</v>
+        <v>22.4432</v>
       </c>
       <c r="C84" t="n">
-        <v>18.4798</v>
+        <v>18.4649</v>
       </c>
       <c r="D84" t="n">
-        <v>43.1929</v>
+        <v>44.3143</v>
       </c>
       <c r="E84" t="n">
-        <v>16.1042</v>
+        <v>16.0644</v>
       </c>
       <c r="F84" t="n">
-        <v>29.7205</v>
+        <v>29.1661</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.943</v>
+        <v>21.9155</v>
       </c>
       <c r="C85" t="n">
-        <v>18.1808</v>
+        <v>18.2438</v>
       </c>
       <c r="D85" t="n">
-        <v>44.7199</v>
+        <v>45.9455</v>
       </c>
       <c r="E85" t="n">
-        <v>15.8121</v>
+        <v>15.7936</v>
       </c>
       <c r="F85" t="n">
-        <v>29.4183</v>
+        <v>28.8853</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.4019</v>
+        <v>21.3981</v>
       </c>
       <c r="C86" t="n">
-        <v>18.1306</v>
+        <v>18.1004</v>
       </c>
       <c r="D86" t="n">
-        <v>43.9573</v>
+        <v>44.4811</v>
       </c>
       <c r="E86" t="n">
-        <v>15.5345</v>
+        <v>15.4579</v>
       </c>
       <c r="F86" t="n">
-        <v>29.0934</v>
+        <v>28.6308</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.9006</v>
+        <v>20.8975</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9838</v>
+        <v>17.9637</v>
       </c>
       <c r="D87" t="n">
-        <v>43.7462</v>
+        <v>44.1799</v>
       </c>
       <c r="E87" t="n">
-        <v>15.2213</v>
+        <v>15.2154</v>
       </c>
       <c r="F87" t="n">
-        <v>28.8129</v>
+        <v>28.3566</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3538</v>
+        <v>20.3549</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8884</v>
+        <v>17.8745</v>
       </c>
       <c r="D88" t="n">
-        <v>43.2839</v>
+        <v>43.8329</v>
       </c>
       <c r="E88" t="n">
-        <v>14.8852</v>
+        <v>14.9049</v>
       </c>
       <c r="F88" t="n">
-        <v>28.4335</v>
+        <v>28.0301</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8304</v>
+        <v>19.8267</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7711</v>
+        <v>17.7552</v>
       </c>
       <c r="D89" t="n">
-        <v>43.0821</v>
+        <v>44.4254</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6388</v>
+        <v>14.6024</v>
       </c>
       <c r="F89" t="n">
-        <v>28.0697</v>
+        <v>27.7409</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2955</v>
+        <v>19.2669</v>
       </c>
       <c r="C90" t="n">
-        <v>17.6827</v>
+        <v>17.712</v>
       </c>
       <c r="D90" t="n">
-        <v>43.0512</v>
+        <v>43.4227</v>
       </c>
       <c r="E90" t="n">
-        <v>14.306</v>
+        <v>14.2927</v>
       </c>
       <c r="F90" t="n">
-        <v>27.7313</v>
+        <v>27.4174</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.6823</v>
+        <v>18.7154</v>
       </c>
       <c r="C91" t="n">
-        <v>17.5692</v>
+        <v>17.5808</v>
       </c>
       <c r="D91" t="n">
-        <v>42.4424</v>
+        <v>43.0753</v>
       </c>
       <c r="E91" t="n">
-        <v>13.9949</v>
+        <v>13.998</v>
       </c>
       <c r="F91" t="n">
-        <v>27.3562</v>
+        <v>27.1102</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.0817</v>
+        <v>18.1015</v>
       </c>
       <c r="C92" t="n">
-        <v>17.4994</v>
+        <v>17.5186</v>
       </c>
       <c r="D92" t="n">
-        <v>47.9701</v>
+        <v>49.6804</v>
       </c>
       <c r="E92" t="n">
-        <v>18.1924</v>
+        <v>18.2687</v>
       </c>
       <c r="F92" t="n">
-        <v>31.6814</v>
+        <v>31.0265</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.3682</v>
+        <v>17.414</v>
       </c>
       <c r="C93" t="n">
-        <v>17.4131</v>
+        <v>17.4231</v>
       </c>
       <c r="D93" t="n">
-        <v>46.1778</v>
+        <v>48.0327</v>
       </c>
       <c r="E93" t="n">
-        <v>17.817</v>
+        <v>17.8502</v>
       </c>
       <c r="F93" t="n">
-        <v>31.6824</v>
+        <v>30.9673</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6371</v>
+        <v>16.6448</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0236</v>
+        <v>19.0247</v>
       </c>
       <c r="D94" t="n">
-        <v>44.837</v>
+        <v>45.8295</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4113</v>
+        <v>17.4284</v>
       </c>
       <c r="F94" t="n">
-        <v>31.3142</v>
+        <v>30.6816</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8611</v>
+        <v>23.8671</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8358</v>
+        <v>18.8461</v>
       </c>
       <c r="D95" t="n">
-        <v>44.0557</v>
+        <v>45.341</v>
       </c>
       <c r="E95" t="n">
-        <v>17.0464</v>
+        <v>17.1042</v>
       </c>
       <c r="F95" t="n">
-        <v>30.7183</v>
+        <v>30.0737</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4454</v>
+        <v>23.4564</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6839</v>
+        <v>18.6529</v>
       </c>
       <c r="D96" t="n">
-        <v>43.5134</v>
+        <v>44.7112</v>
       </c>
       <c r="E96" t="n">
-        <v>16.5767</v>
+        <v>16.5722</v>
       </c>
       <c r="F96" t="n">
-        <v>30.4244</v>
+        <v>29.8774</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0198</v>
+        <v>23.0153</v>
       </c>
       <c r="C97" t="n">
-        <v>18.5004</v>
+        <v>18.5109</v>
       </c>
       <c r="D97" t="n">
-        <v>45.6527</v>
+        <v>47.0089</v>
       </c>
       <c r="E97" t="n">
-        <v>16.2276</v>
+        <v>16.288</v>
       </c>
       <c r="F97" t="n">
-        <v>30.0831</v>
+        <v>29.5893</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5419</v>
+        <v>22.5492</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3393</v>
+        <v>18.3445</v>
       </c>
       <c r="D98" t="n">
-        <v>45.0719</v>
+        <v>46.5551</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9114</v>
+        <v>15.902</v>
       </c>
       <c r="F98" t="n">
-        <v>29.7246</v>
+        <v>29.2983</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0529</v>
+        <v>22.0323</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2032</v>
+        <v>18.1968</v>
       </c>
       <c r="D99" t="n">
-        <v>45.0199</v>
+        <v>45.7532</v>
       </c>
       <c r="E99" t="n">
-        <v>15.7123</v>
+        <v>15.6013</v>
       </c>
       <c r="F99" t="n">
-        <v>29.228</v>
+        <v>28.9852</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5246</v>
+        <v>21.5077</v>
       </c>
       <c r="C100" t="n">
-        <v>18.187</v>
+        <v>18.1701</v>
       </c>
       <c r="D100" t="n">
-        <v>42.341</v>
+        <v>42.9964</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3864</v>
+        <v>15.3246</v>
       </c>
       <c r="F100" t="n">
-        <v>28.934</v>
+        <v>28.6652</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9913</v>
+        <v>20.9832</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0749</v>
+        <v>18.0474</v>
       </c>
       <c r="D101" t="n">
-        <v>42.195</v>
+        <v>42.5707</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0267</v>
+        <v>15.1261</v>
       </c>
       <c r="F101" t="n">
-        <v>28.5722</v>
+        <v>28.0955</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.479</v>
+        <v>20.4582</v>
       </c>
       <c r="C102" t="n">
-        <v>17.9658</v>
+        <v>17.9457</v>
       </c>
       <c r="D102" t="n">
-        <v>41.3944</v>
+        <v>41.7363</v>
       </c>
       <c r="E102" t="n">
-        <v>14.7645</v>
+        <v>14.7698</v>
       </c>
       <c r="F102" t="n">
-        <v>28.2896</v>
+        <v>27.8359</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9271</v>
+        <v>19.9125</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8525</v>
+        <v>17.8475</v>
       </c>
       <c r="D103" t="n">
-        <v>40.963</v>
+        <v>41.8178</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4823</v>
+        <v>14.49</v>
       </c>
       <c r="F103" t="n">
-        <v>27.9035</v>
+        <v>27.5277</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.4129</v>
+        <v>19.4119</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7491</v>
+        <v>17.7369</v>
       </c>
       <c r="D104" t="n">
-        <v>40.7126</v>
+        <v>40.9953</v>
       </c>
       <c r="E104" t="n">
-        <v>14.2183</v>
+        <v>14.218</v>
       </c>
       <c r="F104" t="n">
-        <v>27.6025</v>
+        <v>27.2399</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.826</v>
+        <v>18.8338</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6576</v>
+        <v>17.6528</v>
       </c>
       <c r="D105" t="n">
-        <v>40.7602</v>
+        <v>41.1431</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9339</v>
+        <v>13.9233</v>
       </c>
       <c r="F105" t="n">
-        <v>27.2477</v>
+        <v>26.9071</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2275</v>
+        <v>18.2346</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5832</v>
+        <v>17.5748</v>
       </c>
       <c r="D106" t="n">
-        <v>40.1417</v>
+        <v>40.4232</v>
       </c>
       <c r="E106" t="n">
-        <v>13.7088</v>
+        <v>13.6114</v>
       </c>
       <c r="F106" t="n">
-        <v>26.887</v>
+        <v>26.6245</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6093</v>
+        <v>17.6222</v>
       </c>
       <c r="C107" t="n">
-        <v>17.5057</v>
+        <v>17.5053</v>
       </c>
       <c r="D107" t="n">
-        <v>45.5145</v>
+        <v>45.7088</v>
       </c>
       <c r="E107" t="n">
-        <v>17.7678</v>
+        <v>17.8178</v>
       </c>
       <c r="F107" t="n">
-        <v>31.2126</v>
+        <v>30.6856</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8916</v>
+        <v>16.8775</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1372</v>
+        <v>19.1473</v>
       </c>
       <c r="D108" t="n">
-        <v>46.3699</v>
+        <v>46.5589</v>
       </c>
       <c r="E108" t="n">
-        <v>17.3677</v>
+        <v>17.388</v>
       </c>
       <c r="F108" t="n">
-        <v>30.9741</v>
+        <v>30.2987</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9451</v>
+        <v>15.9255</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9853</v>
+        <v>18.963</v>
       </c>
       <c r="D109" t="n">
-        <v>45.7483</v>
+        <v>45.9662</v>
       </c>
       <c r="E109" t="n">
-        <v>16.9959</v>
+        <v>17.0497</v>
       </c>
       <c r="F109" t="n">
-        <v>30.655</v>
+        <v>29.9708</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5629</v>
+        <v>23.5582</v>
       </c>
       <c r="C110" t="n">
-        <v>18.692</v>
+        <v>18.6876</v>
       </c>
       <c r="D110" t="n">
-        <v>45.1687</v>
+        <v>45.3993</v>
       </c>
       <c r="E110" t="n">
-        <v>16.7943</v>
+        <v>16.8111</v>
       </c>
       <c r="F110" t="n">
-        <v>30.2639</v>
+        <v>29.6378</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1685</v>
+        <v>23.1266</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5348</v>
+        <v>18.542</v>
       </c>
       <c r="D111" t="n">
-        <v>44.6119</v>
+        <v>44.7651</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4665</v>
+        <v>16.4893</v>
       </c>
       <c r="F111" t="n">
-        <v>29.8908</v>
+        <v>29.3526</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6461</v>
+        <v>22.6546</v>
       </c>
       <c r="C112" t="n">
-        <v>18.3807</v>
+        <v>18.3799</v>
       </c>
       <c r="D112" t="n">
-        <v>41.2843</v>
+        <v>41.4645</v>
       </c>
       <c r="E112" t="n">
-        <v>16.1771</v>
+        <v>16.2049</v>
       </c>
       <c r="F112" t="n">
-        <v>29.579</v>
+        <v>29.0204</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1467</v>
+        <v>22.1453</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2682</v>
+        <v>18.2298</v>
       </c>
       <c r="D113" t="n">
-        <v>40.9057</v>
+        <v>41.004</v>
       </c>
       <c r="E113" t="n">
-        <v>15.9401</v>
+        <v>15.8412</v>
       </c>
       <c r="F113" t="n">
-        <v>29.2133</v>
+        <v>28.7306</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6317</v>
+        <v>21.6361</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1255</v>
+        <v>18.1297</v>
       </c>
       <c r="D114" t="n">
-        <v>43.101</v>
+        <v>43.1371</v>
       </c>
       <c r="E114" t="n">
-        <v>15.6199</v>
+        <v>15.6099</v>
       </c>
       <c r="F114" t="n">
-        <v>28.95</v>
+        <v>28.4072</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.0979</v>
+        <v>21.1006</v>
       </c>
       <c r="C115" t="n">
-        <v>17.9841</v>
+        <v>17.9755</v>
       </c>
       <c r="D115" t="n">
-        <v>42.7051</v>
+        <v>42.8362</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3491</v>
+        <v>15.4211</v>
       </c>
       <c r="F115" t="n">
-        <v>28.584</v>
+        <v>28.0992</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5791</v>
+        <v>20.5979</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8655</v>
+        <v>17.8379</v>
       </c>
       <c r="D116" t="n">
-        <v>42.2999</v>
+        <v>42.4281</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8446</v>
+        <v>14.8585</v>
       </c>
       <c r="F116" t="n">
-        <v>28.3156</v>
+        <v>27.9186</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.0359</v>
+        <v>20.1129</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7724</v>
+        <v>17.7437</v>
       </c>
       <c r="D117" t="n">
-        <v>41.9745</v>
+        <v>42.0934</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5548</v>
+        <v>14.6246</v>
       </c>
       <c r="F117" t="n">
-        <v>28.0168</v>
+        <v>27.6071</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5243</v>
+        <v>19.5109</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6742</v>
+        <v>17.6533</v>
       </c>
       <c r="D118" t="n">
-        <v>40.796</v>
+        <v>41.7169</v>
       </c>
       <c r="E118" t="n">
-        <v>14.319</v>
+        <v>14.2901</v>
       </c>
       <c r="F118" t="n">
-        <v>27.69</v>
+        <v>27.2813</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.951</v>
+        <v>18.9502</v>
       </c>
       <c r="C119" t="n">
-        <v>17.5938</v>
+        <v>17.5866</v>
       </c>
       <c r="D119" t="n">
-        <v>40.5525</v>
+        <v>41.4212</v>
       </c>
       <c r="E119" t="n">
-        <v>14.0009</v>
+        <v>14.0052</v>
       </c>
       <c r="F119" t="n">
-        <v>27.3765</v>
+        <v>26.9772</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3815</v>
+        <v>18.3911</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5244</v>
+        <v>17.5186</v>
       </c>
       <c r="D120" t="n">
-        <v>40.3193</v>
+        <v>41.1219</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7219</v>
+        <v>13.7241</v>
       </c>
       <c r="F120" t="n">
-        <v>27.0117</v>
+        <v>26.6851</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7444</v>
+        <v>17.7357</v>
       </c>
       <c r="C121" t="n">
-        <v>17.439</v>
+        <v>17.4416</v>
       </c>
       <c r="D121" t="n">
-        <v>46.8819</v>
+        <v>48.7245</v>
       </c>
       <c r="E121" t="n">
-        <v>18.0933</v>
+        <v>18.0651</v>
       </c>
       <c r="F121" t="n">
-        <v>31.2576</v>
+        <v>30.6605</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.0069</v>
+        <v>17.0272</v>
       </c>
       <c r="C122" t="n">
-        <v>19.2233</v>
+        <v>19.1737</v>
       </c>
       <c r="D122" t="n">
-        <v>46.485</v>
+        <v>46.5575</v>
       </c>
       <c r="E122" t="n">
-        <v>17.463</v>
+        <v>17.491</v>
       </c>
       <c r="F122" t="n">
-        <v>30.8883</v>
+        <v>30.354</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.1157</v>
+        <v>16.0926</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9612</v>
+        <v>18.9674</v>
       </c>
       <c r="D123" t="n">
-        <v>47.1677</v>
+        <v>47.1835</v>
       </c>
       <c r="E123" t="n">
-        <v>17.2073</v>
+        <v>17.1992</v>
       </c>
       <c r="F123" t="n">
-        <v>30.5164</v>
+        <v>29.9911</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6506</v>
+        <v>23.6682</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7413</v>
+        <v>18.7501</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9579</v>
+        <v>43.9598</v>
       </c>
       <c r="E124" t="n">
-        <v>16.8655</v>
+        <v>16.8824</v>
       </c>
       <c r="F124" t="n">
-        <v>30.1733</v>
+        <v>29.6607</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2296</v>
+        <v>23.2205</v>
       </c>
       <c r="C125" t="n">
-        <v>18.6121</v>
+        <v>18.5942</v>
       </c>
       <c r="D125" t="n">
-        <v>43.7566</v>
+        <v>43.7218</v>
       </c>
       <c r="E125" t="n">
-        <v>16.5367</v>
+        <v>16.5372</v>
       </c>
       <c r="F125" t="n">
-        <v>29.9854</v>
+        <v>29.3465</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7614</v>
+        <v>22.7564</v>
       </c>
       <c r="C126" t="n">
-        <v>18.4186</v>
+        <v>18.4197</v>
       </c>
       <c r="D126" t="n">
-        <v>45.2804</v>
+        <v>45.2439</v>
       </c>
       <c r="E126" t="n">
-        <v>16.252</v>
+        <v>16.2338</v>
       </c>
       <c r="F126" t="n">
-        <v>29.4786</v>
+        <v>29.068</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.261</v>
+        <v>22.2592</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2908</v>
+        <v>18.2703</v>
       </c>
       <c r="D127" t="n">
-        <v>44.7013</v>
+        <v>44.6153</v>
       </c>
       <c r="E127" t="n">
-        <v>15.9136</v>
+        <v>15.9174</v>
       </c>
       <c r="F127" t="n">
-        <v>29.1804</v>
+        <v>28.7807</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7637</v>
+        <v>21.7663</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1799</v>
+        <v>18.1769</v>
       </c>
       <c r="D128" t="n">
-        <v>42.4639</v>
+        <v>42.384</v>
       </c>
       <c r="E128" t="n">
-        <v>15.6325</v>
+        <v>15.6219</v>
       </c>
       <c r="F128" t="n">
-        <v>28.9622</v>
+        <v>28.4684</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.209</v>
+        <v>21.2049</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0455</v>
+        <v>18.0212</v>
       </c>
       <c r="D129" t="n">
-        <v>41.9476</v>
+        <v>41.924</v>
       </c>
       <c r="E129" t="n">
-        <v>15.4066</v>
+        <v>15.3987</v>
       </c>
       <c r="F129" t="n">
-        <v>28.5605</v>
+        <v>28.1817</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6988</v>
+        <v>20.6638</v>
       </c>
       <c r="C130" t="n">
-        <v>17.913</v>
+        <v>17.9016</v>
       </c>
       <c r="D130" t="n">
-        <v>41.5127</v>
+        <v>41.543</v>
       </c>
       <c r="E130" t="n">
-        <v>14.8956</v>
+        <v>14.8853</v>
       </c>
       <c r="F130" t="n">
-        <v>28.2853</v>
+        <v>27.9515</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1646</v>
+        <v>20.1446</v>
       </c>
       <c r="C131" t="n">
-        <v>17.826</v>
+        <v>17.8045</v>
       </c>
       <c r="D131" t="n">
-        <v>40.9948</v>
+        <v>41.0228</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6123</v>
+        <v>14.6144</v>
       </c>
       <c r="F131" t="n">
-        <v>28.0236</v>
+        <v>27.6696</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6244</v>
+        <v>19.6191</v>
       </c>
       <c r="C132" t="n">
-        <v>17.7187</v>
+        <v>17.7049</v>
       </c>
       <c r="D132" t="n">
-        <v>40.6069</v>
+        <v>40.6407</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3522</v>
+        <v>14.3467</v>
       </c>
       <c r="F132" t="n">
-        <v>27.6646</v>
+        <v>27.3896</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0792</v>
+        <v>19.0798</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6311</v>
+        <v>17.638</v>
       </c>
       <c r="D133" t="n">
-        <v>40.315</v>
+        <v>40.3497</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0685</v>
+        <v>14.0788</v>
       </c>
       <c r="F133" t="n">
-        <v>27.3893</v>
+        <v>27.0953</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5083</v>
+        <v>18.5462</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5636</v>
+        <v>17.5507</v>
       </c>
       <c r="D134" t="n">
-        <v>40.0019</v>
+        <v>40.0533</v>
       </c>
       <c r="E134" t="n">
-        <v>13.7784</v>
+        <v>13.8477</v>
       </c>
       <c r="F134" t="n">
-        <v>27.088</v>
+        <v>26.7605</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8636</v>
+        <v>17.8806</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4765</v>
+        <v>17.4875</v>
       </c>
       <c r="D135" t="n">
-        <v>47.4733</v>
+        <v>47.4141</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8742</v>
+        <v>17.8706</v>
       </c>
       <c r="F135" t="n">
-        <v>31.3237</v>
+        <v>30.8289</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.1923</v>
+        <v>17.1856</v>
       </c>
       <c r="C136" t="n">
-        <v>19.1988</v>
+        <v>19.1972</v>
       </c>
       <c r="D136" t="n">
-        <v>46.4564</v>
+        <v>46.4054</v>
       </c>
       <c r="E136" t="n">
-        <v>17.59</v>
+        <v>17.6435</v>
       </c>
       <c r="F136" t="n">
-        <v>30.8402</v>
+        <v>30.3568</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.2972</v>
+        <v>16.3149</v>
       </c>
       <c r="C137" t="n">
-        <v>19.0013</v>
+        <v>18.9896</v>
       </c>
       <c r="D137" t="n">
-        <v>45.1865</v>
+        <v>45.2252</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1103</v>
+        <v>17.1051</v>
       </c>
       <c r="F137" t="n">
-        <v>30.5986</v>
+        <v>30.1236</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7395</v>
+        <v>23.7289</v>
       </c>
       <c r="C138" t="n">
-        <v>18.7988</v>
+        <v>18.7692</v>
       </c>
       <c r="D138" t="n">
-        <v>47.0075</v>
+        <v>46.9229</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7598</v>
+        <v>16.7639</v>
       </c>
       <c r="F138" t="n">
-        <v>30.1946</v>
+        <v>29.8104</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3162</v>
+        <v>23.3146</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6419</v>
+        <v>18.6487</v>
       </c>
       <c r="D139" t="n">
-        <v>44.3171</v>
+        <v>44.3516</v>
       </c>
       <c r="E139" t="n">
-        <v>16.551</v>
+        <v>16.5771</v>
       </c>
       <c r="F139" t="n">
-        <v>30.018</v>
+        <v>29.448</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8638</v>
+        <v>22.8571</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4755</v>
+        <v>18.4697</v>
       </c>
       <c r="D140" t="n">
-        <v>43.7195</v>
+        <v>43.6696</v>
       </c>
       <c r="E140" t="n">
-        <v>16.299</v>
+        <v>16.2783</v>
       </c>
       <c r="F140" t="n">
-        <v>29.5876</v>
+        <v>29.1479</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3684</v>
+        <v>22.3683</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3135</v>
+        <v>18.3313</v>
       </c>
       <c r="D141" t="n">
-        <v>43.0287</v>
+        <v>43.0745</v>
       </c>
       <c r="E141" t="n">
-        <v>15.9597</v>
+        <v>15.942</v>
       </c>
       <c r="F141" t="n">
-        <v>29.188</v>
+        <v>28.8705</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8585</v>
+        <v>21.8536</v>
       </c>
       <c r="C142" t="n">
-        <v>18.2068</v>
+        <v>18.1762</v>
       </c>
       <c r="D142" t="n">
-        <v>44.41</v>
+        <v>44.3774</v>
       </c>
       <c r="E142" t="n">
-        <v>15.5134</v>
+        <v>15.5123</v>
       </c>
       <c r="F142" t="n">
-        <v>28.9871</v>
+        <v>28.6869</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.322</v>
+        <v>21.3171</v>
       </c>
       <c r="C143" t="n">
-        <v>18.0898</v>
+        <v>18.072</v>
       </c>
       <c r="D143" t="n">
-        <v>43.6079</v>
+        <v>43.5866</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2088</v>
+        <v>15.209</v>
       </c>
       <c r="F143" t="n">
-        <v>28.5718</v>
+        <v>28.3238</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.1627</v>
+        <v>18.8661</v>
       </c>
       <c r="C2" t="n">
-        <v>14.1355</v>
+        <v>14.1954</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0339</v>
+        <v>32.011</v>
       </c>
       <c r="E2" t="n">
-        <v>7.66204</v>
+        <v>6.99797</v>
       </c>
       <c r="F2" t="n">
-        <v>26.7627</v>
+        <v>26.6541</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4236</v>
+        <v>18.3606</v>
       </c>
       <c r="C3" t="n">
-        <v>14.4583</v>
+        <v>14.5143</v>
       </c>
       <c r="D3" t="n">
-        <v>32.1674</v>
+        <v>32.0463</v>
       </c>
       <c r="E3" t="n">
-        <v>6.94403</v>
+        <v>6.54558</v>
       </c>
       <c r="F3" t="n">
-        <v>26.5475</v>
+        <v>26.5407</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.1792</v>
+        <v>18.095</v>
       </c>
       <c r="C4" t="n">
-        <v>14.7112</v>
+        <v>14.8006</v>
       </c>
       <c r="D4" t="n">
-        <v>32.2504</v>
+        <v>32.1795</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6251</v>
+        <v>6.57812</v>
       </c>
       <c r="F4" t="n">
-        <v>26.1894</v>
+        <v>26.2633</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.5038</v>
+        <v>17.4476</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8241</v>
+        <v>14.809</v>
       </c>
       <c r="D5" t="n">
-        <v>32.6231</v>
+        <v>32.4777</v>
       </c>
       <c r="E5" t="n">
-        <v>6.39803</v>
+        <v>6.11772</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2694</v>
+        <v>26.2808</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.2022</v>
+        <v>17.1553</v>
       </c>
       <c r="C6" t="n">
-        <v>15.082</v>
+        <v>15.1111</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6364</v>
+        <v>32.4513</v>
       </c>
       <c r="E6" t="n">
-        <v>6.15793</v>
+        <v>6.25043</v>
       </c>
       <c r="F6" t="n">
-        <v>26.3904</v>
+        <v>25.9809</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3915</v>
+        <v>16.4488</v>
       </c>
       <c r="C7" t="n">
-        <v>15.345</v>
+        <v>15.3217</v>
       </c>
       <c r="D7" t="n">
-        <v>31.7884</v>
+        <v>31.8698</v>
       </c>
       <c r="E7" t="n">
-        <v>15.7486</v>
+        <v>15.8202</v>
       </c>
       <c r="F7" t="n">
-        <v>30.2949</v>
+        <v>30.1084</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.7681</v>
+        <v>15.8381</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9697</v>
+        <v>16.9474</v>
       </c>
       <c r="D8" t="n">
-        <v>31.8508</v>
+        <v>31.9378</v>
       </c>
       <c r="E8" t="n">
-        <v>15.4492</v>
+        <v>15.5379</v>
       </c>
       <c r="F8" t="n">
-        <v>29.8535</v>
+        <v>29.7721</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.9193</v>
+        <v>15.0049</v>
       </c>
       <c r="C9" t="n">
-        <v>17.1183</v>
+        <v>17.0992</v>
       </c>
       <c r="D9" t="n">
-        <v>31.7785</v>
+        <v>31.9702</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0792</v>
+        <v>15.0038</v>
       </c>
       <c r="F9" t="n">
-        <v>29.8497</v>
+        <v>29.7431</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.9466</v>
+        <v>22.9663</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1091</v>
+        <v>17.1038</v>
       </c>
       <c r="D10" t="n">
-        <v>31.987</v>
+        <v>31.9271</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7859</v>
+        <v>14.707</v>
       </c>
       <c r="F10" t="n">
-        <v>29.3348</v>
+        <v>29.1447</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.4208</v>
+        <v>22.4116</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1868</v>
+        <v>17.1431</v>
       </c>
       <c r="D11" t="n">
-        <v>32.0556</v>
+        <v>32.0944</v>
       </c>
       <c r="E11" t="n">
-        <v>14.4852</v>
+        <v>14.463</v>
       </c>
       <c r="F11" t="n">
-        <v>29.2768</v>
+        <v>29.18</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>21.9573</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0824</v>
+        <v>17.0406</v>
       </c>
       <c r="D12" t="n">
-        <v>32.2773</v>
+        <v>32.0588</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1929</v>
+        <v>14.1904</v>
       </c>
       <c r="F12" t="n">
-        <v>28.9006</v>
+        <v>28.8934</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5553</v>
+        <v>21.5735</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2257</v>
+        <v>17.22</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2191</v>
+        <v>32.2589</v>
       </c>
       <c r="E13" t="n">
-        <v>14.0478</v>
+        <v>13.9721</v>
       </c>
       <c r="F13" t="n">
-        <v>28.6386</v>
+        <v>29.0215</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.2091</v>
+        <v>21.1146</v>
       </c>
       <c r="C14" t="n">
-        <v>17.2023</v>
+        <v>17.2033</v>
       </c>
       <c r="D14" t="n">
-        <v>32.2896</v>
+        <v>32.4966</v>
       </c>
       <c r="E14" t="n">
-        <v>13.7126</v>
+        <v>13.6421</v>
       </c>
       <c r="F14" t="n">
-        <v>28.6698</v>
+        <v>28.5204</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.7563</v>
+        <v>20.711</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2467</v>
+        <v>17.2815</v>
       </c>
       <c r="D15" t="n">
-        <v>32.3851</v>
+        <v>32.3675</v>
       </c>
       <c r="E15" t="n">
-        <v>13.4462</v>
+        <v>13.5142</v>
       </c>
       <c r="F15" t="n">
-        <v>27.9395</v>
+        <v>28.1822</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.0844</v>
+        <v>20.2019</v>
       </c>
       <c r="C16" t="n">
-        <v>17.249</v>
+        <v>17.2323</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5172</v>
+        <v>32.5755</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3276</v>
+        <v>13.2796</v>
       </c>
       <c r="F16" t="n">
-        <v>27.7387</v>
+        <v>27.7436</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.5686</v>
+        <v>19.5504</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1757</v>
+        <v>17.1824</v>
       </c>
       <c r="D17" t="n">
-        <v>32.6233</v>
+        <v>32.6787</v>
       </c>
       <c r="E17" t="n">
-        <v>13.2557</v>
+        <v>13.1215</v>
       </c>
       <c r="F17" t="n">
-        <v>27.4765</v>
+        <v>27.5376</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.0768</v>
+        <v>19.1295</v>
       </c>
       <c r="C18" t="n">
-        <v>17.1781</v>
+        <v>17.1818</v>
       </c>
       <c r="D18" t="n">
-        <v>32.832</v>
+        <v>32.9981</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9624</v>
+        <v>12.9423</v>
       </c>
       <c r="F18" t="n">
-        <v>27.127</v>
+        <v>27.1441</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.6199</v>
+        <v>18.5892</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1637</v>
+        <v>17.1628</v>
       </c>
       <c r="D19" t="n">
-        <v>32.852</v>
+        <v>33.0487</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6632</v>
+        <v>12.6182</v>
       </c>
       <c r="F19" t="n">
-        <v>26.7642</v>
+        <v>26.8441</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.0918</v>
+        <v>18.074</v>
       </c>
       <c r="C20" t="n">
-        <v>17.2492</v>
+        <v>17.2797</v>
       </c>
       <c r="D20" t="n">
-        <v>33.0385</v>
+        <v>33.1079</v>
       </c>
       <c r="E20" t="n">
-        <v>12.3262</v>
+        <v>12.425</v>
       </c>
       <c r="F20" t="n">
-        <v>26.5165</v>
+        <v>26.5423</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.4037</v>
+        <v>17.3865</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1368</v>
+        <v>17.1479</v>
       </c>
       <c r="D21" t="n">
-        <v>32.4972</v>
+        <v>32.5394</v>
       </c>
       <c r="E21" t="n">
-        <v>17.8573</v>
+        <v>17.644</v>
       </c>
       <c r="F21" t="n">
-        <v>30.668</v>
+        <v>30.6504</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7779</v>
+        <v>16.7293</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7214</v>
+        <v>18.7203</v>
       </c>
       <c r="D22" t="n">
-        <v>32.3933</v>
+        <v>32.4115</v>
       </c>
       <c r="E22" t="n">
-        <v>17.0606</v>
+        <v>17.1461</v>
       </c>
       <c r="F22" t="n">
-        <v>30.4133</v>
+        <v>30.4593</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0578</v>
+        <v>16.0329</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5144</v>
+        <v>18.5799</v>
       </c>
       <c r="D23" t="n">
-        <v>32.403</v>
+        <v>32.4344</v>
       </c>
       <c r="E23" t="n">
-        <v>16.6587</v>
+        <v>16.7353</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1589</v>
+        <v>30.2649</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.3137</v>
+        <v>23.3801</v>
       </c>
       <c r="C24" t="n">
-        <v>18.441</v>
+        <v>18.4623</v>
       </c>
       <c r="D24" t="n">
-        <v>32.2873</v>
+        <v>32.2564</v>
       </c>
       <c r="E24" t="n">
-        <v>16.1897</v>
+        <v>16.256</v>
       </c>
       <c r="F24" t="n">
-        <v>29.9498</v>
+        <v>30.0786</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.9111</v>
+        <v>22.8971</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3837</v>
+        <v>18.3836</v>
       </c>
       <c r="D25" t="n">
-        <v>32.7743</v>
+        <v>32.8327</v>
       </c>
       <c r="E25" t="n">
-        <v>15.772</v>
+        <v>15.75</v>
       </c>
       <c r="F25" t="n">
-        <v>29.7251</v>
+        <v>29.7665</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.5691</v>
+        <v>22.4759</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2964</v>
+        <v>18.3243</v>
       </c>
       <c r="D26" t="n">
-        <v>32.82</v>
+        <v>32.8275</v>
       </c>
       <c r="E26" t="n">
-        <v>15.4168</v>
+        <v>15.428</v>
       </c>
       <c r="F26" t="n">
-        <v>29.3992</v>
+        <v>29.3691</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>22.0788</v>
+        <v>21.9524</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1763</v>
+        <v>18.1519</v>
       </c>
       <c r="D27" t="n">
-        <v>32.8417</v>
+        <v>32.8293</v>
       </c>
       <c r="E27" t="n">
-        <v>15.176</v>
+        <v>15.2545</v>
       </c>
       <c r="F27" t="n">
-        <v>29.1392</v>
+        <v>29.0024</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.6684</v>
+        <v>21.535</v>
       </c>
       <c r="C28" t="n">
-        <v>18.0292</v>
+        <v>18.0404</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7396</v>
+        <v>32.7568</v>
       </c>
       <c r="E28" t="n">
-        <v>14.8367</v>
+        <v>14.8282</v>
       </c>
       <c r="F28" t="n">
-        <v>28.8987</v>
+        <v>28.9506</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.0563</v>
+        <v>21.053</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9835</v>
+        <v>17.9738</v>
       </c>
       <c r="D29" t="n">
-        <v>32.7345</v>
+        <v>32.8388</v>
       </c>
       <c r="E29" t="n">
-        <v>14.5327</v>
+        <v>14.563</v>
       </c>
       <c r="F29" t="n">
-        <v>28.4535</v>
+        <v>28.3962</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6641</v>
+        <v>20.6706</v>
       </c>
       <c r="C30" t="n">
-        <v>17.9071</v>
+        <v>17.9023</v>
       </c>
       <c r="D30" t="n">
-        <v>33.0074</v>
+        <v>33.1283</v>
       </c>
       <c r="E30" t="n">
-        <v>14.2519</v>
+        <v>14.21</v>
       </c>
       <c r="F30" t="n">
-        <v>28.3253</v>
+        <v>28.2121</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0455</v>
+        <v>20.0947</v>
       </c>
       <c r="C31" t="n">
-        <v>17.748</v>
+        <v>17.8261</v>
       </c>
       <c r="D31" t="n">
-        <v>33.1096</v>
+        <v>33.0241</v>
       </c>
       <c r="E31" t="n">
-        <v>13.9863</v>
+        <v>13.9753</v>
       </c>
       <c r="F31" t="n">
-        <v>27.9035</v>
+        <v>27.9168</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6351</v>
+        <v>19.6718</v>
       </c>
       <c r="C32" t="n">
-        <v>17.726</v>
+        <v>17.7015</v>
       </c>
       <c r="D32" t="n">
-        <v>33.1541</v>
+        <v>33.1225</v>
       </c>
       <c r="E32" t="n">
-        <v>13.7001</v>
+        <v>13.709</v>
       </c>
       <c r="F32" t="n">
-        <v>27.5311</v>
+        <v>27.5234</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0425</v>
+        <v>19.0628</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6538</v>
+        <v>17.6372</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3213</v>
+        <v>33.3702</v>
       </c>
       <c r="E33" t="n">
-        <v>13.7108</v>
+        <v>13.6704</v>
       </c>
       <c r="F33" t="n">
-        <v>27.1839</v>
+        <v>27.2431</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4699</v>
+        <v>18.4815</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5847</v>
+        <v>17.536</v>
       </c>
       <c r="D34" t="n">
-        <v>33.3871</v>
+        <v>33.4654</v>
       </c>
       <c r="E34" t="n">
-        <v>13.3856</v>
+        <v>13.3961</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9648</v>
+        <v>26.9688</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9179</v>
+        <v>17.9216</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4852</v>
+        <v>17.4928</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7154</v>
+        <v>32.8509</v>
       </c>
       <c r="E35" t="n">
-        <v>18.1944</v>
+        <v>18.0692</v>
       </c>
       <c r="F35" t="n">
-        <v>31.2863</v>
+        <v>31.199</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2544</v>
+        <v>17.2735</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4172</v>
+        <v>17.4425</v>
       </c>
       <c r="D36" t="n">
-        <v>32.7641</v>
+        <v>32.6038</v>
       </c>
       <c r="E36" t="n">
-        <v>17.5221</v>
+        <v>17.6385</v>
       </c>
       <c r="F36" t="n">
-        <v>30.8763</v>
+        <v>30.7413</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.5597</v>
+        <v>16.4799</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8876</v>
+        <v>18.8275</v>
       </c>
       <c r="D37" t="n">
-        <v>32.4822</v>
+        <v>32.8662</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0653</v>
+        <v>17.1493</v>
       </c>
       <c r="F37" t="n">
-        <v>30.4301</v>
+        <v>30.3641</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.7411</v>
+        <v>23.7074</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6968</v>
+        <v>18.7304</v>
       </c>
       <c r="D38" t="n">
-        <v>32.4623</v>
+        <v>32.5162</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7869</v>
+        <v>16.7866</v>
       </c>
       <c r="F38" t="n">
-        <v>30.0498</v>
+        <v>30.0508</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.3591</v>
+        <v>23.342</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5045</v>
+        <v>18.5283</v>
       </c>
       <c r="D39" t="n">
-        <v>32.5422</v>
+        <v>32.4975</v>
       </c>
       <c r="E39" t="n">
-        <v>16.468</v>
+        <v>16.4383</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6715</v>
+        <v>29.6307</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.8674</v>
+        <v>22.9252</v>
       </c>
       <c r="C40" t="n">
-        <v>18.3821</v>
+        <v>18.385</v>
       </c>
       <c r="D40" t="n">
-        <v>32.8861</v>
+        <v>32.9019</v>
       </c>
       <c r="E40" t="n">
-        <v>16.2201</v>
+        <v>16.14</v>
       </c>
       <c r="F40" t="n">
-        <v>29.3312</v>
+        <v>29.3239</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4636</v>
+        <v>22.4501</v>
       </c>
       <c r="C41" t="n">
-        <v>18.2802</v>
+        <v>18.3062</v>
       </c>
       <c r="D41" t="n">
-        <v>33.0196</v>
+        <v>33.0347</v>
       </c>
       <c r="E41" t="n">
-        <v>15.9009</v>
+        <v>15.8666</v>
       </c>
       <c r="F41" t="n">
-        <v>29.149</v>
+        <v>29.0641</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.9685</v>
+        <v>21.961</v>
       </c>
       <c r="C42" t="n">
-        <v>18.0845</v>
+        <v>18.1299</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9738</v>
+        <v>33.0811</v>
       </c>
       <c r="E42" t="n">
-        <v>15.543</v>
+        <v>15.5211</v>
       </c>
       <c r="F42" t="n">
-        <v>28.8322</v>
+        <v>28.8012</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4526</v>
+        <v>21.4409</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9589</v>
+        <v>17.9916</v>
       </c>
       <c r="D43" t="n">
-        <v>32.9035</v>
+        <v>32.8209</v>
       </c>
       <c r="E43" t="n">
-        <v>15.1877</v>
+        <v>15.2165</v>
       </c>
       <c r="F43" t="n">
-        <v>28.5489</v>
+        <v>28.4982</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.896</v>
+        <v>20.8922</v>
       </c>
       <c r="C44" t="n">
-        <v>17.8747</v>
+        <v>17.8789</v>
       </c>
       <c r="D44" t="n">
-        <v>32.829</v>
+        <v>32.8015</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9882</v>
+        <v>14.9412</v>
       </c>
       <c r="F44" t="n">
-        <v>28.3148</v>
+        <v>28.2508</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4371</v>
+        <v>20.4366</v>
       </c>
       <c r="C45" t="n">
-        <v>17.7859</v>
+        <v>17.7812</v>
       </c>
       <c r="D45" t="n">
-        <v>32.9362</v>
+        <v>32.8469</v>
       </c>
       <c r="E45" t="n">
-        <v>14.6118</v>
+        <v>14.5707</v>
       </c>
       <c r="F45" t="n">
-        <v>27.9237</v>
+        <v>27.9257</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8969</v>
+        <v>19.9122</v>
       </c>
       <c r="C46" t="n">
-        <v>17.711</v>
+        <v>17.7111</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9751</v>
+        <v>33.0686</v>
       </c>
       <c r="E46" t="n">
-        <v>14.3039</v>
+        <v>14.2953</v>
       </c>
       <c r="F46" t="n">
-        <v>27.6985</v>
+        <v>27.709</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3543</v>
+        <v>19.3767</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5741</v>
+        <v>17.5794</v>
       </c>
       <c r="D47" t="n">
-        <v>33.0612</v>
+        <v>33.1107</v>
       </c>
       <c r="E47" t="n">
-        <v>14.0109</v>
+        <v>14.0037</v>
       </c>
       <c r="F47" t="n">
-        <v>27.3583</v>
+        <v>27.3479</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8124</v>
+        <v>18.8018</v>
       </c>
       <c r="C48" t="n">
-        <v>17.4952</v>
+        <v>17.5254</v>
       </c>
       <c r="D48" t="n">
-        <v>33.2828</v>
+        <v>33.3038</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6891</v>
+        <v>13.6978</v>
       </c>
       <c r="F48" t="n">
-        <v>27.0369</v>
+        <v>27.0606</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1371</v>
+        <v>18.1209</v>
       </c>
       <c r="C49" t="n">
-        <v>17.3925</v>
+        <v>17.4174</v>
       </c>
       <c r="D49" t="n">
-        <v>33.5016</v>
+        <v>33.5539</v>
       </c>
       <c r="E49" t="n">
-        <v>13.3623</v>
+        <v>13.3545</v>
       </c>
       <c r="F49" t="n">
-        <v>26.8237</v>
+        <v>26.8364</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.5192</v>
+        <v>17.5678</v>
       </c>
       <c r="C50" t="n">
-        <v>17.3568</v>
+        <v>17.363</v>
       </c>
       <c r="D50" t="n">
-        <v>33.08</v>
+        <v>32.9589</v>
       </c>
       <c r="E50" t="n">
-        <v>17.7651</v>
+        <v>17.924</v>
       </c>
       <c r="F50" t="n">
-        <v>30.9145</v>
+        <v>30.8666</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.7987</v>
+        <v>16.8038</v>
       </c>
       <c r="C51" t="n">
-        <v>18.8289</v>
+        <v>18.8614</v>
       </c>
       <c r="D51" t="n">
-        <v>33.3306</v>
+        <v>33.273</v>
       </c>
       <c r="E51" t="n">
-        <v>17.4179</v>
+        <v>17.4552</v>
       </c>
       <c r="F51" t="n">
-        <v>30.5164</v>
+        <v>30.478</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.8807</v>
+        <v>15.8754</v>
       </c>
       <c r="C52" t="n">
-        <v>18.6746</v>
+        <v>18.6446</v>
       </c>
       <c r="D52" t="n">
-        <v>33.1652</v>
+        <v>33.2854</v>
       </c>
       <c r="E52" t="n">
-        <v>17.1091</v>
+        <v>17.108</v>
       </c>
       <c r="F52" t="n">
-        <v>30.1888</v>
+        <v>30.157</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.5035</v>
+        <v>23.4828</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4933</v>
+        <v>18.4926</v>
       </c>
       <c r="D53" t="n">
-        <v>33.1148</v>
+        <v>33.4414</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7439</v>
+        <v>16.7317</v>
       </c>
       <c r="F53" t="n">
-        <v>29.9288</v>
+        <v>29.9052</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1513</v>
+        <v>23.1515</v>
       </c>
       <c r="C54" t="n">
-        <v>18.3964</v>
+        <v>18.3718</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2834</v>
+        <v>33.7242</v>
       </c>
       <c r="E54" t="n">
-        <v>16.4046</v>
+        <v>16.3646</v>
       </c>
       <c r="F54" t="n">
-        <v>29.5214</v>
+        <v>29.5803</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6469</v>
+        <v>22.6314</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2731</v>
+        <v>18.2637</v>
       </c>
       <c r="D55" t="n">
-        <v>33.0573</v>
+        <v>33.3491</v>
       </c>
       <c r="E55" t="n">
-        <v>16.0582</v>
+        <v>16.0742</v>
       </c>
       <c r="F55" t="n">
-        <v>29.2291</v>
+        <v>29.3106</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1384</v>
+        <v>22.1406</v>
       </c>
       <c r="C56" t="n">
-        <v>18.1188</v>
+        <v>18.1007</v>
       </c>
       <c r="D56" t="n">
-        <v>33.2056</v>
+        <v>33.4164</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7989</v>
+        <v>15.8124</v>
       </c>
       <c r="F56" t="n">
-        <v>29.0491</v>
+        <v>29.0396</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.5999</v>
+        <v>21.6057</v>
       </c>
       <c r="C57" t="n">
-        <v>18.0584</v>
+        <v>18.0099</v>
       </c>
       <c r="D57" t="n">
-        <v>33.8383</v>
+        <v>33.9846</v>
       </c>
       <c r="E57" t="n">
-        <v>15.484</v>
+        <v>15.4703</v>
       </c>
       <c r="F57" t="n">
-        <v>28.726</v>
+        <v>28.7324</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0824</v>
+        <v>21.0646</v>
       </c>
       <c r="C58" t="n">
-        <v>17.8987</v>
+        <v>17.9297</v>
       </c>
       <c r="D58" t="n">
-        <v>33.9939</v>
+        <v>34.1396</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1708</v>
+        <v>15.1602</v>
       </c>
       <c r="F58" t="n">
-        <v>28.46</v>
+        <v>28.4602</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5953</v>
+        <v>20.5814</v>
       </c>
       <c r="C59" t="n">
-        <v>17.7875</v>
+        <v>17.7681</v>
       </c>
       <c r="D59" t="n">
-        <v>34.4644</v>
+        <v>34.6664</v>
       </c>
       <c r="E59" t="n">
-        <v>14.9015</v>
+        <v>14.8678</v>
       </c>
       <c r="F59" t="n">
-        <v>28.1763</v>
+        <v>28.2021</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0196</v>
+        <v>20.0009</v>
       </c>
       <c r="C60" t="n">
-        <v>17.7192</v>
+        <v>17.6959</v>
       </c>
       <c r="D60" t="n">
-        <v>34.7263</v>
+        <v>34.8329</v>
       </c>
       <c r="E60" t="n">
-        <v>14.5922</v>
+        <v>14.5877</v>
       </c>
       <c r="F60" t="n">
-        <v>27.8546</v>
+        <v>27.8462</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5256</v>
+        <v>19.5429</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6266</v>
+        <v>17.6263</v>
       </c>
       <c r="D61" t="n">
-        <v>35.1658</v>
+        <v>35.2542</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3029</v>
+        <v>14.2879</v>
       </c>
       <c r="F61" t="n">
-        <v>27.4867</v>
+        <v>27.5599</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9961</v>
+        <v>18.9946</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5518</v>
+        <v>17.5578</v>
       </c>
       <c r="D62" t="n">
-        <v>35.3949</v>
+        <v>35.4377</v>
       </c>
       <c r="E62" t="n">
-        <v>13.992</v>
+        <v>13.9794</v>
       </c>
       <c r="F62" t="n">
-        <v>27.2628</v>
+        <v>27.2819</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3451</v>
+        <v>18.3945</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4563</v>
+        <v>17.4896</v>
       </c>
       <c r="D63" t="n">
-        <v>35.745</v>
+        <v>35.8061</v>
       </c>
       <c r="E63" t="n">
-        <v>13.6664</v>
+        <v>13.6571</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9569</v>
+        <v>26.9615</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7359</v>
+        <v>17.732</v>
       </c>
       <c r="C64" t="n">
-        <v>17.4198</v>
+        <v>17.4572</v>
       </c>
       <c r="D64" t="n">
-        <v>39.5016</v>
+        <v>39.4147</v>
       </c>
       <c r="E64" t="n">
-        <v>18.6201</v>
+        <v>18.6288</v>
       </c>
       <c r="F64" t="n">
-        <v>31.1094</v>
+        <v>31.0958</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0479</v>
+        <v>17.0194</v>
       </c>
       <c r="C65" t="n">
-        <v>19.0255</v>
+        <v>19.039</v>
       </c>
       <c r="D65" t="n">
-        <v>39.4317</v>
+        <v>39.0981</v>
       </c>
       <c r="E65" t="n">
-        <v>18.3179</v>
+        <v>18.3811</v>
       </c>
       <c r="F65" t="n">
-        <v>30.6765</v>
+        <v>30.6944</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1543</v>
+        <v>16.1351</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7708</v>
+        <v>18.7789</v>
       </c>
       <c r="D66" t="n">
-        <v>39.4606</v>
+        <v>39.3026</v>
       </c>
       <c r="E66" t="n">
-        <v>17.6789</v>
+        <v>18.0122</v>
       </c>
       <c r="F66" t="n">
-        <v>30.3441</v>
+        <v>30.3201</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6495</v>
+        <v>23.6353</v>
       </c>
       <c r="C67" t="n">
-        <v>18.5734</v>
+        <v>18.6271</v>
       </c>
       <c r="D67" t="n">
-        <v>39.5662</v>
+        <v>39.5369</v>
       </c>
       <c r="E67" t="n">
-        <v>17.1818</v>
+        <v>17.5685</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0135</v>
+        <v>30.0256</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2724</v>
+        <v>23.2596</v>
       </c>
       <c r="C68" t="n">
-        <v>18.4239</v>
+        <v>18.4842</v>
       </c>
       <c r="D68" t="n">
-        <v>40.9903</v>
+        <v>41.1894</v>
       </c>
       <c r="E68" t="n">
-        <v>16.6721</v>
+        <v>17.0339</v>
       </c>
       <c r="F68" t="n">
-        <v>29.702</v>
+        <v>29.6626</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7521</v>
+        <v>22.7779</v>
       </c>
       <c r="C69" t="n">
-        <v>18.3702</v>
+        <v>18.319</v>
       </c>
       <c r="D69" t="n">
-        <v>41.3656</v>
+        <v>41.3576</v>
       </c>
       <c r="E69" t="n">
-        <v>16.1293</v>
+        <v>16.455</v>
       </c>
       <c r="F69" t="n">
-        <v>29.4767</v>
+        <v>29.4545</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.2951</v>
+        <v>22.3028</v>
       </c>
       <c r="C70" t="n">
-        <v>18.2869</v>
+        <v>18.3252</v>
       </c>
       <c r="D70" t="n">
-        <v>41.2034</v>
+        <v>41.196</v>
       </c>
       <c r="E70" t="n">
-        <v>15.7562</v>
+        <v>16.0223</v>
       </c>
       <c r="F70" t="n">
-        <v>29.2206</v>
+        <v>29.1427</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.7788</v>
+        <v>21.7802</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1787</v>
+        <v>18.1657</v>
       </c>
       <c r="D71" t="n">
-        <v>39.9078</v>
+        <v>39.8238</v>
       </c>
       <c r="E71" t="n">
-        <v>15.4377</v>
+        <v>15.6876</v>
       </c>
       <c r="F71" t="n">
-        <v>28.9826</v>
+        <v>28.8724</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2436</v>
+        <v>21.2363</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0527</v>
+        <v>18.0816</v>
       </c>
       <c r="D72" t="n">
-        <v>39.91</v>
+        <v>39.9113</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3861</v>
+        <v>15.3718</v>
       </c>
       <c r="F72" t="n">
-        <v>28.5899</v>
+        <v>28.5099</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7266</v>
+        <v>20.7343</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9393</v>
+        <v>17.9349</v>
       </c>
       <c r="D73" t="n">
-        <v>39.5395</v>
+        <v>39.4883</v>
       </c>
       <c r="E73" t="n">
-        <v>15.079</v>
+        <v>15.0705</v>
       </c>
       <c r="F73" t="n">
-        <v>28.3101</v>
+        <v>28.2461</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.167</v>
+        <v>20.1817</v>
       </c>
       <c r="C74" t="n">
-        <v>17.8701</v>
+        <v>17.8533</v>
       </c>
       <c r="D74" t="n">
-        <v>39.5706</v>
+        <v>39.9372</v>
       </c>
       <c r="E74" t="n">
-        <v>14.8014</v>
+        <v>14.7787</v>
       </c>
       <c r="F74" t="n">
-        <v>28.0153</v>
+        <v>27.9282</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6615</v>
+        <v>19.6671</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7555</v>
+        <v>17.7441</v>
       </c>
       <c r="D75" t="n">
-        <v>39.9424</v>
+        <v>39.8008</v>
       </c>
       <c r="E75" t="n">
-        <v>14.5298</v>
+        <v>14.4905</v>
       </c>
       <c r="F75" t="n">
-        <v>27.7905</v>
+        <v>27.6955</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1023</v>
+        <v>19.1302</v>
       </c>
       <c r="C76" t="n">
-        <v>17.6646</v>
+        <v>17.6906</v>
       </c>
       <c r="D76" t="n">
-        <v>40.0256</v>
+        <v>39.8426</v>
       </c>
       <c r="E76" t="n">
-        <v>14.2125</v>
+        <v>14.2178</v>
       </c>
       <c r="F76" t="n">
-        <v>27.4598</v>
+        <v>27.3719</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5195</v>
+        <v>18.5456</v>
       </c>
       <c r="C77" t="n">
-        <v>17.6074</v>
+        <v>17.6103</v>
       </c>
       <c r="D77" t="n">
-        <v>39.8523</v>
+        <v>39.7458</v>
       </c>
       <c r="E77" t="n">
-        <v>13.8939</v>
+        <v>13.8799</v>
       </c>
       <c r="F77" t="n">
-        <v>27.1589</v>
+        <v>27.0477</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9073</v>
+        <v>17.9552</v>
       </c>
       <c r="C78" t="n">
-        <v>17.4292</v>
+        <v>17.4419</v>
       </c>
       <c r="D78" t="n">
-        <v>46.7237</v>
+        <v>46.7417</v>
       </c>
       <c r="E78" t="n">
-        <v>18.3296</v>
+        <v>18.2783</v>
       </c>
       <c r="F78" t="n">
-        <v>31.0898</v>
+        <v>31.0073</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2118</v>
+        <v>17.2315</v>
       </c>
       <c r="C79" t="n">
-        <v>19.3649</v>
+        <v>19.2861</v>
       </c>
       <c r="D79" t="n">
-        <v>47.6454</v>
+        <v>47.7267</v>
       </c>
       <c r="E79" t="n">
-        <v>17.885</v>
+        <v>17.8436</v>
       </c>
       <c r="F79" t="n">
-        <v>30.7645</v>
+        <v>30.6981</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.42</v>
+        <v>16.4133</v>
       </c>
       <c r="C80" t="n">
-        <v>19.198</v>
+        <v>19.1247</v>
       </c>
       <c r="D80" t="n">
-        <v>47.9823</v>
+        <v>48.0222</v>
       </c>
       <c r="E80" t="n">
-        <v>17.3814</v>
+        <v>17.3402</v>
       </c>
       <c r="F80" t="n">
-        <v>30.4542</v>
+        <v>30.3642</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7758</v>
+        <v>23.7828</v>
       </c>
       <c r="C81" t="n">
-        <v>18.9291</v>
+        <v>18.9411</v>
       </c>
       <c r="D81" t="n">
-        <v>47.3889</v>
+        <v>47.34</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0036</v>
+        <v>17.0102</v>
       </c>
       <c r="F81" t="n">
-        <v>30.165</v>
+        <v>30.0286</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3889</v>
+        <v>23.3847</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7376</v>
+        <v>18.7364</v>
       </c>
       <c r="D82" t="n">
-        <v>45.1585</v>
+        <v>45.0326</v>
       </c>
       <c r="E82" t="n">
-        <v>16.7236</v>
+        <v>16.6682</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7657</v>
+        <v>29.709</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9295</v>
+        <v>22.9279</v>
       </c>
       <c r="C83" t="n">
-        <v>18.6122</v>
+        <v>18.5878</v>
       </c>
       <c r="D83" t="n">
-        <v>44.7682</v>
+        <v>44.6514</v>
       </c>
       <c r="E83" t="n">
-        <v>16.4083</v>
+        <v>16.396</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4952</v>
+        <v>29.4518</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4432</v>
+        <v>22.4326</v>
       </c>
       <c r="C84" t="n">
-        <v>18.4649</v>
+        <v>18.3987</v>
       </c>
       <c r="D84" t="n">
-        <v>44.3143</v>
+        <v>44.2928</v>
       </c>
       <c r="E84" t="n">
-        <v>16.0644</v>
+        <v>16.0407</v>
       </c>
       <c r="F84" t="n">
-        <v>29.1661</v>
+        <v>29.0994</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9155</v>
+        <v>21.9082</v>
       </c>
       <c r="C85" t="n">
-        <v>18.2438</v>
+        <v>18.2234</v>
       </c>
       <c r="D85" t="n">
-        <v>45.9455</v>
+        <v>45.9158</v>
       </c>
       <c r="E85" t="n">
-        <v>15.7936</v>
+        <v>15.7761</v>
       </c>
       <c r="F85" t="n">
-        <v>28.8853</v>
+        <v>28.8066</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.3981</v>
+        <v>21.4085</v>
       </c>
       <c r="C86" t="n">
-        <v>18.1004</v>
+        <v>18.0829</v>
       </c>
       <c r="D86" t="n">
-        <v>44.4811</v>
+        <v>44.4885</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4579</v>
+        <v>15.4736</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6308</v>
+        <v>28.5644</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.8975</v>
+        <v>20.8892</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9637</v>
+        <v>17.9747</v>
       </c>
       <c r="D87" t="n">
-        <v>44.1799</v>
+        <v>44.1446</v>
       </c>
       <c r="E87" t="n">
-        <v>15.2154</v>
+        <v>15.1963</v>
       </c>
       <c r="F87" t="n">
-        <v>28.3566</v>
+        <v>28.2891</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3549</v>
+        <v>20.3476</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8745</v>
+        <v>17.8495</v>
       </c>
       <c r="D88" t="n">
-        <v>43.8329</v>
+        <v>43.8086</v>
       </c>
       <c r="E88" t="n">
-        <v>14.9049</v>
+        <v>14.8944</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0301</v>
+        <v>27.9554</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8267</v>
+        <v>19.8309</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7552</v>
+        <v>17.7461</v>
       </c>
       <c r="D89" t="n">
-        <v>44.4254</v>
+        <v>44.3578</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6024</v>
+        <v>14.5884</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7409</v>
+        <v>27.6687</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2669</v>
+        <v>19.2953</v>
       </c>
       <c r="C90" t="n">
-        <v>17.712</v>
+        <v>17.6931</v>
       </c>
       <c r="D90" t="n">
-        <v>43.4227</v>
+        <v>43.3881</v>
       </c>
       <c r="E90" t="n">
-        <v>14.2927</v>
+        <v>14.2841</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4174</v>
+        <v>27.371</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7154</v>
+        <v>18.7228</v>
       </c>
       <c r="C91" t="n">
-        <v>17.5808</v>
+        <v>17.5711</v>
       </c>
       <c r="D91" t="n">
-        <v>43.0753</v>
+        <v>43.0975</v>
       </c>
       <c r="E91" t="n">
-        <v>13.998</v>
+        <v>14.0007</v>
       </c>
       <c r="F91" t="n">
-        <v>27.1102</v>
+        <v>27.0613</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1015</v>
+        <v>18.081</v>
       </c>
       <c r="C92" t="n">
-        <v>17.5186</v>
+        <v>17.4995</v>
       </c>
       <c r="D92" t="n">
-        <v>49.6804</v>
+        <v>49.5605</v>
       </c>
       <c r="E92" t="n">
-        <v>18.2687</v>
+        <v>18.2678</v>
       </c>
       <c r="F92" t="n">
-        <v>31.0265</v>
+        <v>31.1106</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.414</v>
+        <v>17.4179</v>
       </c>
       <c r="C93" t="n">
-        <v>17.4231</v>
+        <v>17.401</v>
       </c>
       <c r="D93" t="n">
-        <v>48.0327</v>
+        <v>48.0076</v>
       </c>
       <c r="E93" t="n">
-        <v>17.8502</v>
+        <v>17.8625</v>
       </c>
       <c r="F93" t="n">
-        <v>30.9673</v>
+        <v>30.8903</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6448</v>
+        <v>16.6267</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0247</v>
+        <v>19.0295</v>
       </c>
       <c r="D94" t="n">
-        <v>45.8295</v>
+        <v>45.8195</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4284</v>
+        <v>17.4508</v>
       </c>
       <c r="F94" t="n">
-        <v>30.6816</v>
+        <v>30.3251</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8671</v>
+        <v>23.8772</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8461</v>
+        <v>18.8324</v>
       </c>
       <c r="D95" t="n">
-        <v>45.341</v>
+        <v>45.0459</v>
       </c>
       <c r="E95" t="n">
-        <v>17.1042</v>
+        <v>17.1573</v>
       </c>
       <c r="F95" t="n">
-        <v>30.0737</v>
+        <v>29.8192</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4564</v>
+        <v>23.4693</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6529</v>
+        <v>18.6493</v>
       </c>
       <c r="D96" t="n">
-        <v>44.7112</v>
+        <v>44.4478</v>
       </c>
       <c r="E96" t="n">
-        <v>16.5722</v>
+        <v>16.6469</v>
       </c>
       <c r="F96" t="n">
-        <v>29.8774</v>
+        <v>29.6417</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0153</v>
+        <v>23.0254</v>
       </c>
       <c r="C97" t="n">
-        <v>18.5109</v>
+        <v>18.4869</v>
       </c>
       <c r="D97" t="n">
-        <v>47.0089</v>
+        <v>46.684</v>
       </c>
       <c r="E97" t="n">
-        <v>16.288</v>
+        <v>16.232</v>
       </c>
       <c r="F97" t="n">
-        <v>29.5893</v>
+        <v>29.2922</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5492</v>
+        <v>22.5567</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3445</v>
+        <v>18.3411</v>
       </c>
       <c r="D98" t="n">
-        <v>46.5551</v>
+        <v>46.0889</v>
       </c>
       <c r="E98" t="n">
-        <v>15.902</v>
+        <v>15.9078</v>
       </c>
       <c r="F98" t="n">
-        <v>29.2983</v>
+        <v>29.0454</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0323</v>
+        <v>22.0455</v>
       </c>
       <c r="C99" t="n">
-        <v>18.1968</v>
+        <v>18.2037</v>
       </c>
       <c r="D99" t="n">
-        <v>45.7532</v>
+        <v>45.4665</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6013</v>
+        <v>15.6182</v>
       </c>
       <c r="F99" t="n">
-        <v>28.9852</v>
+        <v>28.7235</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5077</v>
+        <v>21.5134</v>
       </c>
       <c r="C100" t="n">
-        <v>18.1701</v>
+        <v>18.1696</v>
       </c>
       <c r="D100" t="n">
-        <v>42.9964</v>
+        <v>42.8337</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3246</v>
+        <v>15.393</v>
       </c>
       <c r="F100" t="n">
-        <v>28.6652</v>
+        <v>28.4286</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9832</v>
+        <v>20.9805</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0474</v>
+        <v>18.0529</v>
       </c>
       <c r="D101" t="n">
-        <v>42.5707</v>
+        <v>42.5781</v>
       </c>
       <c r="E101" t="n">
-        <v>15.1261</v>
+        <v>15.126</v>
       </c>
       <c r="F101" t="n">
-        <v>28.0955</v>
+        <v>28.1136</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4582</v>
+        <v>20.4543</v>
       </c>
       <c r="C102" t="n">
-        <v>17.9457</v>
+        <v>17.944</v>
       </c>
       <c r="D102" t="n">
-        <v>41.7363</v>
+        <v>41.7578</v>
       </c>
       <c r="E102" t="n">
-        <v>14.7698</v>
+        <v>14.7581</v>
       </c>
       <c r="F102" t="n">
-        <v>27.8359</v>
+        <v>27.8203</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9125</v>
+        <v>19.8969</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8475</v>
+        <v>17.8411</v>
       </c>
       <c r="D103" t="n">
-        <v>41.8178</v>
+        <v>41.8549</v>
       </c>
       <c r="E103" t="n">
-        <v>14.49</v>
+        <v>14.4793</v>
       </c>
       <c r="F103" t="n">
-        <v>27.5277</v>
+        <v>27.5349</v>
       </c>
     </row>
     <row r="104">
@@ -7122,16 +7122,16 @@
         <v>19.4119</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7369</v>
+        <v>17.7626</v>
       </c>
       <c r="D104" t="n">
-        <v>40.9953</v>
+        <v>41.0205</v>
       </c>
       <c r="E104" t="n">
-        <v>14.218</v>
+        <v>14.1996</v>
       </c>
       <c r="F104" t="n">
-        <v>27.2399</v>
+        <v>27.238</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8338</v>
+        <v>18.8196</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6528</v>
+        <v>17.6558</v>
       </c>
       <c r="D105" t="n">
-        <v>41.1431</v>
+        <v>41.1273</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9233</v>
+        <v>13.9455</v>
       </c>
       <c r="F105" t="n">
-        <v>26.9071</v>
+        <v>26.9124</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2346</v>
+        <v>18.2399</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5748</v>
+        <v>17.5767</v>
       </c>
       <c r="D106" t="n">
-        <v>40.4232</v>
+        <v>40.4279</v>
       </c>
       <c r="E106" t="n">
-        <v>13.6114</v>
+        <v>13.6281</v>
       </c>
       <c r="F106" t="n">
-        <v>26.6245</v>
+        <v>26.6158</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6222</v>
+        <v>17.6404</v>
       </c>
       <c r="C107" t="n">
-        <v>17.5053</v>
+        <v>17.5049</v>
       </c>
       <c r="D107" t="n">
-        <v>45.7088</v>
+        <v>45.7683</v>
       </c>
       <c r="E107" t="n">
-        <v>17.8178</v>
+        <v>17.7667</v>
       </c>
       <c r="F107" t="n">
-        <v>30.6856</v>
+        <v>30.6416</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8775</v>
+        <v>16.8766</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1473</v>
+        <v>19.1408</v>
       </c>
       <c r="D108" t="n">
-        <v>46.5589</v>
+        <v>46.7578</v>
       </c>
       <c r="E108" t="n">
-        <v>17.388</v>
+        <v>17.4663</v>
       </c>
       <c r="F108" t="n">
-        <v>30.2987</v>
+        <v>30.2958</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9255</v>
+        <v>15.9478</v>
       </c>
       <c r="C109" t="n">
-        <v>18.963</v>
+        <v>18.9586</v>
       </c>
       <c r="D109" t="n">
-        <v>45.9662</v>
+        <v>45.9888</v>
       </c>
       <c r="E109" t="n">
-        <v>17.0497</v>
+        <v>16.974</v>
       </c>
       <c r="F109" t="n">
-        <v>29.9708</v>
+        <v>29.9763</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5582</v>
+        <v>23.6009</v>
       </c>
       <c r="C110" t="n">
-        <v>18.6876</v>
+        <v>18.6892</v>
       </c>
       <c r="D110" t="n">
-        <v>45.3993</v>
+        <v>45.3765</v>
       </c>
       <c r="E110" t="n">
-        <v>16.8111</v>
+        <v>16.8109</v>
       </c>
       <c r="F110" t="n">
-        <v>29.6378</v>
+        <v>29.6376</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1266</v>
+        <v>23.1292</v>
       </c>
       <c r="C111" t="n">
-        <v>18.542</v>
+        <v>18.5541</v>
       </c>
       <c r="D111" t="n">
-        <v>44.7651</v>
+        <v>44.867</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4893</v>
+        <v>16.4874</v>
       </c>
       <c r="F111" t="n">
-        <v>29.3526</v>
+        <v>29.3215</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6546</v>
+        <v>22.658</v>
       </c>
       <c r="C112" t="n">
-        <v>18.3799</v>
+        <v>18.3783</v>
       </c>
       <c r="D112" t="n">
-        <v>41.4645</v>
+        <v>41.4846</v>
       </c>
       <c r="E112" t="n">
-        <v>16.2049</v>
+        <v>16.1767</v>
       </c>
       <c r="F112" t="n">
-        <v>29.0204</v>
+        <v>29.017</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1453</v>
+        <v>22.1487</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2298</v>
+        <v>18.2378</v>
       </c>
       <c r="D113" t="n">
-        <v>41.004</v>
+        <v>41.0171</v>
       </c>
       <c r="E113" t="n">
-        <v>15.8412</v>
+        <v>15.8664</v>
       </c>
       <c r="F113" t="n">
-        <v>28.7306</v>
+        <v>28.7454</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6361</v>
+        <v>21.6365</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1297</v>
+        <v>18.1547</v>
       </c>
       <c r="D114" t="n">
-        <v>43.1371</v>
+        <v>43.1354</v>
       </c>
       <c r="E114" t="n">
-        <v>15.6099</v>
+        <v>15.6129</v>
       </c>
       <c r="F114" t="n">
-        <v>28.4072</v>
+        <v>28.458</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.1006</v>
+        <v>21.105</v>
       </c>
       <c r="C115" t="n">
-        <v>17.9755</v>
+        <v>17.9952</v>
       </c>
       <c r="D115" t="n">
-        <v>42.8362</v>
+        <v>42.793</v>
       </c>
       <c r="E115" t="n">
-        <v>15.4211</v>
+        <v>15.3233</v>
       </c>
       <c r="F115" t="n">
-        <v>28.0992</v>
+        <v>28.1557</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5979</v>
+        <v>20.5692</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8379</v>
+        <v>17.8791</v>
       </c>
       <c r="D116" t="n">
-        <v>42.4281</v>
+        <v>42.412</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8585</v>
+        <v>14.8201</v>
       </c>
       <c r="F116" t="n">
-        <v>27.9186</v>
+        <v>27.9177</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.1129</v>
+        <v>20.0324</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7437</v>
+        <v>17.7688</v>
       </c>
       <c r="D117" t="n">
-        <v>42.0934</v>
+        <v>42.0999</v>
       </c>
       <c r="E117" t="n">
-        <v>14.6246</v>
+        <v>14.5548</v>
       </c>
       <c r="F117" t="n">
-        <v>27.6071</v>
+        <v>27.5763</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5109</v>
+        <v>19.5043</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6533</v>
+        <v>17.6682</v>
       </c>
       <c r="D118" t="n">
-        <v>41.7169</v>
+        <v>41.7121</v>
       </c>
       <c r="E118" t="n">
-        <v>14.2901</v>
+        <v>14.283</v>
       </c>
       <c r="F118" t="n">
-        <v>27.2813</v>
+        <v>27.3017</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9502</v>
+        <v>18.9508</v>
       </c>
       <c r="C119" t="n">
-        <v>17.5866</v>
+        <v>17.6015</v>
       </c>
       <c r="D119" t="n">
-        <v>41.4212</v>
+        <v>41.4176</v>
       </c>
       <c r="E119" t="n">
-        <v>14.0052</v>
+        <v>14.0115</v>
       </c>
       <c r="F119" t="n">
-        <v>26.9772</v>
+        <v>26.9983</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3911</v>
+        <v>18.3832</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5186</v>
+        <v>17.5153</v>
       </c>
       <c r="D120" t="n">
-        <v>41.1219</v>
+        <v>41.104</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7241</v>
+        <v>13.7254</v>
       </c>
       <c r="F120" t="n">
-        <v>26.6851</v>
+        <v>26.6842</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7357</v>
+        <v>17.7291</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4416</v>
+        <v>17.4395</v>
       </c>
       <c r="D121" t="n">
-        <v>48.7245</v>
+        <v>48.6973</v>
       </c>
       <c r="E121" t="n">
-        <v>18.0651</v>
+        <v>18.0788</v>
       </c>
       <c r="F121" t="n">
-        <v>30.6605</v>
+        <v>30.6094</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.0272</v>
+        <v>17.0244</v>
       </c>
       <c r="C122" t="n">
-        <v>19.1737</v>
+        <v>19.1389</v>
       </c>
       <c r="D122" t="n">
-        <v>46.5575</v>
+        <v>48.309</v>
       </c>
       <c r="E122" t="n">
-        <v>17.491</v>
+        <v>17.4286</v>
       </c>
       <c r="F122" t="n">
-        <v>30.354</v>
+        <v>30.339</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.0926</v>
+        <v>16.0989</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9674</v>
+        <v>18.9338</v>
       </c>
       <c r="D123" t="n">
-        <v>47.1835</v>
+        <v>49.2294</v>
       </c>
       <c r="E123" t="n">
-        <v>17.1992</v>
+        <v>17.1714</v>
       </c>
       <c r="F123" t="n">
-        <v>29.9911</v>
+        <v>30.0283</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6682</v>
+        <v>23.6384</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7501</v>
+        <v>18.7559</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9598</v>
+        <v>45.3756</v>
       </c>
       <c r="E124" t="n">
-        <v>16.8824</v>
+        <v>16.8583</v>
       </c>
       <c r="F124" t="n">
-        <v>29.6607</v>
+        <v>29.6951</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2205</v>
+        <v>23.2131</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5942</v>
+        <v>18.5761</v>
       </c>
       <c r="D125" t="n">
-        <v>43.7218</v>
+        <v>45.1637</v>
       </c>
       <c r="E125" t="n">
-        <v>16.5372</v>
+        <v>16.5641</v>
       </c>
       <c r="F125" t="n">
-        <v>29.3465</v>
+        <v>29.3909</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7564</v>
+        <v>22.7493</v>
       </c>
       <c r="C126" t="n">
-        <v>18.4197</v>
+        <v>18.4199</v>
       </c>
       <c r="D126" t="n">
-        <v>45.2439</v>
+        <v>46.908</v>
       </c>
       <c r="E126" t="n">
-        <v>16.2338</v>
+        <v>16.2244</v>
       </c>
       <c r="F126" t="n">
-        <v>29.068</v>
+        <v>29.0406</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2592</v>
+        <v>22.247</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2703</v>
+        <v>18.2728</v>
       </c>
       <c r="D127" t="n">
-        <v>44.6153</v>
+        <v>46.229</v>
       </c>
       <c r="E127" t="n">
-        <v>15.9174</v>
+        <v>15.8943</v>
       </c>
       <c r="F127" t="n">
-        <v>28.7807</v>
+        <v>28.7548</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7663</v>
+        <v>21.7779</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1769</v>
+        <v>18.1655</v>
       </c>
       <c r="D128" t="n">
-        <v>42.384</v>
+        <v>43.6235</v>
       </c>
       <c r="E128" t="n">
-        <v>15.6219</v>
+        <v>15.6203</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4684</v>
+        <v>28.4895</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.2049</v>
+        <v>21.2156</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0212</v>
+        <v>18.0227</v>
       </c>
       <c r="D129" t="n">
-        <v>41.924</v>
+        <v>42.9976</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3987</v>
+        <v>15.3984</v>
       </c>
       <c r="F129" t="n">
-        <v>28.1817</v>
+        <v>28.2244</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6638</v>
+        <v>20.6731</v>
       </c>
       <c r="C130" t="n">
-        <v>17.9016</v>
+        <v>17.905</v>
       </c>
       <c r="D130" t="n">
-        <v>41.543</v>
+        <v>42.4994</v>
       </c>
       <c r="E130" t="n">
-        <v>14.8853</v>
+        <v>14.888</v>
       </c>
       <c r="F130" t="n">
-        <v>27.9515</v>
+        <v>27.9682</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1446</v>
+        <v>20.1585</v>
       </c>
       <c r="C131" t="n">
-        <v>17.8045</v>
+        <v>17.7988</v>
       </c>
       <c r="D131" t="n">
-        <v>41.0228</v>
+        <v>41.9077</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6144</v>
+        <v>14.6093</v>
       </c>
       <c r="F131" t="n">
-        <v>27.6696</v>
+        <v>27.699</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6191</v>
+        <v>19.619</v>
       </c>
       <c r="C132" t="n">
-        <v>17.7049</v>
+        <v>17.6868</v>
       </c>
       <c r="D132" t="n">
-        <v>40.6407</v>
+        <v>41.4875</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3467</v>
+        <v>14.3393</v>
       </c>
       <c r="F132" t="n">
-        <v>27.3896</v>
+        <v>27.3916</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0798</v>
+        <v>19.0658</v>
       </c>
       <c r="C133" t="n">
-        <v>17.638</v>
+        <v>17.6194</v>
       </c>
       <c r="D133" t="n">
-        <v>40.3497</v>
+        <v>41.132</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0788</v>
+        <v>14.0657</v>
       </c>
       <c r="F133" t="n">
-        <v>27.0953</v>
+        <v>27.1081</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5462</v>
+        <v>18.528</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5507</v>
+        <v>17.5563</v>
       </c>
       <c r="D134" t="n">
-        <v>40.0533</v>
+        <v>40.7941</v>
       </c>
       <c r="E134" t="n">
-        <v>13.8477</v>
+        <v>13.7868</v>
       </c>
       <c r="F134" t="n">
-        <v>26.7605</v>
+        <v>26.7827</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8806</v>
+        <v>17.8946</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4875</v>
+        <v>17.4592</v>
       </c>
       <c r="D135" t="n">
-        <v>47.4141</v>
+        <v>49.2886</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8706</v>
+        <v>17.8557</v>
       </c>
       <c r="F135" t="n">
-        <v>30.8289</v>
+        <v>30.794</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.1856</v>
+        <v>17.2226</v>
       </c>
       <c r="C136" t="n">
-        <v>19.1972</v>
+        <v>19.2062</v>
       </c>
       <c r="D136" t="n">
-        <v>46.4054</v>
+        <v>48.1486</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6435</v>
+        <v>17.6419</v>
       </c>
       <c r="F136" t="n">
-        <v>30.3568</v>
+        <v>30.3498</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.3149</v>
+        <v>16.3486</v>
       </c>
       <c r="C137" t="n">
-        <v>18.9896</v>
+        <v>19.0043</v>
       </c>
       <c r="D137" t="n">
-        <v>45.2252</v>
+        <v>46.6447</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1051</v>
+        <v>17.1205</v>
       </c>
       <c r="F137" t="n">
-        <v>30.1236</v>
+        <v>30.217</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7289</v>
+        <v>23.7405</v>
       </c>
       <c r="C138" t="n">
-        <v>18.7692</v>
+        <v>18.7972</v>
       </c>
       <c r="D138" t="n">
-        <v>46.9229</v>
+        <v>48.9668</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7639</v>
+        <v>16.776</v>
       </c>
       <c r="F138" t="n">
-        <v>29.8104</v>
+        <v>29.7864</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3146</v>
+        <v>23.3213</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6487</v>
+        <v>18.667</v>
       </c>
       <c r="D139" t="n">
-        <v>44.3516</v>
+        <v>45.7267</v>
       </c>
       <c r="E139" t="n">
-        <v>16.5771</v>
+        <v>16.5962</v>
       </c>
       <c r="F139" t="n">
-        <v>29.448</v>
+        <v>29.4066</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8571</v>
+        <v>22.8529</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4697</v>
+        <v>18.4825</v>
       </c>
       <c r="D140" t="n">
-        <v>43.6696</v>
+        <v>45.2443</v>
       </c>
       <c r="E140" t="n">
-        <v>16.2783</v>
+        <v>16.3236</v>
       </c>
       <c r="F140" t="n">
-        <v>29.1479</v>
+        <v>29.104</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3683</v>
+        <v>22.3655</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3313</v>
+        <v>18.3417</v>
       </c>
       <c r="D141" t="n">
-        <v>43.0745</v>
+        <v>44.3373</v>
       </c>
       <c r="E141" t="n">
-        <v>15.942</v>
+        <v>15.954</v>
       </c>
       <c r="F141" t="n">
-        <v>28.8705</v>
+        <v>28.8106</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8536</v>
+        <v>21.8482</v>
       </c>
       <c r="C142" t="n">
-        <v>18.1762</v>
+        <v>18.2061</v>
       </c>
       <c r="D142" t="n">
-        <v>44.3774</v>
+        <v>45.8939</v>
       </c>
       <c r="E142" t="n">
-        <v>15.5123</v>
+        <v>15.5094</v>
       </c>
       <c r="F142" t="n">
-        <v>28.6869</v>
+        <v>28.5853</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.3171</v>
+        <v>21.312</v>
       </c>
       <c r="C143" t="n">
-        <v>18.072</v>
+        <v>18.0926</v>
       </c>
       <c r="D143" t="n">
-        <v>43.5866</v>
+        <v>45.1059</v>
       </c>
       <c r="E143" t="n">
-        <v>15.209</v>
+        <v>15.1985</v>
       </c>
       <c r="F143" t="n">
-        <v>28.3238</v>
+        <v>28.3248</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.8661</v>
+        <v>19.1163</v>
       </c>
       <c r="C2" t="n">
-        <v>14.1954</v>
+        <v>14.1003</v>
       </c>
       <c r="D2" t="n">
-        <v>32.011</v>
+        <v>31.9521</v>
       </c>
       <c r="E2" t="n">
-        <v>6.99797</v>
+        <v>7.43183</v>
       </c>
       <c r="F2" t="n">
-        <v>26.6541</v>
+        <v>26.3458</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.3606</v>
+        <v>18.4072</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5143</v>
+        <v>14.4666</v>
       </c>
       <c r="D3" t="n">
-        <v>32.0463</v>
+        <v>31.8255</v>
       </c>
       <c r="E3" t="n">
-        <v>6.54558</v>
+        <v>7.22235</v>
       </c>
       <c r="F3" t="n">
-        <v>26.5407</v>
+        <v>26.3288</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.095</v>
+        <v>18.1406</v>
       </c>
       <c r="C4" t="n">
-        <v>14.8006</v>
+        <v>14.8738</v>
       </c>
       <c r="D4" t="n">
-        <v>32.1795</v>
+        <v>31.9122</v>
       </c>
       <c r="E4" t="n">
-        <v>6.57812</v>
+        <v>6.44799</v>
       </c>
       <c r="F4" t="n">
-        <v>26.2633</v>
+        <v>25.9945</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.4476</v>
+        <v>17.5169</v>
       </c>
       <c r="C5" t="n">
-        <v>14.809</v>
+        <v>14.8375</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4777</v>
+        <v>32.4158</v>
       </c>
       <c r="E5" t="n">
-        <v>6.11772</v>
+        <v>6.1328</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2808</v>
+        <v>26.2969</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.1553</v>
+        <v>17.101</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1111</v>
+        <v>15.0656</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4513</v>
+        <v>32.2127</v>
       </c>
       <c r="E6" t="n">
-        <v>6.25043</v>
+        <v>5.5858</v>
       </c>
       <c r="F6" t="n">
-        <v>25.9809</v>
+        <v>25.996</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.4488</v>
+        <v>16.3711</v>
       </c>
       <c r="C7" t="n">
-        <v>15.3217</v>
+        <v>15.4534</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8698</v>
+        <v>31.5184</v>
       </c>
       <c r="E7" t="n">
-        <v>15.8202</v>
+        <v>15.6474</v>
       </c>
       <c r="F7" t="n">
-        <v>30.1084</v>
+        <v>30.0785</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.8381</v>
+        <v>15.7546</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9474</v>
+        <v>16.9174</v>
       </c>
       <c r="D8" t="n">
-        <v>31.9378</v>
+        <v>31.7899</v>
       </c>
       <c r="E8" t="n">
-        <v>15.5379</v>
+        <v>15.1322</v>
       </c>
       <c r="F8" t="n">
-        <v>29.7721</v>
+        <v>29.6923</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.0049</v>
+        <v>14.8939</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0992</v>
+        <v>17.0685</v>
       </c>
       <c r="D9" t="n">
-        <v>31.9702</v>
+        <v>31.7764</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0038</v>
+        <v>14.888</v>
       </c>
       <c r="F9" t="n">
-        <v>29.7431</v>
+        <v>29.4002</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.9663</v>
+        <v>22.84</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1038</v>
+        <v>17.1704</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9271</v>
+        <v>31.605</v>
       </c>
       <c r="E10" t="n">
-        <v>14.707</v>
+        <v>14.5681</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1447</v>
+        <v>29.1738</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.4116</v>
+        <v>22.3919</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1431</v>
+        <v>17.1805</v>
       </c>
       <c r="D11" t="n">
-        <v>32.0944</v>
+        <v>31.8926</v>
       </c>
       <c r="E11" t="n">
-        <v>14.463</v>
+        <v>14.2063</v>
       </c>
       <c r="F11" t="n">
-        <v>29.18</v>
+        <v>28.8803</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.9573</v>
+        <v>22.0227</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0406</v>
+        <v>17.1017</v>
       </c>
       <c r="D12" t="n">
-        <v>32.0588</v>
+        <v>31.801</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1904</v>
+        <v>14.2259</v>
       </c>
       <c r="F12" t="n">
-        <v>28.8934</v>
+        <v>28.7004</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5735</v>
+        <v>21.5558</v>
       </c>
       <c r="C13" t="n">
-        <v>17.22</v>
+        <v>17.2506</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2589</v>
+        <v>32.0097</v>
       </c>
       <c r="E13" t="n">
-        <v>13.9721</v>
+        <v>14.0122</v>
       </c>
       <c r="F13" t="n">
-        <v>29.0215</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.1146</v>
+        <v>21.1921</v>
       </c>
       <c r="C14" t="n">
-        <v>17.2033</v>
+        <v>17.2184</v>
       </c>
       <c r="D14" t="n">
-        <v>32.4966</v>
+        <v>32.0605</v>
       </c>
       <c r="E14" t="n">
-        <v>13.6421</v>
+        <v>13.5045</v>
       </c>
       <c r="F14" t="n">
-        <v>28.5204</v>
+        <v>28.4351</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.711</v>
+        <v>20.7962</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2815</v>
+        <v>17.2937</v>
       </c>
       <c r="D15" t="n">
-        <v>32.3675</v>
+        <v>32.2384</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5142</v>
+        <v>13.1983</v>
       </c>
       <c r="F15" t="n">
-        <v>28.1822</v>
+        <v>27.7495</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.2019</v>
+        <v>20.1749</v>
       </c>
       <c r="C16" t="n">
-        <v>17.2323</v>
+        <v>17.2304</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5755</v>
+        <v>32.4615</v>
       </c>
       <c r="E16" t="n">
-        <v>13.2796</v>
+        <v>12.9821</v>
       </c>
       <c r="F16" t="n">
-        <v>27.7436</v>
+        <v>27.6133</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.5504</v>
+        <v>19.5247</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1824</v>
+        <v>17.2274</v>
       </c>
       <c r="D17" t="n">
-        <v>32.6787</v>
+        <v>32.4016</v>
       </c>
       <c r="E17" t="n">
-        <v>13.1215</v>
+        <v>12.7854</v>
       </c>
       <c r="F17" t="n">
-        <v>27.5376</v>
+        <v>27.2651</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.1295</v>
+        <v>19.1419</v>
       </c>
       <c r="C18" t="n">
-        <v>17.1818</v>
+        <v>17.2105</v>
       </c>
       <c r="D18" t="n">
-        <v>32.9981</v>
+        <v>32.6726</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9423</v>
+        <v>12.5863</v>
       </c>
       <c r="F18" t="n">
-        <v>27.1441</v>
+        <v>26.9324</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.5892</v>
+        <v>18.6258</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1628</v>
+        <v>17.1686</v>
       </c>
       <c r="D19" t="n">
-        <v>33.0487</v>
+        <v>32.8424</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6182</v>
+        <v>12.2758</v>
       </c>
       <c r="F19" t="n">
-        <v>26.8441</v>
+        <v>26.592</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.074</v>
+        <v>18.0393</v>
       </c>
       <c r="C20" t="n">
-        <v>17.2797</v>
+        <v>17.3062</v>
       </c>
       <c r="D20" t="n">
-        <v>33.1079</v>
+        <v>32.8574</v>
       </c>
       <c r="E20" t="n">
-        <v>12.425</v>
+        <v>12.2167</v>
       </c>
       <c r="F20" t="n">
-        <v>26.5423</v>
+        <v>26.3529</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.3865</v>
+        <v>17.4675</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1479</v>
+        <v>17.1395</v>
       </c>
       <c r="D21" t="n">
-        <v>32.5394</v>
+        <v>32.4108</v>
       </c>
       <c r="E21" t="n">
-        <v>17.644</v>
+        <v>17.6487</v>
       </c>
       <c r="F21" t="n">
-        <v>30.6504</v>
+        <v>30.4514</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7293</v>
+        <v>16.7462</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7203</v>
+        <v>18.7351</v>
       </c>
       <c r="D22" t="n">
-        <v>32.4115</v>
+        <v>32.2181</v>
       </c>
       <c r="E22" t="n">
-        <v>17.1461</v>
+        <v>16.9407</v>
       </c>
       <c r="F22" t="n">
-        <v>30.4593</v>
+        <v>30.2564</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0329</v>
+        <v>16.0349</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5799</v>
+        <v>18.593</v>
       </c>
       <c r="D23" t="n">
-        <v>32.4344</v>
+        <v>32.1812</v>
       </c>
       <c r="E23" t="n">
-        <v>16.7353</v>
+        <v>16.5281</v>
       </c>
       <c r="F23" t="n">
-        <v>30.2649</v>
+        <v>30.0545</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.3801</v>
+        <v>23.4514</v>
       </c>
       <c r="C24" t="n">
-        <v>18.4623</v>
+        <v>18.4079</v>
       </c>
       <c r="D24" t="n">
-        <v>32.2564</v>
+        <v>32.0987</v>
       </c>
       <c r="E24" t="n">
-        <v>16.256</v>
+        <v>16.1749</v>
       </c>
       <c r="F24" t="n">
-        <v>30.0786</v>
+        <v>29.8348</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.8971</v>
+        <v>22.9323</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3836</v>
+        <v>18.3503</v>
       </c>
       <c r="D25" t="n">
-        <v>32.8327</v>
+        <v>32.5587</v>
       </c>
       <c r="E25" t="n">
-        <v>15.75</v>
+        <v>15.7744</v>
       </c>
       <c r="F25" t="n">
-        <v>29.7665</v>
+        <v>29.5464</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.4759</v>
+        <v>22.4794</v>
       </c>
       <c r="C26" t="n">
-        <v>18.3243</v>
+        <v>18.2674</v>
       </c>
       <c r="D26" t="n">
-        <v>32.8275</v>
+        <v>32.567</v>
       </c>
       <c r="E26" t="n">
-        <v>15.428</v>
+        <v>15.3441</v>
       </c>
       <c r="F26" t="n">
-        <v>29.3691</v>
+        <v>29.208</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.9524</v>
+        <v>21.9871</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1519</v>
+        <v>18.1527</v>
       </c>
       <c r="D27" t="n">
-        <v>32.8293</v>
+        <v>32.5764</v>
       </c>
       <c r="E27" t="n">
-        <v>15.2545</v>
+        <v>15.1533</v>
       </c>
       <c r="F27" t="n">
-        <v>29.0024</v>
+        <v>28.915</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.535</v>
+        <v>21.5604</v>
       </c>
       <c r="C28" t="n">
-        <v>18.0404</v>
+        <v>17.9939</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7568</v>
+        <v>32.5721</v>
       </c>
       <c r="E28" t="n">
-        <v>14.8282</v>
+        <v>14.7932</v>
       </c>
       <c r="F28" t="n">
-        <v>28.9506</v>
+        <v>28.6669</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.053</v>
+        <v>21.0496</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9738</v>
+        <v>18.0227</v>
       </c>
       <c r="D29" t="n">
-        <v>32.8388</v>
+        <v>32.6156</v>
       </c>
       <c r="E29" t="n">
-        <v>14.563</v>
+        <v>14.5844</v>
       </c>
       <c r="F29" t="n">
-        <v>28.3962</v>
+        <v>28.332</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6706</v>
+        <v>20.6191</v>
       </c>
       <c r="C30" t="n">
-        <v>17.9023</v>
+        <v>17.9393</v>
       </c>
       <c r="D30" t="n">
-        <v>33.1283</v>
+        <v>32.8855</v>
       </c>
       <c r="E30" t="n">
-        <v>14.21</v>
+        <v>14.2259</v>
       </c>
       <c r="F30" t="n">
-        <v>28.2121</v>
+        <v>28.0841</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0947</v>
+        <v>20.076</v>
       </c>
       <c r="C31" t="n">
-        <v>17.8261</v>
+        <v>17.787</v>
       </c>
       <c r="D31" t="n">
-        <v>33.0241</v>
+        <v>32.826</v>
       </c>
       <c r="E31" t="n">
-        <v>13.9753</v>
+        <v>13.9387</v>
       </c>
       <c r="F31" t="n">
-        <v>27.9168</v>
+        <v>27.6898</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6718</v>
+        <v>19.6693</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7015</v>
+        <v>17.7472</v>
       </c>
       <c r="D32" t="n">
-        <v>33.1225</v>
+        <v>32.9751</v>
       </c>
       <c r="E32" t="n">
-        <v>13.709</v>
+        <v>13.7013</v>
       </c>
       <c r="F32" t="n">
-        <v>27.5234</v>
+        <v>27.3436</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0628</v>
+        <v>19.0571</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6372</v>
+        <v>17.6592</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3702</v>
+        <v>32.9509</v>
       </c>
       <c r="E33" t="n">
-        <v>13.6704</v>
+        <v>13.7078</v>
       </c>
       <c r="F33" t="n">
-        <v>27.2431</v>
+        <v>26.8891</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4815</v>
+        <v>18.4868</v>
       </c>
       <c r="C34" t="n">
-        <v>17.536</v>
+        <v>17.5711</v>
       </c>
       <c r="D34" t="n">
-        <v>33.4654</v>
+        <v>33.0081</v>
       </c>
       <c r="E34" t="n">
-        <v>13.3961</v>
+        <v>13.4087</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9688</v>
+        <v>26.6695</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9216</v>
+        <v>17.9331</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4928</v>
+        <v>17.5119</v>
       </c>
       <c r="D35" t="n">
-        <v>32.8509</v>
+        <v>32.6011</v>
       </c>
       <c r="E35" t="n">
-        <v>18.0692</v>
+        <v>18.0322</v>
       </c>
       <c r="F35" t="n">
-        <v>31.199</v>
+        <v>30.9755</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2735</v>
+        <v>17.2845</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4425</v>
+        <v>17.4343</v>
       </c>
       <c r="D36" t="n">
-        <v>32.6038</v>
+        <v>32.487</v>
       </c>
       <c r="E36" t="n">
-        <v>17.6385</v>
+        <v>17.4533</v>
       </c>
       <c r="F36" t="n">
-        <v>30.7413</v>
+        <v>30.4256</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.4799</v>
+        <v>16.6013</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8275</v>
+        <v>18.8536</v>
       </c>
       <c r="D37" t="n">
-        <v>32.8662</v>
+        <v>32.3068</v>
       </c>
       <c r="E37" t="n">
-        <v>17.1493</v>
+        <v>17.0297</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3641</v>
+        <v>30.1627</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.7074</v>
+        <v>23.6872</v>
       </c>
       <c r="C38" t="n">
-        <v>18.7304</v>
+        <v>18.7336</v>
       </c>
       <c r="D38" t="n">
-        <v>32.5162</v>
+        <v>32.2595</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7866</v>
+        <v>16.6959</v>
       </c>
       <c r="F38" t="n">
-        <v>30.0508</v>
+        <v>29.7872</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.342</v>
+        <v>23.3482</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5283</v>
+        <v>18.5234</v>
       </c>
       <c r="D39" t="n">
-        <v>32.4975</v>
+        <v>32.3401</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4383</v>
+        <v>16.3052</v>
       </c>
       <c r="F39" t="n">
-        <v>29.6307</v>
+        <v>29.4591</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.9252</v>
+        <v>22.946</v>
       </c>
       <c r="C40" t="n">
-        <v>18.385</v>
+        <v>18.3877</v>
       </c>
       <c r="D40" t="n">
-        <v>32.9019</v>
+        <v>32.6649</v>
       </c>
       <c r="E40" t="n">
-        <v>16.14</v>
+        <v>16.0288</v>
       </c>
       <c r="F40" t="n">
-        <v>29.3239</v>
+        <v>29.0953</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4501</v>
+        <v>22.4779</v>
       </c>
       <c r="C41" t="n">
-        <v>18.3062</v>
+        <v>18.2451</v>
       </c>
       <c r="D41" t="n">
-        <v>33.0347</v>
+        <v>32.6846</v>
       </c>
       <c r="E41" t="n">
-        <v>15.8666</v>
+        <v>15.7167</v>
       </c>
       <c r="F41" t="n">
-        <v>29.0641</v>
+        <v>28.9182</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.961</v>
+        <v>21.9662</v>
       </c>
       <c r="C42" t="n">
-        <v>18.1299</v>
+        <v>18.1089</v>
       </c>
       <c r="D42" t="n">
-        <v>33.0811</v>
+        <v>32.8461</v>
       </c>
       <c r="E42" t="n">
-        <v>15.5211</v>
+        <v>15.4384</v>
       </c>
       <c r="F42" t="n">
-        <v>28.8012</v>
+        <v>28.654</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4409</v>
+        <v>21.4506</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9916</v>
+        <v>17.9789</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8209</v>
+        <v>32.621</v>
       </c>
       <c r="E43" t="n">
-        <v>15.2165</v>
+        <v>15.1066</v>
       </c>
       <c r="F43" t="n">
-        <v>28.4982</v>
+        <v>28.3129</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.8922</v>
+        <v>20.9092</v>
       </c>
       <c r="C44" t="n">
-        <v>17.8789</v>
+        <v>17.9311</v>
       </c>
       <c r="D44" t="n">
-        <v>32.8015</v>
+        <v>32.5732</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9412</v>
+        <v>14.8683</v>
       </c>
       <c r="F44" t="n">
-        <v>28.2508</v>
+        <v>28.0693</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4366</v>
+        <v>20.4545</v>
       </c>
       <c r="C45" t="n">
-        <v>17.7812</v>
+        <v>17.8362</v>
       </c>
       <c r="D45" t="n">
-        <v>32.8469</v>
+        <v>32.6894</v>
       </c>
       <c r="E45" t="n">
-        <v>14.5707</v>
+        <v>14.5277</v>
       </c>
       <c r="F45" t="n">
-        <v>27.9257</v>
+        <v>27.7297</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9122</v>
+        <v>19.9474</v>
       </c>
       <c r="C46" t="n">
-        <v>17.7111</v>
+        <v>17.7304</v>
       </c>
       <c r="D46" t="n">
-        <v>33.0686</v>
+        <v>32.9184</v>
       </c>
       <c r="E46" t="n">
-        <v>14.2953</v>
+        <v>14.2379</v>
       </c>
       <c r="F46" t="n">
-        <v>27.709</v>
+        <v>27.5113</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3767</v>
+        <v>19.3843</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5794</v>
+        <v>17.6005</v>
       </c>
       <c r="D47" t="n">
-        <v>33.1107</v>
+        <v>32.9516</v>
       </c>
       <c r="E47" t="n">
-        <v>14.0037</v>
+        <v>13.943</v>
       </c>
       <c r="F47" t="n">
-        <v>27.3479</v>
+        <v>27.1085</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8018</v>
+        <v>18.7903</v>
       </c>
       <c r="C48" t="n">
-        <v>17.5254</v>
+        <v>17.5478</v>
       </c>
       <c r="D48" t="n">
-        <v>33.3038</v>
+        <v>33.1981</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6978</v>
+        <v>13.704</v>
       </c>
       <c r="F48" t="n">
-        <v>27.0606</v>
+        <v>26.8131</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1209</v>
+        <v>18.1611</v>
       </c>
       <c r="C49" t="n">
-        <v>17.4174</v>
+        <v>17.4326</v>
       </c>
       <c r="D49" t="n">
-        <v>33.5539</v>
+        <v>33.3249</v>
       </c>
       <c r="E49" t="n">
-        <v>13.3545</v>
+        <v>13.3653</v>
       </c>
       <c r="F49" t="n">
-        <v>26.8364</v>
+        <v>26.644</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.5678</v>
+        <v>17.5554</v>
       </c>
       <c r="C50" t="n">
-        <v>17.363</v>
+        <v>17.39</v>
       </c>
       <c r="D50" t="n">
-        <v>32.9589</v>
+        <v>33.0983</v>
       </c>
       <c r="E50" t="n">
-        <v>17.924</v>
+        <v>17.792</v>
       </c>
       <c r="F50" t="n">
-        <v>30.8666</v>
+        <v>30.6093</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.8038</v>
+        <v>16.8142</v>
       </c>
       <c r="C51" t="n">
-        <v>18.8614</v>
+        <v>18.869</v>
       </c>
       <c r="D51" t="n">
-        <v>33.273</v>
+        <v>33.2624</v>
       </c>
       <c r="E51" t="n">
-        <v>17.4552</v>
+        <v>17.2845</v>
       </c>
       <c r="F51" t="n">
-        <v>30.478</v>
+        <v>30.2236</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.8754</v>
+        <v>15.8761</v>
       </c>
       <c r="C52" t="n">
-        <v>18.6446</v>
+        <v>18.7095</v>
       </c>
       <c r="D52" t="n">
-        <v>33.2854</v>
+        <v>33.2147</v>
       </c>
       <c r="E52" t="n">
-        <v>17.108</v>
+        <v>16.994</v>
       </c>
       <c r="F52" t="n">
-        <v>30.157</v>
+        <v>29.9293</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.4828</v>
+        <v>23.4956</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4926</v>
+        <v>18.4919</v>
       </c>
       <c r="D53" t="n">
-        <v>33.4414</v>
+        <v>33.2793</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7317</v>
+        <v>16.6751</v>
       </c>
       <c r="F53" t="n">
-        <v>29.9052</v>
+        <v>29.7284</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1515</v>
+        <v>23.1658</v>
       </c>
       <c r="C54" t="n">
-        <v>18.3718</v>
+        <v>18.401</v>
       </c>
       <c r="D54" t="n">
-        <v>33.7242</v>
+        <v>33.299</v>
       </c>
       <c r="E54" t="n">
-        <v>16.3646</v>
+        <v>16.2604</v>
       </c>
       <c r="F54" t="n">
-        <v>29.5803</v>
+        <v>29.3326</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6314</v>
+        <v>22.6273</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2637</v>
+        <v>18.2629</v>
       </c>
       <c r="D55" t="n">
-        <v>33.3491</v>
+        <v>33.0321</v>
       </c>
       <c r="E55" t="n">
-        <v>16.0742</v>
+        <v>15.9536</v>
       </c>
       <c r="F55" t="n">
-        <v>29.3106</v>
+        <v>28.9555</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1406</v>
+        <v>22.1487</v>
       </c>
       <c r="C56" t="n">
-        <v>18.1007</v>
+        <v>18.1231</v>
       </c>
       <c r="D56" t="n">
-        <v>33.4164</v>
+        <v>33.0799</v>
       </c>
       <c r="E56" t="n">
-        <v>15.8124</v>
+        <v>15.547</v>
       </c>
       <c r="F56" t="n">
-        <v>29.0396</v>
+        <v>28.8209</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.6057</v>
+        <v>21.606</v>
       </c>
       <c r="C57" t="n">
-        <v>18.0099</v>
+        <v>18.0276</v>
       </c>
       <c r="D57" t="n">
-        <v>33.9846</v>
+        <v>33.5734</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4703</v>
+        <v>15.2453</v>
       </c>
       <c r="F57" t="n">
-        <v>28.7324</v>
+        <v>28.5338</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0646</v>
+        <v>21.0794</v>
       </c>
       <c r="C58" t="n">
-        <v>17.9297</v>
+        <v>17.9154</v>
       </c>
       <c r="D58" t="n">
-        <v>34.1396</v>
+        <v>33.6741</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1602</v>
+        <v>14.9426</v>
       </c>
       <c r="F58" t="n">
-        <v>28.4602</v>
+        <v>28.2391</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5814</v>
+        <v>20.5717</v>
       </c>
       <c r="C59" t="n">
-        <v>17.7681</v>
+        <v>17.809</v>
       </c>
       <c r="D59" t="n">
-        <v>34.6664</v>
+        <v>34.1006</v>
       </c>
       <c r="E59" t="n">
-        <v>14.8678</v>
+        <v>14.6334</v>
       </c>
       <c r="F59" t="n">
-        <v>28.2021</v>
+        <v>27.9723</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0009</v>
+        <v>20.0195</v>
       </c>
       <c r="C60" t="n">
-        <v>17.6959</v>
+        <v>17.7361</v>
       </c>
       <c r="D60" t="n">
-        <v>34.8329</v>
+        <v>34.2831</v>
       </c>
       <c r="E60" t="n">
-        <v>14.5877</v>
+        <v>14.3287</v>
       </c>
       <c r="F60" t="n">
-        <v>27.8462</v>
+        <v>27.6386</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5429</v>
+        <v>19.5148</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6263</v>
+        <v>17.6426</v>
       </c>
       <c r="D61" t="n">
-        <v>35.2542</v>
+        <v>34.7751</v>
       </c>
       <c r="E61" t="n">
-        <v>14.2879</v>
+        <v>14.2671</v>
       </c>
       <c r="F61" t="n">
-        <v>27.5599</v>
+        <v>27.2447</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9946</v>
+        <v>19.0206</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5578</v>
+        <v>17.568</v>
       </c>
       <c r="D62" t="n">
-        <v>35.4377</v>
+        <v>35.1571</v>
       </c>
       <c r="E62" t="n">
-        <v>13.9794</v>
+        <v>13.8297</v>
       </c>
       <c r="F62" t="n">
-        <v>27.2819</v>
+        <v>27.0041</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3945</v>
+        <v>18.3209</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4896</v>
+        <v>17.4911</v>
       </c>
       <c r="D63" t="n">
-        <v>35.8061</v>
+        <v>35.4788</v>
       </c>
       <c r="E63" t="n">
-        <v>13.6571</v>
+        <v>13.5082</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9615</v>
+        <v>26.7106</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.732</v>
+        <v>17.7265</v>
       </c>
       <c r="C64" t="n">
-        <v>17.4572</v>
+        <v>17.4591</v>
       </c>
       <c r="D64" t="n">
-        <v>39.4147</v>
+        <v>39.2077</v>
       </c>
       <c r="E64" t="n">
-        <v>18.6288</v>
+        <v>18.1334</v>
       </c>
       <c r="F64" t="n">
-        <v>31.0958</v>
+        <v>30.8586</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0194</v>
+        <v>17.0504</v>
       </c>
       <c r="C65" t="n">
-        <v>19.039</v>
+        <v>19.0531</v>
       </c>
       <c r="D65" t="n">
-        <v>39.0981</v>
+        <v>38.8108</v>
       </c>
       <c r="E65" t="n">
-        <v>18.3811</v>
+        <v>17.8096</v>
       </c>
       <c r="F65" t="n">
-        <v>30.6944</v>
+        <v>30.5538</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1351</v>
+        <v>16.1954</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7789</v>
+        <v>18.7982</v>
       </c>
       <c r="D66" t="n">
-        <v>39.3026</v>
+        <v>38.811</v>
       </c>
       <c r="E66" t="n">
-        <v>18.0122</v>
+        <v>17.3289</v>
       </c>
       <c r="F66" t="n">
-        <v>30.3201</v>
+        <v>30.1875</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6353</v>
+        <v>23.6498</v>
       </c>
       <c r="C67" t="n">
-        <v>18.6271</v>
+        <v>18.6292</v>
       </c>
       <c r="D67" t="n">
-        <v>39.5369</v>
+        <v>38.8512</v>
       </c>
       <c r="E67" t="n">
-        <v>17.5685</v>
+        <v>16.915</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0256</v>
+        <v>29.8863</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2596</v>
+        <v>23.2501</v>
       </c>
       <c r="C68" t="n">
-        <v>18.4842</v>
+        <v>18.4795</v>
       </c>
       <c r="D68" t="n">
-        <v>41.1894</v>
+        <v>40.1911</v>
       </c>
       <c r="E68" t="n">
-        <v>17.0339</v>
+        <v>16.5089</v>
       </c>
       <c r="F68" t="n">
-        <v>29.6626</v>
+        <v>29.5785</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7779</v>
+        <v>22.7789</v>
       </c>
       <c r="C69" t="n">
-        <v>18.319</v>
+        <v>18.3774</v>
       </c>
       <c r="D69" t="n">
-        <v>41.3576</v>
+        <v>40.1947</v>
       </c>
       <c r="E69" t="n">
-        <v>16.455</v>
+        <v>16.0968</v>
       </c>
       <c r="F69" t="n">
-        <v>29.4545</v>
+        <v>29.3047</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.3028</v>
+        <v>22.2971</v>
       </c>
       <c r="C70" t="n">
-        <v>18.3252</v>
+        <v>18.3164</v>
       </c>
       <c r="D70" t="n">
-        <v>41.196</v>
+        <v>40.1857</v>
       </c>
       <c r="E70" t="n">
-        <v>16.0223</v>
+        <v>15.7377</v>
       </c>
       <c r="F70" t="n">
-        <v>29.1427</v>
+        <v>28.9673</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.7802</v>
+        <v>21.785</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1657</v>
+        <v>18.1732</v>
       </c>
       <c r="D71" t="n">
-        <v>39.8238</v>
+        <v>39.0307</v>
       </c>
       <c r="E71" t="n">
-        <v>15.6876</v>
+        <v>15.3539</v>
       </c>
       <c r="F71" t="n">
-        <v>28.8724</v>
+        <v>28.7354</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2363</v>
+        <v>21.2616</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0816</v>
+        <v>18.076</v>
       </c>
       <c r="D72" t="n">
-        <v>39.9113</v>
+        <v>38.9895</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3718</v>
+        <v>15.2886</v>
       </c>
       <c r="F72" t="n">
-        <v>28.5099</v>
+        <v>28.2804</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7343</v>
+        <v>20.7565</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9349</v>
+        <v>17.9501</v>
       </c>
       <c r="D73" t="n">
-        <v>39.4883</v>
+        <v>38.9125</v>
       </c>
       <c r="E73" t="n">
-        <v>15.0705</v>
+        <v>15.03</v>
       </c>
       <c r="F73" t="n">
-        <v>28.2461</v>
+        <v>28.025</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1817</v>
+        <v>20.1888</v>
       </c>
       <c r="C74" t="n">
-        <v>17.8533</v>
+        <v>17.8774</v>
       </c>
       <c r="D74" t="n">
-        <v>39.9372</v>
+        <v>39.1713</v>
       </c>
       <c r="E74" t="n">
-        <v>14.7787</v>
+        <v>14.7331</v>
       </c>
       <c r="F74" t="n">
-        <v>27.9282</v>
+        <v>27.685</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6671</v>
+        <v>19.6621</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7441</v>
+        <v>17.7591</v>
       </c>
       <c r="D75" t="n">
-        <v>39.8008</v>
+        <v>39.0695</v>
       </c>
       <c r="E75" t="n">
-        <v>14.4905</v>
+        <v>14.4494</v>
       </c>
       <c r="F75" t="n">
-        <v>27.6955</v>
+        <v>27.5146</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1302</v>
+        <v>19.1474</v>
       </c>
       <c r="C76" t="n">
-        <v>17.6906</v>
+        <v>17.7054</v>
       </c>
       <c r="D76" t="n">
-        <v>39.8426</v>
+        <v>39.0591</v>
       </c>
       <c r="E76" t="n">
-        <v>14.2178</v>
+        <v>14.0327</v>
       </c>
       <c r="F76" t="n">
-        <v>27.3719</v>
+        <v>27.2107</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5456</v>
+        <v>18.5588</v>
       </c>
       <c r="C77" t="n">
-        <v>17.6103</v>
+        <v>17.615</v>
       </c>
       <c r="D77" t="n">
-        <v>39.7458</v>
+        <v>39.1341</v>
       </c>
       <c r="E77" t="n">
-        <v>13.8799</v>
+        <v>13.6847</v>
       </c>
       <c r="F77" t="n">
-        <v>27.0477</v>
+        <v>26.8793</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9552</v>
+        <v>17.9632</v>
       </c>
       <c r="C78" t="n">
-        <v>17.4419</v>
+        <v>17.446</v>
       </c>
       <c r="D78" t="n">
-        <v>46.7417</v>
+        <v>45.2374</v>
       </c>
       <c r="E78" t="n">
-        <v>18.2783</v>
+        <v>18.2238</v>
       </c>
       <c r="F78" t="n">
-        <v>31.0073</v>
+        <v>30.838</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2315</v>
+        <v>17.2508</v>
       </c>
       <c r="C79" t="n">
-        <v>19.2861</v>
+        <v>19.3624</v>
       </c>
       <c r="D79" t="n">
-        <v>47.7267</v>
+        <v>45.7076</v>
       </c>
       <c r="E79" t="n">
-        <v>17.8436</v>
+        <v>17.7532</v>
       </c>
       <c r="F79" t="n">
-        <v>30.6981</v>
+        <v>30.4895</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.4133</v>
+        <v>16.3862</v>
       </c>
       <c r="C80" t="n">
-        <v>19.1247</v>
+        <v>19.1828</v>
       </c>
       <c r="D80" t="n">
-        <v>48.0222</v>
+        <v>46.2118</v>
       </c>
       <c r="E80" t="n">
-        <v>17.3402</v>
+        <v>17.3811</v>
       </c>
       <c r="F80" t="n">
-        <v>30.3642</v>
+        <v>30.1424</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7828</v>
+        <v>23.7804</v>
       </c>
       <c r="C81" t="n">
-        <v>18.9411</v>
+        <v>18.9272</v>
       </c>
       <c r="D81" t="n">
-        <v>47.34</v>
+        <v>45.7088</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0102</v>
+        <v>17.0285</v>
       </c>
       <c r="F81" t="n">
-        <v>30.0286</v>
+        <v>29.8534</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3847</v>
+        <v>23.3896</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7364</v>
+        <v>18.7615</v>
       </c>
       <c r="D82" t="n">
-        <v>45.0326</v>
+        <v>43.6251</v>
       </c>
       <c r="E82" t="n">
-        <v>16.6682</v>
+        <v>16.6917</v>
       </c>
       <c r="F82" t="n">
-        <v>29.709</v>
+        <v>29.5374</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9279</v>
+        <v>22.9307</v>
       </c>
       <c r="C83" t="n">
-        <v>18.5878</v>
+        <v>18.5872</v>
       </c>
       <c r="D83" t="n">
-        <v>44.6514</v>
+        <v>43.2692</v>
       </c>
       <c r="E83" t="n">
-        <v>16.396</v>
+        <v>16.3722</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4518</v>
+        <v>29.2218</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4326</v>
+        <v>22.4377</v>
       </c>
       <c r="C84" t="n">
-        <v>18.3987</v>
+        <v>18.5241</v>
       </c>
       <c r="D84" t="n">
-        <v>44.2928</v>
+        <v>42.7806</v>
       </c>
       <c r="E84" t="n">
-        <v>16.0407</v>
+        <v>16.0797</v>
       </c>
       <c r="F84" t="n">
-        <v>29.0994</v>
+        <v>28.9315</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9082</v>
+        <v>21.9585</v>
       </c>
       <c r="C85" t="n">
-        <v>18.2234</v>
+        <v>18.2064</v>
       </c>
       <c r="D85" t="n">
-        <v>45.9158</v>
+        <v>44.0292</v>
       </c>
       <c r="E85" t="n">
-        <v>15.7761</v>
+        <v>15.7578</v>
       </c>
       <c r="F85" t="n">
-        <v>28.8066</v>
+        <v>28.6453</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.4085</v>
+        <v>21.408</v>
       </c>
       <c r="C86" t="n">
-        <v>18.0829</v>
+        <v>18.0995</v>
       </c>
       <c r="D86" t="n">
-        <v>44.4885</v>
+        <v>43.5651</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4736</v>
+        <v>15.4786</v>
       </c>
       <c r="F86" t="n">
-        <v>28.5644</v>
+        <v>28.3892</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.8892</v>
+        <v>20.9643</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9747</v>
+        <v>17.9733</v>
       </c>
       <c r="D87" t="n">
-        <v>44.1446</v>
+        <v>43.193</v>
       </c>
       <c r="E87" t="n">
-        <v>15.1963</v>
+        <v>15.1726</v>
       </c>
       <c r="F87" t="n">
-        <v>28.2891</v>
+        <v>28.1002</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3476</v>
+        <v>20.3622</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8495</v>
+        <v>17.8736</v>
       </c>
       <c r="D88" t="n">
-        <v>43.8086</v>
+        <v>42.836</v>
       </c>
       <c r="E88" t="n">
-        <v>14.8944</v>
+        <v>14.9002</v>
       </c>
       <c r="F88" t="n">
-        <v>27.9554</v>
+        <v>27.7599</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8309</v>
+        <v>19.8419</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7461</v>
+        <v>17.7649</v>
       </c>
       <c r="D89" t="n">
-        <v>44.3578</v>
+        <v>42.7067</v>
       </c>
       <c r="E89" t="n">
-        <v>14.5884</v>
+        <v>14.6185</v>
       </c>
       <c r="F89" t="n">
-        <v>27.6687</v>
+        <v>27.4945</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.2953</v>
+        <v>19.3026</v>
       </c>
       <c r="C90" t="n">
-        <v>17.6931</v>
+        <v>17.6975</v>
       </c>
       <c r="D90" t="n">
-        <v>43.3881</v>
+        <v>42.4753</v>
       </c>
       <c r="E90" t="n">
-        <v>14.2841</v>
+        <v>14.2989</v>
       </c>
       <c r="F90" t="n">
-        <v>27.371</v>
+        <v>27.1656</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7228</v>
+        <v>18.734</v>
       </c>
       <c r="C91" t="n">
-        <v>17.5711</v>
+        <v>17.5726</v>
       </c>
       <c r="D91" t="n">
-        <v>43.0975</v>
+        <v>42.1471</v>
       </c>
       <c r="E91" t="n">
-        <v>14.0007</v>
+        <v>13.9987</v>
       </c>
       <c r="F91" t="n">
-        <v>27.0613</v>
+        <v>26.8499</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.081</v>
+        <v>18.101</v>
       </c>
       <c r="C92" t="n">
-        <v>17.4995</v>
+        <v>17.5022</v>
       </c>
       <c r="D92" t="n">
-        <v>49.5605</v>
+        <v>47.5054</v>
       </c>
       <c r="E92" t="n">
-        <v>18.2678</v>
+        <v>18.2664</v>
       </c>
       <c r="F92" t="n">
-        <v>31.1106</v>
+        <v>30.8218</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.4179</v>
+        <v>17.4282</v>
       </c>
       <c r="C93" t="n">
-        <v>17.401</v>
+        <v>17.4829</v>
       </c>
       <c r="D93" t="n">
-        <v>48.0076</v>
+        <v>46.0438</v>
       </c>
       <c r="E93" t="n">
-        <v>17.8625</v>
+        <v>17.8273</v>
       </c>
       <c r="F93" t="n">
-        <v>30.8903</v>
+        <v>30.5991</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6267</v>
+        <v>16.6394</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0295</v>
+        <v>19.0379</v>
       </c>
       <c r="D94" t="n">
-        <v>45.8195</v>
+        <v>44.4665</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4508</v>
+        <v>17.4532</v>
       </c>
       <c r="F94" t="n">
-        <v>30.3251</v>
+        <v>30.42</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8772</v>
+        <v>23.8832</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8324</v>
+        <v>18.8613</v>
       </c>
       <c r="D95" t="n">
-        <v>45.0459</v>
+        <v>43.7641</v>
       </c>
       <c r="E95" t="n">
-        <v>17.1573</v>
+        <v>17.0647</v>
       </c>
       <c r="F95" t="n">
-        <v>29.8192</v>
+        <v>29.8666</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4693</v>
+        <v>23.4762</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6493</v>
+        <v>18.6669</v>
       </c>
       <c r="D96" t="n">
-        <v>44.4478</v>
+        <v>43.2462</v>
       </c>
       <c r="E96" t="n">
-        <v>16.6469</v>
+        <v>16.578</v>
       </c>
       <c r="F96" t="n">
-        <v>29.6417</v>
+        <v>29.6544</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0254</v>
+        <v>23.044</v>
       </c>
       <c r="C97" t="n">
-        <v>18.4869</v>
+        <v>18.499</v>
       </c>
       <c r="D97" t="n">
-        <v>46.684</v>
+        <v>45.2747</v>
       </c>
       <c r="E97" t="n">
-        <v>16.232</v>
+        <v>16.2225</v>
       </c>
       <c r="F97" t="n">
-        <v>29.2922</v>
+        <v>29.3793</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5567</v>
+        <v>22.5746</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3411</v>
+        <v>18.3598</v>
       </c>
       <c r="D98" t="n">
-        <v>46.0889</v>
+        <v>44.7705</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9078</v>
+        <v>15.9137</v>
       </c>
       <c r="F98" t="n">
-        <v>29.0454</v>
+        <v>29.0275</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0455</v>
+        <v>22.0558</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2037</v>
+        <v>18.2156</v>
       </c>
       <c r="D99" t="n">
-        <v>45.4665</v>
+        <v>44.1874</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6182</v>
+        <v>15.628</v>
       </c>
       <c r="F99" t="n">
-        <v>28.7235</v>
+        <v>28.7381</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5134</v>
+        <v>21.5251</v>
       </c>
       <c r="C100" t="n">
-        <v>18.1696</v>
+        <v>18.2049</v>
       </c>
       <c r="D100" t="n">
-        <v>42.8337</v>
+        <v>41.6312</v>
       </c>
       <c r="E100" t="n">
-        <v>15.393</v>
+        <v>15.3036</v>
       </c>
       <c r="F100" t="n">
-        <v>28.4286</v>
+        <v>28.4409</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9805</v>
+        <v>20.9899</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0529</v>
+        <v>18.0553</v>
       </c>
       <c r="D101" t="n">
-        <v>42.5781</v>
+        <v>41.2339</v>
       </c>
       <c r="E101" t="n">
-        <v>15.126</v>
+        <v>15.0426</v>
       </c>
       <c r="F101" t="n">
-        <v>28.1136</v>
+        <v>28.1339</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4543</v>
+        <v>20.4669</v>
       </c>
       <c r="C102" t="n">
-        <v>17.944</v>
+        <v>17.9621</v>
       </c>
       <c r="D102" t="n">
-        <v>41.7578</v>
+        <v>40.9032</v>
       </c>
       <c r="E102" t="n">
-        <v>14.7581</v>
+        <v>14.7653</v>
       </c>
       <c r="F102" t="n">
-        <v>27.8203</v>
+        <v>27.8446</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.8969</v>
+        <v>19.9285</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8411</v>
+        <v>17.8574</v>
       </c>
       <c r="D103" t="n">
-        <v>41.8549</v>
+        <v>40.9676</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4793</v>
+        <v>14.4847</v>
       </c>
       <c r="F103" t="n">
-        <v>27.5349</v>
+        <v>27.5504</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.4119</v>
+        <v>19.4083</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7626</v>
+        <v>17.7738</v>
       </c>
       <c r="D104" t="n">
-        <v>41.0205</v>
+        <v>40.2712</v>
       </c>
       <c r="E104" t="n">
-        <v>14.1996</v>
+        <v>14.2203</v>
       </c>
       <c r="F104" t="n">
-        <v>27.238</v>
+        <v>27.2614</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8196</v>
+        <v>18.8294</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6558</v>
+        <v>17.6533</v>
       </c>
       <c r="D105" t="n">
-        <v>41.1273</v>
+        <v>40.3552</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9455</v>
+        <v>13.9334</v>
       </c>
       <c r="F105" t="n">
-        <v>26.9124</v>
+        <v>26.9409</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2399</v>
+        <v>18.2648</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5767</v>
+        <v>17.577</v>
       </c>
       <c r="D106" t="n">
-        <v>40.4279</v>
+        <v>39.7585</v>
       </c>
       <c r="E106" t="n">
-        <v>13.6281</v>
+        <v>13.6461</v>
       </c>
       <c r="F106" t="n">
-        <v>26.6158</v>
+        <v>26.6229</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6404</v>
+        <v>17.6094</v>
       </c>
       <c r="C107" t="n">
-        <v>17.5049</v>
+        <v>17.5095</v>
       </c>
       <c r="D107" t="n">
-        <v>45.7683</v>
+        <v>44.7774</v>
       </c>
       <c r="E107" t="n">
-        <v>17.7667</v>
+        <v>17.7711</v>
       </c>
       <c r="F107" t="n">
-        <v>30.6416</v>
+        <v>30.6856</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8766</v>
+        <v>16.8495</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1408</v>
+        <v>19.1572</v>
       </c>
       <c r="D108" t="n">
-        <v>46.7578</v>
+        <v>45.4285</v>
       </c>
       <c r="E108" t="n">
-        <v>17.4663</v>
+        <v>17.354</v>
       </c>
       <c r="F108" t="n">
-        <v>30.2958</v>
+        <v>30.3002</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9478</v>
+        <v>15.9229</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9586</v>
+        <v>18.9742</v>
       </c>
       <c r="D109" t="n">
-        <v>45.9888</v>
+        <v>44.7194</v>
       </c>
       <c r="E109" t="n">
-        <v>16.974</v>
+        <v>17.0441</v>
       </c>
       <c r="F109" t="n">
-        <v>29.9763</v>
+        <v>29.9717</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.6009</v>
+        <v>23.5747</v>
       </c>
       <c r="C110" t="n">
-        <v>18.6892</v>
+        <v>18.7133</v>
       </c>
       <c r="D110" t="n">
-        <v>45.3765</v>
+        <v>44.193</v>
       </c>
       <c r="E110" t="n">
-        <v>16.8109</v>
+        <v>16.8124</v>
       </c>
       <c r="F110" t="n">
-        <v>29.6376</v>
+        <v>29.566</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1292</v>
+        <v>23.1421</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5541</v>
+        <v>18.5731</v>
       </c>
       <c r="D111" t="n">
-        <v>44.867</v>
+        <v>43.6404</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4874</v>
+        <v>16.4884</v>
       </c>
       <c r="F111" t="n">
-        <v>29.3215</v>
+        <v>29.3115</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.658</v>
+        <v>22.6575</v>
       </c>
       <c r="C112" t="n">
-        <v>18.3783</v>
+        <v>18.4016</v>
       </c>
       <c r="D112" t="n">
-        <v>41.4846</v>
+        <v>40.7725</v>
       </c>
       <c r="E112" t="n">
-        <v>16.1767</v>
+        <v>16.1958</v>
       </c>
       <c r="F112" t="n">
-        <v>29.017</v>
+        <v>29.0034</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1487</v>
+        <v>22.1581</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2378</v>
+        <v>18.2426</v>
       </c>
       <c r="D113" t="n">
-        <v>41.0171</v>
+        <v>40.3964</v>
       </c>
       <c r="E113" t="n">
-        <v>15.8664</v>
+        <v>15.8719</v>
       </c>
       <c r="F113" t="n">
-        <v>28.7454</v>
+        <v>28.6706</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6365</v>
+        <v>21.632</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1547</v>
+        <v>18.1273</v>
       </c>
       <c r="D114" t="n">
-        <v>43.1354</v>
+        <v>42.1346</v>
       </c>
       <c r="E114" t="n">
-        <v>15.6129</v>
+        <v>15.5864</v>
       </c>
       <c r="F114" t="n">
-        <v>28.458</v>
+        <v>28.4066</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.105</v>
+        <v>21.1047</v>
       </c>
       <c r="C115" t="n">
-        <v>17.9952</v>
+        <v>17.9964</v>
       </c>
       <c r="D115" t="n">
-        <v>42.793</v>
+        <v>41.7802</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3233</v>
+        <v>15.3341</v>
       </c>
       <c r="F115" t="n">
-        <v>28.1557</v>
+        <v>28.1207</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5692</v>
+        <v>20.5734</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8791</v>
+        <v>17.8737</v>
       </c>
       <c r="D116" t="n">
-        <v>42.412</v>
+        <v>41.3928</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8201</v>
+        <v>14.8346</v>
       </c>
       <c r="F116" t="n">
-        <v>27.9177</v>
+        <v>27.9404</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.0324</v>
+        <v>20.0404</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7688</v>
+        <v>17.7812</v>
       </c>
       <c r="D117" t="n">
-        <v>42.0999</v>
+        <v>41.0933</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5548</v>
+        <v>14.5507</v>
       </c>
       <c r="F117" t="n">
-        <v>27.5763</v>
+        <v>27.606</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5043</v>
+        <v>19.5212</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6682</v>
+        <v>17.6936</v>
       </c>
       <c r="D118" t="n">
-        <v>41.7121</v>
+        <v>40.7987</v>
       </c>
       <c r="E118" t="n">
-        <v>14.283</v>
+        <v>14.2852</v>
       </c>
       <c r="F118" t="n">
-        <v>27.3017</v>
+        <v>27.2972</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9508</v>
+        <v>18.9382</v>
       </c>
       <c r="C119" t="n">
-        <v>17.6015</v>
+        <v>17.612</v>
       </c>
       <c r="D119" t="n">
-        <v>41.4176</v>
+        <v>40.5365</v>
       </c>
       <c r="E119" t="n">
-        <v>14.0115</v>
+        <v>14.0016</v>
       </c>
       <c r="F119" t="n">
-        <v>26.9983</v>
+        <v>26.9922</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3832</v>
+        <v>18.3638</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5153</v>
+        <v>17.5285</v>
       </c>
       <c r="D120" t="n">
-        <v>41.104</v>
+        <v>40.3221</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7254</v>
+        <v>13.7175</v>
       </c>
       <c r="F120" t="n">
-        <v>26.6842</v>
+        <v>26.7201</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7291</v>
+        <v>17.7122</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4395</v>
+        <v>17.4355</v>
       </c>
       <c r="D121" t="n">
-        <v>48.6973</v>
+        <v>46.8162</v>
       </c>
       <c r="E121" t="n">
-        <v>18.0788</v>
+        <v>18.0796</v>
       </c>
       <c r="F121" t="n">
-        <v>30.6094</v>
+        <v>30.6584</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.0244</v>
+        <v>17.0082</v>
       </c>
       <c r="C122" t="n">
-        <v>19.1389</v>
+        <v>19.1795</v>
       </c>
       <c r="D122" t="n">
-        <v>48.309</v>
+        <v>47.0311</v>
       </c>
       <c r="E122" t="n">
-        <v>17.4286</v>
+        <v>17.4253</v>
       </c>
       <c r="F122" t="n">
-        <v>30.339</v>
+        <v>30.3729</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.0989</v>
+        <v>16.1026</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9338</v>
+        <v>18.9483</v>
       </c>
       <c r="D123" t="n">
-        <v>49.2294</v>
+        <v>47.1587</v>
       </c>
       <c r="E123" t="n">
-        <v>17.1714</v>
+        <v>17.2385</v>
       </c>
       <c r="F123" t="n">
-        <v>30.0283</v>
+        <v>29.9942</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6384</v>
+        <v>23.6416</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7559</v>
+        <v>18.7689</v>
       </c>
       <c r="D124" t="n">
-        <v>45.3756</v>
+        <v>43.9414</v>
       </c>
       <c r="E124" t="n">
-        <v>16.8583</v>
+        <v>16.8431</v>
       </c>
       <c r="F124" t="n">
-        <v>29.6951</v>
+        <v>29.6404</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2131</v>
+        <v>23.2237</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5761</v>
+        <v>18.5999</v>
       </c>
       <c r="D125" t="n">
-        <v>45.1637</v>
+        <v>43.7607</v>
       </c>
       <c r="E125" t="n">
-        <v>16.5641</v>
+        <v>16.5491</v>
       </c>
       <c r="F125" t="n">
-        <v>29.3909</v>
+        <v>29.3361</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7493</v>
+        <v>22.7609</v>
       </c>
       <c r="C126" t="n">
-        <v>18.4199</v>
+        <v>18.4116</v>
       </c>
       <c r="D126" t="n">
-        <v>46.908</v>
+        <v>45.383</v>
       </c>
       <c r="E126" t="n">
-        <v>16.2244</v>
+        <v>16.2405</v>
       </c>
       <c r="F126" t="n">
-        <v>29.0406</v>
+        <v>29.0763</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.247</v>
+        <v>22.2692</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2728</v>
+        <v>18.2637</v>
       </c>
       <c r="D127" t="n">
-        <v>46.229</v>
+        <v>44.7355</v>
       </c>
       <c r="E127" t="n">
-        <v>15.8943</v>
+        <v>15.9228</v>
       </c>
       <c r="F127" t="n">
-        <v>28.7548</v>
+        <v>28.7711</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7779</v>
+        <v>21.7533</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1655</v>
+        <v>18.1542</v>
       </c>
       <c r="D128" t="n">
-        <v>43.6235</v>
+        <v>42.3931</v>
       </c>
       <c r="E128" t="n">
-        <v>15.6203</v>
+        <v>15.6049</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4895</v>
+        <v>28.4485</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.2156</v>
+        <v>21.2105</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0227</v>
+        <v>18.0302</v>
       </c>
       <c r="D129" t="n">
-        <v>42.9976</v>
+        <v>41.9272</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3984</v>
+        <v>15.3823</v>
       </c>
       <c r="F129" t="n">
-        <v>28.2244</v>
+        <v>28.1531</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6731</v>
+        <v>20.6684</v>
       </c>
       <c r="C130" t="n">
-        <v>17.905</v>
+        <v>17.9144</v>
       </c>
       <c r="D130" t="n">
-        <v>42.4994</v>
+        <v>41.4794</v>
       </c>
       <c r="E130" t="n">
-        <v>14.888</v>
+        <v>14.941</v>
       </c>
       <c r="F130" t="n">
-        <v>27.9682</v>
+        <v>27.9716</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1585</v>
+        <v>20.1332</v>
       </c>
       <c r="C131" t="n">
-        <v>17.7988</v>
+        <v>17.8113</v>
       </c>
       <c r="D131" t="n">
-        <v>41.9077</v>
+        <v>40.9428</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6093</v>
+        <v>14.605</v>
       </c>
       <c r="F131" t="n">
-        <v>27.699</v>
+        <v>27.6663</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.619</v>
+        <v>19.6201</v>
       </c>
       <c r="C132" t="n">
-        <v>17.6868</v>
+        <v>17.7102</v>
       </c>
       <c r="D132" t="n">
-        <v>41.4875</v>
+        <v>40.5889</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3393</v>
+        <v>14.3413</v>
       </c>
       <c r="F132" t="n">
-        <v>27.3916</v>
+        <v>27.3392</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0658</v>
+        <v>19.0744</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6194</v>
+        <v>17.6157</v>
       </c>
       <c r="D133" t="n">
-        <v>41.132</v>
+        <v>40.3187</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0657</v>
+        <v>14.0626</v>
       </c>
       <c r="F133" t="n">
-        <v>27.1081</v>
+        <v>27.0946</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.528</v>
+        <v>18.4926</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5563</v>
+        <v>17.5568</v>
       </c>
       <c r="D134" t="n">
-        <v>40.7941</v>
+        <v>39.983</v>
       </c>
       <c r="E134" t="n">
-        <v>13.7868</v>
+        <v>13.7817</v>
       </c>
       <c r="F134" t="n">
-        <v>26.7827</v>
+        <v>26.7919</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8946</v>
+        <v>17.8691</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4592</v>
+        <v>17.466</v>
       </c>
       <c r="D135" t="n">
-        <v>49.2886</v>
+        <v>47.4799</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8557</v>
+        <v>17.8626</v>
       </c>
       <c r="F135" t="n">
-        <v>30.794</v>
+        <v>30.8036</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.2226</v>
+        <v>17.1919</v>
       </c>
       <c r="C136" t="n">
-        <v>19.2062</v>
+        <v>19.1831</v>
       </c>
       <c r="D136" t="n">
-        <v>48.1486</v>
+        <v>46.4604</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6419</v>
+        <v>17.6145</v>
       </c>
       <c r="F136" t="n">
-        <v>30.3498</v>
+        <v>30.3293</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.3486</v>
+        <v>16.313</v>
       </c>
       <c r="C137" t="n">
-        <v>19.0043</v>
+        <v>19.0029</v>
       </c>
       <c r="D137" t="n">
-        <v>46.6447</v>
+        <v>45.22</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1205</v>
+        <v>17.1142</v>
       </c>
       <c r="F137" t="n">
-        <v>30.217</v>
+        <v>30.1262</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7405</v>
+        <v>23.7317</v>
       </c>
       <c r="C138" t="n">
-        <v>18.7972</v>
+        <v>18.8199</v>
       </c>
       <c r="D138" t="n">
-        <v>48.9668</v>
+        <v>46.9508</v>
       </c>
       <c r="E138" t="n">
-        <v>16.776</v>
+        <v>16.7447</v>
       </c>
       <c r="F138" t="n">
-        <v>29.7864</v>
+        <v>29.8019</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3213</v>
+        <v>23.3201</v>
       </c>
       <c r="C139" t="n">
-        <v>18.667</v>
+        <v>18.6528</v>
       </c>
       <c r="D139" t="n">
-        <v>45.7267</v>
+        <v>44.2538</v>
       </c>
       <c r="E139" t="n">
-        <v>16.5962</v>
+        <v>16.5582</v>
       </c>
       <c r="F139" t="n">
-        <v>29.4066</v>
+        <v>29.4263</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8529</v>
+        <v>22.8501</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4825</v>
+        <v>18.4708</v>
       </c>
       <c r="D140" t="n">
-        <v>45.2443</v>
+        <v>43.711</v>
       </c>
       <c r="E140" t="n">
-        <v>16.3236</v>
+        <v>16.2506</v>
       </c>
       <c r="F140" t="n">
-        <v>29.104</v>
+        <v>29.1265</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3655</v>
+        <v>22.368</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3417</v>
+        <v>18.323</v>
       </c>
       <c r="D141" t="n">
-        <v>44.3373</v>
+        <v>43.0462</v>
       </c>
       <c r="E141" t="n">
-        <v>15.954</v>
+        <v>15.9821</v>
       </c>
       <c r="F141" t="n">
-        <v>28.8106</v>
+        <v>28.823</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8482</v>
+        <v>21.8533</v>
       </c>
       <c r="C142" t="n">
-        <v>18.2061</v>
+        <v>18.1993</v>
       </c>
       <c r="D142" t="n">
-        <v>45.8939</v>
+        <v>44.4087</v>
       </c>
       <c r="E142" t="n">
-        <v>15.5094</v>
+        <v>15.5154</v>
       </c>
       <c r="F142" t="n">
-        <v>28.5853</v>
+        <v>28.689</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.312</v>
+        <v>21.318</v>
       </c>
       <c r="C143" t="n">
-        <v>18.0926</v>
+        <v>18.0845</v>
       </c>
       <c r="D143" t="n">
-        <v>45.1059</v>
+        <v>43.6433</v>
       </c>
       <c r="E143" t="n">
-        <v>15.1985</v>
+        <v>15.2067</v>
       </c>
       <c r="F143" t="n">
-        <v>28.3248</v>
+        <v>28.3234</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.1163</v>
+        <v>19.0382</v>
       </c>
       <c r="C2" t="n">
-        <v>14.1003</v>
+        <v>14.1039</v>
       </c>
       <c r="D2" t="n">
-        <v>31.9521</v>
+        <v>32.0074</v>
       </c>
       <c r="E2" t="n">
-        <v>7.43183</v>
+        <v>6.67578</v>
       </c>
       <c r="F2" t="n">
-        <v>26.3458</v>
+        <v>26.7315</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4072</v>
+        <v>18.5067</v>
       </c>
       <c r="C3" t="n">
-        <v>14.4666</v>
+        <v>14.4221</v>
       </c>
       <c r="D3" t="n">
-        <v>31.8255</v>
+        <v>32.0463</v>
       </c>
       <c r="E3" t="n">
-        <v>7.22235</v>
+        <v>6.5097</v>
       </c>
       <c r="F3" t="n">
-        <v>26.3288</v>
+        <v>26.4966</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.1406</v>
+        <v>18.0515</v>
       </c>
       <c r="C4" t="n">
-        <v>14.8738</v>
+        <v>14.7674</v>
       </c>
       <c r="D4" t="n">
-        <v>31.9122</v>
+        <v>32.0804</v>
       </c>
       <c r="E4" t="n">
-        <v>6.44799</v>
+        <v>5.63828</v>
       </c>
       <c r="F4" t="n">
-        <v>25.9945</v>
+        <v>26.3609</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.5169</v>
+        <v>17.6548</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8375</v>
+        <v>14.8145</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4158</v>
+        <v>32.4607</v>
       </c>
       <c r="E5" t="n">
-        <v>6.1328</v>
+        <v>5.60799</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2969</v>
+        <v>26.4141</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.101</v>
+        <v>17.012</v>
       </c>
       <c r="C6" t="n">
-        <v>15.0656</v>
+        <v>15.0909</v>
       </c>
       <c r="D6" t="n">
-        <v>32.2127</v>
+        <v>32.5005</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5858</v>
+        <v>5.8673</v>
       </c>
       <c r="F6" t="n">
-        <v>25.996</v>
+        <v>26.0147</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.3711</v>
+        <v>16.4173</v>
       </c>
       <c r="C7" t="n">
-        <v>15.4534</v>
+        <v>15.3453</v>
       </c>
       <c r="D7" t="n">
-        <v>31.5184</v>
+        <v>31.8464</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6474</v>
+        <v>15.8894</v>
       </c>
       <c r="F7" t="n">
-        <v>30.0785</v>
+        <v>30.2541</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.7546</v>
+        <v>15.819</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9174</v>
+        <v>16.9961</v>
       </c>
       <c r="D8" t="n">
-        <v>31.7899</v>
+        <v>31.9784</v>
       </c>
       <c r="E8" t="n">
-        <v>15.1322</v>
+        <v>15.4811</v>
       </c>
       <c r="F8" t="n">
-        <v>29.6923</v>
+        <v>29.8978</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8939</v>
+        <v>14.9438</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0685</v>
+        <v>17.0893</v>
       </c>
       <c r="D9" t="n">
-        <v>31.7764</v>
+        <v>32.0091</v>
       </c>
       <c r="E9" t="n">
-        <v>14.888</v>
+        <v>15.0757</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4002</v>
+        <v>29.7058</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.84</v>
+        <v>22.7922</v>
       </c>
       <c r="C10" t="n">
-        <v>17.1704</v>
+        <v>17.0696</v>
       </c>
       <c r="D10" t="n">
-        <v>31.605</v>
+        <v>31.9972</v>
       </c>
       <c r="E10" t="n">
-        <v>14.5681</v>
+        <v>14.8483</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1738</v>
+        <v>29.3588</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.3919</v>
+        <v>22.4318</v>
       </c>
       <c r="C11" t="n">
-        <v>17.1805</v>
+        <v>17.195</v>
       </c>
       <c r="D11" t="n">
-        <v>31.8926</v>
+        <v>32.1201</v>
       </c>
       <c r="E11" t="n">
-        <v>14.2063</v>
+        <v>14.4063</v>
       </c>
       <c r="F11" t="n">
-        <v>28.8803</v>
+        <v>29.2587</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>22.0227</v>
+        <v>21.951</v>
       </c>
       <c r="C12" t="n">
-        <v>17.1017</v>
+        <v>17.0875</v>
       </c>
       <c r="D12" t="n">
-        <v>31.801</v>
+        <v>32.2063</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2259</v>
+        <v>14.3423</v>
       </c>
       <c r="F12" t="n">
-        <v>28.7004</v>
+        <v>28.9864</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5558</v>
+        <v>21.5221</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2506</v>
+        <v>17.1835</v>
       </c>
       <c r="D13" t="n">
-        <v>32.0097</v>
+        <v>32.1952</v>
       </c>
       <c r="E13" t="n">
-        <v>14.0122</v>
+        <v>14.1363</v>
       </c>
       <c r="F13" t="n">
-        <v>28.54</v>
+        <v>28.8472</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.1921</v>
+        <v>21.1072</v>
       </c>
       <c r="C14" t="n">
-        <v>17.2184</v>
+        <v>17.1739</v>
       </c>
       <c r="D14" t="n">
-        <v>32.0605</v>
+        <v>32.5782</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5045</v>
+        <v>13.6625</v>
       </c>
       <c r="F14" t="n">
-        <v>28.4351</v>
+        <v>28.5038</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.7962</v>
+        <v>20.7241</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2937</v>
+        <v>17.3254</v>
       </c>
       <c r="D15" t="n">
-        <v>32.2384</v>
+        <v>32.5349</v>
       </c>
       <c r="E15" t="n">
-        <v>13.1983</v>
+        <v>13.5724</v>
       </c>
       <c r="F15" t="n">
-        <v>27.7495</v>
+        <v>27.9378</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.1749</v>
+        <v>20.1116</v>
       </c>
       <c r="C16" t="n">
-        <v>17.2304</v>
+        <v>17.2315</v>
       </c>
       <c r="D16" t="n">
-        <v>32.4615</v>
+        <v>32.5459</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9821</v>
+        <v>13.3938</v>
       </c>
       <c r="F16" t="n">
-        <v>27.6133</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.5247</v>
+        <v>19.5615</v>
       </c>
       <c r="C17" t="n">
-        <v>17.2274</v>
+        <v>17.1903</v>
       </c>
       <c r="D17" t="n">
-        <v>32.4016</v>
+        <v>32.6101</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7854</v>
+        <v>13.2255</v>
       </c>
       <c r="F17" t="n">
-        <v>27.2651</v>
+        <v>27.4514</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.1419</v>
+        <v>19.0783</v>
       </c>
       <c r="C18" t="n">
-        <v>17.2105</v>
+        <v>17.1445</v>
       </c>
       <c r="D18" t="n">
-        <v>32.6726</v>
+        <v>32.8568</v>
       </c>
       <c r="E18" t="n">
-        <v>12.5863</v>
+        <v>12.9031</v>
       </c>
       <c r="F18" t="n">
-        <v>26.9324</v>
+        <v>27.1232</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.6258</v>
+        <v>18.6146</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1686</v>
+        <v>17.1241</v>
       </c>
       <c r="D19" t="n">
-        <v>32.8424</v>
+        <v>32.9416</v>
       </c>
       <c r="E19" t="n">
-        <v>12.2758</v>
+        <v>12.6775</v>
       </c>
       <c r="F19" t="n">
-        <v>26.592</v>
+        <v>26.7752</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.0393</v>
+        <v>18.0452</v>
       </c>
       <c r="C20" t="n">
-        <v>17.3062</v>
+        <v>17.2157</v>
       </c>
       <c r="D20" t="n">
-        <v>32.8574</v>
+        <v>33.1156</v>
       </c>
       <c r="E20" t="n">
-        <v>12.2167</v>
+        <v>12.3878</v>
       </c>
       <c r="F20" t="n">
-        <v>26.3529</v>
+        <v>26.4697</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.4675</v>
+        <v>17.4289</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1395</v>
+        <v>17.1346</v>
       </c>
       <c r="D21" t="n">
-        <v>32.4108</v>
+        <v>32.7239</v>
       </c>
       <c r="E21" t="n">
-        <v>17.6487</v>
+        <v>17.7535</v>
       </c>
       <c r="F21" t="n">
-        <v>30.4514</v>
+        <v>30.6344</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7462</v>
+        <v>16.7367</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7351</v>
+        <v>18.6862</v>
       </c>
       <c r="D22" t="n">
-        <v>32.2181</v>
+        <v>32.4812</v>
       </c>
       <c r="E22" t="n">
-        <v>16.9407</v>
+        <v>17.0747</v>
       </c>
       <c r="F22" t="n">
-        <v>30.2564</v>
+        <v>30.3661</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0349</v>
+        <v>16.0172</v>
       </c>
       <c r="C23" t="n">
-        <v>18.593</v>
+        <v>18.5149</v>
       </c>
       <c r="D23" t="n">
-        <v>32.1812</v>
+        <v>32.6951</v>
       </c>
       <c r="E23" t="n">
-        <v>16.5281</v>
+        <v>16.6615</v>
       </c>
       <c r="F23" t="n">
-        <v>30.0545</v>
+        <v>30.1748</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.4514</v>
+        <v>23.3544</v>
       </c>
       <c r="C24" t="n">
-        <v>18.4079</v>
+        <v>18.3838</v>
       </c>
       <c r="D24" t="n">
-        <v>32.0987</v>
+        <v>32.5319</v>
       </c>
       <c r="E24" t="n">
-        <v>16.1749</v>
+        <v>16.4447</v>
       </c>
       <c r="F24" t="n">
-        <v>29.8348</v>
+        <v>29.8892</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.9323</v>
+        <v>22.8861</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3503</v>
+        <v>18.3187</v>
       </c>
       <c r="D25" t="n">
-        <v>32.5587</v>
+        <v>32.8323</v>
       </c>
       <c r="E25" t="n">
-        <v>15.7744</v>
+        <v>16.0635</v>
       </c>
       <c r="F25" t="n">
-        <v>29.5464</v>
+        <v>29.5819</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.4794</v>
+        <v>22.4202</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2674</v>
+        <v>18.2827</v>
       </c>
       <c r="D26" t="n">
-        <v>32.567</v>
+        <v>32.9051</v>
       </c>
       <c r="E26" t="n">
-        <v>15.3441</v>
+        <v>15.6202</v>
       </c>
       <c r="F26" t="n">
-        <v>29.208</v>
+        <v>29.2418</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.9871</v>
+        <v>21.9774</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1527</v>
+        <v>18.1136</v>
       </c>
       <c r="D27" t="n">
-        <v>32.5764</v>
+        <v>32.9598</v>
       </c>
       <c r="E27" t="n">
-        <v>15.1533</v>
+        <v>15.4867</v>
       </c>
       <c r="F27" t="n">
-        <v>28.915</v>
+        <v>28.9849</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.5604</v>
+        <v>21.5607</v>
       </c>
       <c r="C28" t="n">
-        <v>17.9939</v>
+        <v>18.0067</v>
       </c>
       <c r="D28" t="n">
-        <v>32.5721</v>
+        <v>32.8289</v>
       </c>
       <c r="E28" t="n">
-        <v>14.7932</v>
+        <v>15.1124</v>
       </c>
       <c r="F28" t="n">
-        <v>28.6669</v>
+        <v>28.7897</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.0496</v>
+        <v>21.1013</v>
       </c>
       <c r="C29" t="n">
-        <v>18.0227</v>
+        <v>17.9621</v>
       </c>
       <c r="D29" t="n">
-        <v>32.6156</v>
+        <v>32.8815</v>
       </c>
       <c r="E29" t="n">
-        <v>14.5844</v>
+        <v>14.8158</v>
       </c>
       <c r="F29" t="n">
-        <v>28.332</v>
+        <v>28.3919</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6191</v>
+        <v>20.6245</v>
       </c>
       <c r="C30" t="n">
-        <v>17.9393</v>
+        <v>17.8985</v>
       </c>
       <c r="D30" t="n">
-        <v>32.8855</v>
+        <v>33.1354</v>
       </c>
       <c r="E30" t="n">
-        <v>14.2259</v>
+        <v>14.4561</v>
       </c>
       <c r="F30" t="n">
-        <v>28.0841</v>
+        <v>28.1718</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.076</v>
+        <v>20.0592</v>
       </c>
       <c r="C31" t="n">
-        <v>17.787</v>
+        <v>17.8471</v>
       </c>
       <c r="D31" t="n">
-        <v>32.826</v>
+        <v>32.9781</v>
       </c>
       <c r="E31" t="n">
-        <v>13.9387</v>
+        <v>14.1755</v>
       </c>
       <c r="F31" t="n">
-        <v>27.6898</v>
+        <v>27.8601</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6693</v>
+        <v>19.6532</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7472</v>
+        <v>17.7426</v>
       </c>
       <c r="D32" t="n">
-        <v>32.9751</v>
+        <v>33.168</v>
       </c>
       <c r="E32" t="n">
-        <v>13.7013</v>
+        <v>13.8663</v>
       </c>
       <c r="F32" t="n">
-        <v>27.3436</v>
+        <v>27.5213</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0571</v>
+        <v>19.0743</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6592</v>
+        <v>17.5835</v>
       </c>
       <c r="D33" t="n">
-        <v>32.9509</v>
+        <v>33.3228</v>
       </c>
       <c r="E33" t="n">
-        <v>13.7078</v>
+        <v>13.6297</v>
       </c>
       <c r="F33" t="n">
-        <v>26.8891</v>
+        <v>27.1773</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4868</v>
+        <v>18.4265</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5711</v>
+        <v>17.5199</v>
       </c>
       <c r="D34" t="n">
-        <v>33.0081</v>
+        <v>33.3387</v>
       </c>
       <c r="E34" t="n">
-        <v>13.4087</v>
+        <v>13.3561</v>
       </c>
       <c r="F34" t="n">
-        <v>26.6695</v>
+        <v>26.9303</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9331</v>
+        <v>17.924</v>
       </c>
       <c r="C35" t="n">
-        <v>17.5119</v>
+        <v>17.4683</v>
       </c>
       <c r="D35" t="n">
-        <v>32.6011</v>
+        <v>32.7885</v>
       </c>
       <c r="E35" t="n">
-        <v>18.0322</v>
+        <v>18.1625</v>
       </c>
       <c r="F35" t="n">
-        <v>30.9755</v>
+        <v>31.1893</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2845</v>
+        <v>17.2497</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4343</v>
+        <v>17.4245</v>
       </c>
       <c r="D36" t="n">
-        <v>32.487</v>
+        <v>32.6039</v>
       </c>
       <c r="E36" t="n">
-        <v>17.4533</v>
+        <v>17.631</v>
       </c>
       <c r="F36" t="n">
-        <v>30.4256</v>
+        <v>30.711</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.6013</v>
+        <v>16.3954</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8536</v>
+        <v>18.8446</v>
       </c>
       <c r="D37" t="n">
-        <v>32.3068</v>
+        <v>32.8039</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0297</v>
+        <v>17.1271</v>
       </c>
       <c r="F37" t="n">
-        <v>30.1627</v>
+        <v>30.3569</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.6872</v>
+        <v>23.7146</v>
       </c>
       <c r="C38" t="n">
-        <v>18.7336</v>
+        <v>18.6689</v>
       </c>
       <c r="D38" t="n">
-        <v>32.2595</v>
+        <v>32.4713</v>
       </c>
       <c r="E38" t="n">
-        <v>16.6959</v>
+        <v>16.7961</v>
       </c>
       <c r="F38" t="n">
-        <v>29.7872</v>
+        <v>30.0332</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.3482</v>
+        <v>23.3237</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5234</v>
+        <v>18.5082</v>
       </c>
       <c r="D39" t="n">
-        <v>32.3401</v>
+        <v>32.5681</v>
       </c>
       <c r="E39" t="n">
-        <v>16.3052</v>
+        <v>16.4288</v>
       </c>
       <c r="F39" t="n">
-        <v>29.4591</v>
+        <v>29.7258</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.946</v>
+        <v>22.889</v>
       </c>
       <c r="C40" t="n">
-        <v>18.3877</v>
+        <v>18.3891</v>
       </c>
       <c r="D40" t="n">
-        <v>32.6649</v>
+        <v>32.9036</v>
       </c>
       <c r="E40" t="n">
-        <v>16.0288</v>
+        <v>16.1561</v>
       </c>
       <c r="F40" t="n">
-        <v>29.0953</v>
+        <v>29.4058</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4779</v>
+        <v>22.4333</v>
       </c>
       <c r="C41" t="n">
-        <v>18.2451</v>
+        <v>18.2503</v>
       </c>
       <c r="D41" t="n">
-        <v>32.6846</v>
+        <v>32.9993</v>
       </c>
       <c r="E41" t="n">
-        <v>15.7167</v>
+        <v>15.8497</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9182</v>
+        <v>29.1097</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.9662</v>
+        <v>21.961</v>
       </c>
       <c r="C42" t="n">
-        <v>18.1089</v>
+        <v>18.1017</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8461</v>
+        <v>32.9369</v>
       </c>
       <c r="E42" t="n">
-        <v>15.4384</v>
+        <v>15.4864</v>
       </c>
       <c r="F42" t="n">
-        <v>28.654</v>
+        <v>28.8613</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4506</v>
+        <v>21.4113</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9789</v>
+        <v>17.9317</v>
       </c>
       <c r="D43" t="n">
-        <v>32.621</v>
+        <v>32.7426</v>
       </c>
       <c r="E43" t="n">
-        <v>15.1066</v>
+        <v>15.1816</v>
       </c>
       <c r="F43" t="n">
-        <v>28.3129</v>
+        <v>28.5713</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.9092</v>
+        <v>20.879</v>
       </c>
       <c r="C44" t="n">
-        <v>17.9311</v>
+        <v>17.9081</v>
       </c>
       <c r="D44" t="n">
-        <v>32.5732</v>
+        <v>32.7649</v>
       </c>
       <c r="E44" t="n">
-        <v>14.8683</v>
+        <v>14.9124</v>
       </c>
       <c r="F44" t="n">
-        <v>28.0693</v>
+        <v>28.3624</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4545</v>
+        <v>20.4265</v>
       </c>
       <c r="C45" t="n">
-        <v>17.8362</v>
+        <v>17.7836</v>
       </c>
       <c r="D45" t="n">
-        <v>32.6894</v>
+        <v>32.8128</v>
       </c>
       <c r="E45" t="n">
-        <v>14.5277</v>
+        <v>14.5797</v>
       </c>
       <c r="F45" t="n">
-        <v>27.7297</v>
+        <v>27.9518</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9474</v>
+        <v>19.9061</v>
       </c>
       <c r="C46" t="n">
-        <v>17.7304</v>
+        <v>17.6957</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9184</v>
+        <v>32.9345</v>
       </c>
       <c r="E46" t="n">
-        <v>14.2379</v>
+        <v>14.3029</v>
       </c>
       <c r="F46" t="n">
-        <v>27.5113</v>
+        <v>27.779</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3843</v>
+        <v>19.3685</v>
       </c>
       <c r="C47" t="n">
-        <v>17.6005</v>
+        <v>17.5549</v>
       </c>
       <c r="D47" t="n">
-        <v>32.9516</v>
+        <v>33.0635</v>
       </c>
       <c r="E47" t="n">
-        <v>13.943</v>
+        <v>13.9939</v>
       </c>
       <c r="F47" t="n">
-        <v>27.1085</v>
+        <v>27.4394</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.7903</v>
+        <v>18.7879</v>
       </c>
       <c r="C48" t="n">
-        <v>17.5478</v>
+        <v>17.4938</v>
       </c>
       <c r="D48" t="n">
-        <v>33.1981</v>
+        <v>33.1796</v>
       </c>
       <c r="E48" t="n">
-        <v>13.704</v>
+        <v>13.6697</v>
       </c>
       <c r="F48" t="n">
-        <v>26.8131</v>
+        <v>27.0702</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1611</v>
+        <v>18.1503</v>
       </c>
       <c r="C49" t="n">
-        <v>17.4326</v>
+        <v>17.3871</v>
       </c>
       <c r="D49" t="n">
-        <v>33.3249</v>
+        <v>33.5348</v>
       </c>
       <c r="E49" t="n">
-        <v>13.3653</v>
+        <v>13.3536</v>
       </c>
       <c r="F49" t="n">
-        <v>26.644</v>
+        <v>26.7399</v>
       </c>
     </row>
     <row r="50">
@@ -6042,16 +6042,16 @@
         <v>17.5554</v>
       </c>
       <c r="C50" t="n">
-        <v>17.39</v>
+        <v>17.3226</v>
       </c>
       <c r="D50" t="n">
-        <v>33.0983</v>
+        <v>32.7086</v>
       </c>
       <c r="E50" t="n">
-        <v>17.792</v>
+        <v>17.7545</v>
       </c>
       <c r="F50" t="n">
-        <v>30.6093</v>
+        <v>30.8524</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.8142</v>
+        <v>16.7866</v>
       </c>
       <c r="C51" t="n">
-        <v>18.869</v>
+        <v>18.8259</v>
       </c>
       <c r="D51" t="n">
-        <v>33.2624</v>
+        <v>33.0067</v>
       </c>
       <c r="E51" t="n">
-        <v>17.2845</v>
+        <v>17.3747</v>
       </c>
       <c r="F51" t="n">
-        <v>30.2236</v>
+        <v>30.4879</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.8761</v>
+        <v>15.8657</v>
       </c>
       <c r="C52" t="n">
-        <v>18.7095</v>
+        <v>18.6302</v>
       </c>
       <c r="D52" t="n">
-        <v>33.2147</v>
+        <v>32.9631</v>
       </c>
       <c r="E52" t="n">
-        <v>16.994</v>
+        <v>17.0992</v>
       </c>
       <c r="F52" t="n">
-        <v>29.9293</v>
+        <v>30.1518</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.4956</v>
+        <v>23.4704</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4919</v>
+        <v>18.4845</v>
       </c>
       <c r="D53" t="n">
-        <v>33.2793</v>
+        <v>33.1496</v>
       </c>
       <c r="E53" t="n">
-        <v>16.6751</v>
+        <v>16.6773</v>
       </c>
       <c r="F53" t="n">
-        <v>29.7284</v>
+        <v>29.8883</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1658</v>
+        <v>23.1204</v>
       </c>
       <c r="C54" t="n">
-        <v>18.401</v>
+        <v>18.4277</v>
       </c>
       <c r="D54" t="n">
-        <v>33.299</v>
+        <v>33.3317</v>
       </c>
       <c r="E54" t="n">
-        <v>16.2604</v>
+        <v>16.3588</v>
       </c>
       <c r="F54" t="n">
-        <v>29.3326</v>
+        <v>29.5309</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6273</v>
+        <v>22.6118</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2629</v>
+        <v>18.2357</v>
       </c>
       <c r="D55" t="n">
-        <v>33.0321</v>
+        <v>33.1548</v>
       </c>
       <c r="E55" t="n">
-        <v>15.9536</v>
+        <v>16.0573</v>
       </c>
       <c r="F55" t="n">
-        <v>28.9555</v>
+        <v>29.2084</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1487</v>
+        <v>22.1401</v>
       </c>
       <c r="C56" t="n">
-        <v>18.1231</v>
+        <v>18.07</v>
       </c>
       <c r="D56" t="n">
-        <v>33.0799</v>
+        <v>33.3301</v>
       </c>
       <c r="E56" t="n">
-        <v>15.547</v>
+        <v>15.7637</v>
       </c>
       <c r="F56" t="n">
-        <v>28.8209</v>
+        <v>28.9378</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.606</v>
+        <v>21.58</v>
       </c>
       <c r="C57" t="n">
-        <v>18.0276</v>
+        <v>17.9931</v>
       </c>
       <c r="D57" t="n">
-        <v>33.5734</v>
+        <v>33.7164</v>
       </c>
       <c r="E57" t="n">
-        <v>15.2453</v>
+        <v>15.469</v>
       </c>
       <c r="F57" t="n">
-        <v>28.5338</v>
+        <v>28.6435</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0794</v>
+        <v>21.0514</v>
       </c>
       <c r="C58" t="n">
-        <v>17.9154</v>
+        <v>17.8925</v>
       </c>
       <c r="D58" t="n">
-        <v>33.6741</v>
+        <v>33.8329</v>
       </c>
       <c r="E58" t="n">
-        <v>14.9426</v>
+        <v>15.1873</v>
       </c>
       <c r="F58" t="n">
-        <v>28.2391</v>
+        <v>28.4674</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5717</v>
+        <v>20.5779</v>
       </c>
       <c r="C59" t="n">
-        <v>17.809</v>
+        <v>17.7605</v>
       </c>
       <c r="D59" t="n">
-        <v>34.1006</v>
+        <v>34.2679</v>
       </c>
       <c r="E59" t="n">
-        <v>14.6334</v>
+        <v>14.9024</v>
       </c>
       <c r="F59" t="n">
-        <v>27.9723</v>
+        <v>28.1724</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>20.0195</v>
+        <v>19.9976</v>
       </c>
       <c r="C60" t="n">
-        <v>17.7361</v>
+        <v>17.6987</v>
       </c>
       <c r="D60" t="n">
-        <v>34.2831</v>
+        <v>34.5346</v>
       </c>
       <c r="E60" t="n">
-        <v>14.3287</v>
+        <v>14.6061</v>
       </c>
       <c r="F60" t="n">
-        <v>27.6386</v>
+        <v>27.7927</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5148</v>
+        <v>19.5238</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6426</v>
+        <v>17.6028</v>
       </c>
       <c r="D61" t="n">
-        <v>34.7751</v>
+        <v>34.8895</v>
       </c>
       <c r="E61" t="n">
-        <v>14.2671</v>
+        <v>14.3085</v>
       </c>
       <c r="F61" t="n">
-        <v>27.2447</v>
+        <v>27.4728</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>19.0206</v>
+        <v>18.9763</v>
       </c>
       <c r="C62" t="n">
-        <v>17.568</v>
+        <v>17.5309</v>
       </c>
       <c r="D62" t="n">
-        <v>35.1571</v>
+        <v>35.1762</v>
       </c>
       <c r="E62" t="n">
-        <v>13.8297</v>
+        <v>13.9936</v>
       </c>
       <c r="F62" t="n">
-        <v>27.0041</v>
+        <v>27.1825</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3209</v>
+        <v>18.3567</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4911</v>
+        <v>17.4662</v>
       </c>
       <c r="D63" t="n">
-        <v>35.4788</v>
+        <v>35.3251</v>
       </c>
       <c r="E63" t="n">
-        <v>13.5082</v>
+        <v>13.5723</v>
       </c>
       <c r="F63" t="n">
-        <v>26.7106</v>
+        <v>26.9225</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7265</v>
+        <v>17.7581</v>
       </c>
       <c r="C64" t="n">
-        <v>17.4591</v>
+        <v>17.3949</v>
       </c>
       <c r="D64" t="n">
-        <v>39.2077</v>
+        <v>39.3146</v>
       </c>
       <c r="E64" t="n">
-        <v>18.1334</v>
+        <v>18.3965</v>
       </c>
       <c r="F64" t="n">
-        <v>30.8586</v>
+        <v>31.0519</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0504</v>
+        <v>17.0203</v>
       </c>
       <c r="C65" t="n">
-        <v>19.0531</v>
+        <v>18.9398</v>
       </c>
       <c r="D65" t="n">
-        <v>38.8108</v>
+        <v>38.8239</v>
       </c>
       <c r="E65" t="n">
-        <v>17.8096</v>
+        <v>17.6794</v>
       </c>
       <c r="F65" t="n">
-        <v>30.5538</v>
+        <v>30.6697</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1954</v>
+        <v>16.1528</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7982</v>
+        <v>18.7553</v>
       </c>
       <c r="D66" t="n">
-        <v>38.811</v>
+        <v>38.962</v>
       </c>
       <c r="E66" t="n">
-        <v>17.3289</v>
+        <v>17.234</v>
       </c>
       <c r="F66" t="n">
-        <v>30.1875</v>
+        <v>30.3025</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6498</v>
+        <v>23.6378</v>
       </c>
       <c r="C67" t="n">
-        <v>18.6292</v>
+        <v>18.576</v>
       </c>
       <c r="D67" t="n">
-        <v>38.8512</v>
+        <v>38.9403</v>
       </c>
       <c r="E67" t="n">
-        <v>16.915</v>
+        <v>16.8382</v>
       </c>
       <c r="F67" t="n">
-        <v>29.8863</v>
+        <v>30.0708</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2501</v>
+        <v>23.2343</v>
       </c>
       <c r="C68" t="n">
-        <v>18.4795</v>
+        <v>18.444</v>
       </c>
       <c r="D68" t="n">
-        <v>40.1911</v>
+        <v>40.4206</v>
       </c>
       <c r="E68" t="n">
-        <v>16.5089</v>
+        <v>16.4314</v>
       </c>
       <c r="F68" t="n">
-        <v>29.5785</v>
+        <v>29.721</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7789</v>
+        <v>22.7325</v>
       </c>
       <c r="C69" t="n">
-        <v>18.3774</v>
+        <v>18.3223</v>
       </c>
       <c r="D69" t="n">
-        <v>40.1947</v>
+        <v>40.2729</v>
       </c>
       <c r="E69" t="n">
-        <v>16.0968</v>
+        <v>16.0524</v>
       </c>
       <c r="F69" t="n">
-        <v>29.3047</v>
+        <v>29.462</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.2971</v>
+        <v>22.2777</v>
       </c>
       <c r="C70" t="n">
-        <v>18.3164</v>
+        <v>18.2647</v>
       </c>
       <c r="D70" t="n">
-        <v>40.1857</v>
+        <v>40.2884</v>
       </c>
       <c r="E70" t="n">
-        <v>15.7377</v>
+        <v>15.6887</v>
       </c>
       <c r="F70" t="n">
-        <v>28.9673</v>
+        <v>29.1428</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.785</v>
+        <v>21.7558</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1732</v>
+        <v>18.1324</v>
       </c>
       <c r="D71" t="n">
-        <v>39.0307</v>
+        <v>39.1542</v>
       </c>
       <c r="E71" t="n">
-        <v>15.3539</v>
+        <v>15.4171</v>
       </c>
       <c r="F71" t="n">
-        <v>28.7354</v>
+        <v>28.8912</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2616</v>
+        <v>21.2205</v>
       </c>
       <c r="C72" t="n">
-        <v>18.076</v>
+        <v>18.0359</v>
       </c>
       <c r="D72" t="n">
-        <v>38.9895</v>
+        <v>39.2055</v>
       </c>
       <c r="E72" t="n">
-        <v>15.2886</v>
+        <v>15.3894</v>
       </c>
       <c r="F72" t="n">
-        <v>28.2804</v>
+        <v>28.5326</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7565</v>
+        <v>20.7147</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9501</v>
+        <v>17.9081</v>
       </c>
       <c r="D73" t="n">
-        <v>38.9125</v>
+        <v>39.191</v>
       </c>
       <c r="E73" t="n">
-        <v>15.03</v>
+        <v>15.0708</v>
       </c>
       <c r="F73" t="n">
-        <v>28.025</v>
+        <v>28.2361</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1888</v>
+        <v>20.1635</v>
       </c>
       <c r="C74" t="n">
-        <v>17.8774</v>
+        <v>17.824</v>
       </c>
       <c r="D74" t="n">
-        <v>39.1713</v>
+        <v>39.3686</v>
       </c>
       <c r="E74" t="n">
-        <v>14.7331</v>
+        <v>14.7833</v>
       </c>
       <c r="F74" t="n">
-        <v>27.685</v>
+        <v>27.9136</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6621</v>
+        <v>19.6548</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7591</v>
+        <v>17.7245</v>
       </c>
       <c r="D75" t="n">
-        <v>39.0695</v>
+        <v>39.2769</v>
       </c>
       <c r="E75" t="n">
-        <v>14.4494</v>
+        <v>14.5065</v>
       </c>
       <c r="F75" t="n">
-        <v>27.5146</v>
+        <v>27.6315</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1474</v>
+        <v>19.1133</v>
       </c>
       <c r="C76" t="n">
-        <v>17.7054</v>
+        <v>17.6435</v>
       </c>
       <c r="D76" t="n">
-        <v>39.0591</v>
+        <v>39.3018</v>
       </c>
       <c r="E76" t="n">
-        <v>14.0327</v>
+        <v>14.199</v>
       </c>
       <c r="F76" t="n">
-        <v>27.2107</v>
+        <v>27.3569</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5588</v>
+        <v>18.5204</v>
       </c>
       <c r="C77" t="n">
-        <v>17.615</v>
+        <v>17.5809</v>
       </c>
       <c r="D77" t="n">
-        <v>39.1341</v>
+        <v>39.2922</v>
       </c>
       <c r="E77" t="n">
-        <v>13.6847</v>
+        <v>13.8713</v>
       </c>
       <c r="F77" t="n">
-        <v>26.8793</v>
+        <v>27.0539</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9632</v>
+        <v>17.9232</v>
       </c>
       <c r="C78" t="n">
-        <v>17.446</v>
+        <v>17.3902</v>
       </c>
       <c r="D78" t="n">
-        <v>45.2374</v>
+        <v>45.7514</v>
       </c>
       <c r="E78" t="n">
-        <v>18.2238</v>
+        <v>18.2982</v>
       </c>
       <c r="F78" t="n">
-        <v>30.838</v>
+        <v>30.9674</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2508</v>
+        <v>17.2049</v>
       </c>
       <c r="C79" t="n">
-        <v>19.3624</v>
+        <v>19.257</v>
       </c>
       <c r="D79" t="n">
-        <v>45.7076</v>
+        <v>45.9646</v>
       </c>
       <c r="E79" t="n">
-        <v>17.7532</v>
+        <v>17.842</v>
       </c>
       <c r="F79" t="n">
-        <v>30.4895</v>
+        <v>30.6437</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.3862</v>
+        <v>16.3741</v>
       </c>
       <c r="C80" t="n">
-        <v>19.1828</v>
+        <v>19.0363</v>
       </c>
       <c r="D80" t="n">
-        <v>46.2118</v>
+        <v>46.4748</v>
       </c>
       <c r="E80" t="n">
-        <v>17.3811</v>
+        <v>17.4855</v>
       </c>
       <c r="F80" t="n">
-        <v>30.1424</v>
+        <v>30.3402</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7804</v>
+        <v>23.7616</v>
       </c>
       <c r="C81" t="n">
-        <v>18.9272</v>
+        <v>18.9084</v>
       </c>
       <c r="D81" t="n">
-        <v>45.7088</v>
+        <v>45.8974</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0285</v>
+        <v>17.0119</v>
       </c>
       <c r="F81" t="n">
-        <v>29.8534</v>
+        <v>30.0126</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3896</v>
+        <v>23.3965</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7615</v>
+        <v>18.708</v>
       </c>
       <c r="D82" t="n">
-        <v>43.6251</v>
+        <v>43.792</v>
       </c>
       <c r="E82" t="n">
-        <v>16.6917</v>
+        <v>16.6933</v>
       </c>
       <c r="F82" t="n">
-        <v>29.5374</v>
+        <v>29.7081</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9307</v>
+        <v>22.9334</v>
       </c>
       <c r="C83" t="n">
-        <v>18.5872</v>
+        <v>18.5741</v>
       </c>
       <c r="D83" t="n">
-        <v>43.2692</v>
+        <v>43.5743</v>
       </c>
       <c r="E83" t="n">
-        <v>16.3722</v>
+        <v>16.3923</v>
       </c>
       <c r="F83" t="n">
-        <v>29.2218</v>
+        <v>29.4117</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4377</v>
+        <v>22.4129</v>
       </c>
       <c r="C84" t="n">
-        <v>18.5241</v>
+        <v>18.4292</v>
       </c>
       <c r="D84" t="n">
-        <v>42.7806</v>
+        <v>42.9894</v>
       </c>
       <c r="E84" t="n">
-        <v>16.0797</v>
+        <v>16.0693</v>
       </c>
       <c r="F84" t="n">
-        <v>28.9315</v>
+        <v>29.1189</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9585</v>
+        <v>21.9367</v>
       </c>
       <c r="C85" t="n">
-        <v>18.2064</v>
+        <v>18.2011</v>
       </c>
       <c r="D85" t="n">
-        <v>44.0292</v>
+        <v>44.1934</v>
       </c>
       <c r="E85" t="n">
-        <v>15.7578</v>
+        <v>15.758</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6453</v>
+        <v>28.7994</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.408</v>
+        <v>21.4047</v>
       </c>
       <c r="C86" t="n">
-        <v>18.0995</v>
+        <v>18.099</v>
       </c>
       <c r="D86" t="n">
-        <v>43.5651</v>
+        <v>43.6882</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4786</v>
+        <v>15.475</v>
       </c>
       <c r="F86" t="n">
-        <v>28.3892</v>
+        <v>28.5324</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.9643</v>
+        <v>20.8752</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9733</v>
+        <v>17.9545</v>
       </c>
       <c r="D87" t="n">
-        <v>43.193</v>
+        <v>43.3314</v>
       </c>
       <c r="E87" t="n">
-        <v>15.1726</v>
+        <v>15.1778</v>
       </c>
       <c r="F87" t="n">
-        <v>28.1002</v>
+        <v>28.2654</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3622</v>
+        <v>20.3586</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8736</v>
+        <v>17.8458</v>
       </c>
       <c r="D88" t="n">
-        <v>42.836</v>
+        <v>43.0373</v>
       </c>
       <c r="E88" t="n">
-        <v>14.9002</v>
+        <v>14.8934</v>
       </c>
       <c r="F88" t="n">
-        <v>27.7599</v>
+        <v>27.9387</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8419</v>
+        <v>19.8352</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7649</v>
+        <v>17.7462</v>
       </c>
       <c r="D89" t="n">
-        <v>42.7067</v>
+        <v>42.8604</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6185</v>
+        <v>14.6033</v>
       </c>
       <c r="F89" t="n">
-        <v>27.4945</v>
+        <v>27.6452</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.3026</v>
+        <v>19.3075</v>
       </c>
       <c r="C90" t="n">
-        <v>17.6975</v>
+        <v>17.6445</v>
       </c>
       <c r="D90" t="n">
-        <v>42.4753</v>
+        <v>42.5963</v>
       </c>
       <c r="E90" t="n">
-        <v>14.2989</v>
+        <v>14.2872</v>
       </c>
       <c r="F90" t="n">
-        <v>27.1656</v>
+        <v>27.3242</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.734</v>
+        <v>18.7102</v>
       </c>
       <c r="C91" t="n">
-        <v>17.5726</v>
+        <v>17.5561</v>
       </c>
       <c r="D91" t="n">
-        <v>42.1471</v>
+        <v>42.3196</v>
       </c>
       <c r="E91" t="n">
-        <v>13.9987</v>
+        <v>13.9982</v>
       </c>
       <c r="F91" t="n">
-        <v>26.8499</v>
+        <v>27.0184</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.101</v>
+        <v>18.0902</v>
       </c>
       <c r="C92" t="n">
-        <v>17.5022</v>
+        <v>17.4828</v>
       </c>
       <c r="D92" t="n">
-        <v>47.5054</v>
+        <v>47.7974</v>
       </c>
       <c r="E92" t="n">
-        <v>18.2664</v>
+        <v>18.2354</v>
       </c>
       <c r="F92" t="n">
-        <v>30.8218</v>
+        <v>31.1544</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.4282</v>
+        <v>17.365</v>
       </c>
       <c r="C93" t="n">
-        <v>17.4829</v>
+        <v>17.4024</v>
       </c>
       <c r="D93" t="n">
-        <v>46.0438</v>
+        <v>46.3299</v>
       </c>
       <c r="E93" t="n">
-        <v>17.8273</v>
+        <v>17.7966</v>
       </c>
       <c r="F93" t="n">
-        <v>30.5991</v>
+        <v>31.0898</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6394</v>
+        <v>16.6492</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0379</v>
+        <v>19.0491</v>
       </c>
       <c r="D94" t="n">
-        <v>44.4665</v>
+        <v>44.7746</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4532</v>
+        <v>17.4048</v>
       </c>
       <c r="F94" t="n">
-        <v>30.42</v>
+        <v>30.4977</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8832</v>
+        <v>23.8686</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8613</v>
+        <v>18.8492</v>
       </c>
       <c r="D95" t="n">
-        <v>43.7641</v>
+        <v>44.1332</v>
       </c>
       <c r="E95" t="n">
-        <v>17.0647</v>
+        <v>17.1069</v>
       </c>
       <c r="F95" t="n">
-        <v>29.8666</v>
+        <v>30.1458</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4762</v>
+        <v>23.4616</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6669</v>
+        <v>18.6523</v>
       </c>
       <c r="D96" t="n">
-        <v>43.2462</v>
+        <v>43.591</v>
       </c>
       <c r="E96" t="n">
-        <v>16.578</v>
+        <v>16.5779</v>
       </c>
       <c r="F96" t="n">
-        <v>29.6544</v>
+        <v>29.8799</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.044</v>
+        <v>23.0237</v>
       </c>
       <c r="C97" t="n">
-        <v>18.499</v>
+        <v>18.5099</v>
       </c>
       <c r="D97" t="n">
-        <v>45.2747</v>
+        <v>45.6829</v>
       </c>
       <c r="E97" t="n">
-        <v>16.2225</v>
+        <v>16.2264</v>
       </c>
       <c r="F97" t="n">
-        <v>29.3793</v>
+        <v>29.6218</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5746</v>
+        <v>22.5467</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3598</v>
+        <v>18.3502</v>
       </c>
       <c r="D98" t="n">
-        <v>44.7705</v>
+        <v>45.1986</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9137</v>
+        <v>15.9154</v>
       </c>
       <c r="F98" t="n">
-        <v>29.0275</v>
+        <v>29.3296</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0558</v>
+        <v>22.0385</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2156</v>
+        <v>18.2089</v>
       </c>
       <c r="D99" t="n">
-        <v>44.1874</v>
+        <v>44.4565</v>
       </c>
       <c r="E99" t="n">
-        <v>15.628</v>
+        <v>15.6197</v>
       </c>
       <c r="F99" t="n">
-        <v>28.7381</v>
+        <v>28.9792</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5251</v>
+        <v>21.5142</v>
       </c>
       <c r="C100" t="n">
-        <v>18.2049</v>
+        <v>18.1737</v>
       </c>
       <c r="D100" t="n">
-        <v>41.6312</v>
+        <v>41.994</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3036</v>
+        <v>15.3022</v>
       </c>
       <c r="F100" t="n">
-        <v>28.4409</v>
+        <v>28.6713</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9899</v>
+        <v>20.9775</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0553</v>
+        <v>18.0639</v>
       </c>
       <c r="D101" t="n">
-        <v>41.2339</v>
+        <v>41.8585</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0426</v>
+        <v>15.0345</v>
       </c>
       <c r="F101" t="n">
-        <v>28.1339</v>
+        <v>28.3882</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4669</v>
+        <v>20.4535</v>
       </c>
       <c r="C102" t="n">
-        <v>17.9621</v>
+        <v>17.974</v>
       </c>
       <c r="D102" t="n">
-        <v>40.9032</v>
+        <v>41.1617</v>
       </c>
       <c r="E102" t="n">
-        <v>14.7653</v>
+        <v>14.8235</v>
       </c>
       <c r="F102" t="n">
-        <v>27.8446</v>
+        <v>28.0872</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9285</v>
+        <v>19.9069</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8574</v>
+        <v>17.8616</v>
       </c>
       <c r="D103" t="n">
-        <v>40.9676</v>
+        <v>41.2515</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4847</v>
+        <v>14.5805</v>
       </c>
       <c r="F103" t="n">
-        <v>27.5504</v>
+        <v>27.8042</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.4083</v>
+        <v>19.3913</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7738</v>
+        <v>17.7635</v>
       </c>
       <c r="D104" t="n">
-        <v>40.2712</v>
+        <v>40.4845</v>
       </c>
       <c r="E104" t="n">
-        <v>14.2203</v>
+        <v>14.2216</v>
       </c>
       <c r="F104" t="n">
-        <v>27.2614</v>
+        <v>27.4941</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8294</v>
+        <v>18.8114</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6533</v>
+        <v>17.6428</v>
       </c>
       <c r="D105" t="n">
-        <v>40.3552</v>
+        <v>40.6539</v>
       </c>
       <c r="E105" t="n">
-        <v>13.9334</v>
+        <v>13.948</v>
       </c>
       <c r="F105" t="n">
-        <v>26.9409</v>
+        <v>27.1757</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2648</v>
+        <v>18.2161</v>
       </c>
       <c r="C106" t="n">
-        <v>17.577</v>
+        <v>17.5632</v>
       </c>
       <c r="D106" t="n">
-        <v>39.7585</v>
+        <v>40.0295</v>
       </c>
       <c r="E106" t="n">
-        <v>13.6461</v>
+        <v>13.6214</v>
       </c>
       <c r="F106" t="n">
-        <v>26.6229</v>
+        <v>26.8856</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6094</v>
+        <v>17.6129</v>
       </c>
       <c r="C107" t="n">
-        <v>17.5095</v>
+        <v>17.4897</v>
       </c>
       <c r="D107" t="n">
-        <v>44.7774</v>
+        <v>45.1783</v>
       </c>
       <c r="E107" t="n">
-        <v>17.7711</v>
+        <v>17.7168</v>
       </c>
       <c r="F107" t="n">
-        <v>30.6856</v>
+        <v>30.8986</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8495</v>
+        <v>16.8582</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1572</v>
+        <v>19.1284</v>
       </c>
       <c r="D108" t="n">
-        <v>45.4285</v>
+        <v>46.1391</v>
       </c>
       <c r="E108" t="n">
-        <v>17.354</v>
+        <v>17.3566</v>
       </c>
       <c r="F108" t="n">
-        <v>30.3002</v>
+        <v>30.5205</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9229</v>
+        <v>15.8977</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9742</v>
+        <v>18.9687</v>
       </c>
       <c r="D109" t="n">
-        <v>44.7194</v>
+        <v>45.4336</v>
       </c>
       <c r="E109" t="n">
-        <v>17.0441</v>
+        <v>16.9796</v>
       </c>
       <c r="F109" t="n">
-        <v>29.9717</v>
+        <v>30.2578</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5747</v>
+        <v>23.5532</v>
       </c>
       <c r="C110" t="n">
-        <v>18.7133</v>
+        <v>18.6911</v>
       </c>
       <c r="D110" t="n">
-        <v>44.193</v>
+        <v>44.6296</v>
       </c>
       <c r="E110" t="n">
-        <v>16.8124</v>
+        <v>16.7999</v>
       </c>
       <c r="F110" t="n">
-        <v>29.566</v>
+        <v>29.8621</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1421</v>
+        <v>23.1246</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5731</v>
+        <v>18.5525</v>
       </c>
       <c r="D111" t="n">
-        <v>43.6404</v>
+        <v>44.1809</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4884</v>
+        <v>16.4387</v>
       </c>
       <c r="F111" t="n">
-        <v>29.3115</v>
+        <v>29.5702</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6575</v>
+        <v>22.6432</v>
       </c>
       <c r="C112" t="n">
-        <v>18.4016</v>
+        <v>18.393</v>
       </c>
       <c r="D112" t="n">
-        <v>40.7725</v>
+        <v>40.9144</v>
       </c>
       <c r="E112" t="n">
-        <v>16.1958</v>
+        <v>16.0818</v>
       </c>
       <c r="F112" t="n">
-        <v>29.0034</v>
+        <v>29.2864</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1581</v>
+        <v>22.1403</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2426</v>
+        <v>18.2524</v>
       </c>
       <c r="D113" t="n">
-        <v>40.3964</v>
+        <v>40.6142</v>
       </c>
       <c r="E113" t="n">
-        <v>15.8719</v>
+        <v>15.7492</v>
       </c>
       <c r="F113" t="n">
-        <v>28.6706</v>
+        <v>28.9847</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.632</v>
+        <v>21.6195</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1273</v>
+        <v>18.132</v>
       </c>
       <c r="D114" t="n">
-        <v>42.1346</v>
+        <v>42.4487</v>
       </c>
       <c r="E114" t="n">
-        <v>15.5864</v>
+        <v>15.5818</v>
       </c>
       <c r="F114" t="n">
-        <v>28.4066</v>
+        <v>28.6786</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.1047</v>
+        <v>21.0887</v>
       </c>
       <c r="C115" t="n">
-        <v>17.9964</v>
+        <v>17.9755</v>
       </c>
       <c r="D115" t="n">
-        <v>41.7802</v>
+        <v>42.0144</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3341</v>
+        <v>15.3318</v>
       </c>
       <c r="F115" t="n">
-        <v>28.1207</v>
+        <v>28.3978</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5734</v>
+        <v>20.5503</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8737</v>
+        <v>17.8639</v>
       </c>
       <c r="D116" t="n">
-        <v>41.3928</v>
+        <v>41.6794</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8346</v>
+        <v>14.8382</v>
       </c>
       <c r="F116" t="n">
-        <v>27.9404</v>
+        <v>28.1566</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.0404</v>
+        <v>20.0212</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7812</v>
+        <v>17.7661</v>
       </c>
       <c r="D117" t="n">
-        <v>41.0933</v>
+        <v>41.354</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5507</v>
+        <v>14.5484</v>
       </c>
       <c r="F117" t="n">
-        <v>27.606</v>
+        <v>27.8503</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.5212</v>
+        <v>19.4935</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6936</v>
+        <v>17.6737</v>
       </c>
       <c r="D118" t="n">
-        <v>40.7987</v>
+        <v>41.0729</v>
       </c>
       <c r="E118" t="n">
-        <v>14.2852</v>
+        <v>14.274</v>
       </c>
       <c r="F118" t="n">
-        <v>27.2972</v>
+        <v>27.5607</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9382</v>
+        <v>18.9249</v>
       </c>
       <c r="C119" t="n">
-        <v>17.612</v>
+        <v>17.5962</v>
       </c>
       <c r="D119" t="n">
-        <v>40.5365</v>
+        <v>40.7935</v>
       </c>
       <c r="E119" t="n">
-        <v>14.0016</v>
+        <v>13.9996</v>
       </c>
       <c r="F119" t="n">
-        <v>26.9922</v>
+        <v>27.2324</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3638</v>
+        <v>18.3675</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5285</v>
+        <v>17.5211</v>
       </c>
       <c r="D120" t="n">
-        <v>40.3221</v>
+        <v>40.584</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7175</v>
+        <v>13.7083</v>
       </c>
       <c r="F120" t="n">
-        <v>26.7201</v>
+        <v>26.9404</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7122</v>
+        <v>17.7032</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4355</v>
+        <v>17.4193</v>
       </c>
       <c r="D121" t="n">
-        <v>46.8162</v>
+        <v>47.4152</v>
       </c>
       <c r="E121" t="n">
-        <v>18.0796</v>
+        <v>18.0429</v>
       </c>
       <c r="F121" t="n">
-        <v>30.6584</v>
+        <v>30.8877</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.0082</v>
+        <v>16.9909</v>
       </c>
       <c r="C122" t="n">
-        <v>19.1795</v>
+        <v>19.145</v>
       </c>
       <c r="D122" t="n">
-        <v>47.0311</v>
+        <v>47.0354</v>
       </c>
       <c r="E122" t="n">
-        <v>17.4253</v>
+        <v>17.4207</v>
       </c>
       <c r="F122" t="n">
-        <v>30.3729</v>
+        <v>30.5811</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.1026</v>
+        <v>16.089</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9483</v>
+        <v>18.9201</v>
       </c>
       <c r="D123" t="n">
-        <v>47.1587</v>
+        <v>47.7306</v>
       </c>
       <c r="E123" t="n">
-        <v>17.2385</v>
+        <v>17.0822</v>
       </c>
       <c r="F123" t="n">
-        <v>29.9942</v>
+        <v>30.253</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6416</v>
+        <v>23.6294</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7689</v>
+        <v>18.7713</v>
       </c>
       <c r="D124" t="n">
-        <v>43.9414</v>
+        <v>44.56</v>
       </c>
       <c r="E124" t="n">
-        <v>16.8431</v>
+        <v>16.7346</v>
       </c>
       <c r="F124" t="n">
-        <v>29.6404</v>
+        <v>29.8828</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2237</v>
+        <v>23.1952</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5999</v>
+        <v>18.5674</v>
       </c>
       <c r="D125" t="n">
-        <v>43.7607</v>
+        <v>44.2804</v>
       </c>
       <c r="E125" t="n">
-        <v>16.5491</v>
+        <v>16.4743</v>
       </c>
       <c r="F125" t="n">
-        <v>29.3361</v>
+        <v>29.5808</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7609</v>
+        <v>22.7446</v>
       </c>
       <c r="C126" t="n">
-        <v>18.4116</v>
+        <v>18.3899</v>
       </c>
       <c r="D126" t="n">
-        <v>45.383</v>
+        <v>45.6477</v>
       </c>
       <c r="E126" t="n">
-        <v>16.2405</v>
+        <v>16.1077</v>
       </c>
       <c r="F126" t="n">
-        <v>29.0763</v>
+        <v>29.31</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2692</v>
+        <v>22.2453</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2637</v>
+        <v>18.2491</v>
       </c>
       <c r="D127" t="n">
-        <v>44.7355</v>
+        <v>45.035</v>
       </c>
       <c r="E127" t="n">
-        <v>15.9228</v>
+        <v>15.8245</v>
       </c>
       <c r="F127" t="n">
-        <v>28.7711</v>
+        <v>29.0119</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7533</v>
+        <v>21.7498</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1542</v>
+        <v>18.172</v>
       </c>
       <c r="D128" t="n">
-        <v>42.3931</v>
+        <v>42.8137</v>
       </c>
       <c r="E128" t="n">
-        <v>15.6049</v>
+        <v>15.5039</v>
       </c>
       <c r="F128" t="n">
-        <v>28.4485</v>
+        <v>28.6862</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.2105</v>
+        <v>21.1885</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0302</v>
+        <v>18.0124</v>
       </c>
       <c r="D129" t="n">
-        <v>41.9272</v>
+        <v>42.2784</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3823</v>
+        <v>15.3824</v>
       </c>
       <c r="F129" t="n">
-        <v>28.1531</v>
+        <v>28.3855</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6684</v>
+        <v>20.6502</v>
       </c>
       <c r="C130" t="n">
-        <v>17.9144</v>
+        <v>17.892</v>
       </c>
       <c r="D130" t="n">
-        <v>41.4794</v>
+        <v>41.8463</v>
       </c>
       <c r="E130" t="n">
-        <v>14.941</v>
+        <v>14.8877</v>
       </c>
       <c r="F130" t="n">
-        <v>27.9716</v>
+        <v>28.2135</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1332</v>
+        <v>20.1321</v>
       </c>
       <c r="C131" t="n">
-        <v>17.8113</v>
+        <v>17.7825</v>
       </c>
       <c r="D131" t="n">
-        <v>40.9428</v>
+        <v>41.3301</v>
       </c>
       <c r="E131" t="n">
-        <v>14.605</v>
+        <v>14.6093</v>
       </c>
       <c r="F131" t="n">
-        <v>27.6663</v>
+        <v>27.9171</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6201</v>
+        <v>19.6138</v>
       </c>
       <c r="C132" t="n">
-        <v>17.7102</v>
+        <v>17.6854</v>
       </c>
       <c r="D132" t="n">
-        <v>40.5889</v>
+        <v>40.9212</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3413</v>
+        <v>14.3386</v>
       </c>
       <c r="F132" t="n">
-        <v>27.3392</v>
+        <v>27.6008</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0744</v>
+        <v>19.0592</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6157</v>
+        <v>17.6134</v>
       </c>
       <c r="D133" t="n">
-        <v>40.3187</v>
+        <v>40.6506</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0626</v>
+        <v>14.0661</v>
       </c>
       <c r="F133" t="n">
-        <v>27.0946</v>
+        <v>27.324</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.4926</v>
+        <v>18.4813</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5568</v>
+        <v>17.5279</v>
       </c>
       <c r="D134" t="n">
-        <v>39.983</v>
+        <v>40.3419</v>
       </c>
       <c r="E134" t="n">
-        <v>13.7817</v>
+        <v>13.7761</v>
       </c>
       <c r="F134" t="n">
-        <v>26.7919</v>
+        <v>27.0095</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8691</v>
+        <v>17.875</v>
       </c>
       <c r="C135" t="n">
-        <v>17.466</v>
+        <v>17.4484</v>
       </c>
       <c r="D135" t="n">
-        <v>47.4799</v>
+        <v>48.0463</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8626</v>
+        <v>17.8593</v>
       </c>
       <c r="F135" t="n">
-        <v>30.8036</v>
+        <v>31.0523</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.1919</v>
+        <v>17.1893</v>
       </c>
       <c r="C136" t="n">
-        <v>19.1831</v>
+        <v>19.1707</v>
       </c>
       <c r="D136" t="n">
-        <v>46.4604</v>
+        <v>46.7307</v>
       </c>
       <c r="E136" t="n">
-        <v>17.6145</v>
+        <v>17.5116</v>
       </c>
       <c r="F136" t="n">
-        <v>30.3293</v>
+        <v>30.6312</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.313</v>
+        <v>16.2974</v>
       </c>
       <c r="C137" t="n">
-        <v>19.0029</v>
+        <v>18.9487</v>
       </c>
       <c r="D137" t="n">
-        <v>45.22</v>
+        <v>45.4952</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1142</v>
+        <v>17.0985</v>
       </c>
       <c r="F137" t="n">
-        <v>30.1262</v>
+        <v>30.3607</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7317</v>
+        <v>23.7164</v>
       </c>
       <c r="C138" t="n">
-        <v>18.8199</v>
+        <v>18.7748</v>
       </c>
       <c r="D138" t="n">
-        <v>46.9508</v>
+        <v>47.3321</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7447</v>
+        <v>16.7357</v>
       </c>
       <c r="F138" t="n">
-        <v>29.8019</v>
+        <v>30.0166</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3201</v>
+        <v>23.3013</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6528</v>
+        <v>18.6092</v>
       </c>
       <c r="D139" t="n">
-        <v>44.2538</v>
+        <v>44.5048</v>
       </c>
       <c r="E139" t="n">
-        <v>16.5582</v>
+        <v>16.4438</v>
       </c>
       <c r="F139" t="n">
-        <v>29.4263</v>
+        <v>29.7233</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8501</v>
+        <v>22.833</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4708</v>
+        <v>18.4628</v>
       </c>
       <c r="D140" t="n">
-        <v>43.711</v>
+        <v>44.0169</v>
       </c>
       <c r="E140" t="n">
-        <v>16.2506</v>
+        <v>16.1868</v>
       </c>
       <c r="F140" t="n">
-        <v>29.1265</v>
+        <v>29.3615</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.368</v>
+        <v>22.3454</v>
       </c>
       <c r="C141" t="n">
-        <v>18.323</v>
+        <v>18.3086</v>
       </c>
       <c r="D141" t="n">
-        <v>43.0462</v>
+        <v>43.2571</v>
       </c>
       <c r="E141" t="n">
-        <v>15.9821</v>
+        <v>15.8334</v>
       </c>
       <c r="F141" t="n">
-        <v>28.823</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8533</v>
+        <v>21.833</v>
       </c>
       <c r="C142" t="n">
-        <v>18.1993</v>
+        <v>18.1809</v>
       </c>
       <c r="D142" t="n">
-        <v>44.4087</v>
+        <v>44.6911</v>
       </c>
       <c r="E142" t="n">
-        <v>15.5154</v>
+        <v>15.4957</v>
       </c>
       <c r="F142" t="n">
-        <v>28.689</v>
+        <v>28.881</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.318</v>
+        <v>21.2968</v>
       </c>
       <c r="C143" t="n">
-        <v>18.0845</v>
+        <v>18.0613</v>
       </c>
       <c r="D143" t="n">
-        <v>43.6433</v>
+        <v>44.012</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2067</v>
+        <v>15.2005</v>
       </c>
       <c r="F143" t="n">
-        <v>28.3234</v>
+        <v>28.6836</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>19.0382</v>
+        <v>18.9893</v>
       </c>
       <c r="C2" t="n">
-        <v>14.1039</v>
+        <v>14.095</v>
       </c>
       <c r="D2" t="n">
-        <v>32.0074</v>
+        <v>32.2549</v>
       </c>
       <c r="E2" t="n">
-        <v>6.67578</v>
+        <v>7.38714</v>
       </c>
       <c r="F2" t="n">
-        <v>26.7315</v>
+        <v>26.7032</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.5067</v>
+        <v>18.6032</v>
       </c>
       <c r="C3" t="n">
-        <v>14.4221</v>
+        <v>14.5177</v>
       </c>
       <c r="D3" t="n">
-        <v>32.0463</v>
+        <v>32.2944</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5097</v>
+        <v>6.80363</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4966</v>
+        <v>26.4927</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.0515</v>
+        <v>18.2193</v>
       </c>
       <c r="C4" t="n">
-        <v>14.7674</v>
+        <v>14.6376</v>
       </c>
       <c r="D4" t="n">
-        <v>32.0804</v>
+        <v>32.3322</v>
       </c>
       <c r="E4" t="n">
-        <v>5.63828</v>
+        <v>6.27425</v>
       </c>
       <c r="F4" t="n">
-        <v>26.3609</v>
+        <v>26.2734</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.6548</v>
+        <v>17.4582</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8145</v>
+        <v>14.8249</v>
       </c>
       <c r="D5" t="n">
-        <v>32.4607</v>
+        <v>32.5584</v>
       </c>
       <c r="E5" t="n">
-        <v>5.60799</v>
+        <v>16.1807</v>
       </c>
       <c r="F5" t="n">
-        <v>26.4141</v>
+        <v>30.6902</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.012</v>
+        <v>17.0071</v>
       </c>
       <c r="C6" t="n">
-        <v>15.0909</v>
+        <v>15.1483</v>
       </c>
       <c r="D6" t="n">
-        <v>32.5005</v>
+        <v>32.69</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8673</v>
+        <v>15.6328</v>
       </c>
       <c r="F6" t="n">
-        <v>26.0147</v>
+        <v>30.4012</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.4173</v>
+        <v>16.4197</v>
       </c>
       <c r="C7" t="n">
-        <v>15.3453</v>
+        <v>15.408</v>
       </c>
       <c r="D7" t="n">
-        <v>31.8464</v>
+        <v>31.7991</v>
       </c>
       <c r="E7" t="n">
-        <v>15.8894</v>
+        <v>15.2323</v>
       </c>
       <c r="F7" t="n">
-        <v>30.2541</v>
+        <v>30.0568</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.819</v>
+        <v>15.6561</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9961</v>
+        <v>16.9414</v>
       </c>
       <c r="D8" t="n">
-        <v>31.9784</v>
+        <v>31.8856</v>
       </c>
       <c r="E8" t="n">
-        <v>15.4811</v>
+        <v>15.2762</v>
       </c>
       <c r="F8" t="n">
-        <v>29.8978</v>
+        <v>29.8243</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.9438</v>
+        <v>14.9601</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0893</v>
+        <v>17.0698</v>
       </c>
       <c r="D9" t="n">
-        <v>32.0091</v>
+        <v>32.26</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0757</v>
+        <v>15.0012</v>
       </c>
       <c r="F9" t="n">
-        <v>29.7058</v>
+        <v>29.5845</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.7922</v>
+        <v>22.731</v>
       </c>
       <c r="C10" t="n">
-        <v>17.0696</v>
+        <v>17.0713</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9972</v>
+        <v>31.9862</v>
       </c>
       <c r="E10" t="n">
-        <v>14.8483</v>
+        <v>14.8185</v>
       </c>
       <c r="F10" t="n">
-        <v>29.3588</v>
+        <v>29.258</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.4318</v>
+        <v>22.2742</v>
       </c>
       <c r="C11" t="n">
-        <v>17.195</v>
+        <v>17.2054</v>
       </c>
       <c r="D11" t="n">
-        <v>32.1201</v>
+        <v>32.3037</v>
       </c>
       <c r="E11" t="n">
-        <v>14.4063</v>
+        <v>14.5344</v>
       </c>
       <c r="F11" t="n">
-        <v>29.2587</v>
+        <v>29.0356</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.951</v>
+        <v>21.8716</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0875</v>
+        <v>17.0612</v>
       </c>
       <c r="D12" t="n">
-        <v>32.2063</v>
+        <v>32.24</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3423</v>
+        <v>14.3461</v>
       </c>
       <c r="F12" t="n">
-        <v>28.9864</v>
+        <v>28.8784</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.5221</v>
+        <v>21.4833</v>
       </c>
       <c r="C13" t="n">
-        <v>17.1835</v>
+        <v>17.2917</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1952</v>
+        <v>32.4504</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1363</v>
+        <v>14.1563</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8472</v>
+        <v>28.6462</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.1072</v>
+        <v>21.123</v>
       </c>
       <c r="C14" t="n">
-        <v>17.1739</v>
+        <v>17.258</v>
       </c>
       <c r="D14" t="n">
-        <v>32.5782</v>
+        <v>32.8874</v>
       </c>
       <c r="E14" t="n">
-        <v>13.6625</v>
+        <v>13.8164</v>
       </c>
       <c r="F14" t="n">
-        <v>28.5038</v>
+        <v>28.3806</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.7241</v>
+        <v>20.6846</v>
       </c>
       <c r="C15" t="n">
-        <v>17.3254</v>
+        <v>17.2567</v>
       </c>
       <c r="D15" t="n">
-        <v>32.5349</v>
+        <v>32.8989</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5724</v>
+        <v>13.5747</v>
       </c>
       <c r="F15" t="n">
-        <v>27.9378</v>
+        <v>27.9361</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.1116</v>
+        <v>20.0746</v>
       </c>
       <c r="C16" t="n">
-        <v>17.2315</v>
+        <v>17.188</v>
       </c>
       <c r="D16" t="n">
-        <v>32.5459</v>
+        <v>32.8473</v>
       </c>
       <c r="E16" t="n">
-        <v>13.3938</v>
+        <v>13.4001</v>
       </c>
       <c r="F16" t="n">
-        <v>27.64</v>
+        <v>27.7304</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.5615</v>
+        <v>19.6239</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1903</v>
+        <v>17.1458</v>
       </c>
       <c r="D17" t="n">
-        <v>32.6101</v>
+        <v>33.0171</v>
       </c>
       <c r="E17" t="n">
-        <v>13.2255</v>
+        <v>13.2022</v>
       </c>
       <c r="F17" t="n">
-        <v>27.4514</v>
+        <v>27.4352</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.0783</v>
+        <v>19.1211</v>
       </c>
       <c r="C18" t="n">
-        <v>17.1445</v>
+        <v>17.1639</v>
       </c>
       <c r="D18" t="n">
-        <v>32.8568</v>
+        <v>33.0502</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9031</v>
+        <v>12.9759</v>
       </c>
       <c r="F18" t="n">
-        <v>27.1232</v>
+        <v>27.1664</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.6146</v>
+        <v>18.5504</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1241</v>
+        <v>17.1483</v>
       </c>
       <c r="D19" t="n">
-        <v>32.9416</v>
+        <v>33.1705</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6775</v>
+        <v>12.6944</v>
       </c>
       <c r="F19" t="n">
-        <v>26.7752</v>
+        <v>26.7636</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.0452</v>
+        <v>18.1271</v>
       </c>
       <c r="C20" t="n">
-        <v>17.2157</v>
+        <v>17.3204</v>
       </c>
       <c r="D20" t="n">
-        <v>33.1156</v>
+        <v>33.3711</v>
       </c>
       <c r="E20" t="n">
-        <v>12.3878</v>
+        <v>18.1072</v>
       </c>
       <c r="F20" t="n">
-        <v>26.4697</v>
+        <v>30.9175</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.4289</v>
+        <v>17.5149</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1346</v>
+        <v>17.1335</v>
       </c>
       <c r="D21" t="n">
-        <v>32.7239</v>
+        <v>32.5865</v>
       </c>
       <c r="E21" t="n">
-        <v>17.7535</v>
+        <v>17.6525</v>
       </c>
       <c r="F21" t="n">
-        <v>30.6344</v>
+        <v>30.7313</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7367</v>
+        <v>16.7314</v>
       </c>
       <c r="C22" t="n">
-        <v>18.6862</v>
+        <v>18.6704</v>
       </c>
       <c r="D22" t="n">
-        <v>32.4812</v>
+        <v>32.6185</v>
       </c>
       <c r="E22" t="n">
-        <v>17.0747</v>
+        <v>17.1331</v>
       </c>
       <c r="F22" t="n">
-        <v>30.3661</v>
+        <v>30.4499</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0172</v>
+        <v>16.0163</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5149</v>
+        <v>18.5514</v>
       </c>
       <c r="D23" t="n">
-        <v>32.6951</v>
+        <v>32.6618</v>
       </c>
       <c r="E23" t="n">
-        <v>16.6615</v>
+        <v>16.7724</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1748</v>
+        <v>30.1566</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.3544</v>
+        <v>23.3471</v>
       </c>
       <c r="C24" t="n">
-        <v>18.3838</v>
+        <v>18.429</v>
       </c>
       <c r="D24" t="n">
-        <v>32.5319</v>
+        <v>32.3758</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4447</v>
+        <v>16.4142</v>
       </c>
       <c r="F24" t="n">
-        <v>29.8892</v>
+        <v>30.0032</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.8861</v>
+        <v>22.9312</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3187</v>
+        <v>18.3556</v>
       </c>
       <c r="D25" t="n">
-        <v>32.8323</v>
+        <v>32.5805</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0635</v>
+        <v>16.0298</v>
       </c>
       <c r="F25" t="n">
-        <v>29.5819</v>
+        <v>29.6226</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.4202</v>
+        <v>22.457</v>
       </c>
       <c r="C26" t="n">
-        <v>18.2827</v>
+        <v>18.278</v>
       </c>
       <c r="D26" t="n">
-        <v>32.9051</v>
+        <v>32.6394</v>
       </c>
       <c r="E26" t="n">
-        <v>15.6202</v>
+        <v>15.606</v>
       </c>
       <c r="F26" t="n">
-        <v>29.2418</v>
+        <v>29.4508</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>21.9774</v>
+        <v>22.0268</v>
       </c>
       <c r="C27" t="n">
-        <v>18.1136</v>
+        <v>17.999</v>
       </c>
       <c r="D27" t="n">
-        <v>32.9598</v>
+        <v>32.6051</v>
       </c>
       <c r="E27" t="n">
-        <v>15.4867</v>
+        <v>15.4159</v>
       </c>
       <c r="F27" t="n">
-        <v>28.9849</v>
+        <v>29.0436</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.5607</v>
+        <v>21.5674</v>
       </c>
       <c r="C28" t="n">
-        <v>18.0067</v>
+        <v>17.9761</v>
       </c>
       <c r="D28" t="n">
-        <v>32.8289</v>
+        <v>32.7904</v>
       </c>
       <c r="E28" t="n">
-        <v>15.1124</v>
+        <v>15.157</v>
       </c>
       <c r="F28" t="n">
-        <v>28.7897</v>
+        <v>28.7695</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>21.1013</v>
+        <v>20.9747</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9621</v>
+        <v>17.9262</v>
       </c>
       <c r="D29" t="n">
-        <v>32.8815</v>
+        <v>32.9338</v>
       </c>
       <c r="E29" t="n">
-        <v>14.8158</v>
+        <v>14.8462</v>
       </c>
       <c r="F29" t="n">
-        <v>28.3919</v>
+        <v>28.3422</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6245</v>
+        <v>20.6284</v>
       </c>
       <c r="C30" t="n">
-        <v>17.8985</v>
+        <v>17.8898</v>
       </c>
       <c r="D30" t="n">
-        <v>33.1354</v>
+        <v>33.0251</v>
       </c>
       <c r="E30" t="n">
-        <v>14.4561</v>
+        <v>14.5122</v>
       </c>
       <c r="F30" t="n">
-        <v>28.1718</v>
+        <v>28.171</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0592</v>
+        <v>20.0383</v>
       </c>
       <c r="C31" t="n">
-        <v>17.8471</v>
+        <v>17.6887</v>
       </c>
       <c r="D31" t="n">
-        <v>32.9781</v>
+        <v>33.1119</v>
       </c>
       <c r="E31" t="n">
-        <v>14.1755</v>
+        <v>14.18</v>
       </c>
       <c r="F31" t="n">
-        <v>27.8601</v>
+        <v>27.8427</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.6532</v>
+        <v>19.657</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7426</v>
+        <v>17.7451</v>
       </c>
       <c r="D32" t="n">
-        <v>33.168</v>
+        <v>33.1972</v>
       </c>
       <c r="E32" t="n">
-        <v>13.8663</v>
+        <v>13.894</v>
       </c>
       <c r="F32" t="n">
-        <v>27.5213</v>
+        <v>27.5084</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0743</v>
+        <v>19.0674</v>
       </c>
       <c r="C33" t="n">
-        <v>17.5835</v>
+        <v>17.6191</v>
       </c>
       <c r="D33" t="n">
-        <v>33.3228</v>
+        <v>33.4384</v>
       </c>
       <c r="E33" t="n">
-        <v>13.6297</v>
+        <v>13.5883</v>
       </c>
       <c r="F33" t="n">
-        <v>27.1773</v>
+        <v>27.1542</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4265</v>
+        <v>18.4757</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5199</v>
+        <v>17.5543</v>
       </c>
       <c r="D34" t="n">
-        <v>33.3387</v>
+        <v>33.5499</v>
       </c>
       <c r="E34" t="n">
-        <v>13.3561</v>
+        <v>18.4729</v>
       </c>
       <c r="F34" t="n">
-        <v>26.9303</v>
+        <v>31.532</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.924</v>
+        <v>17.858</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4683</v>
+        <v>17.4405</v>
       </c>
       <c r="D35" t="n">
-        <v>32.7885</v>
+        <v>32.5994</v>
       </c>
       <c r="E35" t="n">
-        <v>18.1625</v>
+        <v>17.8417</v>
       </c>
       <c r="F35" t="n">
-        <v>31.1893</v>
+        <v>31.2217</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2497</v>
+        <v>17.2998</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4245</v>
+        <v>17.4386</v>
       </c>
       <c r="D36" t="n">
-        <v>32.6039</v>
+        <v>32.6528</v>
       </c>
       <c r="E36" t="n">
-        <v>17.631</v>
+        <v>17.5871</v>
       </c>
       <c r="F36" t="n">
-        <v>30.711</v>
+        <v>30.8356</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.3954</v>
+        <v>16.4463</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8446</v>
+        <v>18.8006</v>
       </c>
       <c r="D37" t="n">
-        <v>32.8039</v>
+        <v>32.7242</v>
       </c>
       <c r="E37" t="n">
-        <v>17.1271</v>
+        <v>17.0968</v>
       </c>
       <c r="F37" t="n">
-        <v>30.3569</v>
+        <v>30.4894</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.7146</v>
+        <v>23.7134</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6689</v>
+        <v>18.6646</v>
       </c>
       <c r="D38" t="n">
-        <v>32.4713</v>
+        <v>32.6328</v>
       </c>
       <c r="E38" t="n">
-        <v>16.7961</v>
+        <v>16.8129</v>
       </c>
       <c r="F38" t="n">
-        <v>30.0332</v>
+        <v>30.2402</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.3237</v>
+        <v>23.2784</v>
       </c>
       <c r="C39" t="n">
-        <v>18.5082</v>
+        <v>18.4758</v>
       </c>
       <c r="D39" t="n">
-        <v>32.5681</v>
+        <v>32.6038</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4288</v>
+        <v>16.4515</v>
       </c>
       <c r="F39" t="n">
-        <v>29.7258</v>
+        <v>29.8822</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.889</v>
+        <v>22.9375</v>
       </c>
       <c r="C40" t="n">
-        <v>18.3891</v>
+        <v>18.3573</v>
       </c>
       <c r="D40" t="n">
-        <v>32.9036</v>
+        <v>32.943</v>
       </c>
       <c r="E40" t="n">
-        <v>16.1561</v>
+        <v>16.1802</v>
       </c>
       <c r="F40" t="n">
-        <v>29.4058</v>
+        <v>29.4673</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4333</v>
+        <v>22.4341</v>
       </c>
       <c r="C41" t="n">
-        <v>18.2503</v>
+        <v>18.2407</v>
       </c>
       <c r="D41" t="n">
-        <v>32.9993</v>
+        <v>33.0494</v>
       </c>
       <c r="E41" t="n">
-        <v>15.8497</v>
+        <v>15.854</v>
       </c>
       <c r="F41" t="n">
-        <v>29.1097</v>
+        <v>29.2202</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.961</v>
+        <v>21.9346</v>
       </c>
       <c r="C42" t="n">
-        <v>18.1017</v>
+        <v>18.0492</v>
       </c>
       <c r="D42" t="n">
-        <v>32.9369</v>
+        <v>32.8716</v>
       </c>
       <c r="E42" t="n">
-        <v>15.4864</v>
+        <v>15.5145</v>
       </c>
       <c r="F42" t="n">
-        <v>28.8613</v>
+        <v>28.9435</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4113</v>
+        <v>21.4397</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9317</v>
+        <v>17.9133</v>
       </c>
       <c r="D43" t="n">
-        <v>32.7426</v>
+        <v>32.8786</v>
       </c>
       <c r="E43" t="n">
-        <v>15.1816</v>
+        <v>15.2457</v>
       </c>
       <c r="F43" t="n">
-        <v>28.5713</v>
+        <v>28.7751</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.879</v>
+        <v>20.8791</v>
       </c>
       <c r="C44" t="n">
-        <v>17.9081</v>
+        <v>17.8195</v>
       </c>
       <c r="D44" t="n">
-        <v>32.7649</v>
+        <v>33.0554</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9124</v>
+        <v>14.9289</v>
       </c>
       <c r="F44" t="n">
-        <v>28.3624</v>
+        <v>28.4269</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4265</v>
+        <v>20.4318</v>
       </c>
       <c r="C45" t="n">
-        <v>17.7836</v>
+        <v>17.7305</v>
       </c>
       <c r="D45" t="n">
-        <v>32.8128</v>
+        <v>33.0853</v>
       </c>
       <c r="E45" t="n">
-        <v>14.5797</v>
+        <v>14.617</v>
       </c>
       <c r="F45" t="n">
-        <v>27.9518</v>
+        <v>28.0203</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.9061</v>
+        <v>19.8883</v>
       </c>
       <c r="C46" t="n">
-        <v>17.6957</v>
+        <v>17.6723</v>
       </c>
       <c r="D46" t="n">
-        <v>32.9345</v>
+        <v>33.1353</v>
       </c>
       <c r="E46" t="n">
-        <v>14.3029</v>
+        <v>14.3393</v>
       </c>
       <c r="F46" t="n">
-        <v>27.779</v>
+        <v>27.9474</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3685</v>
+        <v>19.3636</v>
       </c>
       <c r="C47" t="n">
-        <v>17.5549</v>
+        <v>17.538</v>
       </c>
       <c r="D47" t="n">
-        <v>33.0635</v>
+        <v>33.174</v>
       </c>
       <c r="E47" t="n">
-        <v>13.9939</v>
+        <v>14.0338</v>
       </c>
       <c r="F47" t="n">
-        <v>27.4394</v>
+        <v>27.5678</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.7879</v>
+        <v>18.8411</v>
       </c>
       <c r="C48" t="n">
-        <v>17.4938</v>
+        <v>17.4226</v>
       </c>
       <c r="D48" t="n">
-        <v>33.1796</v>
+        <v>33.2869</v>
       </c>
       <c r="E48" t="n">
-        <v>13.6697</v>
+        <v>18.2477</v>
       </c>
       <c r="F48" t="n">
-        <v>27.0702</v>
+        <v>31.7909</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.1503</v>
+        <v>18.2947</v>
       </c>
       <c r="C49" t="n">
-        <v>17.3871</v>
+        <v>17.3579</v>
       </c>
       <c r="D49" t="n">
-        <v>33.5348</v>
+        <v>33.8789</v>
       </c>
       <c r="E49" t="n">
-        <v>13.3536</v>
+        <v>18.0857</v>
       </c>
       <c r="F49" t="n">
-        <v>26.7399</v>
+        <v>31.3011</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.5554</v>
+        <v>17.616</v>
       </c>
       <c r="C50" t="n">
-        <v>17.3226</v>
+        <v>17.2958</v>
       </c>
       <c r="D50" t="n">
-        <v>32.7086</v>
+        <v>33.2759</v>
       </c>
       <c r="E50" t="n">
-        <v>17.7545</v>
+        <v>17.6881</v>
       </c>
       <c r="F50" t="n">
-        <v>30.8524</v>
+        <v>30.9741</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.7866</v>
+        <v>16.8072</v>
       </c>
       <c r="C51" t="n">
-        <v>18.8259</v>
+        <v>18.7925</v>
       </c>
       <c r="D51" t="n">
-        <v>33.0067</v>
+        <v>33.3917</v>
       </c>
       <c r="E51" t="n">
-        <v>17.3747</v>
+        <v>17.3163</v>
       </c>
       <c r="F51" t="n">
-        <v>30.4879</v>
+        <v>30.7156</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.8657</v>
+        <v>15.9605</v>
       </c>
       <c r="C52" t="n">
-        <v>18.6302</v>
+        <v>18.5874</v>
       </c>
       <c r="D52" t="n">
-        <v>32.9631</v>
+        <v>33.4983</v>
       </c>
       <c r="E52" t="n">
-        <v>17.0992</v>
+        <v>17.0393</v>
       </c>
       <c r="F52" t="n">
-        <v>30.1518</v>
+        <v>30.2686</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.4704</v>
+        <v>23.51</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4845</v>
+        <v>18.4419</v>
       </c>
       <c r="D53" t="n">
-        <v>33.1496</v>
+        <v>33.6607</v>
       </c>
       <c r="E53" t="n">
-        <v>16.6773</v>
+        <v>16.7238</v>
       </c>
       <c r="F53" t="n">
-        <v>29.8883</v>
+        <v>29.963</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.1204</v>
+        <v>23.0815</v>
       </c>
       <c r="C54" t="n">
-        <v>18.4277</v>
+        <v>18.3162</v>
       </c>
       <c r="D54" t="n">
-        <v>33.3317</v>
+        <v>33.2864</v>
       </c>
       <c r="E54" t="n">
-        <v>16.3588</v>
+        <v>16.3832</v>
       </c>
       <c r="F54" t="n">
-        <v>29.5309</v>
+        <v>29.7027</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6118</v>
+        <v>22.6011</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2357</v>
+        <v>18.2007</v>
       </c>
       <c r="D55" t="n">
-        <v>33.1548</v>
+        <v>33.2579</v>
       </c>
       <c r="E55" t="n">
-        <v>16.0573</v>
+        <v>16.0294</v>
       </c>
       <c r="F55" t="n">
-        <v>29.2084</v>
+        <v>29.2985</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.1401</v>
+        <v>22.0988</v>
       </c>
       <c r="C56" t="n">
-        <v>18.07</v>
+        <v>18.0904</v>
       </c>
       <c r="D56" t="n">
-        <v>33.3301</v>
+        <v>33.779</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7637</v>
+        <v>15.7653</v>
       </c>
       <c r="F56" t="n">
-        <v>28.9378</v>
+        <v>29.1129</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.58</v>
+        <v>21.5869</v>
       </c>
       <c r="C57" t="n">
-        <v>17.9931</v>
+        <v>17.9275</v>
       </c>
       <c r="D57" t="n">
-        <v>33.7164</v>
+        <v>33.8791</v>
       </c>
       <c r="E57" t="n">
-        <v>15.469</v>
+        <v>15.4884</v>
       </c>
       <c r="F57" t="n">
-        <v>28.6435</v>
+        <v>28.7912</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0514</v>
+        <v>21.0745</v>
       </c>
       <c r="C58" t="n">
-        <v>17.8925</v>
+        <v>17.8696</v>
       </c>
       <c r="D58" t="n">
-        <v>33.8329</v>
+        <v>34.0906</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1873</v>
+        <v>15.1721</v>
       </c>
       <c r="F58" t="n">
-        <v>28.4674</v>
+        <v>28.6237</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5779</v>
+        <v>20.5858</v>
       </c>
       <c r="C59" t="n">
-        <v>17.7605</v>
+        <v>17.7664</v>
       </c>
       <c r="D59" t="n">
-        <v>34.2679</v>
+        <v>34.2738</v>
       </c>
       <c r="E59" t="n">
-        <v>14.9024</v>
+        <v>14.9109</v>
       </c>
       <c r="F59" t="n">
-        <v>28.1724</v>
+        <v>28.3246</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.9976</v>
+        <v>19.978</v>
       </c>
       <c r="C60" t="n">
-        <v>17.6987</v>
+        <v>17.6641</v>
       </c>
       <c r="D60" t="n">
-        <v>34.5346</v>
+        <v>34.4576</v>
       </c>
       <c r="E60" t="n">
-        <v>14.6061</v>
+        <v>14.6092</v>
       </c>
       <c r="F60" t="n">
-        <v>27.7927</v>
+        <v>27.8796</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5238</v>
+        <v>19.5057</v>
       </c>
       <c r="C61" t="n">
-        <v>17.6028</v>
+        <v>17.5754</v>
       </c>
       <c r="D61" t="n">
-        <v>34.8895</v>
+        <v>34.6032</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3085</v>
+        <v>14.3096</v>
       </c>
       <c r="F61" t="n">
-        <v>27.4728</v>
+        <v>27.5348</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9763</v>
+        <v>18.9865</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5309</v>
+        <v>17.5537</v>
       </c>
       <c r="D62" t="n">
-        <v>35.1762</v>
+        <v>35.0319</v>
       </c>
       <c r="E62" t="n">
-        <v>13.9936</v>
+        <v>14.0084</v>
       </c>
       <c r="F62" t="n">
-        <v>27.1825</v>
+        <v>27.2536</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.3567</v>
+        <v>18.364</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4662</v>
+        <v>17.4129</v>
       </c>
       <c r="D63" t="n">
-        <v>35.3251</v>
+        <v>35.2525</v>
       </c>
       <c r="E63" t="n">
-        <v>13.5723</v>
+        <v>19.0609</v>
       </c>
       <c r="F63" t="n">
-        <v>26.9225</v>
+        <v>31.4509</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7581</v>
+        <v>17.7218</v>
       </c>
       <c r="C64" t="n">
-        <v>17.3949</v>
+        <v>17.3889</v>
       </c>
       <c r="D64" t="n">
-        <v>39.3146</v>
+        <v>38.2325</v>
       </c>
       <c r="E64" t="n">
-        <v>18.3965</v>
+        <v>18.6567</v>
       </c>
       <c r="F64" t="n">
-        <v>31.0519</v>
+        <v>31.1197</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0203</v>
+        <v>17.0273</v>
       </c>
       <c r="C65" t="n">
-        <v>18.9398</v>
+        <v>18.9395</v>
       </c>
       <c r="D65" t="n">
-        <v>38.8239</v>
+        <v>38.4408</v>
       </c>
       <c r="E65" t="n">
-        <v>17.6794</v>
+        <v>17.9014</v>
       </c>
       <c r="F65" t="n">
-        <v>30.6697</v>
+        <v>30.7473</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1528</v>
+        <v>16.1927</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7553</v>
+        <v>18.7157</v>
       </c>
       <c r="D66" t="n">
-        <v>38.962</v>
+        <v>38.6714</v>
       </c>
       <c r="E66" t="n">
-        <v>17.234</v>
+        <v>17.7347</v>
       </c>
       <c r="F66" t="n">
-        <v>30.3025</v>
+        <v>30.4155</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6378</v>
+        <v>23.6465</v>
       </c>
       <c r="C67" t="n">
-        <v>18.576</v>
+        <v>18.5699</v>
       </c>
       <c r="D67" t="n">
-        <v>38.9403</v>
+        <v>38.7025</v>
       </c>
       <c r="E67" t="n">
-        <v>16.8382</v>
+        <v>17.1202</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0708</v>
+        <v>30.0852</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.2343</v>
+        <v>23.1999</v>
       </c>
       <c r="C68" t="n">
-        <v>18.444</v>
+        <v>18.376</v>
       </c>
       <c r="D68" t="n">
-        <v>40.4206</v>
+        <v>40.0756</v>
       </c>
       <c r="E68" t="n">
-        <v>16.4314</v>
+        <v>16.9146</v>
       </c>
       <c r="F68" t="n">
-        <v>29.721</v>
+        <v>29.7835</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7325</v>
+        <v>22.7702</v>
       </c>
       <c r="C69" t="n">
-        <v>18.3223</v>
+        <v>18.3028</v>
       </c>
       <c r="D69" t="n">
-        <v>40.2729</v>
+        <v>40.2459</v>
       </c>
       <c r="E69" t="n">
-        <v>16.0524</v>
+        <v>16.4029</v>
       </c>
       <c r="F69" t="n">
-        <v>29.462</v>
+        <v>29.5633</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.2777</v>
+        <v>22.295</v>
       </c>
       <c r="C70" t="n">
-        <v>18.2647</v>
+        <v>18.2858</v>
       </c>
       <c r="D70" t="n">
-        <v>40.2884</v>
+        <v>39.2504</v>
       </c>
       <c r="E70" t="n">
-        <v>15.6887</v>
+        <v>16.01</v>
       </c>
       <c r="F70" t="n">
-        <v>29.1428</v>
+        <v>29.2382</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.7558</v>
+        <v>21.7673</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1324</v>
+        <v>18.1377</v>
       </c>
       <c r="D71" t="n">
-        <v>39.1542</v>
+        <v>39.2062</v>
       </c>
       <c r="E71" t="n">
-        <v>15.4171</v>
+        <v>15.6742</v>
       </c>
       <c r="F71" t="n">
-        <v>28.8912</v>
+        <v>28.9749</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2205</v>
+        <v>21.2481</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0359</v>
+        <v>18.0114</v>
       </c>
       <c r="D72" t="n">
-        <v>39.2055</v>
+        <v>39.2459</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3894</v>
+        <v>15.3761</v>
       </c>
       <c r="F72" t="n">
-        <v>28.5326</v>
+        <v>28.6082</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7147</v>
+        <v>20.7359</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9081</v>
+        <v>17.9022</v>
       </c>
       <c r="D73" t="n">
-        <v>39.191</v>
+        <v>39.3844</v>
       </c>
       <c r="E73" t="n">
-        <v>15.0708</v>
+        <v>15.0951</v>
       </c>
       <c r="F73" t="n">
-        <v>28.2361</v>
+        <v>28.3213</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1635</v>
+        <v>20.1661</v>
       </c>
       <c r="C74" t="n">
-        <v>17.824</v>
+        <v>17.8438</v>
       </c>
       <c r="D74" t="n">
-        <v>39.3686</v>
+        <v>39.3272</v>
       </c>
       <c r="E74" t="n">
-        <v>14.7833</v>
+        <v>14.787</v>
       </c>
       <c r="F74" t="n">
-        <v>27.9136</v>
+        <v>28.0055</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6548</v>
+        <v>19.6755</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7245</v>
+        <v>17.7369</v>
       </c>
       <c r="D75" t="n">
-        <v>39.2769</v>
+        <v>39.3307</v>
       </c>
       <c r="E75" t="n">
-        <v>14.5065</v>
+        <v>14.5261</v>
       </c>
       <c r="F75" t="n">
-        <v>27.6315</v>
+        <v>27.7387</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.1133</v>
+        <v>19.0985</v>
       </c>
       <c r="C76" t="n">
-        <v>17.6435</v>
+        <v>17.6694</v>
       </c>
       <c r="D76" t="n">
-        <v>39.3018</v>
+        <v>39.2548</v>
       </c>
       <c r="E76" t="n">
-        <v>14.199</v>
+        <v>14.2219</v>
       </c>
       <c r="F76" t="n">
-        <v>27.3569</v>
+        <v>27.4274</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5204</v>
+        <v>18.5292</v>
       </c>
       <c r="C77" t="n">
-        <v>17.5809</v>
+        <v>17.5928</v>
       </c>
       <c r="D77" t="n">
-        <v>39.2922</v>
+        <v>39.2169</v>
       </c>
       <c r="E77" t="n">
-        <v>13.8713</v>
+        <v>18.6861</v>
       </c>
       <c r="F77" t="n">
-        <v>27.0539</v>
+        <v>31.5233</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9232</v>
+        <v>17.9206</v>
       </c>
       <c r="C78" t="n">
-        <v>17.3902</v>
+        <v>17.4144</v>
       </c>
       <c r="D78" t="n">
-        <v>45.7514</v>
+        <v>47.4629</v>
       </c>
       <c r="E78" t="n">
-        <v>18.2982</v>
+        <v>18.2159</v>
       </c>
       <c r="F78" t="n">
-        <v>30.9674</v>
+        <v>31.101</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2049</v>
+        <v>17.2005</v>
       </c>
       <c r="C79" t="n">
-        <v>19.257</v>
+        <v>19.1834</v>
       </c>
       <c r="D79" t="n">
-        <v>45.9646</v>
+        <v>47.1306</v>
       </c>
       <c r="E79" t="n">
-        <v>17.842</v>
+        <v>17.6759</v>
       </c>
       <c r="F79" t="n">
-        <v>30.6437</v>
+        <v>30.776</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.3741</v>
+        <v>16.3856</v>
       </c>
       <c r="C80" t="n">
-        <v>19.0363</v>
+        <v>19.0194</v>
       </c>
       <c r="D80" t="n">
-        <v>46.4748</v>
+        <v>46.6955</v>
       </c>
       <c r="E80" t="n">
-        <v>17.4855</v>
+        <v>17.351</v>
       </c>
       <c r="F80" t="n">
-        <v>30.3402</v>
+        <v>30.4489</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7616</v>
+        <v>23.7927</v>
       </c>
       <c r="C81" t="n">
-        <v>18.9084</v>
+        <v>18.8676</v>
       </c>
       <c r="D81" t="n">
-        <v>45.8974</v>
+        <v>45.9928</v>
       </c>
       <c r="E81" t="n">
-        <v>17.0119</v>
+        <v>16.9658</v>
       </c>
       <c r="F81" t="n">
-        <v>30.0126</v>
+        <v>30.0818</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3965</v>
+        <v>23.3584</v>
       </c>
       <c r="C82" t="n">
-        <v>18.708</v>
+        <v>18.7355</v>
       </c>
       <c r="D82" t="n">
-        <v>43.792</v>
+        <v>45.5704</v>
       </c>
       <c r="E82" t="n">
-        <v>16.6933</v>
+        <v>16.6718</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7081</v>
+        <v>29.7982</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9334</v>
+        <v>22.9024</v>
       </c>
       <c r="C83" t="n">
-        <v>18.5741</v>
+        <v>18.5737</v>
       </c>
       <c r="D83" t="n">
-        <v>43.5743</v>
+        <v>43.494</v>
       </c>
       <c r="E83" t="n">
-        <v>16.3923</v>
+        <v>16.3782</v>
       </c>
       <c r="F83" t="n">
-        <v>29.4117</v>
+        <v>29.5203</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4129</v>
+        <v>22.4584</v>
       </c>
       <c r="C84" t="n">
-        <v>18.4292</v>
+        <v>18.4193</v>
       </c>
       <c r="D84" t="n">
-        <v>42.9894</v>
+        <v>44.6806</v>
       </c>
       <c r="E84" t="n">
-        <v>16.0693</v>
+        <v>16.0566</v>
       </c>
       <c r="F84" t="n">
-        <v>29.1189</v>
+        <v>29.1826</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9367</v>
+        <v>21.9353</v>
       </c>
       <c r="C85" t="n">
         <v>18.2011</v>
       </c>
       <c r="D85" t="n">
-        <v>44.1934</v>
+        <v>44.6375</v>
       </c>
       <c r="E85" t="n">
-        <v>15.758</v>
+        <v>15.7944</v>
       </c>
       <c r="F85" t="n">
-        <v>28.7994</v>
+        <v>28.8732</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.4047</v>
+        <v>21.4055</v>
       </c>
       <c r="C86" t="n">
-        <v>18.099</v>
+        <v>18.0798</v>
       </c>
       <c r="D86" t="n">
-        <v>43.6882</v>
+        <v>43.8378</v>
       </c>
       <c r="E86" t="n">
-        <v>15.475</v>
+        <v>15.4928</v>
       </c>
       <c r="F86" t="n">
-        <v>28.5324</v>
+        <v>28.6292</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.8752</v>
+        <v>20.8702</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9545</v>
+        <v>17.9519</v>
       </c>
       <c r="D87" t="n">
-        <v>43.3314</v>
+        <v>43.7112</v>
       </c>
       <c r="E87" t="n">
-        <v>15.1778</v>
+        <v>15.1874</v>
       </c>
       <c r="F87" t="n">
-        <v>28.2654</v>
+        <v>28.348</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3586</v>
+        <v>20.3535</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8458</v>
+        <v>17.8891</v>
       </c>
       <c r="D88" t="n">
-        <v>43.0373</v>
+        <v>43.4709</v>
       </c>
       <c r="E88" t="n">
-        <v>14.8934</v>
+        <v>14.9121</v>
       </c>
       <c r="F88" t="n">
-        <v>27.9387</v>
+        <v>28.0262</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8352</v>
+        <v>19.8405</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7462</v>
+        <v>17.7443</v>
       </c>
       <c r="D89" t="n">
-        <v>42.8604</v>
+        <v>42.914</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6033</v>
+        <v>14.6312</v>
       </c>
       <c r="F89" t="n">
-        <v>27.6452</v>
+        <v>27.7192</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.3075</v>
+        <v>19.3093</v>
       </c>
       <c r="C90" t="n">
-        <v>17.6445</v>
+        <v>17.7189</v>
       </c>
       <c r="D90" t="n">
-        <v>42.5963</v>
+        <v>43.0378</v>
       </c>
       <c r="E90" t="n">
-        <v>14.2872</v>
+        <v>14.3036</v>
       </c>
       <c r="F90" t="n">
-        <v>27.3242</v>
+        <v>27.4058</v>
       </c>
     </row>
     <row r="91">
@@ -6862,16 +6862,16 @@
         <v>18.7102</v>
       </c>
       <c r="C91" t="n">
-        <v>17.5561</v>
+        <v>17.6098</v>
       </c>
       <c r="D91" t="n">
-        <v>42.3196</v>
+        <v>42.6406</v>
       </c>
       <c r="E91" t="n">
-        <v>13.9982</v>
+        <v>18.6397</v>
       </c>
       <c r="F91" t="n">
-        <v>27.0184</v>
+        <v>31.5178</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.0902</v>
+        <v>18.1026</v>
       </c>
       <c r="C92" t="n">
-        <v>17.4828</v>
+        <v>17.485</v>
       </c>
       <c r="D92" t="n">
-        <v>47.7974</v>
+        <v>46.0405</v>
       </c>
       <c r="E92" t="n">
-        <v>18.2354</v>
+        <v>18.1653</v>
       </c>
       <c r="F92" t="n">
-        <v>31.1544</v>
+        <v>31.1532</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.365</v>
+        <v>17.3975</v>
       </c>
       <c r="C93" t="n">
-        <v>17.4024</v>
+        <v>17.3588</v>
       </c>
       <c r="D93" t="n">
-        <v>46.3299</v>
+        <v>45.4818</v>
       </c>
       <c r="E93" t="n">
-        <v>17.7966</v>
+        <v>17.7879</v>
       </c>
       <c r="F93" t="n">
-        <v>31.0898</v>
+        <v>31.1481</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6492</v>
+        <v>16.6514</v>
       </c>
       <c r="C94" t="n">
-        <v>19.0491</v>
+        <v>18.9727</v>
       </c>
       <c r="D94" t="n">
-        <v>44.7746</v>
+        <v>44.9962</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4048</v>
+        <v>17.4611</v>
       </c>
       <c r="F94" t="n">
-        <v>30.4977</v>
+        <v>30.5184</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8686</v>
+        <v>23.8735</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8492</v>
+        <v>18.8396</v>
       </c>
       <c r="D95" t="n">
-        <v>44.1332</v>
+        <v>44.391</v>
       </c>
       <c r="E95" t="n">
-        <v>17.1069</v>
+        <v>17.0142</v>
       </c>
       <c r="F95" t="n">
-        <v>30.1458</v>
+        <v>30.1853</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4616</v>
+        <v>23.4688</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6523</v>
+        <v>18.6617</v>
       </c>
       <c r="D96" t="n">
-        <v>43.591</v>
+        <v>43.8289</v>
       </c>
       <c r="E96" t="n">
-        <v>16.5779</v>
+        <v>16.5764</v>
       </c>
       <c r="F96" t="n">
-        <v>29.8799</v>
+        <v>30.0416</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0237</v>
+        <v>23.0124</v>
       </c>
       <c r="C97" t="n">
-        <v>18.5099</v>
+        <v>18.4975</v>
       </c>
       <c r="D97" t="n">
-        <v>45.6829</v>
+        <v>45.7348</v>
       </c>
       <c r="E97" t="n">
-        <v>16.2264</v>
+        <v>16.2253</v>
       </c>
       <c r="F97" t="n">
-        <v>29.6218</v>
+        <v>29.7328</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5467</v>
+        <v>22.5543</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3502</v>
+        <v>18.3459</v>
       </c>
       <c r="D98" t="n">
-        <v>45.1986</v>
+        <v>45.0734</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9154</v>
+        <v>15.9171</v>
       </c>
       <c r="F98" t="n">
-        <v>29.3296</v>
+        <v>29.447</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0385</v>
+        <v>22.0326</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2089</v>
+        <v>18.2694</v>
       </c>
       <c r="D99" t="n">
-        <v>44.4565</v>
+        <v>42.7386</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6197</v>
+        <v>15.6309</v>
       </c>
       <c r="F99" t="n">
-        <v>28.9792</v>
+        <v>29.1187</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5142</v>
+        <v>21.5119</v>
       </c>
       <c r="C100" t="n">
-        <v>18.1737</v>
+        <v>18.1899</v>
       </c>
       <c r="D100" t="n">
-        <v>41.994</v>
+        <v>42.4273</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3022</v>
+        <v>15.3094</v>
       </c>
       <c r="F100" t="n">
-        <v>28.6713</v>
+        <v>28.7811</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9775</v>
+        <v>20.9828</v>
       </c>
       <c r="C101" t="n">
-        <v>18.0639</v>
+        <v>18.046</v>
       </c>
       <c r="D101" t="n">
-        <v>41.8585</v>
+        <v>41.5878</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0345</v>
+        <v>15.0465</v>
       </c>
       <c r="F101" t="n">
-        <v>28.3882</v>
+        <v>28.3741</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4535</v>
+        <v>20.4546</v>
       </c>
       <c r="C102" t="n">
-        <v>17.974</v>
+        <v>17.9713</v>
       </c>
       <c r="D102" t="n">
-        <v>41.1617</v>
+        <v>41.4906</v>
       </c>
       <c r="E102" t="n">
-        <v>14.8235</v>
+        <v>14.7681</v>
       </c>
       <c r="F102" t="n">
-        <v>28.0872</v>
+        <v>28.0896</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9069</v>
+        <v>19.9183</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8616</v>
+        <v>17.8559</v>
       </c>
       <c r="D103" t="n">
-        <v>41.2515</v>
+        <v>40.8718</v>
       </c>
       <c r="E103" t="n">
-        <v>14.5805</v>
+        <v>14.4953</v>
       </c>
       <c r="F103" t="n">
-        <v>27.8042</v>
+        <v>27.7961</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.3913</v>
+        <v>19.4139</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7635</v>
+        <v>17.7744</v>
       </c>
       <c r="D104" t="n">
-        <v>40.4845</v>
+        <v>40.8629</v>
       </c>
       <c r="E104" t="n">
-        <v>14.2216</v>
+        <v>14.2137</v>
       </c>
       <c r="F104" t="n">
-        <v>27.4941</v>
+        <v>27.5047</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8114</v>
+        <v>18.8113</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6428</v>
+        <v>17.6458</v>
       </c>
       <c r="D105" t="n">
-        <v>40.6539</v>
+        <v>40.3043</v>
       </c>
       <c r="E105" t="n">
-        <v>13.948</v>
+        <v>18.4709</v>
       </c>
       <c r="F105" t="n">
-        <v>27.1757</v>
+        <v>31.6486</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.2161</v>
+        <v>18.225</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5632</v>
+        <v>17.5662</v>
       </c>
       <c r="D106" t="n">
-        <v>40.0295</v>
+        <v>41.7462</v>
       </c>
       <c r="E106" t="n">
-        <v>13.6214</v>
+        <v>18.0659</v>
       </c>
       <c r="F106" t="n">
-        <v>26.8856</v>
+        <v>31.2705</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.6129</v>
+        <v>17.5607</v>
       </c>
       <c r="C107" t="n">
-        <v>17.4897</v>
+        <v>17.4951</v>
       </c>
       <c r="D107" t="n">
-        <v>45.1783</v>
+        <v>43.8623</v>
       </c>
       <c r="E107" t="n">
-        <v>17.7168</v>
+        <v>17.6997</v>
       </c>
       <c r="F107" t="n">
-        <v>30.8986</v>
+        <v>30.8952</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8582</v>
+        <v>16.8358</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1284</v>
+        <v>19.1345</v>
       </c>
       <c r="D108" t="n">
-        <v>46.1391</v>
+        <v>45.9076</v>
       </c>
       <c r="E108" t="n">
-        <v>17.3566</v>
+        <v>17.3714</v>
       </c>
       <c r="F108" t="n">
-        <v>30.5205</v>
+        <v>30.5498</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.8977</v>
+        <v>15.9175</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9687</v>
+        <v>18.9645</v>
       </c>
       <c r="D109" t="n">
-        <v>45.4336</v>
+        <v>45.2946</v>
       </c>
       <c r="E109" t="n">
-        <v>16.9796</v>
+        <v>16.9755</v>
       </c>
       <c r="F109" t="n">
-        <v>30.2578</v>
+        <v>30.2307</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5532</v>
+        <v>23.5642</v>
       </c>
       <c r="C110" t="n">
-        <v>18.6911</v>
+        <v>18.6834</v>
       </c>
       <c r="D110" t="n">
-        <v>44.6296</v>
+        <v>44.7187</v>
       </c>
       <c r="E110" t="n">
-        <v>16.7999</v>
+        <v>16.7242</v>
       </c>
       <c r="F110" t="n">
-        <v>29.8621</v>
+        <v>29.8554</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1246</v>
+        <v>23.1268</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5525</v>
+        <v>18.5335</v>
       </c>
       <c r="D111" t="n">
-        <v>44.1809</v>
+        <v>41.5582</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4387</v>
+        <v>16.4091</v>
       </c>
       <c r="F111" t="n">
-        <v>29.5702</v>
+        <v>29.5083</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6432</v>
+        <v>22.6477</v>
       </c>
       <c r="C112" t="n">
-        <v>18.393</v>
+        <v>18.3977</v>
       </c>
       <c r="D112" t="n">
-        <v>40.9144</v>
+        <v>41.1109</v>
       </c>
       <c r="E112" t="n">
-        <v>16.0818</v>
+        <v>16.0967</v>
       </c>
       <c r="F112" t="n">
-        <v>29.2864</v>
+        <v>29.2568</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1403</v>
+        <v>22.1498</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2524</v>
+        <v>18.2721</v>
       </c>
       <c r="D113" t="n">
-        <v>40.6142</v>
+        <v>43.2034</v>
       </c>
       <c r="E113" t="n">
-        <v>15.7492</v>
+        <v>15.7607</v>
       </c>
       <c r="F113" t="n">
-        <v>28.9847</v>
+        <v>28.9124</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6195</v>
+        <v>21.6335</v>
       </c>
       <c r="C114" t="n">
-        <v>18.132</v>
+        <v>18.1247</v>
       </c>
       <c r="D114" t="n">
-        <v>42.4487</v>
+        <v>42.6885</v>
       </c>
       <c r="E114" t="n">
-        <v>15.5818</v>
+        <v>15.588</v>
       </c>
       <c r="F114" t="n">
-        <v>28.6786</v>
+        <v>28.6244</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.0887</v>
+        <v>21.0937</v>
       </c>
       <c r="C115" t="n">
-        <v>17.9755</v>
+        <v>18.0009</v>
       </c>
       <c r="D115" t="n">
-        <v>42.0144</v>
+        <v>42.21</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3318</v>
+        <v>15.3271</v>
       </c>
       <c r="F115" t="n">
-        <v>28.3978</v>
+        <v>28.3361</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5503</v>
+        <v>20.5545</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8639</v>
+        <v>17.8688</v>
       </c>
       <c r="D116" t="n">
-        <v>41.6794</v>
+        <v>41.8981</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8382</v>
+        <v>14.8408</v>
       </c>
       <c r="F116" t="n">
-        <v>28.1566</v>
+        <v>28.1735</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.0212</v>
+        <v>20.0287</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7661</v>
+        <v>17.7655</v>
       </c>
       <c r="D117" t="n">
-        <v>41.354</v>
+        <v>41.4611</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5484</v>
+        <v>14.5605</v>
       </c>
       <c r="F117" t="n">
-        <v>27.8503</v>
+        <v>27.834</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4935</v>
+        <v>19.4922</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6737</v>
+        <v>17.6699</v>
       </c>
       <c r="D118" t="n">
-        <v>41.0729</v>
+        <v>41.1301</v>
       </c>
       <c r="E118" t="n">
-        <v>14.274</v>
+        <v>14.28</v>
       </c>
       <c r="F118" t="n">
-        <v>27.5607</v>
+        <v>27.5458</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9249</v>
+        <v>18.9424</v>
       </c>
       <c r="C119" t="n">
-        <v>17.5962</v>
+        <v>17.5933</v>
       </c>
       <c r="D119" t="n">
-        <v>40.7935</v>
+        <v>40.833</v>
       </c>
       <c r="E119" t="n">
-        <v>13.9996</v>
+        <v>18.7819</v>
       </c>
       <c r="F119" t="n">
-        <v>27.2324</v>
+        <v>31.6062</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3675</v>
+        <v>18.3534</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5211</v>
+        <v>17.5099</v>
       </c>
       <c r="D120" t="n">
-        <v>40.584</v>
+        <v>38.7001</v>
       </c>
       <c r="E120" t="n">
-        <v>13.7083</v>
+        <v>18.3811</v>
       </c>
       <c r="F120" t="n">
-        <v>26.9404</v>
+        <v>31.1927</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7032</v>
+        <v>17.7222</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4193</v>
+        <v>17.4202</v>
       </c>
       <c r="D121" t="n">
-        <v>47.4152</v>
+        <v>48.4844</v>
       </c>
       <c r="E121" t="n">
-        <v>18.0429</v>
+        <v>17.9843</v>
       </c>
       <c r="F121" t="n">
-        <v>30.8877</v>
+        <v>30.8371</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>16.9909</v>
+        <v>16.9618</v>
       </c>
       <c r="C122" t="n">
-        <v>19.145</v>
+        <v>19.1154</v>
       </c>
       <c r="D122" t="n">
-        <v>47.0354</v>
+        <v>47.9656</v>
       </c>
       <c r="E122" t="n">
-        <v>17.4207</v>
+        <v>17.4123</v>
       </c>
       <c r="F122" t="n">
-        <v>30.5811</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.089</v>
+        <v>16.1429</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9201</v>
+        <v>18.9891</v>
       </c>
       <c r="D123" t="n">
-        <v>47.7306</v>
+        <v>45.1135</v>
       </c>
       <c r="E123" t="n">
-        <v>17.0822</v>
+        <v>17.0522</v>
       </c>
       <c r="F123" t="n">
-        <v>30.253</v>
+        <v>30.1736</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6294</v>
+        <v>23.6356</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7713</v>
+        <v>18.7278</v>
       </c>
       <c r="D124" t="n">
-        <v>44.56</v>
+        <v>46.9069</v>
       </c>
       <c r="E124" t="n">
-        <v>16.7346</v>
+        <v>16.7486</v>
       </c>
       <c r="F124" t="n">
-        <v>29.8828</v>
+        <v>29.8844</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.1952</v>
+        <v>23.2047</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5674</v>
+        <v>18.5558</v>
       </c>
       <c r="D125" t="n">
-        <v>44.2804</v>
+        <v>46.3308</v>
       </c>
       <c r="E125" t="n">
-        <v>16.4743</v>
+        <v>16.4812</v>
       </c>
       <c r="F125" t="n">
-        <v>29.5808</v>
+        <v>29.6686</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7446</v>
+        <v>22.7429</v>
       </c>
       <c r="C126" t="n">
-        <v>18.3899</v>
+        <v>18.3992</v>
       </c>
       <c r="D126" t="n">
-        <v>45.6477</v>
+        <v>45.8398</v>
       </c>
       <c r="E126" t="n">
-        <v>16.1077</v>
+        <v>16.1611</v>
       </c>
       <c r="F126" t="n">
-        <v>29.31</v>
+        <v>29.3801</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2453</v>
+        <v>22.2537</v>
       </c>
       <c r="C127" t="n">
-        <v>18.2491</v>
+        <v>18.3021</v>
       </c>
       <c r="D127" t="n">
-        <v>45.035</v>
+        <v>43.3108</v>
       </c>
       <c r="E127" t="n">
-        <v>15.8245</v>
+        <v>15.786</v>
       </c>
       <c r="F127" t="n">
-        <v>29.0119</v>
+        <v>29.0673</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7498</v>
+        <v>21.7413</v>
       </c>
       <c r="C128" t="n">
-        <v>18.172</v>
+        <v>18.1553</v>
       </c>
       <c r="D128" t="n">
-        <v>42.8137</v>
+        <v>42.8232</v>
       </c>
       <c r="E128" t="n">
-        <v>15.5039</v>
+        <v>15.4756</v>
       </c>
       <c r="F128" t="n">
-        <v>28.6862</v>
+        <v>28.7657</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.1885</v>
+        <v>21.1928</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0124</v>
+        <v>18.0318</v>
       </c>
       <c r="D129" t="n">
-        <v>42.2784</v>
+        <v>42.3056</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3824</v>
+        <v>15.3891</v>
       </c>
       <c r="F129" t="n">
-        <v>28.3855</v>
+        <v>28.4824</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6502</v>
+        <v>20.6651</v>
       </c>
       <c r="C130" t="n">
-        <v>17.892</v>
+        <v>17.8962</v>
       </c>
       <c r="D130" t="n">
-        <v>41.8463</v>
+        <v>41.9076</v>
       </c>
       <c r="E130" t="n">
-        <v>14.8877</v>
+        <v>14.8847</v>
       </c>
       <c r="F130" t="n">
-        <v>28.2135</v>
+        <v>28.3124</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1321</v>
+        <v>20.1377</v>
       </c>
       <c r="C131" t="n">
-        <v>17.7825</v>
+        <v>17.7997</v>
       </c>
       <c r="D131" t="n">
-        <v>41.3301</v>
+        <v>41.4329</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6093</v>
+        <v>14.6113</v>
       </c>
       <c r="F131" t="n">
-        <v>27.9171</v>
+        <v>28.0271</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6138</v>
+        <v>19.6075</v>
       </c>
       <c r="C132" t="n">
-        <v>17.6854</v>
+        <v>17.7069</v>
       </c>
       <c r="D132" t="n">
-        <v>40.9212</v>
+        <v>40.8472</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3386</v>
+        <v>14.3682</v>
       </c>
       <c r="F132" t="n">
-        <v>27.6008</v>
+        <v>27.3598</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.0592</v>
+        <v>19.16</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6134</v>
+        <v>17.6303</v>
       </c>
       <c r="D133" t="n">
-        <v>40.6506</v>
+        <v>40.3899</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0661</v>
+        <v>14.0715</v>
       </c>
       <c r="F133" t="n">
-        <v>27.324</v>
+        <v>27.0978</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.4813</v>
+        <v>18.5218</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5279</v>
+        <v>17.5428</v>
       </c>
       <c r="D134" t="n">
-        <v>40.3419</v>
+        <v>40.0693</v>
       </c>
       <c r="E134" t="n">
-        <v>13.7761</v>
+        <v>18.2469</v>
       </c>
       <c r="F134" t="n">
-        <v>27.0095</v>
+        <v>31.1688</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.875</v>
+        <v>17.8823</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4484</v>
+        <v>17.4635</v>
       </c>
       <c r="D135" t="n">
-        <v>48.0463</v>
+        <v>46.6514</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8593</v>
+        <v>17.8577</v>
       </c>
       <c r="F135" t="n">
-        <v>31.0523</v>
+        <v>30.7783</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.1893</v>
+        <v>17.1589</v>
       </c>
       <c r="C136" t="n">
-        <v>19.1707</v>
+        <v>19.194</v>
       </c>
       <c r="D136" t="n">
-        <v>46.7307</v>
+        <v>46.2559</v>
       </c>
       <c r="E136" t="n">
-        <v>17.5116</v>
+        <v>17.5473</v>
       </c>
       <c r="F136" t="n">
-        <v>30.6312</v>
+        <v>30.3463</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.2974</v>
+        <v>16.3635</v>
       </c>
       <c r="C137" t="n">
-        <v>18.9487</v>
+        <v>18.9868</v>
       </c>
       <c r="D137" t="n">
-        <v>45.4952</v>
+        <v>47.9206</v>
       </c>
       <c r="E137" t="n">
-        <v>17.0985</v>
+        <v>17.1134</v>
       </c>
       <c r="F137" t="n">
-        <v>30.3607</v>
+        <v>30.0796</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7164</v>
+        <v>23.7461</v>
       </c>
       <c r="C138" t="n">
-        <v>18.7748</v>
+        <v>18.7985</v>
       </c>
       <c r="D138" t="n">
-        <v>47.3321</v>
+        <v>47.324</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7357</v>
+        <v>16.7682</v>
       </c>
       <c r="F138" t="n">
-        <v>30.0166</v>
+        <v>29.8168</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.3013</v>
+        <v>23.324</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6092</v>
+        <v>18.6552</v>
       </c>
       <c r="D139" t="n">
-        <v>44.5048</v>
+        <v>46.5482</v>
       </c>
       <c r="E139" t="n">
-        <v>16.4438</v>
+        <v>16.4576</v>
       </c>
       <c r="F139" t="n">
-        <v>29.7233</v>
+        <v>29.4136</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.833</v>
+        <v>22.8618</v>
       </c>
       <c r="C140" t="n">
-        <v>18.4628</v>
+        <v>18.48</v>
       </c>
       <c r="D140" t="n">
-        <v>44.0169</v>
+        <v>43.6678</v>
       </c>
       <c r="E140" t="n">
-        <v>16.1868</v>
+        <v>16.1671</v>
       </c>
       <c r="F140" t="n">
-        <v>29.3615</v>
+        <v>29.0923</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3454</v>
+        <v>22.3793</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3086</v>
+        <v>18.3395</v>
       </c>
       <c r="D141" t="n">
-        <v>43.2571</v>
+        <v>45.0609</v>
       </c>
       <c r="E141" t="n">
-        <v>15.8334</v>
+        <v>15.8432</v>
       </c>
       <c r="F141" t="n">
-        <v>29.06</v>
+        <v>28.8055</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.833</v>
+        <v>21.8663</v>
       </c>
       <c r="C142" t="n">
-        <v>18.1809</v>
+        <v>18.2051</v>
       </c>
       <c r="D142" t="n">
-        <v>44.6911</v>
+        <v>44.3132</v>
       </c>
       <c r="E142" t="n">
-        <v>15.4957</v>
+        <v>15.514</v>
       </c>
       <c r="F142" t="n">
-        <v>28.881</v>
+        <v>28.6074</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.2968</v>
+        <v>21.3336</v>
       </c>
       <c r="C143" t="n">
-        <v>18.0613</v>
+        <v>18.086</v>
       </c>
       <c r="D143" t="n">
-        <v>44.012</v>
+        <v>44.0336</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2005</v>
+        <v>15.2053</v>
       </c>
       <c r="F143" t="n">
-        <v>28.6836</v>
+        <v>28.3023</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running erasure.xlsx
+++ b/gcc-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>18.9893</v>
+        <v>18.8983</v>
       </c>
       <c r="C2" t="n">
-        <v>14.095</v>
+        <v>14.1665</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2549</v>
+        <v>32.0689</v>
       </c>
       <c r="E2" t="n">
-        <v>7.38714</v>
+        <v>6.90693</v>
       </c>
       <c r="F2" t="n">
-        <v>26.7032</v>
+        <v>26.5219</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6032</v>
+        <v>18.5419</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5177</v>
+        <v>14.4977</v>
       </c>
       <c r="D3" t="n">
-        <v>32.2944</v>
+        <v>32.4131</v>
       </c>
       <c r="E3" t="n">
-        <v>6.80363</v>
+        <v>6.5693</v>
       </c>
       <c r="F3" t="n">
-        <v>26.4927</v>
+        <v>26.5026</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>18.2193</v>
+        <v>18.056</v>
       </c>
       <c r="C4" t="n">
-        <v>14.6376</v>
+        <v>14.7653</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3322</v>
+        <v>32.4319</v>
       </c>
       <c r="E4" t="n">
-        <v>6.27425</v>
+        <v>5.93795</v>
       </c>
       <c r="F4" t="n">
-        <v>26.2734</v>
+        <v>26.2861</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>17.4582</v>
+        <v>17.4715</v>
       </c>
       <c r="C5" t="n">
-        <v>14.8249</v>
+        <v>14.7638</v>
       </c>
       <c r="D5" t="n">
-        <v>32.5584</v>
+        <v>32.5801</v>
       </c>
       <c r="E5" t="n">
-        <v>16.1807</v>
+        <v>15.963</v>
       </c>
       <c r="F5" t="n">
-        <v>30.6902</v>
+        <v>30.7088</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>17.0071</v>
+        <v>17.0705</v>
       </c>
       <c r="C6" t="n">
-        <v>15.1483</v>
+        <v>15.0821</v>
       </c>
       <c r="D6" t="n">
-        <v>32.69</v>
+        <v>32.8493</v>
       </c>
       <c r="E6" t="n">
-        <v>15.6328</v>
+        <v>15.2911</v>
       </c>
       <c r="F6" t="n">
-        <v>30.4012</v>
+        <v>30.2002</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>16.4197</v>
+        <v>16.3746</v>
       </c>
       <c r="C7" t="n">
-        <v>15.408</v>
+        <v>15.3495</v>
       </c>
       <c r="D7" t="n">
-        <v>31.7991</v>
+        <v>31.9676</v>
       </c>
       <c r="E7" t="n">
-        <v>15.2323</v>
+        <v>15.3521</v>
       </c>
       <c r="F7" t="n">
-        <v>30.0568</v>
+        <v>30.0457</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>15.6561</v>
+        <v>15.6918</v>
       </c>
       <c r="C8" t="n">
-        <v>16.9414</v>
+        <v>16.9783</v>
       </c>
       <c r="D8" t="n">
-        <v>31.8856</v>
+        <v>31.8242</v>
       </c>
       <c r="E8" t="n">
-        <v>15.2762</v>
+        <v>15.3067</v>
       </c>
       <c r="F8" t="n">
-        <v>29.8243</v>
+        <v>29.8411</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.9601</v>
+        <v>15.0562</v>
       </c>
       <c r="C9" t="n">
-        <v>17.0698</v>
+        <v>17.114</v>
       </c>
       <c r="D9" t="n">
-        <v>32.26</v>
+        <v>32.0367</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0012</v>
+        <v>14.8791</v>
       </c>
       <c r="F9" t="n">
-        <v>29.5845</v>
+        <v>29.7008</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>22.731</v>
+        <v>22.8224</v>
       </c>
       <c r="C10" t="n">
-        <v>17.0713</v>
+        <v>17.1217</v>
       </c>
       <c r="D10" t="n">
-        <v>31.9862</v>
+        <v>32.1037</v>
       </c>
       <c r="E10" t="n">
-        <v>14.8185</v>
+        <v>14.5517</v>
       </c>
       <c r="F10" t="n">
-        <v>29.258</v>
+        <v>29.1984</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>22.2742</v>
+        <v>22.3281</v>
       </c>
       <c r="C11" t="n">
-        <v>17.2054</v>
+        <v>17.1529</v>
       </c>
       <c r="D11" t="n">
-        <v>32.3037</v>
+        <v>32.2421</v>
       </c>
       <c r="E11" t="n">
-        <v>14.5344</v>
+        <v>14.5058</v>
       </c>
       <c r="F11" t="n">
-        <v>29.0356</v>
+        <v>29.1338</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>21.8716</v>
+        <v>21.9656</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0612</v>
+        <v>17.075</v>
       </c>
       <c r="D12" t="n">
-        <v>32.24</v>
+        <v>32.4453</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3461</v>
+        <v>14.394</v>
       </c>
       <c r="F12" t="n">
-        <v>28.8784</v>
+        <v>28.8824</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>21.4833</v>
+        <v>21.5661</v>
       </c>
       <c r="C13" t="n">
-        <v>17.2917</v>
+        <v>17.1999</v>
       </c>
       <c r="D13" t="n">
-        <v>32.4504</v>
+        <v>32.5215</v>
       </c>
       <c r="E13" t="n">
-        <v>14.1563</v>
+        <v>14.2596</v>
       </c>
       <c r="F13" t="n">
-        <v>28.6462</v>
+        <v>28.6205</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>21.123</v>
+        <v>21.0697</v>
       </c>
       <c r="C14" t="n">
-        <v>17.258</v>
+        <v>17.2074</v>
       </c>
       <c r="D14" t="n">
-        <v>32.8874</v>
+        <v>32.6727</v>
       </c>
       <c r="E14" t="n">
-        <v>13.8164</v>
+        <v>13.9083</v>
       </c>
       <c r="F14" t="n">
-        <v>28.3806</v>
+        <v>28.3794</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>20.6846</v>
+        <v>20.5499</v>
       </c>
       <c r="C15" t="n">
-        <v>17.2567</v>
+        <v>17.3117</v>
       </c>
       <c r="D15" t="n">
-        <v>32.8989</v>
+        <v>32.965</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5747</v>
+        <v>13.5766</v>
       </c>
       <c r="F15" t="n">
-        <v>27.9361</v>
+        <v>28.0596</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>20.0746</v>
+        <v>20.1747</v>
       </c>
       <c r="C16" t="n">
-        <v>17.188</v>
+        <v>17.2364</v>
       </c>
       <c r="D16" t="n">
-        <v>32.8473</v>
+        <v>32.964</v>
       </c>
       <c r="E16" t="n">
-        <v>13.4001</v>
+        <v>13.3634</v>
       </c>
       <c r="F16" t="n">
-        <v>27.7304</v>
+        <v>27.7198</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>19.6239</v>
+        <v>19.6369</v>
       </c>
       <c r="C17" t="n">
-        <v>17.1458</v>
+        <v>17.2</v>
       </c>
       <c r="D17" t="n">
-        <v>33.0171</v>
+        <v>33.0455</v>
       </c>
       <c r="E17" t="n">
-        <v>13.2022</v>
+        <v>13.2086</v>
       </c>
       <c r="F17" t="n">
-        <v>27.4352</v>
+        <v>27.4769</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>19.1211</v>
+        <v>19.1154</v>
       </c>
       <c r="C18" t="n">
-        <v>17.1639</v>
+        <v>17.2025</v>
       </c>
       <c r="D18" t="n">
-        <v>33.0502</v>
+        <v>33.324</v>
       </c>
       <c r="E18" t="n">
-        <v>12.9759</v>
+        <v>13.0291</v>
       </c>
       <c r="F18" t="n">
-        <v>27.1664</v>
+        <v>27.1626</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>18.5504</v>
+        <v>18.5368</v>
       </c>
       <c r="C19" t="n">
-        <v>17.1483</v>
+        <v>17.0957</v>
       </c>
       <c r="D19" t="n">
-        <v>33.1705</v>
+        <v>33.3694</v>
       </c>
       <c r="E19" t="n">
-        <v>12.6944</v>
+        <v>12.6144</v>
       </c>
       <c r="F19" t="n">
-        <v>26.7636</v>
+        <v>26.7721</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>18.1271</v>
+        <v>18.1157</v>
       </c>
       <c r="C20" t="n">
-        <v>17.3204</v>
+        <v>17.1603</v>
       </c>
       <c r="D20" t="n">
-        <v>33.3711</v>
+        <v>33.454</v>
       </c>
       <c r="E20" t="n">
-        <v>18.1072</v>
+        <v>17.9124</v>
       </c>
       <c r="F20" t="n">
-        <v>30.9175</v>
+        <v>30.938</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>17.5149</v>
+        <v>17.4451</v>
       </c>
       <c r="C21" t="n">
-        <v>17.1335</v>
+        <v>17.2163</v>
       </c>
       <c r="D21" t="n">
-        <v>32.5865</v>
+        <v>32.7605</v>
       </c>
       <c r="E21" t="n">
-        <v>17.6525</v>
+        <v>17.4692</v>
       </c>
       <c r="F21" t="n">
-        <v>30.7313</v>
+        <v>30.8096</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>16.7314</v>
+        <v>16.6948</v>
       </c>
       <c r="C22" t="n">
-        <v>18.6704</v>
+        <v>18.6997</v>
       </c>
       <c r="D22" t="n">
-        <v>32.6185</v>
+        <v>32.7193</v>
       </c>
       <c r="E22" t="n">
-        <v>17.1331</v>
+        <v>17.1569</v>
       </c>
       <c r="F22" t="n">
-        <v>30.4499</v>
+        <v>30.3864</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>16.0163</v>
+        <v>15.9646</v>
       </c>
       <c r="C23" t="n">
-        <v>18.5514</v>
+        <v>18.5734</v>
       </c>
       <c r="D23" t="n">
-        <v>32.6618</v>
+        <v>32.6387</v>
       </c>
       <c r="E23" t="n">
-        <v>16.7724</v>
+        <v>16.6955</v>
       </c>
       <c r="F23" t="n">
-        <v>30.1566</v>
+        <v>30.202</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>23.3471</v>
+        <v>23.3154</v>
       </c>
       <c r="C24" t="n">
-        <v>18.429</v>
+        <v>18.4741</v>
       </c>
       <c r="D24" t="n">
-        <v>32.3758</v>
+        <v>32.67</v>
       </c>
       <c r="E24" t="n">
-        <v>16.4142</v>
+        <v>16.4381</v>
       </c>
       <c r="F24" t="n">
-        <v>30.0032</v>
+        <v>29.9097</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>22.9312</v>
+        <v>22.9222</v>
       </c>
       <c r="C25" t="n">
-        <v>18.3556</v>
+        <v>18.3091</v>
       </c>
       <c r="D25" t="n">
-        <v>32.5805</v>
+        <v>32.9961</v>
       </c>
       <c r="E25" t="n">
-        <v>16.0298</v>
+        <v>15.9583</v>
       </c>
       <c r="F25" t="n">
-        <v>29.6226</v>
+        <v>29.7145</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>22.457</v>
+        <v>22.4579</v>
       </c>
       <c r="C26" t="n">
-        <v>18.278</v>
+        <v>18.2996</v>
       </c>
       <c r="D26" t="n">
-        <v>32.6394</v>
+        <v>32.833</v>
       </c>
       <c r="E26" t="n">
-        <v>15.606</v>
+        <v>15.6832</v>
       </c>
       <c r="F26" t="n">
-        <v>29.4508</v>
+        <v>29.4136</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>22.0268</v>
+        <v>22.0159</v>
       </c>
       <c r="C27" t="n">
-        <v>17.999</v>
+        <v>18.1927</v>
       </c>
       <c r="D27" t="n">
-        <v>32.6051</v>
+        <v>32.8398</v>
       </c>
       <c r="E27" t="n">
-        <v>15.4159</v>
+        <v>15.3971</v>
       </c>
       <c r="F27" t="n">
-        <v>29.0436</v>
+        <v>29.0164</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>21.5674</v>
+        <v>21.5379</v>
       </c>
       <c r="C28" t="n">
-        <v>17.9761</v>
+        <v>18.0132</v>
       </c>
       <c r="D28" t="n">
-        <v>32.7904</v>
+        <v>33.1628</v>
       </c>
       <c r="E28" t="n">
-        <v>15.157</v>
+        <v>15.2181</v>
       </c>
       <c r="F28" t="n">
-        <v>28.7695</v>
+        <v>28.8367</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>20.9747</v>
+        <v>21.0535</v>
       </c>
       <c r="C29" t="n">
-        <v>17.9262</v>
+        <v>17.9213</v>
       </c>
       <c r="D29" t="n">
-        <v>32.9338</v>
+        <v>33.1711</v>
       </c>
       <c r="E29" t="n">
-        <v>14.8462</v>
+        <v>14.7509</v>
       </c>
       <c r="F29" t="n">
-        <v>28.3422</v>
+        <v>28.3705</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>20.6284</v>
+        <v>20.635</v>
       </c>
       <c r="C30" t="n">
-        <v>17.8898</v>
+        <v>17.9018</v>
       </c>
       <c r="D30" t="n">
-        <v>33.0251</v>
+        <v>33.1512</v>
       </c>
       <c r="E30" t="n">
-        <v>14.5122</v>
+        <v>14.5016</v>
       </c>
       <c r="F30" t="n">
-        <v>28.171</v>
+        <v>28.137</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>20.0383</v>
+        <v>20.0781</v>
       </c>
       <c r="C31" t="n">
-        <v>17.6887</v>
+        <v>17.7526</v>
       </c>
       <c r="D31" t="n">
-        <v>33.1119</v>
+        <v>33.1772</v>
       </c>
       <c r="E31" t="n">
-        <v>14.18</v>
+        <v>14.2254</v>
       </c>
       <c r="F31" t="n">
-        <v>27.8427</v>
+        <v>27.8817</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>19.657</v>
+        <v>19.6304</v>
       </c>
       <c r="C32" t="n">
-        <v>17.7451</v>
+        <v>17.7078</v>
       </c>
       <c r="D32" t="n">
-        <v>33.1972</v>
+        <v>33.315</v>
       </c>
       <c r="E32" t="n">
-        <v>13.894</v>
+        <v>13.9257</v>
       </c>
       <c r="F32" t="n">
-        <v>27.5084</v>
+        <v>27.5326</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>19.0674</v>
+        <v>19.0566</v>
       </c>
       <c r="C33" t="n">
-        <v>17.6191</v>
+        <v>17.6206</v>
       </c>
       <c r="D33" t="n">
-        <v>33.4384</v>
+        <v>33.491</v>
       </c>
       <c r="E33" t="n">
-        <v>13.5883</v>
+        <v>13.6222</v>
       </c>
       <c r="F33" t="n">
-        <v>27.1542</v>
+        <v>27.1965</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>18.4757</v>
+        <v>18.4611</v>
       </c>
       <c r="C34" t="n">
-        <v>17.5543</v>
+        <v>17.5571</v>
       </c>
       <c r="D34" t="n">
-        <v>33.5499</v>
+        <v>33.4962</v>
       </c>
       <c r="E34" t="n">
-        <v>18.4729</v>
+        <v>18.4161</v>
       </c>
       <c r="F34" t="n">
-        <v>31.532</v>
+        <v>31.4015</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>17.858</v>
+        <v>17.8419</v>
       </c>
       <c r="C35" t="n">
-        <v>17.4405</v>
+        <v>17.4892</v>
       </c>
       <c r="D35" t="n">
-        <v>32.5994</v>
+        <v>32.6039</v>
       </c>
       <c r="E35" t="n">
-        <v>17.8417</v>
+        <v>17.8799</v>
       </c>
       <c r="F35" t="n">
-        <v>31.2217</v>
+        <v>31.103</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.2998</v>
+        <v>17.3011</v>
       </c>
       <c r="C36" t="n">
-        <v>17.4386</v>
+        <v>17.4553</v>
       </c>
       <c r="D36" t="n">
-        <v>32.6528</v>
+        <v>32.7235</v>
       </c>
       <c r="E36" t="n">
-        <v>17.5871</v>
+        <v>17.5521</v>
       </c>
       <c r="F36" t="n">
-        <v>30.8356</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>16.4463</v>
+        <v>16.4458</v>
       </c>
       <c r="C37" t="n">
-        <v>18.8006</v>
+        <v>18.8755</v>
       </c>
       <c r="D37" t="n">
-        <v>32.7242</v>
+        <v>32.6006</v>
       </c>
       <c r="E37" t="n">
-        <v>17.0968</v>
+        <v>17.0625</v>
       </c>
       <c r="F37" t="n">
-        <v>30.4894</v>
+        <v>30.2677</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>23.7134</v>
+        <v>23.694</v>
       </c>
       <c r="C38" t="n">
-        <v>18.6646</v>
+        <v>18.6474</v>
       </c>
       <c r="D38" t="n">
-        <v>32.6328</v>
+        <v>32.6452</v>
       </c>
       <c r="E38" t="n">
-        <v>16.8129</v>
+        <v>16.8124</v>
       </c>
       <c r="F38" t="n">
-        <v>30.2402</v>
+        <v>29.9836</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>23.2784</v>
+        <v>23.2527</v>
       </c>
       <c r="C39" t="n">
-        <v>18.4758</v>
+        <v>18.4905</v>
       </c>
       <c r="D39" t="n">
-        <v>32.6038</v>
+        <v>32.6746</v>
       </c>
       <c r="E39" t="n">
-        <v>16.4515</v>
+        <v>16.4335</v>
       </c>
       <c r="F39" t="n">
-        <v>29.8822</v>
+        <v>29.682</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>22.9375</v>
+        <v>22.9086</v>
       </c>
       <c r="C40" t="n">
-        <v>18.3573</v>
+        <v>18.448</v>
       </c>
       <c r="D40" t="n">
-        <v>32.943</v>
+        <v>32.973</v>
       </c>
       <c r="E40" t="n">
-        <v>16.1802</v>
+        <v>16.1325</v>
       </c>
       <c r="F40" t="n">
-        <v>29.4673</v>
+        <v>29.3488</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>22.4341</v>
+        <v>22.4385</v>
       </c>
       <c r="C41" t="n">
-        <v>18.2407</v>
+        <v>18.2561</v>
       </c>
       <c r="D41" t="n">
-        <v>33.0494</v>
+        <v>33.0793</v>
       </c>
       <c r="E41" t="n">
-        <v>15.854</v>
+        <v>15.8545</v>
       </c>
       <c r="F41" t="n">
-        <v>29.2202</v>
+        <v>29.1011</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>21.9346</v>
+        <v>21.9398</v>
       </c>
       <c r="C42" t="n">
-        <v>18.0492</v>
+        <v>18.0922</v>
       </c>
       <c r="D42" t="n">
-        <v>32.8716</v>
+        <v>32.9238</v>
       </c>
       <c r="E42" t="n">
-        <v>15.5145</v>
+        <v>15.5226</v>
       </c>
       <c r="F42" t="n">
-        <v>28.9435</v>
+        <v>28.7673</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>21.4397</v>
+        <v>21.4381</v>
       </c>
       <c r="C43" t="n">
-        <v>17.9133</v>
+        <v>17.9481</v>
       </c>
       <c r="D43" t="n">
-        <v>32.8786</v>
+        <v>32.8422</v>
       </c>
       <c r="E43" t="n">
-        <v>15.2457</v>
+        <v>15.2168</v>
       </c>
       <c r="F43" t="n">
-        <v>28.7751</v>
+        <v>28.5113</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>20.8791</v>
+        <v>20.8607</v>
       </c>
       <c r="C44" t="n">
-        <v>17.8195</v>
+        <v>17.9079</v>
       </c>
       <c r="D44" t="n">
-        <v>33.0554</v>
+        <v>32.905</v>
       </c>
       <c r="E44" t="n">
-        <v>14.9289</v>
+        <v>14.9598</v>
       </c>
       <c r="F44" t="n">
-        <v>28.4269</v>
+        <v>28.2664</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>20.4318</v>
+        <v>20.4014</v>
       </c>
       <c r="C45" t="n">
-        <v>17.7305</v>
+        <v>17.7846</v>
       </c>
       <c r="D45" t="n">
-        <v>33.0853</v>
+        <v>32.9589</v>
       </c>
       <c r="E45" t="n">
-        <v>14.617</v>
+        <v>14.6033</v>
       </c>
       <c r="F45" t="n">
-        <v>28.0203</v>
+        <v>27.9016</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>19.8883</v>
+        <v>19.8987</v>
       </c>
       <c r="C46" t="n">
-        <v>17.6723</v>
+        <v>17.7032</v>
       </c>
       <c r="D46" t="n">
-        <v>33.1353</v>
+        <v>33.0758</v>
       </c>
       <c r="E46" t="n">
-        <v>14.3393</v>
+        <v>14.3131</v>
       </c>
       <c r="F46" t="n">
-        <v>27.9474</v>
+        <v>27.6971</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>19.3636</v>
+        <v>19.3372</v>
       </c>
       <c r="C47" t="n">
-        <v>17.538</v>
+        <v>17.5675</v>
       </c>
       <c r="D47" t="n">
-        <v>33.174</v>
+        <v>33.3172</v>
       </c>
       <c r="E47" t="n">
-        <v>14.0338</v>
+        <v>14.0472</v>
       </c>
       <c r="F47" t="n">
-        <v>27.5678</v>
+        <v>27.3808</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>18.8411</v>
+        <v>18.8153</v>
       </c>
       <c r="C48" t="n">
-        <v>17.4226</v>
+        <v>17.4629</v>
       </c>
       <c r="D48" t="n">
-        <v>33.2869</v>
+        <v>33.2729</v>
       </c>
       <c r="E48" t="n">
-        <v>18.2477</v>
+        <v>18.4536</v>
       </c>
       <c r="F48" t="n">
-        <v>31.7909</v>
+        <v>31.3777</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>18.2947</v>
+        <v>18.2174</v>
       </c>
       <c r="C49" t="n">
-        <v>17.3579</v>
+        <v>17.4054</v>
       </c>
       <c r="D49" t="n">
-        <v>33.8789</v>
+        <v>33.8221</v>
       </c>
       <c r="E49" t="n">
-        <v>18.0857</v>
+        <v>18.0308</v>
       </c>
       <c r="F49" t="n">
-        <v>31.3011</v>
+        <v>31.061</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>17.616</v>
+        <v>17.6505</v>
       </c>
       <c r="C50" t="n">
-        <v>17.2958</v>
+        <v>17.3434</v>
       </c>
       <c r="D50" t="n">
-        <v>33.2759</v>
+        <v>33.3235</v>
       </c>
       <c r="E50" t="n">
-        <v>17.6881</v>
+        <v>17.67</v>
       </c>
       <c r="F50" t="n">
-        <v>30.9741</v>
+        <v>30.8252</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>16.8072</v>
+        <v>16.7845</v>
       </c>
       <c r="C51" t="n">
-        <v>18.7925</v>
+        <v>18.8366</v>
       </c>
       <c r="D51" t="n">
-        <v>33.3917</v>
+        <v>33.4325</v>
       </c>
       <c r="E51" t="n">
-        <v>17.3163</v>
+        <v>17.4035</v>
       </c>
       <c r="F51" t="n">
-        <v>30.7156</v>
+        <v>30.4426</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.9605</v>
+        <v>15.9334</v>
       </c>
       <c r="C52" t="n">
-        <v>18.5874</v>
+        <v>18.646</v>
       </c>
       <c r="D52" t="n">
-        <v>33.4983</v>
+        <v>33.5423</v>
       </c>
       <c r="E52" t="n">
-        <v>17.0393</v>
+        <v>17.0527</v>
       </c>
       <c r="F52" t="n">
-        <v>30.2686</v>
+        <v>30.1436</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>23.51</v>
+        <v>23.5058</v>
       </c>
       <c r="C53" t="n">
-        <v>18.4419</v>
+        <v>18.4809</v>
       </c>
       <c r="D53" t="n">
-        <v>33.6607</v>
+        <v>33.6622</v>
       </c>
       <c r="E53" t="n">
-        <v>16.7238</v>
+        <v>16.6787</v>
       </c>
       <c r="F53" t="n">
-        <v>29.963</v>
+        <v>29.8668</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>23.0815</v>
+        <v>23.082</v>
       </c>
       <c r="C54" t="n">
-        <v>18.3162</v>
+        <v>18.3578</v>
       </c>
       <c r="D54" t="n">
-        <v>33.2864</v>
+        <v>33.305</v>
       </c>
       <c r="E54" t="n">
-        <v>16.3832</v>
+        <v>16.3574</v>
       </c>
       <c r="F54" t="n">
-        <v>29.7027</v>
+        <v>29.5278</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>22.6011</v>
+        <v>22.5893</v>
       </c>
       <c r="C55" t="n">
-        <v>18.2007</v>
+        <v>18.2498</v>
       </c>
       <c r="D55" t="n">
-        <v>33.2579</v>
+        <v>33.3208</v>
       </c>
       <c r="E55" t="n">
-        <v>16.0294</v>
+        <v>16.1139</v>
       </c>
       <c r="F55" t="n">
-        <v>29.2985</v>
+        <v>29.2666</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>22.0988</v>
+        <v>22.1004</v>
       </c>
       <c r="C56" t="n">
-        <v>18.0904</v>
+        <v>18.1161</v>
       </c>
       <c r="D56" t="n">
-        <v>33.779</v>
+        <v>33.9487</v>
       </c>
       <c r="E56" t="n">
-        <v>15.7653</v>
+        <v>15.7094</v>
       </c>
       <c r="F56" t="n">
-        <v>29.1129</v>
+        <v>28.9907</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>21.5869</v>
+        <v>21.5819</v>
       </c>
       <c r="C57" t="n">
-        <v>17.9275</v>
+        <v>18.0006</v>
       </c>
       <c r="D57" t="n">
-        <v>33.8791</v>
+        <v>34.0924</v>
       </c>
       <c r="E57" t="n">
-        <v>15.4884</v>
+        <v>15.26</v>
       </c>
       <c r="F57" t="n">
-        <v>28.7912</v>
+        <v>28.667</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>21.0745</v>
+        <v>21.0571</v>
       </c>
       <c r="C58" t="n">
-        <v>17.8696</v>
+        <v>17.9018</v>
       </c>
       <c r="D58" t="n">
-        <v>34.0906</v>
+        <v>34.2463</v>
       </c>
       <c r="E58" t="n">
-        <v>15.1721</v>
+        <v>14.9262</v>
       </c>
       <c r="F58" t="n">
-        <v>28.6237</v>
+        <v>28.4935</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>20.5858</v>
+        <v>20.5839</v>
       </c>
       <c r="C59" t="n">
-        <v>17.7664</v>
+        <v>17.7755</v>
       </c>
       <c r="D59" t="n">
-        <v>34.2738</v>
+        <v>34.3425</v>
       </c>
       <c r="E59" t="n">
-        <v>14.9109</v>
+        <v>14.6942</v>
       </c>
       <c r="F59" t="n">
-        <v>28.3246</v>
+        <v>28.185</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>19.978</v>
+        <v>19.9995</v>
       </c>
       <c r="C60" t="n">
-        <v>17.6641</v>
+        <v>17.7012</v>
       </c>
       <c r="D60" t="n">
-        <v>34.4576</v>
+        <v>34.5494</v>
       </c>
       <c r="E60" t="n">
-        <v>14.6092</v>
+        <v>14.4353</v>
       </c>
       <c r="F60" t="n">
-        <v>27.8796</v>
+        <v>27.8515</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>19.5057</v>
+        <v>19.5039</v>
       </c>
       <c r="C61" t="n">
-        <v>17.5754</v>
+        <v>17.587</v>
       </c>
       <c r="D61" t="n">
-        <v>34.6032</v>
+        <v>34.836</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3096</v>
+        <v>14.3266</v>
       </c>
       <c r="F61" t="n">
-        <v>27.5348</v>
+        <v>27.5026</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>18.9865</v>
+        <v>18.9846</v>
       </c>
       <c r="C62" t="n">
-        <v>17.5537</v>
+        <v>17.5213</v>
       </c>
       <c r="D62" t="n">
-        <v>35.0319</v>
+        <v>35.1849</v>
       </c>
       <c r="E62" t="n">
-        <v>14.0084</v>
+        <v>13.9983</v>
       </c>
       <c r="F62" t="n">
-        <v>27.2536</v>
+        <v>27.2245</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>18.364</v>
+        <v>18.3889</v>
       </c>
       <c r="C63" t="n">
-        <v>17.4129</v>
+        <v>17.4782</v>
       </c>
       <c r="D63" t="n">
-        <v>35.2525</v>
+        <v>35.3964</v>
       </c>
       <c r="E63" t="n">
-        <v>19.0609</v>
+        <v>18.953</v>
       </c>
       <c r="F63" t="n">
-        <v>31.4509</v>
+        <v>31.3381</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>17.7218</v>
+        <v>17.7324</v>
       </c>
       <c r="C64" t="n">
-        <v>17.3889</v>
+        <v>17.3989</v>
       </c>
       <c r="D64" t="n">
-        <v>38.2325</v>
+        <v>38.3152</v>
       </c>
       <c r="E64" t="n">
-        <v>18.6567</v>
+        <v>18.6189</v>
       </c>
       <c r="F64" t="n">
-        <v>31.1197</v>
+        <v>30.9966</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>17.0273</v>
+        <v>17.0499</v>
       </c>
       <c r="C65" t="n">
-        <v>18.9395</v>
+        <v>18.983</v>
       </c>
       <c r="D65" t="n">
-        <v>38.4408</v>
+        <v>38.6171</v>
       </c>
       <c r="E65" t="n">
-        <v>17.9014</v>
+        <v>18.2906</v>
       </c>
       <c r="F65" t="n">
-        <v>30.7473</v>
+        <v>30.6271</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.1927</v>
+        <v>16.1777</v>
       </c>
       <c r="C66" t="n">
-        <v>18.7157</v>
+        <v>18.7444</v>
       </c>
       <c r="D66" t="n">
-        <v>38.6714</v>
+        <v>38.7043</v>
       </c>
       <c r="E66" t="n">
-        <v>17.7347</v>
+        <v>17.8127</v>
       </c>
       <c r="F66" t="n">
-        <v>30.4155</v>
+        <v>30.2579</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>23.6465</v>
+        <v>23.6542</v>
       </c>
       <c r="C67" t="n">
-        <v>18.5699</v>
+        <v>18.5829</v>
       </c>
       <c r="D67" t="n">
-        <v>38.7025</v>
+        <v>38.7847</v>
       </c>
       <c r="E67" t="n">
-        <v>17.1202</v>
+        <v>17.4555</v>
       </c>
       <c r="F67" t="n">
-        <v>30.0852</v>
+        <v>29.9939</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>23.1999</v>
+        <v>23.2004</v>
       </c>
       <c r="C68" t="n">
-        <v>18.376</v>
+        <v>18.4605</v>
       </c>
       <c r="D68" t="n">
-        <v>40.0756</v>
+        <v>40.0707</v>
       </c>
       <c r="E68" t="n">
-        <v>16.9146</v>
+        <v>16.8932</v>
       </c>
       <c r="F68" t="n">
-        <v>29.7835</v>
+        <v>29.7044</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>22.7702</v>
+        <v>22.7485</v>
       </c>
       <c r="C69" t="n">
-        <v>18.3028</v>
+        <v>18.3265</v>
       </c>
       <c r="D69" t="n">
-        <v>40.2459</v>
+        <v>40.1228</v>
       </c>
       <c r="E69" t="n">
-        <v>16.4029</v>
+        <v>16.4759</v>
       </c>
       <c r="F69" t="n">
-        <v>29.5633</v>
+        <v>29.369</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>22.295</v>
+        <v>22.2943</v>
       </c>
       <c r="C70" t="n">
-        <v>18.2858</v>
+        <v>18.3074</v>
       </c>
       <c r="D70" t="n">
-        <v>39.2504</v>
+        <v>39.1511</v>
       </c>
       <c r="E70" t="n">
-        <v>16.01</v>
+        <v>16.0262</v>
       </c>
       <c r="F70" t="n">
-        <v>29.2382</v>
+        <v>29.1194</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>21.7673</v>
+        <v>21.7668</v>
       </c>
       <c r="C71" t="n">
-        <v>18.1377</v>
+        <v>18.1479</v>
       </c>
       <c r="D71" t="n">
-        <v>39.2062</v>
+        <v>39.0128</v>
       </c>
       <c r="E71" t="n">
-        <v>15.6742</v>
+        <v>15.7032</v>
       </c>
       <c r="F71" t="n">
-        <v>28.9749</v>
+        <v>28.8747</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>21.2481</v>
+        <v>21.2312</v>
       </c>
       <c r="C72" t="n">
-        <v>18.0114</v>
+        <v>18.0465</v>
       </c>
       <c r="D72" t="n">
-        <v>39.2459</v>
+        <v>39.1372</v>
       </c>
       <c r="E72" t="n">
-        <v>15.3761</v>
+        <v>15.3953</v>
       </c>
       <c r="F72" t="n">
-        <v>28.6082</v>
+        <v>28.5366</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>20.7359</v>
+        <v>20.7001</v>
       </c>
       <c r="C73" t="n">
-        <v>17.9022</v>
+        <v>17.9206</v>
       </c>
       <c r="D73" t="n">
-        <v>39.3844</v>
+        <v>39.3971</v>
       </c>
       <c r="E73" t="n">
-        <v>15.0951</v>
+        <v>15.0996</v>
       </c>
       <c r="F73" t="n">
-        <v>28.3213</v>
+        <v>28.2099</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>20.1661</v>
+        <v>20.1431</v>
       </c>
       <c r="C74" t="n">
-        <v>17.8438</v>
+        <v>17.8397</v>
       </c>
       <c r="D74" t="n">
-        <v>39.3272</v>
+        <v>39.301</v>
       </c>
       <c r="E74" t="n">
-        <v>14.787</v>
+        <v>14.7849</v>
       </c>
       <c r="F74" t="n">
-        <v>28.0055</v>
+        <v>27.9106</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>19.6755</v>
+        <v>19.6545</v>
       </c>
       <c r="C75" t="n">
-        <v>17.7369</v>
+        <v>17.7851</v>
       </c>
       <c r="D75" t="n">
-        <v>39.3307</v>
+        <v>39.2937</v>
       </c>
       <c r="E75" t="n">
-        <v>14.5261</v>
+        <v>14.5322</v>
       </c>
       <c r="F75" t="n">
-        <v>27.7387</v>
+        <v>27.688</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>19.0985</v>
+        <v>19.1117</v>
       </c>
       <c r="C76" t="n">
-        <v>17.6694</v>
+        <v>17.6475</v>
       </c>
       <c r="D76" t="n">
-        <v>39.2548</v>
+        <v>39.1885</v>
       </c>
       <c r="E76" t="n">
-        <v>14.2219</v>
+        <v>14.2043</v>
       </c>
       <c r="F76" t="n">
-        <v>27.4274</v>
+        <v>27.3518</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>18.5292</v>
+        <v>18.5259</v>
       </c>
       <c r="C77" t="n">
-        <v>17.5928</v>
+        <v>17.5907</v>
       </c>
       <c r="D77" t="n">
-        <v>39.2169</v>
+        <v>39.2069</v>
       </c>
       <c r="E77" t="n">
-        <v>18.6861</v>
+        <v>18.6975</v>
       </c>
       <c r="F77" t="n">
-        <v>31.5233</v>
+        <v>31.387</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.9206</v>
+        <v>17.9251</v>
       </c>
       <c r="C78" t="n">
-        <v>17.4144</v>
+        <v>17.4362</v>
       </c>
       <c r="D78" t="n">
-        <v>47.4629</v>
+        <v>47.3572</v>
       </c>
       <c r="E78" t="n">
-        <v>18.2159</v>
+        <v>18.2541</v>
       </c>
       <c r="F78" t="n">
-        <v>31.101</v>
+        <v>30.984</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>17.2005</v>
+        <v>17.2001</v>
       </c>
       <c r="C79" t="n">
-        <v>19.1834</v>
+        <v>19.2845</v>
       </c>
       <c r="D79" t="n">
-        <v>47.1306</v>
+        <v>46.9229</v>
       </c>
       <c r="E79" t="n">
-        <v>17.6759</v>
+        <v>17.68</v>
       </c>
       <c r="F79" t="n">
-        <v>30.776</v>
+        <v>30.7074</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.3856</v>
+        <v>16.3688</v>
       </c>
       <c r="C80" t="n">
-        <v>19.0194</v>
+        <v>19.0521</v>
       </c>
       <c r="D80" t="n">
-        <v>46.6955</v>
+        <v>46.5649</v>
       </c>
       <c r="E80" t="n">
-        <v>17.351</v>
+        <v>17.3109</v>
       </c>
       <c r="F80" t="n">
-        <v>30.4489</v>
+        <v>30.382</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>23.7927</v>
+        <v>23.7595</v>
       </c>
       <c r="C81" t="n">
-        <v>18.8676</v>
+        <v>18.8728</v>
       </c>
       <c r="D81" t="n">
-        <v>45.9928</v>
+        <v>45.9313</v>
       </c>
       <c r="E81" t="n">
-        <v>16.9658</v>
+        <v>16.9701</v>
       </c>
       <c r="F81" t="n">
-        <v>30.0818</v>
+        <v>30.0499</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>23.3584</v>
+        <v>23.3606</v>
       </c>
       <c r="C82" t="n">
-        <v>18.7355</v>
+        <v>18.7207</v>
       </c>
       <c r="D82" t="n">
-        <v>45.5704</v>
+        <v>45.4811</v>
       </c>
       <c r="E82" t="n">
-        <v>16.6718</v>
+        <v>16.6642</v>
       </c>
       <c r="F82" t="n">
-        <v>29.7982</v>
+        <v>29.7483</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>22.9024</v>
+        <v>22.8952</v>
       </c>
       <c r="C83" t="n">
-        <v>18.5737</v>
+        <v>18.573</v>
       </c>
       <c r="D83" t="n">
-        <v>43.494</v>
+        <v>43.5274</v>
       </c>
       <c r="E83" t="n">
-        <v>16.3782</v>
+        <v>16.3748</v>
       </c>
       <c r="F83" t="n">
-        <v>29.5203</v>
+        <v>29.5024</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>22.4584</v>
+        <v>22.454</v>
       </c>
       <c r="C84" t="n">
-        <v>18.4193</v>
+        <v>18.4244</v>
       </c>
       <c r="D84" t="n">
-        <v>44.6806</v>
+        <v>44.694</v>
       </c>
       <c r="E84" t="n">
-        <v>16.0566</v>
+        <v>16.0531</v>
       </c>
       <c r="F84" t="n">
-        <v>29.1826</v>
+        <v>29.1381</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>21.9353</v>
+        <v>21.9229</v>
       </c>
       <c r="C85" t="n">
-        <v>18.2011</v>
+        <v>18.2217</v>
       </c>
       <c r="D85" t="n">
-        <v>44.6375</v>
+        <v>44.6341</v>
       </c>
       <c r="E85" t="n">
-        <v>15.7944</v>
+        <v>15.7743</v>
       </c>
       <c r="F85" t="n">
-        <v>28.8732</v>
+        <v>28.8243</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>21.4055</v>
+        <v>21.4036</v>
       </c>
       <c r="C86" t="n">
-        <v>18.0798</v>
+        <v>18.1374</v>
       </c>
       <c r="D86" t="n">
-        <v>43.8378</v>
+        <v>43.8357</v>
       </c>
       <c r="E86" t="n">
-        <v>15.4928</v>
+        <v>15.4763</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6292</v>
+        <v>28.5724</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>20.8702</v>
+        <v>20.8999</v>
       </c>
       <c r="C87" t="n">
-        <v>17.9519</v>
+        <v>17.9862</v>
       </c>
       <c r="D87" t="n">
-        <v>43.7112</v>
+        <v>43.6464</v>
       </c>
       <c r="E87" t="n">
-        <v>15.1874</v>
+        <v>15.1755</v>
       </c>
       <c r="F87" t="n">
-        <v>28.348</v>
+        <v>28.2908</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>20.3535</v>
+        <v>20.3475</v>
       </c>
       <c r="C88" t="n">
-        <v>17.8891</v>
+        <v>17.8887</v>
       </c>
       <c r="D88" t="n">
-        <v>43.4709</v>
+        <v>43.4408</v>
       </c>
       <c r="E88" t="n">
-        <v>14.9121</v>
+        <v>14.9156</v>
       </c>
       <c r="F88" t="n">
-        <v>28.0262</v>
+        <v>27.9918</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8405</v>
+        <v>19.8278</v>
       </c>
       <c r="C89" t="n">
-        <v>17.7443</v>
+        <v>17.776</v>
       </c>
       <c r="D89" t="n">
-        <v>42.914</v>
+        <v>42.944</v>
       </c>
       <c r="E89" t="n">
-        <v>14.6312</v>
+        <v>14.6344</v>
       </c>
       <c r="F89" t="n">
-        <v>27.7192</v>
+        <v>27.6955</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>19.3093</v>
+        <v>19.2881</v>
       </c>
       <c r="C90" t="n">
-        <v>17.7189</v>
+        <v>17.6889</v>
       </c>
       <c r="D90" t="n">
-        <v>43.0378</v>
+        <v>43.0939</v>
       </c>
       <c r="E90" t="n">
-        <v>14.3036</v>
+        <v>14.2939</v>
       </c>
       <c r="F90" t="n">
-        <v>27.4058</v>
+        <v>27.3579</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.7102</v>
+        <v>18.7158</v>
       </c>
       <c r="C91" t="n">
-        <v>17.6098</v>
+        <v>17.5898</v>
       </c>
       <c r="D91" t="n">
-        <v>42.6406</v>
+        <v>42.7008</v>
       </c>
       <c r="E91" t="n">
-        <v>18.6397</v>
+        <v>18.5942</v>
       </c>
       <c r="F91" t="n">
-        <v>31.5178</v>
+        <v>31.4924</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>18.1026</v>
+        <v>18.0922</v>
       </c>
       <c r="C92" t="n">
-        <v>17.485</v>
+        <v>17.4933</v>
       </c>
       <c r="D92" t="n">
-        <v>46.0405</v>
+        <v>45.7879</v>
       </c>
       <c r="E92" t="n">
-        <v>18.1653</v>
+        <v>18.174</v>
       </c>
       <c r="F92" t="n">
-        <v>31.1532</v>
+        <v>31.175</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>17.3975</v>
+        <v>17.3847</v>
       </c>
       <c r="C93" t="n">
-        <v>17.3588</v>
+        <v>17.4539</v>
       </c>
       <c r="D93" t="n">
-        <v>45.4818</v>
+        <v>45.3254</v>
       </c>
       <c r="E93" t="n">
-        <v>17.7879</v>
+        <v>17.7863</v>
       </c>
       <c r="F93" t="n">
-        <v>31.1481</v>
+        <v>31.2113</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.6514</v>
+        <v>16.6255</v>
       </c>
       <c r="C94" t="n">
-        <v>18.9727</v>
+        <v>19.028</v>
       </c>
       <c r="D94" t="n">
-        <v>44.9962</v>
+        <v>44.9126</v>
       </c>
       <c r="E94" t="n">
-        <v>17.4611</v>
+        <v>17.4649</v>
       </c>
       <c r="F94" t="n">
-        <v>30.5184</v>
+        <v>30.5695</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>23.8735</v>
+        <v>23.8658</v>
       </c>
       <c r="C95" t="n">
-        <v>18.8396</v>
+        <v>18.8581</v>
       </c>
       <c r="D95" t="n">
-        <v>44.391</v>
+        <v>44.3189</v>
       </c>
       <c r="E95" t="n">
-        <v>17.0142</v>
+        <v>17.0703</v>
       </c>
       <c r="F95" t="n">
-        <v>30.1853</v>
+        <v>30.2567</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>23.4688</v>
+        <v>23.4667</v>
       </c>
       <c r="C96" t="n">
-        <v>18.6617</v>
+        <v>18.665</v>
       </c>
       <c r="D96" t="n">
-        <v>43.8289</v>
+        <v>43.7773</v>
       </c>
       <c r="E96" t="n">
-        <v>16.5764</v>
+        <v>16.5712</v>
       </c>
       <c r="F96" t="n">
-        <v>30.0416</v>
+        <v>30.0354</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>23.0124</v>
+        <v>23.0206</v>
       </c>
       <c r="C97" t="n">
-        <v>18.4975</v>
+        <v>18.5193</v>
       </c>
       <c r="D97" t="n">
-        <v>45.7348</v>
+        <v>45.6199</v>
       </c>
       <c r="E97" t="n">
-        <v>16.2253</v>
+        <v>16.2237</v>
       </c>
       <c r="F97" t="n">
-        <v>29.7328</v>
+        <v>29.6901</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>22.5543</v>
+        <v>22.5486</v>
       </c>
       <c r="C98" t="n">
-        <v>18.3459</v>
+        <v>18.3555</v>
       </c>
       <c r="D98" t="n">
-        <v>45.0734</v>
+        <v>44.9591</v>
       </c>
       <c r="E98" t="n">
-        <v>15.9171</v>
+        <v>15.9247</v>
       </c>
       <c r="F98" t="n">
-        <v>29.447</v>
+        <v>29.3316</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>22.0326</v>
+        <v>22.0361</v>
       </c>
       <c r="C99" t="n">
-        <v>18.2694</v>
+        <v>18.2466</v>
       </c>
       <c r="D99" t="n">
-        <v>42.7386</v>
+        <v>42.6218</v>
       </c>
       <c r="E99" t="n">
-        <v>15.6309</v>
+        <v>15.6274</v>
       </c>
       <c r="F99" t="n">
-        <v>29.1187</v>
+        <v>29.0247</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>21.5119</v>
+        <v>21.5198</v>
       </c>
       <c r="C100" t="n">
-        <v>18.1899</v>
+        <v>18.172</v>
       </c>
       <c r="D100" t="n">
-        <v>42.4273</v>
+        <v>42.3157</v>
       </c>
       <c r="E100" t="n">
-        <v>15.3094</v>
+        <v>15.3161</v>
       </c>
       <c r="F100" t="n">
-        <v>28.7811</v>
+        <v>28.6718</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>20.9828</v>
+        <v>20.9814</v>
       </c>
       <c r="C101" t="n">
-        <v>18.046</v>
+        <v>18.0621</v>
       </c>
       <c r="D101" t="n">
-        <v>41.5878</v>
+        <v>41.5076</v>
       </c>
       <c r="E101" t="n">
-        <v>15.0465</v>
+        <v>15.0549</v>
       </c>
       <c r="F101" t="n">
-        <v>28.3741</v>
+        <v>28.3928</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.4546</v>
+        <v>20.456</v>
       </c>
       <c r="C102" t="n">
-        <v>17.9713</v>
+        <v>17.9841</v>
       </c>
       <c r="D102" t="n">
-        <v>41.4906</v>
+        <v>41.4108</v>
       </c>
       <c r="E102" t="n">
-        <v>14.7681</v>
+        <v>14.7776</v>
       </c>
       <c r="F102" t="n">
-        <v>28.0896</v>
+        <v>28.1001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>19.9183</v>
+        <v>19.9042</v>
       </c>
       <c r="C103" t="n">
-        <v>17.8559</v>
+        <v>17.8497</v>
       </c>
       <c r="D103" t="n">
-        <v>40.8718</v>
+        <v>40.8665</v>
       </c>
       <c r="E103" t="n">
-        <v>14.4953</v>
+        <v>14.5327</v>
       </c>
       <c r="F103" t="n">
-        <v>27.7961</v>
+        <v>27.8038</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>19.4139</v>
+        <v>19.4143</v>
       </c>
       <c r="C104" t="n">
-        <v>17.7744</v>
+        <v>17.7601</v>
       </c>
       <c r="D104" t="n">
-        <v>40.8629</v>
+        <v>40.8346</v>
       </c>
       <c r="E104" t="n">
-        <v>14.2137</v>
+        <v>14.2183</v>
       </c>
       <c r="F104" t="n">
-        <v>27.5047</v>
+        <v>27.4903</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>18.8113</v>
+        <v>18.8406</v>
       </c>
       <c r="C105" t="n">
-        <v>17.6458</v>
+        <v>17.649</v>
       </c>
       <c r="D105" t="n">
-        <v>40.3043</v>
+        <v>40.3138</v>
       </c>
       <c r="E105" t="n">
-        <v>18.4709</v>
+        <v>18.4677</v>
       </c>
       <c r="F105" t="n">
-        <v>31.6486</v>
+        <v>31.6635</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>18.225</v>
+        <v>18.2133</v>
       </c>
       <c r="C106" t="n">
-        <v>17.5662</v>
+        <v>17.5628</v>
       </c>
       <c r="D106" t="n">
-        <v>41.7462</v>
+        <v>41.7527</v>
       </c>
       <c r="E106" t="n">
-        <v>18.0659</v>
+        <v>18.0615</v>
       </c>
       <c r="F106" t="n">
-        <v>31.2705</v>
+        <v>31.2759</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>17.5607</v>
+        <v>17.5615</v>
       </c>
       <c r="C107" t="n">
-        <v>17.4951</v>
+        <v>17.4961</v>
       </c>
       <c r="D107" t="n">
-        <v>43.8623</v>
+        <v>43.884</v>
       </c>
       <c r="E107" t="n">
-        <v>17.6997</v>
+        <v>17.7049</v>
       </c>
       <c r="F107" t="n">
-        <v>30.8952</v>
+        <v>30.8928</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>16.8358</v>
+        <v>16.8295</v>
       </c>
       <c r="C108" t="n">
-        <v>19.1345</v>
+        <v>19.1482</v>
       </c>
       <c r="D108" t="n">
-        <v>45.9076</v>
+        <v>46.0227</v>
       </c>
       <c r="E108" t="n">
-        <v>17.3714</v>
+        <v>17.3576</v>
       </c>
       <c r="F108" t="n">
-        <v>30.5498</v>
+        <v>30.5103</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>15.9175</v>
+        <v>15.9217</v>
       </c>
       <c r="C109" t="n">
-        <v>18.9645</v>
+        <v>18.9718</v>
       </c>
       <c r="D109" t="n">
-        <v>45.2946</v>
+        <v>45.2822</v>
       </c>
       <c r="E109" t="n">
-        <v>16.9755</v>
+        <v>16.963</v>
       </c>
       <c r="F109" t="n">
-        <v>30.2307</v>
+        <v>30.1969</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>23.5642</v>
+        <v>23.5563</v>
       </c>
       <c r="C110" t="n">
-        <v>18.6834</v>
+        <v>18.7328</v>
       </c>
       <c r="D110" t="n">
-        <v>44.7187</v>
+        <v>44.764</v>
       </c>
       <c r="E110" t="n">
-        <v>16.7242</v>
+        <v>16.7468</v>
       </c>
       <c r="F110" t="n">
-        <v>29.8554</v>
+        <v>29.8326</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>23.1268</v>
+        <v>23.1219</v>
       </c>
       <c r="C111" t="n">
-        <v>18.5335</v>
+        <v>18.55</v>
       </c>
       <c r="D111" t="n">
-        <v>41.5582</v>
+        <v>41.5828</v>
       </c>
       <c r="E111" t="n">
-        <v>16.4091</v>
+        <v>16.3902</v>
       </c>
       <c r="F111" t="n">
-        <v>29.5083</v>
+        <v>29.5623</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>22.6477</v>
+        <v>22.6541</v>
       </c>
       <c r="C112" t="n">
-        <v>18.3977</v>
+        <v>18.389</v>
       </c>
       <c r="D112" t="n">
-        <v>41.1109</v>
+        <v>41.1329</v>
       </c>
       <c r="E112" t="n">
-        <v>16.0967</v>
+        <v>16.0674</v>
       </c>
       <c r="F112" t="n">
-        <v>29.2568</v>
+        <v>29.2662</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>22.1498</v>
+        <v>22.1518</v>
       </c>
       <c r="C113" t="n">
-        <v>18.2721</v>
+        <v>18.2725</v>
       </c>
       <c r="D113" t="n">
-        <v>43.2034</v>
+        <v>43.1692</v>
       </c>
       <c r="E113" t="n">
-        <v>15.7607</v>
+        <v>15.7525</v>
       </c>
       <c r="F113" t="n">
-        <v>28.9124</v>
+        <v>28.9689</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>21.6335</v>
+        <v>21.6252</v>
       </c>
       <c r="C114" t="n">
-        <v>18.1247</v>
+        <v>18.1218</v>
       </c>
       <c r="D114" t="n">
-        <v>42.6885</v>
+        <v>42.6895</v>
       </c>
       <c r="E114" t="n">
-        <v>15.588</v>
+        <v>15.5649</v>
       </c>
       <c r="F114" t="n">
-        <v>28.6244</v>
+        <v>28.6987</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>21.0937</v>
+        <v>21.1008</v>
       </c>
       <c r="C115" t="n">
-        <v>18.0009</v>
+        <v>17.9827</v>
       </c>
       <c r="D115" t="n">
-        <v>42.21</v>
+        <v>42.2063</v>
       </c>
       <c r="E115" t="n">
-        <v>15.3271</v>
+        <v>15.326</v>
       </c>
       <c r="F115" t="n">
-        <v>28.3361</v>
+        <v>28.3546</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>20.5545</v>
+        <v>20.5527</v>
       </c>
       <c r="C116" t="n">
-        <v>17.8688</v>
+        <v>17.863</v>
       </c>
       <c r="D116" t="n">
-        <v>41.8981</v>
+        <v>41.9101</v>
       </c>
       <c r="E116" t="n">
-        <v>14.8408</v>
+        <v>14.8391</v>
       </c>
       <c r="F116" t="n">
-        <v>28.1735</v>
+        <v>28.1718</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>20.0287</v>
+        <v>20.0281</v>
       </c>
       <c r="C117" t="n">
-        <v>17.7655</v>
+        <v>17.7592</v>
       </c>
       <c r="D117" t="n">
-        <v>41.4611</v>
+        <v>41.4443</v>
       </c>
       <c r="E117" t="n">
-        <v>14.5605</v>
+        <v>14.562</v>
       </c>
       <c r="F117" t="n">
-        <v>27.834</v>
+        <v>27.8342</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>19.4922</v>
+        <v>19.4961</v>
       </c>
       <c r="C118" t="n">
-        <v>17.6699</v>
+        <v>17.676</v>
       </c>
       <c r="D118" t="n">
-        <v>41.1301</v>
+        <v>41.1355</v>
       </c>
       <c r="E118" t="n">
-        <v>14.28</v>
+        <v>14.2863</v>
       </c>
       <c r="F118" t="n">
-        <v>27.5458</v>
+        <v>27.5265</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>18.9424</v>
+        <v>18.9541</v>
       </c>
       <c r="C119" t="n">
-        <v>17.5933</v>
+        <v>17.5875</v>
       </c>
       <c r="D119" t="n">
-        <v>40.833</v>
+        <v>40.8339</v>
       </c>
       <c r="E119" t="n">
-        <v>18.7819</v>
+        <v>18.774</v>
       </c>
       <c r="F119" t="n">
-        <v>31.6062</v>
+        <v>31.7012</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>18.3534</v>
+        <v>18.3822</v>
       </c>
       <c r="C120" t="n">
-        <v>17.5099</v>
+        <v>17.5086</v>
       </c>
       <c r="D120" t="n">
-        <v>38.7001</v>
+        <v>38.7369</v>
       </c>
       <c r="E120" t="n">
-        <v>18.3811</v>
+        <v>18.379</v>
       </c>
       <c r="F120" t="n">
-        <v>31.1927</v>
+        <v>31.2214</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.7222</v>
+        <v>17.7588</v>
       </c>
       <c r="C121" t="n">
-        <v>17.4202</v>
+        <v>17.4083</v>
       </c>
       <c r="D121" t="n">
-        <v>48.4844</v>
+        <v>48.5315</v>
       </c>
       <c r="E121" t="n">
-        <v>17.9843</v>
+        <v>17.9855</v>
       </c>
       <c r="F121" t="n">
-        <v>30.8371</v>
+        <v>30.8446</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>16.9618</v>
+        <v>16.9531</v>
       </c>
       <c r="C122" t="n">
-        <v>19.1154</v>
+        <v>19.1165</v>
       </c>
       <c r="D122" t="n">
-        <v>47.9656</v>
+        <v>48.0599</v>
       </c>
       <c r="E122" t="n">
-        <v>17.4123</v>
+        <v>17.4537</v>
       </c>
       <c r="F122" t="n">
-        <v>30.65</v>
+        <v>30.6726</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>16.1429</v>
+        <v>16.1147</v>
       </c>
       <c r="C123" t="n">
-        <v>18.9891</v>
+        <v>18.9807</v>
       </c>
       <c r="D123" t="n">
-        <v>45.1135</v>
+        <v>45.1822</v>
       </c>
       <c r="E123" t="n">
-        <v>17.0522</v>
+        <v>17.0965</v>
       </c>
       <c r="F123" t="n">
-        <v>30.1736</v>
+        <v>30.2621</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>23.6356</v>
+        <v>23.6332</v>
       </c>
       <c r="C124" t="n">
-        <v>18.7278</v>
+        <v>18.727</v>
       </c>
       <c r="D124" t="n">
-        <v>46.9069</v>
+        <v>46.9186</v>
       </c>
       <c r="E124" t="n">
-        <v>16.7486</v>
+        <v>16.7159</v>
       </c>
       <c r="F124" t="n">
-        <v>29.8844</v>
+        <v>29.8998</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2047</v>
+        <v>23.2024</v>
       </c>
       <c r="C125" t="n">
-        <v>18.5558</v>
+        <v>18.57</v>
       </c>
       <c r="D125" t="n">
-        <v>46.3308</v>
+        <v>46.3201</v>
       </c>
       <c r="E125" t="n">
-        <v>16.4812</v>
+        <v>16.4565</v>
       </c>
       <c r="F125" t="n">
-        <v>29.6686</v>
+        <v>29.5996</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>22.7429</v>
+        <v>22.7462</v>
       </c>
       <c r="C126" t="n">
-        <v>18.3992</v>
+        <v>18.4158</v>
       </c>
       <c r="D126" t="n">
-        <v>45.8398</v>
+        <v>45.8333</v>
       </c>
       <c r="E126" t="n">
-        <v>16.1611</v>
+        <v>16.0664</v>
       </c>
       <c r="F126" t="n">
-        <v>29.3801</v>
+        <v>29.3175</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>22.2537</v>
+        <v>22.2484</v>
       </c>
       <c r="C127" t="n">
-        <v>18.3021</v>
+        <v>18.3193</v>
       </c>
       <c r="D127" t="n">
-        <v>43.3108</v>
+        <v>43.3344</v>
       </c>
       <c r="E127" t="n">
-        <v>15.786</v>
+        <v>15.7861</v>
       </c>
       <c r="F127" t="n">
-        <v>29.0673</v>
+        <v>28.9639</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>21.7413</v>
+        <v>21.7457</v>
       </c>
       <c r="C128" t="n">
-        <v>18.1553</v>
+        <v>18.1791</v>
       </c>
       <c r="D128" t="n">
-        <v>42.8232</v>
+        <v>42.8071</v>
       </c>
       <c r="E128" t="n">
-        <v>15.4756</v>
+        <v>15.4909</v>
       </c>
       <c r="F128" t="n">
-        <v>28.7657</v>
+        <v>28.6548</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>21.1928</v>
+        <v>21.198</v>
       </c>
       <c r="C129" t="n">
-        <v>18.0318</v>
+        <v>17.9994</v>
       </c>
       <c r="D129" t="n">
-        <v>42.3056</v>
+        <v>42.29</v>
       </c>
       <c r="E129" t="n">
-        <v>15.3891</v>
+        <v>15.3905</v>
       </c>
       <c r="F129" t="n">
-        <v>28.4824</v>
+        <v>28.3624</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>20.6651</v>
+        <v>20.6557</v>
       </c>
       <c r="C130" t="n">
-        <v>17.8962</v>
+        <v>17.8945</v>
       </c>
       <c r="D130" t="n">
-        <v>41.9076</v>
+        <v>41.8627</v>
       </c>
       <c r="E130" t="n">
-        <v>14.8847</v>
+        <v>14.8919</v>
       </c>
       <c r="F130" t="n">
-        <v>28.3124</v>
+        <v>28.1682</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>20.1377</v>
+        <v>20.1399</v>
       </c>
       <c r="C131" t="n">
-        <v>17.7997</v>
+        <v>17.7831</v>
       </c>
       <c r="D131" t="n">
-        <v>41.4329</v>
+        <v>41.3971</v>
       </c>
       <c r="E131" t="n">
-        <v>14.6113</v>
+        <v>14.6263</v>
       </c>
       <c r="F131" t="n">
-        <v>28.0271</v>
+        <v>27.9102</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>19.6075</v>
+        <v>19.6047</v>
       </c>
       <c r="C132" t="n">
-        <v>17.7069</v>
+        <v>17.7014</v>
       </c>
       <c r="D132" t="n">
-        <v>40.8472</v>
+        <v>41.0246</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3682</v>
+        <v>14.3459</v>
       </c>
       <c r="F132" t="n">
-        <v>27.3598</v>
+        <v>27.6131</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>19.16</v>
+        <v>19.0656</v>
       </c>
       <c r="C133" t="n">
-        <v>17.6303</v>
+        <v>17.6105</v>
       </c>
       <c r="D133" t="n">
-        <v>40.3899</v>
+        <v>40.6645</v>
       </c>
       <c r="E133" t="n">
-        <v>14.0715</v>
+        <v>14.0719</v>
       </c>
       <c r="F133" t="n">
-        <v>27.0978</v>
+        <v>27.3107</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>18.5218</v>
+        <v>18.4778</v>
       </c>
       <c r="C134" t="n">
-        <v>17.5428</v>
+        <v>17.5217</v>
       </c>
       <c r="D134" t="n">
-        <v>40.0693</v>
+        <v>40.3416</v>
       </c>
       <c r="E134" t="n">
-        <v>18.2469</v>
+        <v>18.2441</v>
       </c>
       <c r="F134" t="n">
-        <v>31.1688</v>
+        <v>31.3569</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.8823</v>
+        <v>17.843</v>
       </c>
       <c r="C135" t="n">
-        <v>17.4635</v>
+        <v>17.4455</v>
       </c>
       <c r="D135" t="n">
-        <v>46.6514</v>
+        <v>47.0797</v>
       </c>
       <c r="E135" t="n">
-        <v>17.8577</v>
+        <v>17.8646</v>
       </c>
       <c r="F135" t="n">
-        <v>30.7783</v>
+        <v>30.9977</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.1589</v>
+        <v>17.1126</v>
       </c>
       <c r="C136" t="n">
-        <v>19.194</v>
+        <v>19.1669</v>
       </c>
       <c r="D136" t="n">
-        <v>46.2559</v>
+        <v>46.5543</v>
       </c>
       <c r="E136" t="n">
-        <v>17.5473</v>
+        <v>17.5038</v>
       </c>
       <c r="F136" t="n">
-        <v>30.3463</v>
+        <v>30.6946</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>16.3635</v>
+        <v>16.33</v>
       </c>
       <c r="C137" t="n">
-        <v>18.9868</v>
+        <v>18.9765</v>
       </c>
       <c r="D137" t="n">
-        <v>47.9206</v>
+        <v>48.2321</v>
       </c>
       <c r="E137" t="n">
-        <v>17.1134</v>
+        <v>17.1198</v>
       </c>
       <c r="F137" t="n">
-        <v>30.0796</v>
+        <v>30.3723</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>23.7461</v>
+        <v>23.7228</v>
       </c>
       <c r="C138" t="n">
-        <v>18.7985</v>
+        <v>18.7758</v>
       </c>
       <c r="D138" t="n">
-        <v>47.324</v>
+        <v>47.7796</v>
       </c>
       <c r="E138" t="n">
-        <v>16.7682</v>
+        <v>16.7676</v>
       </c>
       <c r="F138" t="n">
-        <v>29.8168</v>
+        <v>30.0673</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>23.324</v>
+        <v>23.3578</v>
       </c>
       <c r="C139" t="n">
-        <v>18.6552</v>
+        <v>18.6164</v>
       </c>
       <c r="D139" t="n">
-        <v>46.5482</v>
+        <v>46.9264</v>
       </c>
       <c r="E139" t="n">
-        <v>16.4576</v>
+        <v>16.4779</v>
       </c>
       <c r="F139" t="n">
-        <v>29.4136</v>
+        <v>29.6829</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>22.8618</v>
+        <v>22.8425</v>
       </c>
       <c r="C140" t="n">
-        <v>18.48</v>
+        <v>18.4668</v>
       </c>
       <c r="D140" t="n">
-        <v>43.6678</v>
+        <v>43.9429</v>
       </c>
       <c r="E140" t="n">
-        <v>16.1671</v>
+        <v>16.1163</v>
       </c>
       <c r="F140" t="n">
-        <v>29.0923</v>
+        <v>29.3647</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>22.3793</v>
+        <v>22.3534</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3395</v>
+        <v>18.3158</v>
       </c>
       <c r="D141" t="n">
-        <v>45.0609</v>
+        <v>45.3858</v>
       </c>
       <c r="E141" t="n">
-        <v>15.8432</v>
+        <v>15.8099</v>
       </c>
       <c r="F141" t="n">
-        <v>28.8055</v>
+        <v>29.0581</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>21.8663</v>
+        <v>21.8473</v>
       </c>
       <c r="C142" t="n">
-        <v>18.2051</v>
+        <v>18.1723</v>
       </c>
       <c r="D142" t="n">
-        <v>44.3132</v>
+        <v>44.5307</v>
       </c>
       <c r="E142" t="n">
-        <v>15.514</v>
+        <v>15.5086</v>
       </c>
       <c r="F142" t="n">
-        <v>28.6074</v>
+        <v>28.9013</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>21.3336</v>
+        <v>21.3047</v>
       </c>
       <c r="C143" t="n">
-        <v>18.086</v>
+        <v>18.0671</v>
       </c>
       <c r="D143" t="n">
-        <v>44.0336</v>
+        <v>44.3149</v>
       </c>
       <c r="E143" t="n">
-        <v>15.2053</v>
+        <v>15.2087</v>
       </c>
       <c r="F143" t="n">
-        <v>28.3023</v>
+        <v>28.6618</v>
       </c>
     </row>
   </sheetData>
